--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -10895,8 +10895,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation sqref="E2:E250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, RK World, Robust Kommerce, Westbury Kommerce" promptTitle="E" prompt="Which group entity this is about." type="list">
-      <formula1>"RK Group,RK World,Robust Kommerce,Westbury Kommerce"</formula1>
+    <dataValidation sqref="E2:E250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, ValueCart, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="E" prompt="Which group entity this is about." type="list">
+      <formula1>"RK Group,ValueCart,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: AmbitionBox, Glassdoor, LinkedIn, X / Twitter, Reddit, Quora, YouTube, Google Reviews, Indeed" promptTitle="F" prompt="Where it was posted." type="list">
       <formula1>"AmbitionBox,Glassdoor,LinkedIn,X / Twitter,Reddit,Quora,YouTube,Google Reviews,Indeed"</formula1>
@@ -12181,8 +12181,8 @@
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, RK World, Robust Kommerce, Westbury Kommerce" promptTitle="B" prompt="One row per entity per week. APPEND, never overwrite." type="list">
-      <formula1>"RK Group,RK World,Robust Kommerce,Westbury Kommerce"</formula1>
+    <dataValidation sqref="B2:B120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, ValueCart, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="B" prompt="One row per entity per week. APPEND, never overwrite." type="list">
+      <formula1>"RK Group,ValueCart,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14318,8 +14318,8 @@
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <dataValidations count="5">
-    <dataValidation sqref="E2:E120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, RK World, Robust Kommerce, Westbury Kommerce" promptTitle="E" prompt="" type="list">
-      <formula1>"RK Group,RK World,Robust Kommerce,Westbury Kommerce"</formula1>
+    <dataValidation sqref="E2:E120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, ValueCart, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="E" prompt="" type="list">
+      <formula1>"RK Group,ValueCart,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: AmbitionBox, Glassdoor, LinkedIn, X / Twitter, Reddit, Quora, YouTube, Google Reviews, Indeed" promptTitle="F" prompt="" type="list">
       <formula1>"AmbitionBox,Glassdoor,LinkedIn,X / Twitter,Reddit,Quora,YouTube,Google Reviews,Indeed"</formula1>
@@ -14344,7 +14344,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22" customWidth="1" style="3" min="1" max="1"/>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>RK Group, R K Group, RKGroup, RK Grp, RK group of companies, RK Groups, RK Enterprises</t>
+          <t>RK Group, R K Group, RKGroup, RK Grp, RK group of companies, RK Groups</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -14393,85 +14393,107 @@
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>("RK Group" OR "R K Group" OR "RKGroup" OR "RK Grp" OR "RK group of companies" OR "RK Groups" OR "RK Enterprises") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
+          <t>("RK Group" OR "R K Group" OR "RKGroup" OR "RK Grp" OR "RK group of companies" OR "RK Groups") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1" s="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>RK World</t>
+          <t>ValueCart</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>RK World, R K World, RKWorld, RK Worlds, RK World Pvt, RK World Private Limited, ValueCart, Value Cart, RK World Infocom, R K World Infocom, RK Worldinfocom, Worldinfocom</t>
+          <t>ValueCart, Value Cart, ValueKart, Value Kart</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("ValueCart" OR "Value Cart" OR "ValueKart" OR "Value Kart")</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>("ValueCart" OR "Value Cart" OR "ValueKart" OR "Value Kart") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1" s="3">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>RK World Infocom</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>RK World, R K World, RKWorld, RK Worlds, RK World Pvt, RK World Private Limited, RK World Infocom, R K World Infocom, RK Worldinfocom, Worldinfocom</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("RK World" OR "R K World" OR "RKWorld" OR "RK Worlds")</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>("RK World" OR "R K World" OR "RKWorld" OR "RK Worlds" OR "RK World Pvt" OR "RK World Private Limited" OR "ValueCart" OR "Value Cart" OR "RK World Infocom" OR "R K World Infocom" OR "RK Worldinfocom" OR "Worldinfocom") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
+          <t>("RK World" OR "R K World" OR "RKWorld" OR "RK Worlds" OR "RK World Pvt" OR "RK World Private Limited" OR "RK World Infocom" OR "R K World Infocom" OR "RK Worldinfocom" OR "Worldinfocom") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1" s="3">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="5" ht="58" customHeight="1" s="3">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Robust Kommerce</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Robust Kommerce, Robust Commerce, Robust Komerce, Robust Kommers, RobustKommerce, Robust E-Commerce, Robust Ecommerce, Robust Results</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("Robust Kommerce" OR "Robust Commerce" OR "Robust Komerce" OR "Robust Kommers")</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>("Robust Kommerce" OR "Robust Commerce" OR "Robust Komerce" OR "Robust Kommers" OR "RobustKommerce" OR "Robust E-Commerce" OR "Robust Ecommerce" OR "Robust Results") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1" s="3">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="6" ht="58" customHeight="1" s="3">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Westbury Kommerce</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Westbury Kommerce, Westbury Commerce, Westbury Komerce, Westburry Kommerce, Westbery Kommerce, West Bury Kommerce, WestburyKommerce</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("Westbury Kommerce" OR "Westbury Commerce" OR "Westbury Komerce" OR "Westburry Kommerce")</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>("Westbury Kommerce" OR "Westbury Commerce" OR "Westbury Komerce" OR "Westburry Kommerce" OR "Westbery Kommerce" OR "West Bury Kommerce" OR "WestburyKommerce") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Generated from config/entities.yaml by: python3 scripts/alert_queries.py --format matrix</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>X-ray strings target review and discussion sites only. Profile X-ray (site:linkedin.com/in/) is excluded on purpose — enumerating individuals' profiles is outside the brief.</t>
         </is>

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -10895,8 +10895,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation sqref="E2:E250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, ValueCart, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="E" prompt="Which group entity this is about." type="list">
-      <formula1>"RK Group,ValueCart,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
+    <dataValidation sqref="E2:E250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="E" prompt="Which group entity this is about." type="list">
+      <formula1>"RK Group,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: AmbitionBox, Glassdoor, LinkedIn, X / Twitter, Reddit, Quora, YouTube, Google Reviews, Indeed" promptTitle="F" prompt="Where it was posted." type="list">
       <formula1>"AmbitionBox,Glassdoor,LinkedIn,X / Twitter,Reddit,Quora,YouTube,Google Reviews,Indeed"</formula1>
@@ -12181,8 +12181,8 @@
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, ValueCart, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="B" prompt="One row per entity per week. APPEND, never overwrite." type="list">
-      <formula1>"RK Group,ValueCart,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
+    <dataValidation sqref="B2:B120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="B" prompt="One row per entity per week. APPEND, never overwrite." type="list">
+      <formula1>"RK Group,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14318,8 +14318,8 @@
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <dataValidations count="5">
-    <dataValidation sqref="E2:E120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, ValueCart, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="E" prompt="" type="list">
-      <formula1>"RK Group,ValueCart,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
+    <dataValidation sqref="E2:E120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="E" prompt="" type="list">
+      <formula1>"RK Group,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: AmbitionBox, Glassdoor, LinkedIn, X / Twitter, Reddit, Quora, YouTube, Google Reviews, Indeed" promptTitle="F" prompt="" type="list">
       <formula1>"AmbitionBox,Glassdoor,LinkedIn,X / Twitter,Reddit,Quora,YouTube,Google Reviews,Indeed"</formula1>
@@ -14344,7 +14344,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22" customWidth="1" style="3" min="1" max="1"/>
@@ -14400,100 +14400,78 @@
     <row r="3" ht="58" customHeight="1" s="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>ValueCart</t>
+          <t>RK World Infocom</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>ValueCart, Value Cart, ValueKart, Value Kart</t>
+          <t>RK World, R K World, RKWorld, RK Worlds, RK World Pvt, RK World Private Limited, RK World Infocom, R K World Infocom, RK Worldinfocom, Worldinfocom</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("ValueCart" OR "Value Cart" OR "ValueKart" OR "Value Kart")</t>
+          <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("RK World" OR "R K World" OR "RKWorld" OR "RK Worlds")</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>("ValueCart" OR "Value Cart" OR "ValueKart" OR "Value Kart") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
+          <t>("RK World" OR "R K World" OR "RKWorld" OR "RK Worlds" OR "RK World Pvt" OR "RK World Private Limited" OR "RK World Infocom" OR "R K World Infocom" OR "RK Worldinfocom" OR "Worldinfocom") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1" s="3">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>RK World Infocom</t>
+          <t>Robust Kommerce</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>RK World, R K World, RKWorld, RK Worlds, RK World Pvt, RK World Private Limited, RK World Infocom, R K World Infocom, RK Worldinfocom, Worldinfocom</t>
+          <t>Robust Kommerce, Robust Commerce, Robust Komerce, Robust Kommers, RobustKommerce, Robust E-Commerce, Robust Ecommerce, Robust Results</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("RK World" OR "R K World" OR "RKWorld" OR "RK Worlds")</t>
+          <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("Robust Kommerce" OR "Robust Commerce" OR "Robust Komerce" OR "Robust Kommers")</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>("RK World" OR "R K World" OR "RKWorld" OR "RK Worlds" OR "RK World Pvt" OR "RK World Private Limited" OR "RK World Infocom" OR "R K World Infocom" OR "RK Worldinfocom" OR "Worldinfocom") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
+          <t>("Robust Kommerce" OR "Robust Commerce" OR "Robust Komerce" OR "Robust Kommers" OR "RobustKommerce" OR "Robust E-Commerce" OR "Robust Ecommerce" OR "Robust Results") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1" s="3">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Robust Kommerce</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Robust Kommerce, Robust Commerce, Robust Komerce, Robust Kommers, RobustKommerce, Robust E-Commerce, Robust Ecommerce, Robust Results</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("Robust Kommerce" OR "Robust Commerce" OR "Robust Komerce" OR "Robust Kommers")</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>("Robust Kommerce" OR "Robust Commerce" OR "Robust Komerce" OR "Robust Kommers" OR "RobustKommerce" OR "Robust E-Commerce" OR "Robust Ecommerce" OR "Robust Results") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1" s="3">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
           <t>Westbury Kommerce</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Westbury Kommerce, Westbury Commerce, Westbury Komerce, Westburry Kommerce, Westbery Kommerce, West Bury Kommerce, WestburyKommerce</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>(site:ambitionbox.com OR site:glassdoor.co.in OR site:indeed.co.in OR site:reddit.com OR site:quora.com) ("Westbury Kommerce" OR "Westbury Commerce" OR "Westbury Komerce" OR "Westburry Kommerce")</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>("Westbury Kommerce" OR "Westbury Commerce" OR "Westbury Komerce" OR "Westburry Kommerce" OR "Westbery Kommerce" OR "West Bury Kommerce" OR "WestburyKommerce") AND (salary OR employee OR appraisal OR interview OR manager OR resign)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Generated from config/entities.yaml by: python3 scripts/alert_queries.py --format matrix</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>X-ray strings target review and discussion sites only. Profile X-ray (site:linkedin.com/in/) is excluded on purpose — enumerating individuals' profiles is outside the brief.</t>
         </is>

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -911,7 +911,7 @@
       <c r="B2" s="6" t="n"/>
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="6">
-        <f>IF($C2="","",$C2-WEEKDAY($C2,3))</f>
+        <f>IF($C2="","",$C2-MOD(WEEKDAY($C2,3)-4,7))</f>
         <v/>
       </c>
       <c r="E2" s="5" t="n"/>
@@ -933,7 +933,7 @@
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6">
-        <f>IF($C3="","",$C3-WEEKDAY($C3,3))</f>
+        <f>IF($C3="","",$C3-MOD(WEEKDAY($C3,3)-4,7))</f>
         <v/>
       </c>
       <c r="E3" s="5" t="n"/>
@@ -955,7 +955,7 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6">
-        <f>IF($C4="","",$C4-WEEKDAY($C4,3))</f>
+        <f>IF($C4="","",$C4-MOD(WEEKDAY($C4,3)-4,7))</f>
         <v/>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -977,7 +977,7 @@
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6">
-        <f>IF($C5="","",$C5-WEEKDAY($C5,3))</f>
+        <f>IF($C5="","",$C5-MOD(WEEKDAY($C5,3)-4,7))</f>
         <v/>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -999,7 +999,7 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6">
-        <f>IF($C6="","",$C6-WEEKDAY($C6,3))</f>
+        <f>IF($C6="","",$C6-MOD(WEEKDAY($C6,3)-4,7))</f>
         <v/>
       </c>
       <c r="E6" s="5" t="n"/>
@@ -1021,7 +1021,7 @@
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6">
-        <f>IF($C7="","",$C7-WEEKDAY($C7,3))</f>
+        <f>IF($C7="","",$C7-MOD(WEEKDAY($C7,3)-4,7))</f>
         <v/>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -1043,7 +1043,7 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6">
-        <f>IF($C8="","",$C8-WEEKDAY($C8,3))</f>
+        <f>IF($C8="","",$C8-MOD(WEEKDAY($C8,3)-4,7))</f>
         <v/>
       </c>
       <c r="E8" s="5" t="n"/>
@@ -1065,7 +1065,7 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6">
-        <f>IF($C9="","",$C9-WEEKDAY($C9,3))</f>
+        <f>IF($C9="","",$C9-MOD(WEEKDAY($C9,3)-4,7))</f>
         <v/>
       </c>
       <c r="E9" s="5" t="n"/>
@@ -1087,7 +1087,7 @@
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6">
-        <f>IF($C10="","",$C10-WEEKDAY($C10,3))</f>
+        <f>IF($C10="","",$C10-MOD(WEEKDAY($C10,3)-4,7))</f>
         <v/>
       </c>
       <c r="E10" s="5" t="n"/>
@@ -1109,7 +1109,7 @@
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6">
-        <f>IF($C11="","",$C11-WEEKDAY($C11,3))</f>
+        <f>IF($C11="","",$C11-MOD(WEEKDAY($C11,3)-4,7))</f>
         <v/>
       </c>
       <c r="E11" s="5" t="n"/>
@@ -1131,7 +1131,7 @@
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6">
-        <f>IF($C12="","",$C12-WEEKDAY($C12,3))</f>
+        <f>IF($C12="","",$C12-MOD(WEEKDAY($C12,3)-4,7))</f>
         <v/>
       </c>
       <c r="E12" s="5" t="n"/>
@@ -1153,7 +1153,7 @@
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6">
-        <f>IF($C13="","",$C13-WEEKDAY($C13,3))</f>
+        <f>IF($C13="","",$C13-MOD(WEEKDAY($C13,3)-4,7))</f>
         <v/>
       </c>
       <c r="E13" s="5" t="n"/>
@@ -1175,7 +1175,7 @@
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6">
-        <f>IF($C14="","",$C14-WEEKDAY($C14,3))</f>
+        <f>IF($C14="","",$C14-MOD(WEEKDAY($C14,3)-4,7))</f>
         <v/>
       </c>
       <c r="E14" s="5" t="n"/>
@@ -1197,7 +1197,7 @@
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6">
-        <f>IF($C15="","",$C15-WEEKDAY($C15,3))</f>
+        <f>IF($C15="","",$C15-MOD(WEEKDAY($C15,3)-4,7))</f>
         <v/>
       </c>
       <c r="E15" s="5" t="n"/>
@@ -1219,7 +1219,7 @@
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6">
-        <f>IF($C16="","",$C16-WEEKDAY($C16,3))</f>
+        <f>IF($C16="","",$C16-MOD(WEEKDAY($C16,3)-4,7))</f>
         <v/>
       </c>
       <c r="E16" s="5" t="n"/>
@@ -1241,7 +1241,7 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6">
-        <f>IF($C17="","",$C17-WEEKDAY($C17,3))</f>
+        <f>IF($C17="","",$C17-MOD(WEEKDAY($C17,3)-4,7))</f>
         <v/>
       </c>
       <c r="E17" s="5" t="n"/>
@@ -1263,7 +1263,7 @@
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6">
-        <f>IF($C18="","",$C18-WEEKDAY($C18,3))</f>
+        <f>IF($C18="","",$C18-MOD(WEEKDAY($C18,3)-4,7))</f>
         <v/>
       </c>
       <c r="E18" s="5" t="n"/>
@@ -1285,7 +1285,7 @@
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6">
-        <f>IF($C19="","",$C19-WEEKDAY($C19,3))</f>
+        <f>IF($C19="","",$C19-MOD(WEEKDAY($C19,3)-4,7))</f>
         <v/>
       </c>
       <c r="E19" s="5" t="n"/>
@@ -1307,7 +1307,7 @@
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6">
-        <f>IF($C20="","",$C20-WEEKDAY($C20,3))</f>
+        <f>IF($C20="","",$C20-MOD(WEEKDAY($C20,3)-4,7))</f>
         <v/>
       </c>
       <c r="E20" s="5" t="n"/>
@@ -1329,7 +1329,7 @@
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6">
-        <f>IF($C21="","",$C21-WEEKDAY($C21,3))</f>
+        <f>IF($C21="","",$C21-MOD(WEEKDAY($C21,3)-4,7))</f>
         <v/>
       </c>
       <c r="E21" s="5" t="n"/>
@@ -1351,7 +1351,7 @@
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6">
-        <f>IF($C22="","",$C22-WEEKDAY($C22,3))</f>
+        <f>IF($C22="","",$C22-MOD(WEEKDAY($C22,3)-4,7))</f>
         <v/>
       </c>
       <c r="E22" s="5" t="n"/>
@@ -1373,7 +1373,7 @@
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6">
-        <f>IF($C23="","",$C23-WEEKDAY($C23,3))</f>
+        <f>IF($C23="","",$C23-MOD(WEEKDAY($C23,3)-4,7))</f>
         <v/>
       </c>
       <c r="E23" s="5" t="n"/>
@@ -1395,7 +1395,7 @@
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6">
-        <f>IF($C24="","",$C24-WEEKDAY($C24,3))</f>
+        <f>IF($C24="","",$C24-MOD(WEEKDAY($C24,3)-4,7))</f>
         <v/>
       </c>
       <c r="E24" s="5" t="n"/>
@@ -1417,7 +1417,7 @@
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6">
-        <f>IF($C25="","",$C25-WEEKDAY($C25,3))</f>
+        <f>IF($C25="","",$C25-MOD(WEEKDAY($C25,3)-4,7))</f>
         <v/>
       </c>
       <c r="E25" s="5" t="n"/>
@@ -1439,7 +1439,7 @@
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6">
-        <f>IF($C26="","",$C26-WEEKDAY($C26,3))</f>
+        <f>IF($C26="","",$C26-MOD(WEEKDAY($C26,3)-4,7))</f>
         <v/>
       </c>
       <c r="E26" s="5" t="n"/>
@@ -1461,7 +1461,7 @@
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6">
-        <f>IF($C27="","",$C27-WEEKDAY($C27,3))</f>
+        <f>IF($C27="","",$C27-MOD(WEEKDAY($C27,3)-4,7))</f>
         <v/>
       </c>
       <c r="E27" s="5" t="n"/>
@@ -1483,7 +1483,7 @@
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="6">
-        <f>IF($C28="","",$C28-WEEKDAY($C28,3))</f>
+        <f>IF($C28="","",$C28-MOD(WEEKDAY($C28,3)-4,7))</f>
         <v/>
       </c>
       <c r="E28" s="5" t="n"/>
@@ -1505,7 +1505,7 @@
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="6">
-        <f>IF($C29="","",$C29-WEEKDAY($C29,3))</f>
+        <f>IF($C29="","",$C29-MOD(WEEKDAY($C29,3)-4,7))</f>
         <v/>
       </c>
       <c r="E29" s="5" t="n"/>
@@ -1527,7 +1527,7 @@
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="6">
-        <f>IF($C30="","",$C30-WEEKDAY($C30,3))</f>
+        <f>IF($C30="","",$C30-MOD(WEEKDAY($C30,3)-4,7))</f>
         <v/>
       </c>
       <c r="E30" s="5" t="n"/>
@@ -1549,7 +1549,7 @@
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="6">
-        <f>IF($C31="","",$C31-WEEKDAY($C31,3))</f>
+        <f>IF($C31="","",$C31-MOD(WEEKDAY($C31,3)-4,7))</f>
         <v/>
       </c>
       <c r="E31" s="5" t="n"/>
@@ -1571,7 +1571,7 @@
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6">
-        <f>IF($C32="","",$C32-WEEKDAY($C32,3))</f>
+        <f>IF($C32="","",$C32-MOD(WEEKDAY($C32,3)-4,7))</f>
         <v/>
       </c>
       <c r="E32" s="5" t="n"/>
@@ -1593,7 +1593,7 @@
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="6">
-        <f>IF($C33="","",$C33-WEEKDAY($C33,3))</f>
+        <f>IF($C33="","",$C33-MOD(WEEKDAY($C33,3)-4,7))</f>
         <v/>
       </c>
       <c r="E33" s="5" t="n"/>
@@ -1615,7 +1615,7 @@
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="6">
-        <f>IF($C34="","",$C34-WEEKDAY($C34,3))</f>
+        <f>IF($C34="","",$C34-MOD(WEEKDAY($C34,3)-4,7))</f>
         <v/>
       </c>
       <c r="E34" s="5" t="n"/>
@@ -1637,7 +1637,7 @@
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="6">
-        <f>IF($C35="","",$C35-WEEKDAY($C35,3))</f>
+        <f>IF($C35="","",$C35-MOD(WEEKDAY($C35,3)-4,7))</f>
         <v/>
       </c>
       <c r="E35" s="5" t="n"/>
@@ -1659,7 +1659,7 @@
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="6">
-        <f>IF($C36="","",$C36-WEEKDAY($C36,3))</f>
+        <f>IF($C36="","",$C36-MOD(WEEKDAY($C36,3)-4,7))</f>
         <v/>
       </c>
       <c r="E36" s="5" t="n"/>
@@ -1681,7 +1681,7 @@
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6">
-        <f>IF($C37="","",$C37-WEEKDAY($C37,3))</f>
+        <f>IF($C37="","",$C37-MOD(WEEKDAY($C37,3)-4,7))</f>
         <v/>
       </c>
       <c r="E37" s="5" t="n"/>
@@ -1703,7 +1703,7 @@
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="6">
-        <f>IF($C38="","",$C38-WEEKDAY($C38,3))</f>
+        <f>IF($C38="","",$C38-MOD(WEEKDAY($C38,3)-4,7))</f>
         <v/>
       </c>
       <c r="E38" s="5" t="n"/>
@@ -1725,7 +1725,7 @@
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="6">
-        <f>IF($C39="","",$C39-WEEKDAY($C39,3))</f>
+        <f>IF($C39="","",$C39-MOD(WEEKDAY($C39,3)-4,7))</f>
         <v/>
       </c>
       <c r="E39" s="5" t="n"/>
@@ -1747,7 +1747,7 @@
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6">
-        <f>IF($C40="","",$C40-WEEKDAY($C40,3))</f>
+        <f>IF($C40="","",$C40-MOD(WEEKDAY($C40,3)-4,7))</f>
         <v/>
       </c>
       <c r="E40" s="5" t="n"/>
@@ -1769,7 +1769,7 @@
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="6">
-        <f>IF($C41="","",$C41-WEEKDAY($C41,3))</f>
+        <f>IF($C41="","",$C41-MOD(WEEKDAY($C41,3)-4,7))</f>
         <v/>
       </c>
       <c r="E41" s="5" t="n"/>
@@ -1791,7 +1791,7 @@
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="6">
-        <f>IF($C42="","",$C42-WEEKDAY($C42,3))</f>
+        <f>IF($C42="","",$C42-MOD(WEEKDAY($C42,3)-4,7))</f>
         <v/>
       </c>
       <c r="E42" s="5" t="n"/>
@@ -1813,7 +1813,7 @@
       <c r="B43" s="6" t="n"/>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6">
-        <f>IF($C43="","",$C43-WEEKDAY($C43,3))</f>
+        <f>IF($C43="","",$C43-MOD(WEEKDAY($C43,3)-4,7))</f>
         <v/>
       </c>
       <c r="E43" s="5" t="n"/>
@@ -1835,7 +1835,7 @@
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="6" t="n"/>
       <c r="D44" s="6">
-        <f>IF($C44="","",$C44-WEEKDAY($C44,3))</f>
+        <f>IF($C44="","",$C44-MOD(WEEKDAY($C44,3)-4,7))</f>
         <v/>
       </c>
       <c r="E44" s="5" t="n"/>
@@ -1857,7 +1857,7 @@
       <c r="B45" s="6" t="n"/>
       <c r="C45" s="6" t="n"/>
       <c r="D45" s="6">
-        <f>IF($C45="","",$C45-WEEKDAY($C45,3))</f>
+        <f>IF($C45="","",$C45-MOD(WEEKDAY($C45,3)-4,7))</f>
         <v/>
       </c>
       <c r="E45" s="5" t="n"/>
@@ -1879,7 +1879,7 @@
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="6" t="n"/>
       <c r="D46" s="6">
-        <f>IF($C46="","",$C46-WEEKDAY($C46,3))</f>
+        <f>IF($C46="","",$C46-MOD(WEEKDAY($C46,3)-4,7))</f>
         <v/>
       </c>
       <c r="E46" s="5" t="n"/>
@@ -1901,7 +1901,7 @@
       <c r="B47" s="6" t="n"/>
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6">
-        <f>IF($C47="","",$C47-WEEKDAY($C47,3))</f>
+        <f>IF($C47="","",$C47-MOD(WEEKDAY($C47,3)-4,7))</f>
         <v/>
       </c>
       <c r="E47" s="5" t="n"/>
@@ -1923,7 +1923,7 @@
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="6" t="n"/>
       <c r="D48" s="6">
-        <f>IF($C48="","",$C48-WEEKDAY($C48,3))</f>
+        <f>IF($C48="","",$C48-MOD(WEEKDAY($C48,3)-4,7))</f>
         <v/>
       </c>
       <c r="E48" s="5" t="n"/>
@@ -1945,7 +1945,7 @@
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="n"/>
       <c r="D49" s="6">
-        <f>IF($C49="","",$C49-WEEKDAY($C49,3))</f>
+        <f>IF($C49="","",$C49-MOD(WEEKDAY($C49,3)-4,7))</f>
         <v/>
       </c>
       <c r="E49" s="5" t="n"/>
@@ -1967,7 +1967,7 @@
       <c r="B50" s="6" t="n"/>
       <c r="C50" s="6" t="n"/>
       <c r="D50" s="6">
-        <f>IF($C50="","",$C50-WEEKDAY($C50,3))</f>
+        <f>IF($C50="","",$C50-MOD(WEEKDAY($C50,3)-4,7))</f>
         <v/>
       </c>
       <c r="E50" s="5" t="n"/>
@@ -1989,7 +1989,7 @@
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="6" t="n"/>
       <c r="D51" s="6">
-        <f>IF($C51="","",$C51-WEEKDAY($C51,3))</f>
+        <f>IF($C51="","",$C51-MOD(WEEKDAY($C51,3)-4,7))</f>
         <v/>
       </c>
       <c r="E51" s="5" t="n"/>
@@ -2011,7 +2011,7 @@
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="6" t="n"/>
       <c r="D52" s="6">
-        <f>IF($C52="","",$C52-WEEKDAY($C52,3))</f>
+        <f>IF($C52="","",$C52-MOD(WEEKDAY($C52,3)-4,7))</f>
         <v/>
       </c>
       <c r="E52" s="5" t="n"/>
@@ -2033,7 +2033,7 @@
       <c r="B53" s="6" t="n"/>
       <c r="C53" s="6" t="n"/>
       <c r="D53" s="6">
-        <f>IF($C53="","",$C53-WEEKDAY($C53,3))</f>
+        <f>IF($C53="","",$C53-MOD(WEEKDAY($C53,3)-4,7))</f>
         <v/>
       </c>
       <c r="E53" s="5" t="n"/>
@@ -2055,7 +2055,7 @@
       <c r="B54" s="6" t="n"/>
       <c r="C54" s="6" t="n"/>
       <c r="D54" s="6">
-        <f>IF($C54="","",$C54-WEEKDAY($C54,3))</f>
+        <f>IF($C54="","",$C54-MOD(WEEKDAY($C54,3)-4,7))</f>
         <v/>
       </c>
       <c r="E54" s="5" t="n"/>
@@ -2077,7 +2077,7 @@
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="6" t="n"/>
       <c r="D55" s="6">
-        <f>IF($C55="","",$C55-WEEKDAY($C55,3))</f>
+        <f>IF($C55="","",$C55-MOD(WEEKDAY($C55,3)-4,7))</f>
         <v/>
       </c>
       <c r="E55" s="5" t="n"/>
@@ -2099,7 +2099,7 @@
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="6" t="n"/>
       <c r="D56" s="6">
-        <f>IF($C56="","",$C56-WEEKDAY($C56,3))</f>
+        <f>IF($C56="","",$C56-MOD(WEEKDAY($C56,3)-4,7))</f>
         <v/>
       </c>
       <c r="E56" s="5" t="n"/>
@@ -2121,7 +2121,7 @@
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="6" t="n"/>
       <c r="D57" s="6">
-        <f>IF($C57="","",$C57-WEEKDAY($C57,3))</f>
+        <f>IF($C57="","",$C57-MOD(WEEKDAY($C57,3)-4,7))</f>
         <v/>
       </c>
       <c r="E57" s="5" t="n"/>
@@ -2143,7 +2143,7 @@
       <c r="B58" s="6" t="n"/>
       <c r="C58" s="6" t="n"/>
       <c r="D58" s="6">
-        <f>IF($C58="","",$C58-WEEKDAY($C58,3))</f>
+        <f>IF($C58="","",$C58-MOD(WEEKDAY($C58,3)-4,7))</f>
         <v/>
       </c>
       <c r="E58" s="5" t="n"/>
@@ -2165,7 +2165,7 @@
       <c r="B59" s="6" t="n"/>
       <c r="C59" s="6" t="n"/>
       <c r="D59" s="6">
-        <f>IF($C59="","",$C59-WEEKDAY($C59,3))</f>
+        <f>IF($C59="","",$C59-MOD(WEEKDAY($C59,3)-4,7))</f>
         <v/>
       </c>
       <c r="E59" s="5" t="n"/>
@@ -2187,7 +2187,7 @@
       <c r="B60" s="6" t="n"/>
       <c r="C60" s="6" t="n"/>
       <c r="D60" s="6">
-        <f>IF($C60="","",$C60-WEEKDAY($C60,3))</f>
+        <f>IF($C60="","",$C60-MOD(WEEKDAY($C60,3)-4,7))</f>
         <v/>
       </c>
       <c r="E60" s="5" t="n"/>
@@ -2209,7 +2209,7 @@
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="6" t="n"/>
       <c r="D61" s="6">
-        <f>IF($C61="","",$C61-WEEKDAY($C61,3))</f>
+        <f>IF($C61="","",$C61-MOD(WEEKDAY($C61,3)-4,7))</f>
         <v/>
       </c>
       <c r="E61" s="5" t="n"/>
@@ -2231,7 +2231,7 @@
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="6" t="n"/>
       <c r="D62" s="6">
-        <f>IF($C62="","",$C62-WEEKDAY($C62,3))</f>
+        <f>IF($C62="","",$C62-MOD(WEEKDAY($C62,3)-4,7))</f>
         <v/>
       </c>
       <c r="E62" s="5" t="n"/>
@@ -2253,7 +2253,7 @@
       <c r="B63" s="6" t="n"/>
       <c r="C63" s="6" t="n"/>
       <c r="D63" s="6">
-        <f>IF($C63="","",$C63-WEEKDAY($C63,3))</f>
+        <f>IF($C63="","",$C63-MOD(WEEKDAY($C63,3)-4,7))</f>
         <v/>
       </c>
       <c r="E63" s="5" t="n"/>
@@ -2275,7 +2275,7 @@
       <c r="B64" s="6" t="n"/>
       <c r="C64" s="6" t="n"/>
       <c r="D64" s="6">
-        <f>IF($C64="","",$C64-WEEKDAY($C64,3))</f>
+        <f>IF($C64="","",$C64-MOD(WEEKDAY($C64,3)-4,7))</f>
         <v/>
       </c>
       <c r="E64" s="5" t="n"/>
@@ -2297,7 +2297,7 @@
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="6" t="n"/>
       <c r="D65" s="6">
-        <f>IF($C65="","",$C65-WEEKDAY($C65,3))</f>
+        <f>IF($C65="","",$C65-MOD(WEEKDAY($C65,3)-4,7))</f>
         <v/>
       </c>
       <c r="E65" s="5" t="n"/>
@@ -2319,7 +2319,7 @@
       <c r="B66" s="6" t="n"/>
       <c r="C66" s="6" t="n"/>
       <c r="D66" s="6">
-        <f>IF($C66="","",$C66-WEEKDAY($C66,3))</f>
+        <f>IF($C66="","",$C66-MOD(WEEKDAY($C66,3)-4,7))</f>
         <v/>
       </c>
       <c r="E66" s="5" t="n"/>
@@ -2341,7 +2341,7 @@
       <c r="B67" s="6" t="n"/>
       <c r="C67" s="6" t="n"/>
       <c r="D67" s="6">
-        <f>IF($C67="","",$C67-WEEKDAY($C67,3))</f>
+        <f>IF($C67="","",$C67-MOD(WEEKDAY($C67,3)-4,7))</f>
         <v/>
       </c>
       <c r="E67" s="5" t="n"/>
@@ -2363,7 +2363,7 @@
       <c r="B68" s="6" t="n"/>
       <c r="C68" s="6" t="n"/>
       <c r="D68" s="6">
-        <f>IF($C68="","",$C68-WEEKDAY($C68,3))</f>
+        <f>IF($C68="","",$C68-MOD(WEEKDAY($C68,3)-4,7))</f>
         <v/>
       </c>
       <c r="E68" s="5" t="n"/>
@@ -2385,7 +2385,7 @@
       <c r="B69" s="6" t="n"/>
       <c r="C69" s="6" t="n"/>
       <c r="D69" s="6">
-        <f>IF($C69="","",$C69-WEEKDAY($C69,3))</f>
+        <f>IF($C69="","",$C69-MOD(WEEKDAY($C69,3)-4,7))</f>
         <v/>
       </c>
       <c r="E69" s="5" t="n"/>
@@ -2407,7 +2407,7 @@
       <c r="B70" s="6" t="n"/>
       <c r="C70" s="6" t="n"/>
       <c r="D70" s="6">
-        <f>IF($C70="","",$C70-WEEKDAY($C70,3))</f>
+        <f>IF($C70="","",$C70-MOD(WEEKDAY($C70,3)-4,7))</f>
         <v/>
       </c>
       <c r="E70" s="5" t="n"/>
@@ -2429,7 +2429,7 @@
       <c r="B71" s="6" t="n"/>
       <c r="C71" s="6" t="n"/>
       <c r="D71" s="6">
-        <f>IF($C71="","",$C71-WEEKDAY($C71,3))</f>
+        <f>IF($C71="","",$C71-MOD(WEEKDAY($C71,3)-4,7))</f>
         <v/>
       </c>
       <c r="E71" s="5" t="n"/>
@@ -2451,7 +2451,7 @@
       <c r="B72" s="6" t="n"/>
       <c r="C72" s="6" t="n"/>
       <c r="D72" s="6">
-        <f>IF($C72="","",$C72-WEEKDAY($C72,3))</f>
+        <f>IF($C72="","",$C72-MOD(WEEKDAY($C72,3)-4,7))</f>
         <v/>
       </c>
       <c r="E72" s="5" t="n"/>
@@ -2473,7 +2473,7 @@
       <c r="B73" s="6" t="n"/>
       <c r="C73" s="6" t="n"/>
       <c r="D73" s="6">
-        <f>IF($C73="","",$C73-WEEKDAY($C73,3))</f>
+        <f>IF($C73="","",$C73-MOD(WEEKDAY($C73,3)-4,7))</f>
         <v/>
       </c>
       <c r="E73" s="5" t="n"/>
@@ -2495,7 +2495,7 @@
       <c r="B74" s="6" t="n"/>
       <c r="C74" s="6" t="n"/>
       <c r="D74" s="6">
-        <f>IF($C74="","",$C74-WEEKDAY($C74,3))</f>
+        <f>IF($C74="","",$C74-MOD(WEEKDAY($C74,3)-4,7))</f>
         <v/>
       </c>
       <c r="E74" s="5" t="n"/>
@@ -2517,7 +2517,7 @@
       <c r="B75" s="6" t="n"/>
       <c r="C75" s="6" t="n"/>
       <c r="D75" s="6">
-        <f>IF($C75="","",$C75-WEEKDAY($C75,3))</f>
+        <f>IF($C75="","",$C75-MOD(WEEKDAY($C75,3)-4,7))</f>
         <v/>
       </c>
       <c r="E75" s="5" t="n"/>
@@ -2539,7 +2539,7 @@
       <c r="B76" s="6" t="n"/>
       <c r="C76" s="6" t="n"/>
       <c r="D76" s="6">
-        <f>IF($C76="","",$C76-WEEKDAY($C76,3))</f>
+        <f>IF($C76="","",$C76-MOD(WEEKDAY($C76,3)-4,7))</f>
         <v/>
       </c>
       <c r="E76" s="5" t="n"/>
@@ -2561,7 +2561,7 @@
       <c r="B77" s="6" t="n"/>
       <c r="C77" s="6" t="n"/>
       <c r="D77" s="6">
-        <f>IF($C77="","",$C77-WEEKDAY($C77,3))</f>
+        <f>IF($C77="","",$C77-MOD(WEEKDAY($C77,3)-4,7))</f>
         <v/>
       </c>
       <c r="E77" s="5" t="n"/>
@@ -2583,7 +2583,7 @@
       <c r="B78" s="6" t="n"/>
       <c r="C78" s="6" t="n"/>
       <c r="D78" s="6">
-        <f>IF($C78="","",$C78-WEEKDAY($C78,3))</f>
+        <f>IF($C78="","",$C78-MOD(WEEKDAY($C78,3)-4,7))</f>
         <v/>
       </c>
       <c r="E78" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       <c r="B79" s="6" t="n"/>
       <c r="C79" s="6" t="n"/>
       <c r="D79" s="6">
-        <f>IF($C79="","",$C79-WEEKDAY($C79,3))</f>
+        <f>IF($C79="","",$C79-MOD(WEEKDAY($C79,3)-4,7))</f>
         <v/>
       </c>
       <c r="E79" s="5" t="n"/>
@@ -2627,7 +2627,7 @@
       <c r="B80" s="6" t="n"/>
       <c r="C80" s="6" t="n"/>
       <c r="D80" s="6">
-        <f>IF($C80="","",$C80-WEEKDAY($C80,3))</f>
+        <f>IF($C80="","",$C80-MOD(WEEKDAY($C80,3)-4,7))</f>
         <v/>
       </c>
       <c r="E80" s="5" t="n"/>
@@ -2649,7 +2649,7 @@
       <c r="B81" s="6" t="n"/>
       <c r="C81" s="6" t="n"/>
       <c r="D81" s="6">
-        <f>IF($C81="","",$C81-WEEKDAY($C81,3))</f>
+        <f>IF($C81="","",$C81-MOD(WEEKDAY($C81,3)-4,7))</f>
         <v/>
       </c>
       <c r="E81" s="5" t="n"/>
@@ -2671,7 +2671,7 @@
       <c r="B82" s="6" t="n"/>
       <c r="C82" s="6" t="n"/>
       <c r="D82" s="6">
-        <f>IF($C82="","",$C82-WEEKDAY($C82,3))</f>
+        <f>IF($C82="","",$C82-MOD(WEEKDAY($C82,3)-4,7))</f>
         <v/>
       </c>
       <c r="E82" s="5" t="n"/>
@@ -2693,7 +2693,7 @@
       <c r="B83" s="6" t="n"/>
       <c r="C83" s="6" t="n"/>
       <c r="D83" s="6">
-        <f>IF($C83="","",$C83-WEEKDAY($C83,3))</f>
+        <f>IF($C83="","",$C83-MOD(WEEKDAY($C83,3)-4,7))</f>
         <v/>
       </c>
       <c r="E83" s="5" t="n"/>
@@ -2715,7 +2715,7 @@
       <c r="B84" s="6" t="n"/>
       <c r="C84" s="6" t="n"/>
       <c r="D84" s="6">
-        <f>IF($C84="","",$C84-WEEKDAY($C84,3))</f>
+        <f>IF($C84="","",$C84-MOD(WEEKDAY($C84,3)-4,7))</f>
         <v/>
       </c>
       <c r="E84" s="5" t="n"/>
@@ -2737,7 +2737,7 @@
       <c r="B85" s="6" t="n"/>
       <c r="C85" s="6" t="n"/>
       <c r="D85" s="6">
-        <f>IF($C85="","",$C85-WEEKDAY($C85,3))</f>
+        <f>IF($C85="","",$C85-MOD(WEEKDAY($C85,3)-4,7))</f>
         <v/>
       </c>
       <c r="E85" s="5" t="n"/>
@@ -2759,7 +2759,7 @@
       <c r="B86" s="6" t="n"/>
       <c r="C86" s="6" t="n"/>
       <c r="D86" s="6">
-        <f>IF($C86="","",$C86-WEEKDAY($C86,3))</f>
+        <f>IF($C86="","",$C86-MOD(WEEKDAY($C86,3)-4,7))</f>
         <v/>
       </c>
       <c r="E86" s="5" t="n"/>
@@ -2781,7 +2781,7 @@
       <c r="B87" s="6" t="n"/>
       <c r="C87" s="6" t="n"/>
       <c r="D87" s="6">
-        <f>IF($C87="","",$C87-WEEKDAY($C87,3))</f>
+        <f>IF($C87="","",$C87-MOD(WEEKDAY($C87,3)-4,7))</f>
         <v/>
       </c>
       <c r="E87" s="5" t="n"/>
@@ -2803,7 +2803,7 @@
       <c r="B88" s="6" t="n"/>
       <c r="C88" s="6" t="n"/>
       <c r="D88" s="6">
-        <f>IF($C88="","",$C88-WEEKDAY($C88,3))</f>
+        <f>IF($C88="","",$C88-MOD(WEEKDAY($C88,3)-4,7))</f>
         <v/>
       </c>
       <c r="E88" s="5" t="n"/>
@@ -2825,7 +2825,7 @@
       <c r="B89" s="6" t="n"/>
       <c r="C89" s="6" t="n"/>
       <c r="D89" s="6">
-        <f>IF($C89="","",$C89-WEEKDAY($C89,3))</f>
+        <f>IF($C89="","",$C89-MOD(WEEKDAY($C89,3)-4,7))</f>
         <v/>
       </c>
       <c r="E89" s="5" t="n"/>
@@ -2847,7 +2847,7 @@
       <c r="B90" s="6" t="n"/>
       <c r="C90" s="6" t="n"/>
       <c r="D90" s="6">
-        <f>IF($C90="","",$C90-WEEKDAY($C90,3))</f>
+        <f>IF($C90="","",$C90-MOD(WEEKDAY($C90,3)-4,7))</f>
         <v/>
       </c>
       <c r="E90" s="5" t="n"/>
@@ -2869,7 +2869,7 @@
       <c r="B91" s="6" t="n"/>
       <c r="C91" s="6" t="n"/>
       <c r="D91" s="6">
-        <f>IF($C91="","",$C91-WEEKDAY($C91,3))</f>
+        <f>IF($C91="","",$C91-MOD(WEEKDAY($C91,3)-4,7))</f>
         <v/>
       </c>
       <c r="E91" s="5" t="n"/>
@@ -2891,7 +2891,7 @@
       <c r="B92" s="6" t="n"/>
       <c r="C92" s="6" t="n"/>
       <c r="D92" s="6">
-        <f>IF($C92="","",$C92-WEEKDAY($C92,3))</f>
+        <f>IF($C92="","",$C92-MOD(WEEKDAY($C92,3)-4,7))</f>
         <v/>
       </c>
       <c r="E92" s="5" t="n"/>
@@ -2913,7 +2913,7 @@
       <c r="B93" s="6" t="n"/>
       <c r="C93" s="6" t="n"/>
       <c r="D93" s="6">
-        <f>IF($C93="","",$C93-WEEKDAY($C93,3))</f>
+        <f>IF($C93="","",$C93-MOD(WEEKDAY($C93,3)-4,7))</f>
         <v/>
       </c>
       <c r="E93" s="5" t="n"/>
@@ -2935,7 +2935,7 @@
       <c r="B94" s="6" t="n"/>
       <c r="C94" s="6" t="n"/>
       <c r="D94" s="6">
-        <f>IF($C94="","",$C94-WEEKDAY($C94,3))</f>
+        <f>IF($C94="","",$C94-MOD(WEEKDAY($C94,3)-4,7))</f>
         <v/>
       </c>
       <c r="E94" s="5" t="n"/>
@@ -2957,7 +2957,7 @@
       <c r="B95" s="6" t="n"/>
       <c r="C95" s="6" t="n"/>
       <c r="D95" s="6">
-        <f>IF($C95="","",$C95-WEEKDAY($C95,3))</f>
+        <f>IF($C95="","",$C95-MOD(WEEKDAY($C95,3)-4,7))</f>
         <v/>
       </c>
       <c r="E95" s="5" t="n"/>
@@ -2979,7 +2979,7 @@
       <c r="B96" s="6" t="n"/>
       <c r="C96" s="6" t="n"/>
       <c r="D96" s="6">
-        <f>IF($C96="","",$C96-WEEKDAY($C96,3))</f>
+        <f>IF($C96="","",$C96-MOD(WEEKDAY($C96,3)-4,7))</f>
         <v/>
       </c>
       <c r="E96" s="5" t="n"/>
@@ -3001,7 +3001,7 @@
       <c r="B97" s="6" t="n"/>
       <c r="C97" s="6" t="n"/>
       <c r="D97" s="6">
-        <f>IF($C97="","",$C97-WEEKDAY($C97,3))</f>
+        <f>IF($C97="","",$C97-MOD(WEEKDAY($C97,3)-4,7))</f>
         <v/>
       </c>
       <c r="E97" s="5" t="n"/>
@@ -3023,7 +3023,7 @@
       <c r="B98" s="6" t="n"/>
       <c r="C98" s="6" t="n"/>
       <c r="D98" s="6">
-        <f>IF($C98="","",$C98-WEEKDAY($C98,3))</f>
+        <f>IF($C98="","",$C98-MOD(WEEKDAY($C98,3)-4,7))</f>
         <v/>
       </c>
       <c r="E98" s="5" t="n"/>
@@ -3045,7 +3045,7 @@
       <c r="B99" s="6" t="n"/>
       <c r="C99" s="6" t="n"/>
       <c r="D99" s="6">
-        <f>IF($C99="","",$C99-WEEKDAY($C99,3))</f>
+        <f>IF($C99="","",$C99-MOD(WEEKDAY($C99,3)-4,7))</f>
         <v/>
       </c>
       <c r="E99" s="5" t="n"/>
@@ -3067,7 +3067,7 @@
       <c r="B100" s="6" t="n"/>
       <c r="C100" s="6" t="n"/>
       <c r="D100" s="6">
-        <f>IF($C100="","",$C100-WEEKDAY($C100,3))</f>
+        <f>IF($C100="","",$C100-MOD(WEEKDAY($C100,3)-4,7))</f>
         <v/>
       </c>
       <c r="E100" s="5" t="n"/>
@@ -3089,7 +3089,7 @@
       <c r="B101" s="6" t="n"/>
       <c r="C101" s="6" t="n"/>
       <c r="D101" s="6">
-        <f>IF($C101="","",$C101-WEEKDAY($C101,3))</f>
+        <f>IF($C101="","",$C101-MOD(WEEKDAY($C101,3)-4,7))</f>
         <v/>
       </c>
       <c r="E101" s="5" t="n"/>
@@ -3111,7 +3111,7 @@
       <c r="B102" s="6" t="n"/>
       <c r="C102" s="6" t="n"/>
       <c r="D102" s="6">
-        <f>IF($C102="","",$C102-WEEKDAY($C102,3))</f>
+        <f>IF($C102="","",$C102-MOD(WEEKDAY($C102,3)-4,7))</f>
         <v/>
       </c>
       <c r="E102" s="5" t="n"/>
@@ -3133,7 +3133,7 @@
       <c r="B103" s="6" t="n"/>
       <c r="C103" s="6" t="n"/>
       <c r="D103" s="6">
-        <f>IF($C103="","",$C103-WEEKDAY($C103,3))</f>
+        <f>IF($C103="","",$C103-MOD(WEEKDAY($C103,3)-4,7))</f>
         <v/>
       </c>
       <c r="E103" s="5" t="n"/>
@@ -3155,7 +3155,7 @@
       <c r="B104" s="6" t="n"/>
       <c r="C104" s="6" t="n"/>
       <c r="D104" s="6">
-        <f>IF($C104="","",$C104-WEEKDAY($C104,3))</f>
+        <f>IF($C104="","",$C104-MOD(WEEKDAY($C104,3)-4,7))</f>
         <v/>
       </c>
       <c r="E104" s="5" t="n"/>
@@ -3177,7 +3177,7 @@
       <c r="B105" s="6" t="n"/>
       <c r="C105" s="6" t="n"/>
       <c r="D105" s="6">
-        <f>IF($C105="","",$C105-WEEKDAY($C105,3))</f>
+        <f>IF($C105="","",$C105-MOD(WEEKDAY($C105,3)-4,7))</f>
         <v/>
       </c>
       <c r="E105" s="5" t="n"/>
@@ -3199,7 +3199,7 @@
       <c r="B106" s="6" t="n"/>
       <c r="C106" s="6" t="n"/>
       <c r="D106" s="6">
-        <f>IF($C106="","",$C106-WEEKDAY($C106,3))</f>
+        <f>IF($C106="","",$C106-MOD(WEEKDAY($C106,3)-4,7))</f>
         <v/>
       </c>
       <c r="E106" s="5" t="n"/>
@@ -3221,7 +3221,7 @@
       <c r="B107" s="6" t="n"/>
       <c r="C107" s="6" t="n"/>
       <c r="D107" s="6">
-        <f>IF($C107="","",$C107-WEEKDAY($C107,3))</f>
+        <f>IF($C107="","",$C107-MOD(WEEKDAY($C107,3)-4,7))</f>
         <v/>
       </c>
       <c r="E107" s="5" t="n"/>
@@ -3243,7 +3243,7 @@
       <c r="B108" s="6" t="n"/>
       <c r="C108" s="6" t="n"/>
       <c r="D108" s="6">
-        <f>IF($C108="","",$C108-WEEKDAY($C108,3))</f>
+        <f>IF($C108="","",$C108-MOD(WEEKDAY($C108,3)-4,7))</f>
         <v/>
       </c>
       <c r="E108" s="5" t="n"/>
@@ -3265,7 +3265,7 @@
       <c r="B109" s="6" t="n"/>
       <c r="C109" s="6" t="n"/>
       <c r="D109" s="6">
-        <f>IF($C109="","",$C109-WEEKDAY($C109,3))</f>
+        <f>IF($C109="","",$C109-MOD(WEEKDAY($C109,3)-4,7))</f>
         <v/>
       </c>
       <c r="E109" s="5" t="n"/>
@@ -3287,7 +3287,7 @@
       <c r="B110" s="6" t="n"/>
       <c r="C110" s="6" t="n"/>
       <c r="D110" s="6">
-        <f>IF($C110="","",$C110-WEEKDAY($C110,3))</f>
+        <f>IF($C110="","",$C110-MOD(WEEKDAY($C110,3)-4,7))</f>
         <v/>
       </c>
       <c r="E110" s="5" t="n"/>
@@ -3309,7 +3309,7 @@
       <c r="B111" s="6" t="n"/>
       <c r="C111" s="6" t="n"/>
       <c r="D111" s="6">
-        <f>IF($C111="","",$C111-WEEKDAY($C111,3))</f>
+        <f>IF($C111="","",$C111-MOD(WEEKDAY($C111,3)-4,7))</f>
         <v/>
       </c>
       <c r="E111" s="5" t="n"/>
@@ -3331,7 +3331,7 @@
       <c r="B112" s="6" t="n"/>
       <c r="C112" s="6" t="n"/>
       <c r="D112" s="6">
-        <f>IF($C112="","",$C112-WEEKDAY($C112,3))</f>
+        <f>IF($C112="","",$C112-MOD(WEEKDAY($C112,3)-4,7))</f>
         <v/>
       </c>
       <c r="E112" s="5" t="n"/>
@@ -3353,7 +3353,7 @@
       <c r="B113" s="6" t="n"/>
       <c r="C113" s="6" t="n"/>
       <c r="D113" s="6">
-        <f>IF($C113="","",$C113-WEEKDAY($C113,3))</f>
+        <f>IF($C113="","",$C113-MOD(WEEKDAY($C113,3)-4,7))</f>
         <v/>
       </c>
       <c r="E113" s="5" t="n"/>
@@ -3375,7 +3375,7 @@
       <c r="B114" s="6" t="n"/>
       <c r="C114" s="6" t="n"/>
       <c r="D114" s="6">
-        <f>IF($C114="","",$C114-WEEKDAY($C114,3))</f>
+        <f>IF($C114="","",$C114-MOD(WEEKDAY($C114,3)-4,7))</f>
         <v/>
       </c>
       <c r="E114" s="5" t="n"/>
@@ -3397,7 +3397,7 @@
       <c r="B115" s="6" t="n"/>
       <c r="C115" s="6" t="n"/>
       <c r="D115" s="6">
-        <f>IF($C115="","",$C115-WEEKDAY($C115,3))</f>
+        <f>IF($C115="","",$C115-MOD(WEEKDAY($C115,3)-4,7))</f>
         <v/>
       </c>
       <c r="E115" s="5" t="n"/>
@@ -3419,7 +3419,7 @@
       <c r="B116" s="6" t="n"/>
       <c r="C116" s="6" t="n"/>
       <c r="D116" s="6">
-        <f>IF($C116="","",$C116-WEEKDAY($C116,3))</f>
+        <f>IF($C116="","",$C116-MOD(WEEKDAY($C116,3)-4,7))</f>
         <v/>
       </c>
       <c r="E116" s="5" t="n"/>
@@ -3441,7 +3441,7 @@
       <c r="B117" s="6" t="n"/>
       <c r="C117" s="6" t="n"/>
       <c r="D117" s="6">
-        <f>IF($C117="","",$C117-WEEKDAY($C117,3))</f>
+        <f>IF($C117="","",$C117-MOD(WEEKDAY($C117,3)-4,7))</f>
         <v/>
       </c>
       <c r="E117" s="5" t="n"/>
@@ -3463,7 +3463,7 @@
       <c r="B118" s="6" t="n"/>
       <c r="C118" s="6" t="n"/>
       <c r="D118" s="6">
-        <f>IF($C118="","",$C118-WEEKDAY($C118,3))</f>
+        <f>IF($C118="","",$C118-MOD(WEEKDAY($C118,3)-4,7))</f>
         <v/>
       </c>
       <c r="E118" s="5" t="n"/>
@@ -3485,7 +3485,7 @@
       <c r="B119" s="6" t="n"/>
       <c r="C119" s="6" t="n"/>
       <c r="D119" s="6">
-        <f>IF($C119="","",$C119-WEEKDAY($C119,3))</f>
+        <f>IF($C119="","",$C119-MOD(WEEKDAY($C119,3)-4,7))</f>
         <v/>
       </c>
       <c r="E119" s="5" t="n"/>
@@ -3507,7 +3507,7 @@
       <c r="B120" s="6" t="n"/>
       <c r="C120" s="6" t="n"/>
       <c r="D120" s="6">
-        <f>IF($C120="","",$C120-WEEKDAY($C120,3))</f>
+        <f>IF($C120="","",$C120-MOD(WEEKDAY($C120,3)-4,7))</f>
         <v/>
       </c>
       <c r="E120" s="5" t="n"/>
@@ -3529,7 +3529,7 @@
       <c r="B121" s="6" t="n"/>
       <c r="C121" s="6" t="n"/>
       <c r="D121" s="6">
-        <f>IF($C121="","",$C121-WEEKDAY($C121,3))</f>
+        <f>IF($C121="","",$C121-MOD(WEEKDAY($C121,3)-4,7))</f>
         <v/>
       </c>
       <c r="E121" s="5" t="n"/>
@@ -3551,7 +3551,7 @@
       <c r="B122" s="6" t="n"/>
       <c r="C122" s="6" t="n"/>
       <c r="D122" s="6">
-        <f>IF($C122="","",$C122-WEEKDAY($C122,3))</f>
+        <f>IF($C122="","",$C122-MOD(WEEKDAY($C122,3)-4,7))</f>
         <v/>
       </c>
       <c r="E122" s="5" t="n"/>
@@ -3573,7 +3573,7 @@
       <c r="B123" s="6" t="n"/>
       <c r="C123" s="6" t="n"/>
       <c r="D123" s="6">
-        <f>IF($C123="","",$C123-WEEKDAY($C123,3))</f>
+        <f>IF($C123="","",$C123-MOD(WEEKDAY($C123,3)-4,7))</f>
         <v/>
       </c>
       <c r="E123" s="5" t="n"/>
@@ -3595,7 +3595,7 @@
       <c r="B124" s="6" t="n"/>
       <c r="C124" s="6" t="n"/>
       <c r="D124" s="6">
-        <f>IF($C124="","",$C124-WEEKDAY($C124,3))</f>
+        <f>IF($C124="","",$C124-MOD(WEEKDAY($C124,3)-4,7))</f>
         <v/>
       </c>
       <c r="E124" s="5" t="n"/>
@@ -3617,7 +3617,7 @@
       <c r="B125" s="6" t="n"/>
       <c r="C125" s="6" t="n"/>
       <c r="D125" s="6">
-        <f>IF($C125="","",$C125-WEEKDAY($C125,3))</f>
+        <f>IF($C125="","",$C125-MOD(WEEKDAY($C125,3)-4,7))</f>
         <v/>
       </c>
       <c r="E125" s="5" t="n"/>
@@ -3639,7 +3639,7 @@
       <c r="B126" s="6" t="n"/>
       <c r="C126" s="6" t="n"/>
       <c r="D126" s="6">
-        <f>IF($C126="","",$C126-WEEKDAY($C126,3))</f>
+        <f>IF($C126="","",$C126-MOD(WEEKDAY($C126,3)-4,7))</f>
         <v/>
       </c>
       <c r="E126" s="5" t="n"/>
@@ -3661,7 +3661,7 @@
       <c r="B127" s="6" t="n"/>
       <c r="C127" s="6" t="n"/>
       <c r="D127" s="6">
-        <f>IF($C127="","",$C127-WEEKDAY($C127,3))</f>
+        <f>IF($C127="","",$C127-MOD(WEEKDAY($C127,3)-4,7))</f>
         <v/>
       </c>
       <c r="E127" s="5" t="n"/>
@@ -3683,7 +3683,7 @@
       <c r="B128" s="6" t="n"/>
       <c r="C128" s="6" t="n"/>
       <c r="D128" s="6">
-        <f>IF($C128="","",$C128-WEEKDAY($C128,3))</f>
+        <f>IF($C128="","",$C128-MOD(WEEKDAY($C128,3)-4,7))</f>
         <v/>
       </c>
       <c r="E128" s="5" t="n"/>
@@ -3705,7 +3705,7 @@
       <c r="B129" s="6" t="n"/>
       <c r="C129" s="6" t="n"/>
       <c r="D129" s="6">
-        <f>IF($C129="","",$C129-WEEKDAY($C129,3))</f>
+        <f>IF($C129="","",$C129-MOD(WEEKDAY($C129,3)-4,7))</f>
         <v/>
       </c>
       <c r="E129" s="5" t="n"/>
@@ -3727,7 +3727,7 @@
       <c r="B130" s="6" t="n"/>
       <c r="C130" s="6" t="n"/>
       <c r="D130" s="6">
-        <f>IF($C130="","",$C130-WEEKDAY($C130,3))</f>
+        <f>IF($C130="","",$C130-MOD(WEEKDAY($C130,3)-4,7))</f>
         <v/>
       </c>
       <c r="E130" s="5" t="n"/>
@@ -3749,7 +3749,7 @@
       <c r="B131" s="6" t="n"/>
       <c r="C131" s="6" t="n"/>
       <c r="D131" s="6">
-        <f>IF($C131="","",$C131-WEEKDAY($C131,3))</f>
+        <f>IF($C131="","",$C131-MOD(WEEKDAY($C131,3)-4,7))</f>
         <v/>
       </c>
       <c r="E131" s="5" t="n"/>
@@ -3771,7 +3771,7 @@
       <c r="B132" s="6" t="n"/>
       <c r="C132" s="6" t="n"/>
       <c r="D132" s="6">
-        <f>IF($C132="","",$C132-WEEKDAY($C132,3))</f>
+        <f>IF($C132="","",$C132-MOD(WEEKDAY($C132,3)-4,7))</f>
         <v/>
       </c>
       <c r="E132" s="5" t="n"/>
@@ -3793,7 +3793,7 @@
       <c r="B133" s="6" t="n"/>
       <c r="C133" s="6" t="n"/>
       <c r="D133" s="6">
-        <f>IF($C133="","",$C133-WEEKDAY($C133,3))</f>
+        <f>IF($C133="","",$C133-MOD(WEEKDAY($C133,3)-4,7))</f>
         <v/>
       </c>
       <c r="E133" s="5" t="n"/>
@@ -3815,7 +3815,7 @@
       <c r="B134" s="6" t="n"/>
       <c r="C134" s="6" t="n"/>
       <c r="D134" s="6">
-        <f>IF($C134="","",$C134-WEEKDAY($C134,3))</f>
+        <f>IF($C134="","",$C134-MOD(WEEKDAY($C134,3)-4,7))</f>
         <v/>
       </c>
       <c r="E134" s="5" t="n"/>
@@ -3837,7 +3837,7 @@
       <c r="B135" s="6" t="n"/>
       <c r="C135" s="6" t="n"/>
       <c r="D135" s="6">
-        <f>IF($C135="","",$C135-WEEKDAY($C135,3))</f>
+        <f>IF($C135="","",$C135-MOD(WEEKDAY($C135,3)-4,7))</f>
         <v/>
       </c>
       <c r="E135" s="5" t="n"/>
@@ -3859,7 +3859,7 @@
       <c r="B136" s="6" t="n"/>
       <c r="C136" s="6" t="n"/>
       <c r="D136" s="6">
-        <f>IF($C136="","",$C136-WEEKDAY($C136,3))</f>
+        <f>IF($C136="","",$C136-MOD(WEEKDAY($C136,3)-4,7))</f>
         <v/>
       </c>
       <c r="E136" s="5" t="n"/>
@@ -3881,7 +3881,7 @@
       <c r="B137" s="6" t="n"/>
       <c r="C137" s="6" t="n"/>
       <c r="D137" s="6">
-        <f>IF($C137="","",$C137-WEEKDAY($C137,3))</f>
+        <f>IF($C137="","",$C137-MOD(WEEKDAY($C137,3)-4,7))</f>
         <v/>
       </c>
       <c r="E137" s="5" t="n"/>
@@ -3903,7 +3903,7 @@
       <c r="B138" s="6" t="n"/>
       <c r="C138" s="6" t="n"/>
       <c r="D138" s="6">
-        <f>IF($C138="","",$C138-WEEKDAY($C138,3))</f>
+        <f>IF($C138="","",$C138-MOD(WEEKDAY($C138,3)-4,7))</f>
         <v/>
       </c>
       <c r="E138" s="5" t="n"/>
@@ -3925,7 +3925,7 @@
       <c r="B139" s="6" t="n"/>
       <c r="C139" s="6" t="n"/>
       <c r="D139" s="6">
-        <f>IF($C139="","",$C139-WEEKDAY($C139,3))</f>
+        <f>IF($C139="","",$C139-MOD(WEEKDAY($C139,3)-4,7))</f>
         <v/>
       </c>
       <c r="E139" s="5" t="n"/>
@@ -3947,7 +3947,7 @@
       <c r="B140" s="6" t="n"/>
       <c r="C140" s="6" t="n"/>
       <c r="D140" s="6">
-        <f>IF($C140="","",$C140-WEEKDAY($C140,3))</f>
+        <f>IF($C140="","",$C140-MOD(WEEKDAY($C140,3)-4,7))</f>
         <v/>
       </c>
       <c r="E140" s="5" t="n"/>
@@ -3969,7 +3969,7 @@
       <c r="B141" s="6" t="n"/>
       <c r="C141" s="6" t="n"/>
       <c r="D141" s="6">
-        <f>IF($C141="","",$C141-WEEKDAY($C141,3))</f>
+        <f>IF($C141="","",$C141-MOD(WEEKDAY($C141,3)-4,7))</f>
         <v/>
       </c>
       <c r="E141" s="5" t="n"/>
@@ -3991,7 +3991,7 @@
       <c r="B142" s="6" t="n"/>
       <c r="C142" s="6" t="n"/>
       <c r="D142" s="6">
-        <f>IF($C142="","",$C142-WEEKDAY($C142,3))</f>
+        <f>IF($C142="","",$C142-MOD(WEEKDAY($C142,3)-4,7))</f>
         <v/>
       </c>
       <c r="E142" s="5" t="n"/>
@@ -4013,7 +4013,7 @@
       <c r="B143" s="6" t="n"/>
       <c r="C143" s="6" t="n"/>
       <c r="D143" s="6">
-        <f>IF($C143="","",$C143-WEEKDAY($C143,3))</f>
+        <f>IF($C143="","",$C143-MOD(WEEKDAY($C143,3)-4,7))</f>
         <v/>
       </c>
       <c r="E143" s="5" t="n"/>
@@ -4035,7 +4035,7 @@
       <c r="B144" s="6" t="n"/>
       <c r="C144" s="6" t="n"/>
       <c r="D144" s="6">
-        <f>IF($C144="","",$C144-WEEKDAY($C144,3))</f>
+        <f>IF($C144="","",$C144-MOD(WEEKDAY($C144,3)-4,7))</f>
         <v/>
       </c>
       <c r="E144" s="5" t="n"/>
@@ -4057,7 +4057,7 @@
       <c r="B145" s="6" t="n"/>
       <c r="C145" s="6" t="n"/>
       <c r="D145" s="6">
-        <f>IF($C145="","",$C145-WEEKDAY($C145,3))</f>
+        <f>IF($C145="","",$C145-MOD(WEEKDAY($C145,3)-4,7))</f>
         <v/>
       </c>
       <c r="E145" s="5" t="n"/>
@@ -4079,7 +4079,7 @@
       <c r="B146" s="6" t="n"/>
       <c r="C146" s="6" t="n"/>
       <c r="D146" s="6">
-        <f>IF($C146="","",$C146-WEEKDAY($C146,3))</f>
+        <f>IF($C146="","",$C146-MOD(WEEKDAY($C146,3)-4,7))</f>
         <v/>
       </c>
       <c r="E146" s="5" t="n"/>
@@ -4101,7 +4101,7 @@
       <c r="B147" s="6" t="n"/>
       <c r="C147" s="6" t="n"/>
       <c r="D147" s="6">
-        <f>IF($C147="","",$C147-WEEKDAY($C147,3))</f>
+        <f>IF($C147="","",$C147-MOD(WEEKDAY($C147,3)-4,7))</f>
         <v/>
       </c>
       <c r="E147" s="5" t="n"/>
@@ -4123,7 +4123,7 @@
       <c r="B148" s="6" t="n"/>
       <c r="C148" s="6" t="n"/>
       <c r="D148" s="6">
-        <f>IF($C148="","",$C148-WEEKDAY($C148,3))</f>
+        <f>IF($C148="","",$C148-MOD(WEEKDAY($C148,3)-4,7))</f>
         <v/>
       </c>
       <c r="E148" s="5" t="n"/>
@@ -4145,7 +4145,7 @@
       <c r="B149" s="6" t="n"/>
       <c r="C149" s="6" t="n"/>
       <c r="D149" s="6">
-        <f>IF($C149="","",$C149-WEEKDAY($C149,3))</f>
+        <f>IF($C149="","",$C149-MOD(WEEKDAY($C149,3)-4,7))</f>
         <v/>
       </c>
       <c r="E149" s="5" t="n"/>
@@ -4167,7 +4167,7 @@
       <c r="B150" s="6" t="n"/>
       <c r="C150" s="6" t="n"/>
       <c r="D150" s="6">
-        <f>IF($C150="","",$C150-WEEKDAY($C150,3))</f>
+        <f>IF($C150="","",$C150-MOD(WEEKDAY($C150,3)-4,7))</f>
         <v/>
       </c>
       <c r="E150" s="5" t="n"/>
@@ -4189,7 +4189,7 @@
       <c r="B151" s="6" t="n"/>
       <c r="C151" s="6" t="n"/>
       <c r="D151" s="6">
-        <f>IF($C151="","",$C151-WEEKDAY($C151,3))</f>
+        <f>IF($C151="","",$C151-MOD(WEEKDAY($C151,3)-4,7))</f>
         <v/>
       </c>
       <c r="E151" s="5" t="n"/>
@@ -4211,7 +4211,7 @@
       <c r="B152" s="6" t="n"/>
       <c r="C152" s="6" t="n"/>
       <c r="D152" s="6">
-        <f>IF($C152="","",$C152-WEEKDAY($C152,3))</f>
+        <f>IF($C152="","",$C152-MOD(WEEKDAY($C152,3)-4,7))</f>
         <v/>
       </c>
       <c r="E152" s="5" t="n"/>
@@ -4233,7 +4233,7 @@
       <c r="B153" s="6" t="n"/>
       <c r="C153" s="6" t="n"/>
       <c r="D153" s="6">
-        <f>IF($C153="","",$C153-WEEKDAY($C153,3))</f>
+        <f>IF($C153="","",$C153-MOD(WEEKDAY($C153,3)-4,7))</f>
         <v/>
       </c>
       <c r="E153" s="5" t="n"/>
@@ -4255,7 +4255,7 @@
       <c r="B154" s="6" t="n"/>
       <c r="C154" s="6" t="n"/>
       <c r="D154" s="6">
-        <f>IF($C154="","",$C154-WEEKDAY($C154,3))</f>
+        <f>IF($C154="","",$C154-MOD(WEEKDAY($C154,3)-4,7))</f>
         <v/>
       </c>
       <c r="E154" s="5" t="n"/>
@@ -4277,7 +4277,7 @@
       <c r="B155" s="6" t="n"/>
       <c r="C155" s="6" t="n"/>
       <c r="D155" s="6">
-        <f>IF($C155="","",$C155-WEEKDAY($C155,3))</f>
+        <f>IF($C155="","",$C155-MOD(WEEKDAY($C155,3)-4,7))</f>
         <v/>
       </c>
       <c r="E155" s="5" t="n"/>
@@ -4299,7 +4299,7 @@
       <c r="B156" s="6" t="n"/>
       <c r="C156" s="6" t="n"/>
       <c r="D156" s="6">
-        <f>IF($C156="","",$C156-WEEKDAY($C156,3))</f>
+        <f>IF($C156="","",$C156-MOD(WEEKDAY($C156,3)-4,7))</f>
         <v/>
       </c>
       <c r="E156" s="5" t="n"/>
@@ -4321,7 +4321,7 @@
       <c r="B157" s="6" t="n"/>
       <c r="C157" s="6" t="n"/>
       <c r="D157" s="6">
-        <f>IF($C157="","",$C157-WEEKDAY($C157,3))</f>
+        <f>IF($C157="","",$C157-MOD(WEEKDAY($C157,3)-4,7))</f>
         <v/>
       </c>
       <c r="E157" s="5" t="n"/>
@@ -4343,7 +4343,7 @@
       <c r="B158" s="6" t="n"/>
       <c r="C158" s="6" t="n"/>
       <c r="D158" s="6">
-        <f>IF($C158="","",$C158-WEEKDAY($C158,3))</f>
+        <f>IF($C158="","",$C158-MOD(WEEKDAY($C158,3)-4,7))</f>
         <v/>
       </c>
       <c r="E158" s="5" t="n"/>
@@ -4365,7 +4365,7 @@
       <c r="B159" s="6" t="n"/>
       <c r="C159" s="6" t="n"/>
       <c r="D159" s="6">
-        <f>IF($C159="","",$C159-WEEKDAY($C159,3))</f>
+        <f>IF($C159="","",$C159-MOD(WEEKDAY($C159,3)-4,7))</f>
         <v/>
       </c>
       <c r="E159" s="5" t="n"/>
@@ -4387,7 +4387,7 @@
       <c r="B160" s="6" t="n"/>
       <c r="C160" s="6" t="n"/>
       <c r="D160" s="6">
-        <f>IF($C160="","",$C160-WEEKDAY($C160,3))</f>
+        <f>IF($C160="","",$C160-MOD(WEEKDAY($C160,3)-4,7))</f>
         <v/>
       </c>
       <c r="E160" s="5" t="n"/>
@@ -4409,7 +4409,7 @@
       <c r="B161" s="6" t="n"/>
       <c r="C161" s="6" t="n"/>
       <c r="D161" s="6">
-        <f>IF($C161="","",$C161-WEEKDAY($C161,3))</f>
+        <f>IF($C161="","",$C161-MOD(WEEKDAY($C161,3)-4,7))</f>
         <v/>
       </c>
       <c r="E161" s="5" t="n"/>
@@ -4431,7 +4431,7 @@
       <c r="B162" s="6" t="n"/>
       <c r="C162" s="6" t="n"/>
       <c r="D162" s="6">
-        <f>IF($C162="","",$C162-WEEKDAY($C162,3))</f>
+        <f>IF($C162="","",$C162-MOD(WEEKDAY($C162,3)-4,7))</f>
         <v/>
       </c>
       <c r="E162" s="5" t="n"/>
@@ -4453,7 +4453,7 @@
       <c r="B163" s="6" t="n"/>
       <c r="C163" s="6" t="n"/>
       <c r="D163" s="6">
-        <f>IF($C163="","",$C163-WEEKDAY($C163,3))</f>
+        <f>IF($C163="","",$C163-MOD(WEEKDAY($C163,3)-4,7))</f>
         <v/>
       </c>
       <c r="E163" s="5" t="n"/>
@@ -4475,7 +4475,7 @@
       <c r="B164" s="6" t="n"/>
       <c r="C164" s="6" t="n"/>
       <c r="D164" s="6">
-        <f>IF($C164="","",$C164-WEEKDAY($C164,3))</f>
+        <f>IF($C164="","",$C164-MOD(WEEKDAY($C164,3)-4,7))</f>
         <v/>
       </c>
       <c r="E164" s="5" t="n"/>
@@ -4497,7 +4497,7 @@
       <c r="B165" s="6" t="n"/>
       <c r="C165" s="6" t="n"/>
       <c r="D165" s="6">
-        <f>IF($C165="","",$C165-WEEKDAY($C165,3))</f>
+        <f>IF($C165="","",$C165-MOD(WEEKDAY($C165,3)-4,7))</f>
         <v/>
       </c>
       <c r="E165" s="5" t="n"/>
@@ -4519,7 +4519,7 @@
       <c r="B166" s="6" t="n"/>
       <c r="C166" s="6" t="n"/>
       <c r="D166" s="6">
-        <f>IF($C166="","",$C166-WEEKDAY($C166,3))</f>
+        <f>IF($C166="","",$C166-MOD(WEEKDAY($C166,3)-4,7))</f>
         <v/>
       </c>
       <c r="E166" s="5" t="n"/>
@@ -4541,7 +4541,7 @@
       <c r="B167" s="6" t="n"/>
       <c r="C167" s="6" t="n"/>
       <c r="D167" s="6">
-        <f>IF($C167="","",$C167-WEEKDAY($C167,3))</f>
+        <f>IF($C167="","",$C167-MOD(WEEKDAY($C167,3)-4,7))</f>
         <v/>
       </c>
       <c r="E167" s="5" t="n"/>
@@ -4563,7 +4563,7 @@
       <c r="B168" s="6" t="n"/>
       <c r="C168" s="6" t="n"/>
       <c r="D168" s="6">
-        <f>IF($C168="","",$C168-WEEKDAY($C168,3))</f>
+        <f>IF($C168="","",$C168-MOD(WEEKDAY($C168,3)-4,7))</f>
         <v/>
       </c>
       <c r="E168" s="5" t="n"/>
@@ -4585,7 +4585,7 @@
       <c r="B169" s="6" t="n"/>
       <c r="C169" s="6" t="n"/>
       <c r="D169" s="6">
-        <f>IF($C169="","",$C169-WEEKDAY($C169,3))</f>
+        <f>IF($C169="","",$C169-MOD(WEEKDAY($C169,3)-4,7))</f>
         <v/>
       </c>
       <c r="E169" s="5" t="n"/>
@@ -4607,7 +4607,7 @@
       <c r="B170" s="6" t="n"/>
       <c r="C170" s="6" t="n"/>
       <c r="D170" s="6">
-        <f>IF($C170="","",$C170-WEEKDAY($C170,3))</f>
+        <f>IF($C170="","",$C170-MOD(WEEKDAY($C170,3)-4,7))</f>
         <v/>
       </c>
       <c r="E170" s="5" t="n"/>
@@ -4629,7 +4629,7 @@
       <c r="B171" s="6" t="n"/>
       <c r="C171" s="6" t="n"/>
       <c r="D171" s="6">
-        <f>IF($C171="","",$C171-WEEKDAY($C171,3))</f>
+        <f>IF($C171="","",$C171-MOD(WEEKDAY($C171,3)-4,7))</f>
         <v/>
       </c>
       <c r="E171" s="5" t="n"/>
@@ -4651,7 +4651,7 @@
       <c r="B172" s="6" t="n"/>
       <c r="C172" s="6" t="n"/>
       <c r="D172" s="6">
-        <f>IF($C172="","",$C172-WEEKDAY($C172,3))</f>
+        <f>IF($C172="","",$C172-MOD(WEEKDAY($C172,3)-4,7))</f>
         <v/>
       </c>
       <c r="E172" s="5" t="n"/>
@@ -4673,7 +4673,7 @@
       <c r="B173" s="6" t="n"/>
       <c r="C173" s="6" t="n"/>
       <c r="D173" s="6">
-        <f>IF($C173="","",$C173-WEEKDAY($C173,3))</f>
+        <f>IF($C173="","",$C173-MOD(WEEKDAY($C173,3)-4,7))</f>
         <v/>
       </c>
       <c r="E173" s="5" t="n"/>
@@ -4695,7 +4695,7 @@
       <c r="B174" s="6" t="n"/>
       <c r="C174" s="6" t="n"/>
       <c r="D174" s="6">
-        <f>IF($C174="","",$C174-WEEKDAY($C174,3))</f>
+        <f>IF($C174="","",$C174-MOD(WEEKDAY($C174,3)-4,7))</f>
         <v/>
       </c>
       <c r="E174" s="5" t="n"/>
@@ -4717,7 +4717,7 @@
       <c r="B175" s="6" t="n"/>
       <c r="C175" s="6" t="n"/>
       <c r="D175" s="6">
-        <f>IF($C175="","",$C175-WEEKDAY($C175,3))</f>
+        <f>IF($C175="","",$C175-MOD(WEEKDAY($C175,3)-4,7))</f>
         <v/>
       </c>
       <c r="E175" s="5" t="n"/>
@@ -4739,7 +4739,7 @@
       <c r="B176" s="6" t="n"/>
       <c r="C176" s="6" t="n"/>
       <c r="D176" s="6">
-        <f>IF($C176="","",$C176-WEEKDAY($C176,3))</f>
+        <f>IF($C176="","",$C176-MOD(WEEKDAY($C176,3)-4,7))</f>
         <v/>
       </c>
       <c r="E176" s="5" t="n"/>
@@ -4761,7 +4761,7 @@
       <c r="B177" s="6" t="n"/>
       <c r="C177" s="6" t="n"/>
       <c r="D177" s="6">
-        <f>IF($C177="","",$C177-WEEKDAY($C177,3))</f>
+        <f>IF($C177="","",$C177-MOD(WEEKDAY($C177,3)-4,7))</f>
         <v/>
       </c>
       <c r="E177" s="5" t="n"/>
@@ -4783,7 +4783,7 @@
       <c r="B178" s="6" t="n"/>
       <c r="C178" s="6" t="n"/>
       <c r="D178" s="6">
-        <f>IF($C178="","",$C178-WEEKDAY($C178,3))</f>
+        <f>IF($C178="","",$C178-MOD(WEEKDAY($C178,3)-4,7))</f>
         <v/>
       </c>
       <c r="E178" s="5" t="n"/>
@@ -4805,7 +4805,7 @@
       <c r="B179" s="6" t="n"/>
       <c r="C179" s="6" t="n"/>
       <c r="D179" s="6">
-        <f>IF($C179="","",$C179-WEEKDAY($C179,3))</f>
+        <f>IF($C179="","",$C179-MOD(WEEKDAY($C179,3)-4,7))</f>
         <v/>
       </c>
       <c r="E179" s="5" t="n"/>
@@ -4827,7 +4827,7 @@
       <c r="B180" s="6" t="n"/>
       <c r="C180" s="6" t="n"/>
       <c r="D180" s="6">
-        <f>IF($C180="","",$C180-WEEKDAY($C180,3))</f>
+        <f>IF($C180="","",$C180-MOD(WEEKDAY($C180,3)-4,7))</f>
         <v/>
       </c>
       <c r="E180" s="5" t="n"/>
@@ -4849,7 +4849,7 @@
       <c r="B181" s="6" t="n"/>
       <c r="C181" s="6" t="n"/>
       <c r="D181" s="6">
-        <f>IF($C181="","",$C181-WEEKDAY($C181,3))</f>
+        <f>IF($C181="","",$C181-MOD(WEEKDAY($C181,3)-4,7))</f>
         <v/>
       </c>
       <c r="E181" s="5" t="n"/>
@@ -4871,7 +4871,7 @@
       <c r="B182" s="6" t="n"/>
       <c r="C182" s="6" t="n"/>
       <c r="D182" s="6">
-        <f>IF($C182="","",$C182-WEEKDAY($C182,3))</f>
+        <f>IF($C182="","",$C182-MOD(WEEKDAY($C182,3)-4,7))</f>
         <v/>
       </c>
       <c r="E182" s="5" t="n"/>
@@ -4893,7 +4893,7 @@
       <c r="B183" s="6" t="n"/>
       <c r="C183" s="6" t="n"/>
       <c r="D183" s="6">
-        <f>IF($C183="","",$C183-WEEKDAY($C183,3))</f>
+        <f>IF($C183="","",$C183-MOD(WEEKDAY($C183,3)-4,7))</f>
         <v/>
       </c>
       <c r="E183" s="5" t="n"/>
@@ -4915,7 +4915,7 @@
       <c r="B184" s="6" t="n"/>
       <c r="C184" s="6" t="n"/>
       <c r="D184" s="6">
-        <f>IF($C184="","",$C184-WEEKDAY($C184,3))</f>
+        <f>IF($C184="","",$C184-MOD(WEEKDAY($C184,3)-4,7))</f>
         <v/>
       </c>
       <c r="E184" s="5" t="n"/>
@@ -4937,7 +4937,7 @@
       <c r="B185" s="6" t="n"/>
       <c r="C185" s="6" t="n"/>
       <c r="D185" s="6">
-        <f>IF($C185="","",$C185-WEEKDAY($C185,3))</f>
+        <f>IF($C185="","",$C185-MOD(WEEKDAY($C185,3)-4,7))</f>
         <v/>
       </c>
       <c r="E185" s="5" t="n"/>
@@ -4959,7 +4959,7 @@
       <c r="B186" s="6" t="n"/>
       <c r="C186" s="6" t="n"/>
       <c r="D186" s="6">
-        <f>IF($C186="","",$C186-WEEKDAY($C186,3))</f>
+        <f>IF($C186="","",$C186-MOD(WEEKDAY($C186,3)-4,7))</f>
         <v/>
       </c>
       <c r="E186" s="5" t="n"/>
@@ -4981,7 +4981,7 @@
       <c r="B187" s="6" t="n"/>
       <c r="C187" s="6" t="n"/>
       <c r="D187" s="6">
-        <f>IF($C187="","",$C187-WEEKDAY($C187,3))</f>
+        <f>IF($C187="","",$C187-MOD(WEEKDAY($C187,3)-4,7))</f>
         <v/>
       </c>
       <c r="E187" s="5" t="n"/>
@@ -5003,7 +5003,7 @@
       <c r="B188" s="6" t="n"/>
       <c r="C188" s="6" t="n"/>
       <c r="D188" s="6">
-        <f>IF($C188="","",$C188-WEEKDAY($C188,3))</f>
+        <f>IF($C188="","",$C188-MOD(WEEKDAY($C188,3)-4,7))</f>
         <v/>
       </c>
       <c r="E188" s="5" t="n"/>
@@ -5025,7 +5025,7 @@
       <c r="B189" s="6" t="n"/>
       <c r="C189" s="6" t="n"/>
       <c r="D189" s="6">
-        <f>IF($C189="","",$C189-WEEKDAY($C189,3))</f>
+        <f>IF($C189="","",$C189-MOD(WEEKDAY($C189,3)-4,7))</f>
         <v/>
       </c>
       <c r="E189" s="5" t="n"/>
@@ -5047,7 +5047,7 @@
       <c r="B190" s="6" t="n"/>
       <c r="C190" s="6" t="n"/>
       <c r="D190" s="6">
-        <f>IF($C190="","",$C190-WEEKDAY($C190,3))</f>
+        <f>IF($C190="","",$C190-MOD(WEEKDAY($C190,3)-4,7))</f>
         <v/>
       </c>
       <c r="E190" s="5" t="n"/>
@@ -5069,7 +5069,7 @@
       <c r="B191" s="6" t="n"/>
       <c r="C191" s="6" t="n"/>
       <c r="D191" s="6">
-        <f>IF($C191="","",$C191-WEEKDAY($C191,3))</f>
+        <f>IF($C191="","",$C191-MOD(WEEKDAY($C191,3)-4,7))</f>
         <v/>
       </c>
       <c r="E191" s="5" t="n"/>
@@ -5091,7 +5091,7 @@
       <c r="B192" s="6" t="n"/>
       <c r="C192" s="6" t="n"/>
       <c r="D192" s="6">
-        <f>IF($C192="","",$C192-WEEKDAY($C192,3))</f>
+        <f>IF($C192="","",$C192-MOD(WEEKDAY($C192,3)-4,7))</f>
         <v/>
       </c>
       <c r="E192" s="5" t="n"/>
@@ -5113,7 +5113,7 @@
       <c r="B193" s="6" t="n"/>
       <c r="C193" s="6" t="n"/>
       <c r="D193" s="6">
-        <f>IF($C193="","",$C193-WEEKDAY($C193,3))</f>
+        <f>IF($C193="","",$C193-MOD(WEEKDAY($C193,3)-4,7))</f>
         <v/>
       </c>
       <c r="E193" s="5" t="n"/>
@@ -5135,7 +5135,7 @@
       <c r="B194" s="6" t="n"/>
       <c r="C194" s="6" t="n"/>
       <c r="D194" s="6">
-        <f>IF($C194="","",$C194-WEEKDAY($C194,3))</f>
+        <f>IF($C194="","",$C194-MOD(WEEKDAY($C194,3)-4,7))</f>
         <v/>
       </c>
       <c r="E194" s="5" t="n"/>
@@ -5157,7 +5157,7 @@
       <c r="B195" s="6" t="n"/>
       <c r="C195" s="6" t="n"/>
       <c r="D195" s="6">
-        <f>IF($C195="","",$C195-WEEKDAY($C195,3))</f>
+        <f>IF($C195="","",$C195-MOD(WEEKDAY($C195,3)-4,7))</f>
         <v/>
       </c>
       <c r="E195" s="5" t="n"/>
@@ -5179,7 +5179,7 @@
       <c r="B196" s="6" t="n"/>
       <c r="C196" s="6" t="n"/>
       <c r="D196" s="6">
-        <f>IF($C196="","",$C196-WEEKDAY($C196,3))</f>
+        <f>IF($C196="","",$C196-MOD(WEEKDAY($C196,3)-4,7))</f>
         <v/>
       </c>
       <c r="E196" s="5" t="n"/>
@@ -5201,7 +5201,7 @@
       <c r="B197" s="6" t="n"/>
       <c r="C197" s="6" t="n"/>
       <c r="D197" s="6">
-        <f>IF($C197="","",$C197-WEEKDAY($C197,3))</f>
+        <f>IF($C197="","",$C197-MOD(WEEKDAY($C197,3)-4,7))</f>
         <v/>
       </c>
       <c r="E197" s="5" t="n"/>
@@ -5223,7 +5223,7 @@
       <c r="B198" s="6" t="n"/>
       <c r="C198" s="6" t="n"/>
       <c r="D198" s="6">
-        <f>IF($C198="","",$C198-WEEKDAY($C198,3))</f>
+        <f>IF($C198="","",$C198-MOD(WEEKDAY($C198,3)-4,7))</f>
         <v/>
       </c>
       <c r="E198" s="5" t="n"/>
@@ -5245,7 +5245,7 @@
       <c r="B199" s="6" t="n"/>
       <c r="C199" s="6" t="n"/>
       <c r="D199" s="6">
-        <f>IF($C199="","",$C199-WEEKDAY($C199,3))</f>
+        <f>IF($C199="","",$C199-MOD(WEEKDAY($C199,3)-4,7))</f>
         <v/>
       </c>
       <c r="E199" s="5" t="n"/>
@@ -5267,7 +5267,7 @@
       <c r="B200" s="6" t="n"/>
       <c r="C200" s="6" t="n"/>
       <c r="D200" s="6">
-        <f>IF($C200="","",$C200-WEEKDAY($C200,3))</f>
+        <f>IF($C200="","",$C200-MOD(WEEKDAY($C200,3)-4,7))</f>
         <v/>
       </c>
       <c r="E200" s="5" t="n"/>
@@ -5289,7 +5289,7 @@
       <c r="B201" s="6" t="n"/>
       <c r="C201" s="6" t="n"/>
       <c r="D201" s="6">
-        <f>IF($C201="","",$C201-WEEKDAY($C201,3))</f>
+        <f>IF($C201="","",$C201-MOD(WEEKDAY($C201,3)-4,7))</f>
         <v/>
       </c>
       <c r="E201" s="5" t="n"/>
@@ -5311,7 +5311,7 @@
       <c r="B202" s="6" t="n"/>
       <c r="C202" s="6" t="n"/>
       <c r="D202" s="6">
-        <f>IF($C202="","",$C202-WEEKDAY($C202,3))</f>
+        <f>IF($C202="","",$C202-MOD(WEEKDAY($C202,3)-4,7))</f>
         <v/>
       </c>
       <c r="E202" s="5" t="n"/>
@@ -5333,7 +5333,7 @@
       <c r="B203" s="6" t="n"/>
       <c r="C203" s="6" t="n"/>
       <c r="D203" s="6">
-        <f>IF($C203="","",$C203-WEEKDAY($C203,3))</f>
+        <f>IF($C203="","",$C203-MOD(WEEKDAY($C203,3)-4,7))</f>
         <v/>
       </c>
       <c r="E203" s="5" t="n"/>
@@ -5355,7 +5355,7 @@
       <c r="B204" s="6" t="n"/>
       <c r="C204" s="6" t="n"/>
       <c r="D204" s="6">
-        <f>IF($C204="","",$C204-WEEKDAY($C204,3))</f>
+        <f>IF($C204="","",$C204-MOD(WEEKDAY($C204,3)-4,7))</f>
         <v/>
       </c>
       <c r="E204" s="5" t="n"/>
@@ -5377,7 +5377,7 @@
       <c r="B205" s="6" t="n"/>
       <c r="C205" s="6" t="n"/>
       <c r="D205" s="6">
-        <f>IF($C205="","",$C205-WEEKDAY($C205,3))</f>
+        <f>IF($C205="","",$C205-MOD(WEEKDAY($C205,3)-4,7))</f>
         <v/>
       </c>
       <c r="E205" s="5" t="n"/>
@@ -5399,7 +5399,7 @@
       <c r="B206" s="6" t="n"/>
       <c r="C206" s="6" t="n"/>
       <c r="D206" s="6">
-        <f>IF($C206="","",$C206-WEEKDAY($C206,3))</f>
+        <f>IF($C206="","",$C206-MOD(WEEKDAY($C206,3)-4,7))</f>
         <v/>
       </c>
       <c r="E206" s="5" t="n"/>
@@ -5421,7 +5421,7 @@
       <c r="B207" s="6" t="n"/>
       <c r="C207" s="6" t="n"/>
       <c r="D207" s="6">
-        <f>IF($C207="","",$C207-WEEKDAY($C207,3))</f>
+        <f>IF($C207="","",$C207-MOD(WEEKDAY($C207,3)-4,7))</f>
         <v/>
       </c>
       <c r="E207" s="5" t="n"/>
@@ -5443,7 +5443,7 @@
       <c r="B208" s="6" t="n"/>
       <c r="C208" s="6" t="n"/>
       <c r="D208" s="6">
-        <f>IF($C208="","",$C208-WEEKDAY($C208,3))</f>
+        <f>IF($C208="","",$C208-MOD(WEEKDAY($C208,3)-4,7))</f>
         <v/>
       </c>
       <c r="E208" s="5" t="n"/>
@@ -5465,7 +5465,7 @@
       <c r="B209" s="6" t="n"/>
       <c r="C209" s="6" t="n"/>
       <c r="D209" s="6">
-        <f>IF($C209="","",$C209-WEEKDAY($C209,3))</f>
+        <f>IF($C209="","",$C209-MOD(WEEKDAY($C209,3)-4,7))</f>
         <v/>
       </c>
       <c r="E209" s="5" t="n"/>
@@ -5487,7 +5487,7 @@
       <c r="B210" s="6" t="n"/>
       <c r="C210" s="6" t="n"/>
       <c r="D210" s="6">
-        <f>IF($C210="","",$C210-WEEKDAY($C210,3))</f>
+        <f>IF($C210="","",$C210-MOD(WEEKDAY($C210,3)-4,7))</f>
         <v/>
       </c>
       <c r="E210" s="5" t="n"/>
@@ -5509,7 +5509,7 @@
       <c r="B211" s="6" t="n"/>
       <c r="C211" s="6" t="n"/>
       <c r="D211" s="6">
-        <f>IF($C211="","",$C211-WEEKDAY($C211,3))</f>
+        <f>IF($C211="","",$C211-MOD(WEEKDAY($C211,3)-4,7))</f>
         <v/>
       </c>
       <c r="E211" s="5" t="n"/>
@@ -5531,7 +5531,7 @@
       <c r="B212" s="6" t="n"/>
       <c r="C212" s="6" t="n"/>
       <c r="D212" s="6">
-        <f>IF($C212="","",$C212-WEEKDAY($C212,3))</f>
+        <f>IF($C212="","",$C212-MOD(WEEKDAY($C212,3)-4,7))</f>
         <v/>
       </c>
       <c r="E212" s="5" t="n"/>
@@ -5553,7 +5553,7 @@
       <c r="B213" s="6" t="n"/>
       <c r="C213" s="6" t="n"/>
       <c r="D213" s="6">
-        <f>IF($C213="","",$C213-WEEKDAY($C213,3))</f>
+        <f>IF($C213="","",$C213-MOD(WEEKDAY($C213,3)-4,7))</f>
         <v/>
       </c>
       <c r="E213" s="5" t="n"/>
@@ -5575,7 +5575,7 @@
       <c r="B214" s="6" t="n"/>
       <c r="C214" s="6" t="n"/>
       <c r="D214" s="6">
-        <f>IF($C214="","",$C214-WEEKDAY($C214,3))</f>
+        <f>IF($C214="","",$C214-MOD(WEEKDAY($C214,3)-4,7))</f>
         <v/>
       </c>
       <c r="E214" s="5" t="n"/>
@@ -5597,7 +5597,7 @@
       <c r="B215" s="6" t="n"/>
       <c r="C215" s="6" t="n"/>
       <c r="D215" s="6">
-        <f>IF($C215="","",$C215-WEEKDAY($C215,3))</f>
+        <f>IF($C215="","",$C215-MOD(WEEKDAY($C215,3)-4,7))</f>
         <v/>
       </c>
       <c r="E215" s="5" t="n"/>
@@ -5619,7 +5619,7 @@
       <c r="B216" s="6" t="n"/>
       <c r="C216" s="6" t="n"/>
       <c r="D216" s="6">
-        <f>IF($C216="","",$C216-WEEKDAY($C216,3))</f>
+        <f>IF($C216="","",$C216-MOD(WEEKDAY($C216,3)-4,7))</f>
         <v/>
       </c>
       <c r="E216" s="5" t="n"/>
@@ -5641,7 +5641,7 @@
       <c r="B217" s="6" t="n"/>
       <c r="C217" s="6" t="n"/>
       <c r="D217" s="6">
-        <f>IF($C217="","",$C217-WEEKDAY($C217,3))</f>
+        <f>IF($C217="","",$C217-MOD(WEEKDAY($C217,3)-4,7))</f>
         <v/>
       </c>
       <c r="E217" s="5" t="n"/>
@@ -5663,7 +5663,7 @@
       <c r="B218" s="6" t="n"/>
       <c r="C218" s="6" t="n"/>
       <c r="D218" s="6">
-        <f>IF($C218="","",$C218-WEEKDAY($C218,3))</f>
+        <f>IF($C218="","",$C218-MOD(WEEKDAY($C218,3)-4,7))</f>
         <v/>
       </c>
       <c r="E218" s="5" t="n"/>
@@ -5685,7 +5685,7 @@
       <c r="B219" s="6" t="n"/>
       <c r="C219" s="6" t="n"/>
       <c r="D219" s="6">
-        <f>IF($C219="","",$C219-WEEKDAY($C219,3))</f>
+        <f>IF($C219="","",$C219-MOD(WEEKDAY($C219,3)-4,7))</f>
         <v/>
       </c>
       <c r="E219" s="5" t="n"/>
@@ -5707,7 +5707,7 @@
       <c r="B220" s="6" t="n"/>
       <c r="C220" s="6" t="n"/>
       <c r="D220" s="6">
-        <f>IF($C220="","",$C220-WEEKDAY($C220,3))</f>
+        <f>IF($C220="","",$C220-MOD(WEEKDAY($C220,3)-4,7))</f>
         <v/>
       </c>
       <c r="E220" s="5" t="n"/>
@@ -5729,7 +5729,7 @@
       <c r="B221" s="6" t="n"/>
       <c r="C221" s="6" t="n"/>
       <c r="D221" s="6">
-        <f>IF($C221="","",$C221-WEEKDAY($C221,3))</f>
+        <f>IF($C221="","",$C221-MOD(WEEKDAY($C221,3)-4,7))</f>
         <v/>
       </c>
       <c r="E221" s="5" t="n"/>
@@ -5751,7 +5751,7 @@
       <c r="B222" s="6" t="n"/>
       <c r="C222" s="6" t="n"/>
       <c r="D222" s="6">
-        <f>IF($C222="","",$C222-WEEKDAY($C222,3))</f>
+        <f>IF($C222="","",$C222-MOD(WEEKDAY($C222,3)-4,7))</f>
         <v/>
       </c>
       <c r="E222" s="5" t="n"/>
@@ -5773,7 +5773,7 @@
       <c r="B223" s="6" t="n"/>
       <c r="C223" s="6" t="n"/>
       <c r="D223" s="6">
-        <f>IF($C223="","",$C223-WEEKDAY($C223,3))</f>
+        <f>IF($C223="","",$C223-MOD(WEEKDAY($C223,3)-4,7))</f>
         <v/>
       </c>
       <c r="E223" s="5" t="n"/>
@@ -5795,7 +5795,7 @@
       <c r="B224" s="6" t="n"/>
       <c r="C224" s="6" t="n"/>
       <c r="D224" s="6">
-        <f>IF($C224="","",$C224-WEEKDAY($C224,3))</f>
+        <f>IF($C224="","",$C224-MOD(WEEKDAY($C224,3)-4,7))</f>
         <v/>
       </c>
       <c r="E224" s="5" t="n"/>
@@ -5817,7 +5817,7 @@
       <c r="B225" s="6" t="n"/>
       <c r="C225" s="6" t="n"/>
       <c r="D225" s="6">
-        <f>IF($C225="","",$C225-WEEKDAY($C225,3))</f>
+        <f>IF($C225="","",$C225-MOD(WEEKDAY($C225,3)-4,7))</f>
         <v/>
       </c>
       <c r="E225" s="5" t="n"/>
@@ -5839,7 +5839,7 @@
       <c r="B226" s="6" t="n"/>
       <c r="C226" s="6" t="n"/>
       <c r="D226" s="6">
-        <f>IF($C226="","",$C226-WEEKDAY($C226,3))</f>
+        <f>IF($C226="","",$C226-MOD(WEEKDAY($C226,3)-4,7))</f>
         <v/>
       </c>
       <c r="E226" s="5" t="n"/>
@@ -5861,7 +5861,7 @@
       <c r="B227" s="6" t="n"/>
       <c r="C227" s="6" t="n"/>
       <c r="D227" s="6">
-        <f>IF($C227="","",$C227-WEEKDAY($C227,3))</f>
+        <f>IF($C227="","",$C227-MOD(WEEKDAY($C227,3)-4,7))</f>
         <v/>
       </c>
       <c r="E227" s="5" t="n"/>
@@ -5883,7 +5883,7 @@
       <c r="B228" s="6" t="n"/>
       <c r="C228" s="6" t="n"/>
       <c r="D228" s="6">
-        <f>IF($C228="","",$C228-WEEKDAY($C228,3))</f>
+        <f>IF($C228="","",$C228-MOD(WEEKDAY($C228,3)-4,7))</f>
         <v/>
       </c>
       <c r="E228" s="5" t="n"/>
@@ -5905,7 +5905,7 @@
       <c r="B229" s="6" t="n"/>
       <c r="C229" s="6" t="n"/>
       <c r="D229" s="6">
-        <f>IF($C229="","",$C229-WEEKDAY($C229,3))</f>
+        <f>IF($C229="","",$C229-MOD(WEEKDAY($C229,3)-4,7))</f>
         <v/>
       </c>
       <c r="E229" s="5" t="n"/>
@@ -5927,7 +5927,7 @@
       <c r="B230" s="6" t="n"/>
       <c r="C230" s="6" t="n"/>
       <c r="D230" s="6">
-        <f>IF($C230="","",$C230-WEEKDAY($C230,3))</f>
+        <f>IF($C230="","",$C230-MOD(WEEKDAY($C230,3)-4,7))</f>
         <v/>
       </c>
       <c r="E230" s="5" t="n"/>
@@ -5949,7 +5949,7 @@
       <c r="B231" s="6" t="n"/>
       <c r="C231" s="6" t="n"/>
       <c r="D231" s="6">
-        <f>IF($C231="","",$C231-WEEKDAY($C231,3))</f>
+        <f>IF($C231="","",$C231-MOD(WEEKDAY($C231,3)-4,7))</f>
         <v/>
       </c>
       <c r="E231" s="5" t="n"/>
@@ -5971,7 +5971,7 @@
       <c r="B232" s="6" t="n"/>
       <c r="C232" s="6" t="n"/>
       <c r="D232" s="6">
-        <f>IF($C232="","",$C232-WEEKDAY($C232,3))</f>
+        <f>IF($C232="","",$C232-MOD(WEEKDAY($C232,3)-4,7))</f>
         <v/>
       </c>
       <c r="E232" s="5" t="n"/>
@@ -5993,7 +5993,7 @@
       <c r="B233" s="6" t="n"/>
       <c r="C233" s="6" t="n"/>
       <c r="D233" s="6">
-        <f>IF($C233="","",$C233-WEEKDAY($C233,3))</f>
+        <f>IF($C233="","",$C233-MOD(WEEKDAY($C233,3)-4,7))</f>
         <v/>
       </c>
       <c r="E233" s="5" t="n"/>
@@ -6015,7 +6015,7 @@
       <c r="B234" s="6" t="n"/>
       <c r="C234" s="6" t="n"/>
       <c r="D234" s="6">
-        <f>IF($C234="","",$C234-WEEKDAY($C234,3))</f>
+        <f>IF($C234="","",$C234-MOD(WEEKDAY($C234,3)-4,7))</f>
         <v/>
       </c>
       <c r="E234" s="5" t="n"/>
@@ -6037,7 +6037,7 @@
       <c r="B235" s="6" t="n"/>
       <c r="C235" s="6" t="n"/>
       <c r="D235" s="6">
-        <f>IF($C235="","",$C235-WEEKDAY($C235,3))</f>
+        <f>IF($C235="","",$C235-MOD(WEEKDAY($C235,3)-4,7))</f>
         <v/>
       </c>
       <c r="E235" s="5" t="n"/>
@@ -6059,7 +6059,7 @@
       <c r="B236" s="6" t="n"/>
       <c r="C236" s="6" t="n"/>
       <c r="D236" s="6">
-        <f>IF($C236="","",$C236-WEEKDAY($C236,3))</f>
+        <f>IF($C236="","",$C236-MOD(WEEKDAY($C236,3)-4,7))</f>
         <v/>
       </c>
       <c r="E236" s="5" t="n"/>
@@ -6081,7 +6081,7 @@
       <c r="B237" s="6" t="n"/>
       <c r="C237" s="6" t="n"/>
       <c r="D237" s="6">
-        <f>IF($C237="","",$C237-WEEKDAY($C237,3))</f>
+        <f>IF($C237="","",$C237-MOD(WEEKDAY($C237,3)-4,7))</f>
         <v/>
       </c>
       <c r="E237" s="5" t="n"/>
@@ -6103,7 +6103,7 @@
       <c r="B238" s="6" t="n"/>
       <c r="C238" s="6" t="n"/>
       <c r="D238" s="6">
-        <f>IF($C238="","",$C238-WEEKDAY($C238,3))</f>
+        <f>IF($C238="","",$C238-MOD(WEEKDAY($C238,3)-4,7))</f>
         <v/>
       </c>
       <c r="E238" s="5" t="n"/>
@@ -6125,7 +6125,7 @@
       <c r="B239" s="6" t="n"/>
       <c r="C239" s="6" t="n"/>
       <c r="D239" s="6">
-        <f>IF($C239="","",$C239-WEEKDAY($C239,3))</f>
+        <f>IF($C239="","",$C239-MOD(WEEKDAY($C239,3)-4,7))</f>
         <v/>
       </c>
       <c r="E239" s="5" t="n"/>
@@ -6147,7 +6147,7 @@
       <c r="B240" s="6" t="n"/>
       <c r="C240" s="6" t="n"/>
       <c r="D240" s="6">
-        <f>IF($C240="","",$C240-WEEKDAY($C240,3))</f>
+        <f>IF($C240="","",$C240-MOD(WEEKDAY($C240,3)-4,7))</f>
         <v/>
       </c>
       <c r="E240" s="5" t="n"/>
@@ -6169,7 +6169,7 @@
       <c r="B241" s="6" t="n"/>
       <c r="C241" s="6" t="n"/>
       <c r="D241" s="6">
-        <f>IF($C241="","",$C241-WEEKDAY($C241,3))</f>
+        <f>IF($C241="","",$C241-MOD(WEEKDAY($C241,3)-4,7))</f>
         <v/>
       </c>
       <c r="E241" s="5" t="n"/>
@@ -6191,7 +6191,7 @@
       <c r="B242" s="6" t="n"/>
       <c r="C242" s="6" t="n"/>
       <c r="D242" s="6">
-        <f>IF($C242="","",$C242-WEEKDAY($C242,3))</f>
+        <f>IF($C242="","",$C242-MOD(WEEKDAY($C242,3)-4,7))</f>
         <v/>
       </c>
       <c r="E242" s="5" t="n"/>
@@ -6213,7 +6213,7 @@
       <c r="B243" s="6" t="n"/>
       <c r="C243" s="6" t="n"/>
       <c r="D243" s="6">
-        <f>IF($C243="","",$C243-WEEKDAY($C243,3))</f>
+        <f>IF($C243="","",$C243-MOD(WEEKDAY($C243,3)-4,7))</f>
         <v/>
       </c>
       <c r="E243" s="5" t="n"/>
@@ -6235,7 +6235,7 @@
       <c r="B244" s="6" t="n"/>
       <c r="C244" s="6" t="n"/>
       <c r="D244" s="6">
-        <f>IF($C244="","",$C244-WEEKDAY($C244,3))</f>
+        <f>IF($C244="","",$C244-MOD(WEEKDAY($C244,3)-4,7))</f>
         <v/>
       </c>
       <c r="E244" s="5" t="n"/>
@@ -6257,7 +6257,7 @@
       <c r="B245" s="6" t="n"/>
       <c r="C245" s="6" t="n"/>
       <c r="D245" s="6">
-        <f>IF($C245="","",$C245-WEEKDAY($C245,3))</f>
+        <f>IF($C245="","",$C245-MOD(WEEKDAY($C245,3)-4,7))</f>
         <v/>
       </c>
       <c r="E245" s="5" t="n"/>
@@ -6279,7 +6279,7 @@
       <c r="B246" s="6" t="n"/>
       <c r="C246" s="6" t="n"/>
       <c r="D246" s="6">
-        <f>IF($C246="","",$C246-WEEKDAY($C246,3))</f>
+        <f>IF($C246="","",$C246-MOD(WEEKDAY($C246,3)-4,7))</f>
         <v/>
       </c>
       <c r="E246" s="5" t="n"/>
@@ -6301,7 +6301,7 @@
       <c r="B247" s="6" t="n"/>
       <c r="C247" s="6" t="n"/>
       <c r="D247" s="6">
-        <f>IF($C247="","",$C247-WEEKDAY($C247,3))</f>
+        <f>IF($C247="","",$C247-MOD(WEEKDAY($C247,3)-4,7))</f>
         <v/>
       </c>
       <c r="E247" s="5" t="n"/>
@@ -6323,7 +6323,7 @@
       <c r="B248" s="6" t="n"/>
       <c r="C248" s="6" t="n"/>
       <c r="D248" s="6">
-        <f>IF($C248="","",$C248-WEEKDAY($C248,3))</f>
+        <f>IF($C248="","",$C248-MOD(WEEKDAY($C248,3)-4,7))</f>
         <v/>
       </c>
       <c r="E248" s="5" t="n"/>
@@ -6345,7 +6345,7 @@
       <c r="B249" s="6" t="n"/>
       <c r="C249" s="6" t="n"/>
       <c r="D249" s="6">
-        <f>IF($C249="","",$C249-WEEKDAY($C249,3))</f>
+        <f>IF($C249="","",$C249-MOD(WEEKDAY($C249,3)-4,7))</f>
         <v/>
       </c>
       <c r="E249" s="5" t="n"/>
@@ -6367,7 +6367,7 @@
       <c r="B250" s="6" t="n"/>
       <c r="C250" s="6" t="n"/>
       <c r="D250" s="6">
-        <f>IF($C250="","",$C250-WEEKDAY($C250,3))</f>
+        <f>IF($C250="","",$C250-MOD(WEEKDAY($C250,3)-4,7))</f>
         <v/>
       </c>
       <c r="E250" s="5" t="n"/>

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -911,7 +911,7 @@
       <c r="B2" s="6" t="n"/>
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="6">
-        <f>IF($C2="","",$C2-MOD(WEEKDAY($C2,3)-4,7))</f>
+        <f>IF($C2="","",$C2-MOD(WEEKDAY($C2,3)-5,7))</f>
         <v/>
       </c>
       <c r="E2" s="5" t="n"/>
@@ -933,7 +933,7 @@
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6">
-        <f>IF($C3="","",$C3-MOD(WEEKDAY($C3,3)-4,7))</f>
+        <f>IF($C3="","",$C3-MOD(WEEKDAY($C3,3)-5,7))</f>
         <v/>
       </c>
       <c r="E3" s="5" t="n"/>
@@ -955,7 +955,7 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6">
-        <f>IF($C4="","",$C4-MOD(WEEKDAY($C4,3)-4,7))</f>
+        <f>IF($C4="","",$C4-MOD(WEEKDAY($C4,3)-5,7))</f>
         <v/>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -977,7 +977,7 @@
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6">
-        <f>IF($C5="","",$C5-MOD(WEEKDAY($C5,3)-4,7))</f>
+        <f>IF($C5="","",$C5-MOD(WEEKDAY($C5,3)-5,7))</f>
         <v/>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -999,7 +999,7 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6">
-        <f>IF($C6="","",$C6-MOD(WEEKDAY($C6,3)-4,7))</f>
+        <f>IF($C6="","",$C6-MOD(WEEKDAY($C6,3)-5,7))</f>
         <v/>
       </c>
       <c r="E6" s="5" t="n"/>
@@ -1021,7 +1021,7 @@
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6">
-        <f>IF($C7="","",$C7-MOD(WEEKDAY($C7,3)-4,7))</f>
+        <f>IF($C7="","",$C7-MOD(WEEKDAY($C7,3)-5,7))</f>
         <v/>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -1043,7 +1043,7 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6">
-        <f>IF($C8="","",$C8-MOD(WEEKDAY($C8,3)-4,7))</f>
+        <f>IF($C8="","",$C8-MOD(WEEKDAY($C8,3)-5,7))</f>
         <v/>
       </c>
       <c r="E8" s="5" t="n"/>
@@ -1065,7 +1065,7 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6">
-        <f>IF($C9="","",$C9-MOD(WEEKDAY($C9,3)-4,7))</f>
+        <f>IF($C9="","",$C9-MOD(WEEKDAY($C9,3)-5,7))</f>
         <v/>
       </c>
       <c r="E9" s="5" t="n"/>
@@ -1087,7 +1087,7 @@
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6">
-        <f>IF($C10="","",$C10-MOD(WEEKDAY($C10,3)-4,7))</f>
+        <f>IF($C10="","",$C10-MOD(WEEKDAY($C10,3)-5,7))</f>
         <v/>
       </c>
       <c r="E10" s="5" t="n"/>
@@ -1109,7 +1109,7 @@
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6">
-        <f>IF($C11="","",$C11-MOD(WEEKDAY($C11,3)-4,7))</f>
+        <f>IF($C11="","",$C11-MOD(WEEKDAY($C11,3)-5,7))</f>
         <v/>
       </c>
       <c r="E11" s="5" t="n"/>
@@ -1131,7 +1131,7 @@
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6">
-        <f>IF($C12="","",$C12-MOD(WEEKDAY($C12,3)-4,7))</f>
+        <f>IF($C12="","",$C12-MOD(WEEKDAY($C12,3)-5,7))</f>
         <v/>
       </c>
       <c r="E12" s="5" t="n"/>
@@ -1153,7 +1153,7 @@
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6">
-        <f>IF($C13="","",$C13-MOD(WEEKDAY($C13,3)-4,7))</f>
+        <f>IF($C13="","",$C13-MOD(WEEKDAY($C13,3)-5,7))</f>
         <v/>
       </c>
       <c r="E13" s="5" t="n"/>
@@ -1175,7 +1175,7 @@
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6">
-        <f>IF($C14="","",$C14-MOD(WEEKDAY($C14,3)-4,7))</f>
+        <f>IF($C14="","",$C14-MOD(WEEKDAY($C14,3)-5,7))</f>
         <v/>
       </c>
       <c r="E14" s="5" t="n"/>
@@ -1197,7 +1197,7 @@
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6">
-        <f>IF($C15="","",$C15-MOD(WEEKDAY($C15,3)-4,7))</f>
+        <f>IF($C15="","",$C15-MOD(WEEKDAY($C15,3)-5,7))</f>
         <v/>
       </c>
       <c r="E15" s="5" t="n"/>
@@ -1219,7 +1219,7 @@
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6">
-        <f>IF($C16="","",$C16-MOD(WEEKDAY($C16,3)-4,7))</f>
+        <f>IF($C16="","",$C16-MOD(WEEKDAY($C16,3)-5,7))</f>
         <v/>
       </c>
       <c r="E16" s="5" t="n"/>
@@ -1241,7 +1241,7 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6">
-        <f>IF($C17="","",$C17-MOD(WEEKDAY($C17,3)-4,7))</f>
+        <f>IF($C17="","",$C17-MOD(WEEKDAY($C17,3)-5,7))</f>
         <v/>
       </c>
       <c r="E17" s="5" t="n"/>
@@ -1263,7 +1263,7 @@
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6">
-        <f>IF($C18="","",$C18-MOD(WEEKDAY($C18,3)-4,7))</f>
+        <f>IF($C18="","",$C18-MOD(WEEKDAY($C18,3)-5,7))</f>
         <v/>
       </c>
       <c r="E18" s="5" t="n"/>
@@ -1285,7 +1285,7 @@
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6">
-        <f>IF($C19="","",$C19-MOD(WEEKDAY($C19,3)-4,7))</f>
+        <f>IF($C19="","",$C19-MOD(WEEKDAY($C19,3)-5,7))</f>
         <v/>
       </c>
       <c r="E19" s="5" t="n"/>
@@ -1307,7 +1307,7 @@
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6">
-        <f>IF($C20="","",$C20-MOD(WEEKDAY($C20,3)-4,7))</f>
+        <f>IF($C20="","",$C20-MOD(WEEKDAY($C20,3)-5,7))</f>
         <v/>
       </c>
       <c r="E20" s="5" t="n"/>
@@ -1329,7 +1329,7 @@
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6">
-        <f>IF($C21="","",$C21-MOD(WEEKDAY($C21,3)-4,7))</f>
+        <f>IF($C21="","",$C21-MOD(WEEKDAY($C21,3)-5,7))</f>
         <v/>
       </c>
       <c r="E21" s="5" t="n"/>
@@ -1351,7 +1351,7 @@
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6">
-        <f>IF($C22="","",$C22-MOD(WEEKDAY($C22,3)-4,7))</f>
+        <f>IF($C22="","",$C22-MOD(WEEKDAY($C22,3)-5,7))</f>
         <v/>
       </c>
       <c r="E22" s="5" t="n"/>
@@ -1373,7 +1373,7 @@
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6">
-        <f>IF($C23="","",$C23-MOD(WEEKDAY($C23,3)-4,7))</f>
+        <f>IF($C23="","",$C23-MOD(WEEKDAY($C23,3)-5,7))</f>
         <v/>
       </c>
       <c r="E23" s="5" t="n"/>
@@ -1395,7 +1395,7 @@
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6">
-        <f>IF($C24="","",$C24-MOD(WEEKDAY($C24,3)-4,7))</f>
+        <f>IF($C24="","",$C24-MOD(WEEKDAY($C24,3)-5,7))</f>
         <v/>
       </c>
       <c r="E24" s="5" t="n"/>
@@ -1417,7 +1417,7 @@
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6">
-        <f>IF($C25="","",$C25-MOD(WEEKDAY($C25,3)-4,7))</f>
+        <f>IF($C25="","",$C25-MOD(WEEKDAY($C25,3)-5,7))</f>
         <v/>
       </c>
       <c r="E25" s="5" t="n"/>
@@ -1439,7 +1439,7 @@
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6">
-        <f>IF($C26="","",$C26-MOD(WEEKDAY($C26,3)-4,7))</f>
+        <f>IF($C26="","",$C26-MOD(WEEKDAY($C26,3)-5,7))</f>
         <v/>
       </c>
       <c r="E26" s="5" t="n"/>
@@ -1461,7 +1461,7 @@
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6">
-        <f>IF($C27="","",$C27-MOD(WEEKDAY($C27,3)-4,7))</f>
+        <f>IF($C27="","",$C27-MOD(WEEKDAY($C27,3)-5,7))</f>
         <v/>
       </c>
       <c r="E27" s="5" t="n"/>
@@ -1483,7 +1483,7 @@
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="6">
-        <f>IF($C28="","",$C28-MOD(WEEKDAY($C28,3)-4,7))</f>
+        <f>IF($C28="","",$C28-MOD(WEEKDAY($C28,3)-5,7))</f>
         <v/>
       </c>
       <c r="E28" s="5" t="n"/>
@@ -1505,7 +1505,7 @@
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="6">
-        <f>IF($C29="","",$C29-MOD(WEEKDAY($C29,3)-4,7))</f>
+        <f>IF($C29="","",$C29-MOD(WEEKDAY($C29,3)-5,7))</f>
         <v/>
       </c>
       <c r="E29" s="5" t="n"/>
@@ -1527,7 +1527,7 @@
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="6">
-        <f>IF($C30="","",$C30-MOD(WEEKDAY($C30,3)-4,7))</f>
+        <f>IF($C30="","",$C30-MOD(WEEKDAY($C30,3)-5,7))</f>
         <v/>
       </c>
       <c r="E30" s="5" t="n"/>
@@ -1549,7 +1549,7 @@
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="6">
-        <f>IF($C31="","",$C31-MOD(WEEKDAY($C31,3)-4,7))</f>
+        <f>IF($C31="","",$C31-MOD(WEEKDAY($C31,3)-5,7))</f>
         <v/>
       </c>
       <c r="E31" s="5" t="n"/>
@@ -1571,7 +1571,7 @@
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6">
-        <f>IF($C32="","",$C32-MOD(WEEKDAY($C32,3)-4,7))</f>
+        <f>IF($C32="","",$C32-MOD(WEEKDAY($C32,3)-5,7))</f>
         <v/>
       </c>
       <c r="E32" s="5" t="n"/>
@@ -1593,7 +1593,7 @@
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="6">
-        <f>IF($C33="","",$C33-MOD(WEEKDAY($C33,3)-4,7))</f>
+        <f>IF($C33="","",$C33-MOD(WEEKDAY($C33,3)-5,7))</f>
         <v/>
       </c>
       <c r="E33" s="5" t="n"/>
@@ -1615,7 +1615,7 @@
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="6">
-        <f>IF($C34="","",$C34-MOD(WEEKDAY($C34,3)-4,7))</f>
+        <f>IF($C34="","",$C34-MOD(WEEKDAY($C34,3)-5,7))</f>
         <v/>
       </c>
       <c r="E34" s="5" t="n"/>
@@ -1637,7 +1637,7 @@
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="6">
-        <f>IF($C35="","",$C35-MOD(WEEKDAY($C35,3)-4,7))</f>
+        <f>IF($C35="","",$C35-MOD(WEEKDAY($C35,3)-5,7))</f>
         <v/>
       </c>
       <c r="E35" s="5" t="n"/>
@@ -1659,7 +1659,7 @@
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="6">
-        <f>IF($C36="","",$C36-MOD(WEEKDAY($C36,3)-4,7))</f>
+        <f>IF($C36="","",$C36-MOD(WEEKDAY($C36,3)-5,7))</f>
         <v/>
       </c>
       <c r="E36" s="5" t="n"/>
@@ -1681,7 +1681,7 @@
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6">
-        <f>IF($C37="","",$C37-MOD(WEEKDAY($C37,3)-4,7))</f>
+        <f>IF($C37="","",$C37-MOD(WEEKDAY($C37,3)-5,7))</f>
         <v/>
       </c>
       <c r="E37" s="5" t="n"/>
@@ -1703,7 +1703,7 @@
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="6">
-        <f>IF($C38="","",$C38-MOD(WEEKDAY($C38,3)-4,7))</f>
+        <f>IF($C38="","",$C38-MOD(WEEKDAY($C38,3)-5,7))</f>
         <v/>
       </c>
       <c r="E38" s="5" t="n"/>
@@ -1725,7 +1725,7 @@
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="6">
-        <f>IF($C39="","",$C39-MOD(WEEKDAY($C39,3)-4,7))</f>
+        <f>IF($C39="","",$C39-MOD(WEEKDAY($C39,3)-5,7))</f>
         <v/>
       </c>
       <c r="E39" s="5" t="n"/>
@@ -1747,7 +1747,7 @@
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6">
-        <f>IF($C40="","",$C40-MOD(WEEKDAY($C40,3)-4,7))</f>
+        <f>IF($C40="","",$C40-MOD(WEEKDAY($C40,3)-5,7))</f>
         <v/>
       </c>
       <c r="E40" s="5" t="n"/>
@@ -1769,7 +1769,7 @@
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="6">
-        <f>IF($C41="","",$C41-MOD(WEEKDAY($C41,3)-4,7))</f>
+        <f>IF($C41="","",$C41-MOD(WEEKDAY($C41,3)-5,7))</f>
         <v/>
       </c>
       <c r="E41" s="5" t="n"/>
@@ -1791,7 +1791,7 @@
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="6">
-        <f>IF($C42="","",$C42-MOD(WEEKDAY($C42,3)-4,7))</f>
+        <f>IF($C42="","",$C42-MOD(WEEKDAY($C42,3)-5,7))</f>
         <v/>
       </c>
       <c r="E42" s="5" t="n"/>
@@ -1813,7 +1813,7 @@
       <c r="B43" s="6" t="n"/>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6">
-        <f>IF($C43="","",$C43-MOD(WEEKDAY($C43,3)-4,7))</f>
+        <f>IF($C43="","",$C43-MOD(WEEKDAY($C43,3)-5,7))</f>
         <v/>
       </c>
       <c r="E43" s="5" t="n"/>
@@ -1835,7 +1835,7 @@
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="6" t="n"/>
       <c r="D44" s="6">
-        <f>IF($C44="","",$C44-MOD(WEEKDAY($C44,3)-4,7))</f>
+        <f>IF($C44="","",$C44-MOD(WEEKDAY($C44,3)-5,7))</f>
         <v/>
       </c>
       <c r="E44" s="5" t="n"/>
@@ -1857,7 +1857,7 @@
       <c r="B45" s="6" t="n"/>
       <c r="C45" s="6" t="n"/>
       <c r="D45" s="6">
-        <f>IF($C45="","",$C45-MOD(WEEKDAY($C45,3)-4,7))</f>
+        <f>IF($C45="","",$C45-MOD(WEEKDAY($C45,3)-5,7))</f>
         <v/>
       </c>
       <c r="E45" s="5" t="n"/>
@@ -1879,7 +1879,7 @@
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="6" t="n"/>
       <c r="D46" s="6">
-        <f>IF($C46="","",$C46-MOD(WEEKDAY($C46,3)-4,7))</f>
+        <f>IF($C46="","",$C46-MOD(WEEKDAY($C46,3)-5,7))</f>
         <v/>
       </c>
       <c r="E46" s="5" t="n"/>
@@ -1901,7 +1901,7 @@
       <c r="B47" s="6" t="n"/>
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6">
-        <f>IF($C47="","",$C47-MOD(WEEKDAY($C47,3)-4,7))</f>
+        <f>IF($C47="","",$C47-MOD(WEEKDAY($C47,3)-5,7))</f>
         <v/>
       </c>
       <c r="E47" s="5" t="n"/>
@@ -1923,7 +1923,7 @@
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="6" t="n"/>
       <c r="D48" s="6">
-        <f>IF($C48="","",$C48-MOD(WEEKDAY($C48,3)-4,7))</f>
+        <f>IF($C48="","",$C48-MOD(WEEKDAY($C48,3)-5,7))</f>
         <v/>
       </c>
       <c r="E48" s="5" t="n"/>
@@ -1945,7 +1945,7 @@
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="n"/>
       <c r="D49" s="6">
-        <f>IF($C49="","",$C49-MOD(WEEKDAY($C49,3)-4,7))</f>
+        <f>IF($C49="","",$C49-MOD(WEEKDAY($C49,3)-5,7))</f>
         <v/>
       </c>
       <c r="E49" s="5" t="n"/>
@@ -1967,7 +1967,7 @@
       <c r="B50" s="6" t="n"/>
       <c r="C50" s="6" t="n"/>
       <c r="D50" s="6">
-        <f>IF($C50="","",$C50-MOD(WEEKDAY($C50,3)-4,7))</f>
+        <f>IF($C50="","",$C50-MOD(WEEKDAY($C50,3)-5,7))</f>
         <v/>
       </c>
       <c r="E50" s="5" t="n"/>
@@ -1989,7 +1989,7 @@
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="6" t="n"/>
       <c r="D51" s="6">
-        <f>IF($C51="","",$C51-MOD(WEEKDAY($C51,3)-4,7))</f>
+        <f>IF($C51="","",$C51-MOD(WEEKDAY($C51,3)-5,7))</f>
         <v/>
       </c>
       <c r="E51" s="5" t="n"/>
@@ -2011,7 +2011,7 @@
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="6" t="n"/>
       <c r="D52" s="6">
-        <f>IF($C52="","",$C52-MOD(WEEKDAY($C52,3)-4,7))</f>
+        <f>IF($C52="","",$C52-MOD(WEEKDAY($C52,3)-5,7))</f>
         <v/>
       </c>
       <c r="E52" s="5" t="n"/>
@@ -2033,7 +2033,7 @@
       <c r="B53" s="6" t="n"/>
       <c r="C53" s="6" t="n"/>
       <c r="D53" s="6">
-        <f>IF($C53="","",$C53-MOD(WEEKDAY($C53,3)-4,7))</f>
+        <f>IF($C53="","",$C53-MOD(WEEKDAY($C53,3)-5,7))</f>
         <v/>
       </c>
       <c r="E53" s="5" t="n"/>
@@ -2055,7 +2055,7 @@
       <c r="B54" s="6" t="n"/>
       <c r="C54" s="6" t="n"/>
       <c r="D54" s="6">
-        <f>IF($C54="","",$C54-MOD(WEEKDAY($C54,3)-4,7))</f>
+        <f>IF($C54="","",$C54-MOD(WEEKDAY($C54,3)-5,7))</f>
         <v/>
       </c>
       <c r="E54" s="5" t="n"/>
@@ -2077,7 +2077,7 @@
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="6" t="n"/>
       <c r="D55" s="6">
-        <f>IF($C55="","",$C55-MOD(WEEKDAY($C55,3)-4,7))</f>
+        <f>IF($C55="","",$C55-MOD(WEEKDAY($C55,3)-5,7))</f>
         <v/>
       </c>
       <c r="E55" s="5" t="n"/>
@@ -2099,7 +2099,7 @@
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="6" t="n"/>
       <c r="D56" s="6">
-        <f>IF($C56="","",$C56-MOD(WEEKDAY($C56,3)-4,7))</f>
+        <f>IF($C56="","",$C56-MOD(WEEKDAY($C56,3)-5,7))</f>
         <v/>
       </c>
       <c r="E56" s="5" t="n"/>
@@ -2121,7 +2121,7 @@
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="6" t="n"/>
       <c r="D57" s="6">
-        <f>IF($C57="","",$C57-MOD(WEEKDAY($C57,3)-4,7))</f>
+        <f>IF($C57="","",$C57-MOD(WEEKDAY($C57,3)-5,7))</f>
         <v/>
       </c>
       <c r="E57" s="5" t="n"/>
@@ -2143,7 +2143,7 @@
       <c r="B58" s="6" t="n"/>
       <c r="C58" s="6" t="n"/>
       <c r="D58" s="6">
-        <f>IF($C58="","",$C58-MOD(WEEKDAY($C58,3)-4,7))</f>
+        <f>IF($C58="","",$C58-MOD(WEEKDAY($C58,3)-5,7))</f>
         <v/>
       </c>
       <c r="E58" s="5" t="n"/>
@@ -2165,7 +2165,7 @@
       <c r="B59" s="6" t="n"/>
       <c r="C59" s="6" t="n"/>
       <c r="D59" s="6">
-        <f>IF($C59="","",$C59-MOD(WEEKDAY($C59,3)-4,7))</f>
+        <f>IF($C59="","",$C59-MOD(WEEKDAY($C59,3)-5,7))</f>
         <v/>
       </c>
       <c r="E59" s="5" t="n"/>
@@ -2187,7 +2187,7 @@
       <c r="B60" s="6" t="n"/>
       <c r="C60" s="6" t="n"/>
       <c r="D60" s="6">
-        <f>IF($C60="","",$C60-MOD(WEEKDAY($C60,3)-4,7))</f>
+        <f>IF($C60="","",$C60-MOD(WEEKDAY($C60,3)-5,7))</f>
         <v/>
       </c>
       <c r="E60" s="5" t="n"/>
@@ -2209,7 +2209,7 @@
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="6" t="n"/>
       <c r="D61" s="6">
-        <f>IF($C61="","",$C61-MOD(WEEKDAY($C61,3)-4,7))</f>
+        <f>IF($C61="","",$C61-MOD(WEEKDAY($C61,3)-5,7))</f>
         <v/>
       </c>
       <c r="E61" s="5" t="n"/>
@@ -2231,7 +2231,7 @@
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="6" t="n"/>
       <c r="D62" s="6">
-        <f>IF($C62="","",$C62-MOD(WEEKDAY($C62,3)-4,7))</f>
+        <f>IF($C62="","",$C62-MOD(WEEKDAY($C62,3)-5,7))</f>
         <v/>
       </c>
       <c r="E62" s="5" t="n"/>
@@ -2253,7 +2253,7 @@
       <c r="B63" s="6" t="n"/>
       <c r="C63" s="6" t="n"/>
       <c r="D63" s="6">
-        <f>IF($C63="","",$C63-MOD(WEEKDAY($C63,3)-4,7))</f>
+        <f>IF($C63="","",$C63-MOD(WEEKDAY($C63,3)-5,7))</f>
         <v/>
       </c>
       <c r="E63" s="5" t="n"/>
@@ -2275,7 +2275,7 @@
       <c r="B64" s="6" t="n"/>
       <c r="C64" s="6" t="n"/>
       <c r="D64" s="6">
-        <f>IF($C64="","",$C64-MOD(WEEKDAY($C64,3)-4,7))</f>
+        <f>IF($C64="","",$C64-MOD(WEEKDAY($C64,3)-5,7))</f>
         <v/>
       </c>
       <c r="E64" s="5" t="n"/>
@@ -2297,7 +2297,7 @@
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="6" t="n"/>
       <c r="D65" s="6">
-        <f>IF($C65="","",$C65-MOD(WEEKDAY($C65,3)-4,7))</f>
+        <f>IF($C65="","",$C65-MOD(WEEKDAY($C65,3)-5,7))</f>
         <v/>
       </c>
       <c r="E65" s="5" t="n"/>
@@ -2319,7 +2319,7 @@
       <c r="B66" s="6" t="n"/>
       <c r="C66" s="6" t="n"/>
       <c r="D66" s="6">
-        <f>IF($C66="","",$C66-MOD(WEEKDAY($C66,3)-4,7))</f>
+        <f>IF($C66="","",$C66-MOD(WEEKDAY($C66,3)-5,7))</f>
         <v/>
       </c>
       <c r="E66" s="5" t="n"/>
@@ -2341,7 +2341,7 @@
       <c r="B67" s="6" t="n"/>
       <c r="C67" s="6" t="n"/>
       <c r="D67" s="6">
-        <f>IF($C67="","",$C67-MOD(WEEKDAY($C67,3)-4,7))</f>
+        <f>IF($C67="","",$C67-MOD(WEEKDAY($C67,3)-5,7))</f>
         <v/>
       </c>
       <c r="E67" s="5" t="n"/>
@@ -2363,7 +2363,7 @@
       <c r="B68" s="6" t="n"/>
       <c r="C68" s="6" t="n"/>
       <c r="D68" s="6">
-        <f>IF($C68="","",$C68-MOD(WEEKDAY($C68,3)-4,7))</f>
+        <f>IF($C68="","",$C68-MOD(WEEKDAY($C68,3)-5,7))</f>
         <v/>
       </c>
       <c r="E68" s="5" t="n"/>
@@ -2385,7 +2385,7 @@
       <c r="B69" s="6" t="n"/>
       <c r="C69" s="6" t="n"/>
       <c r="D69" s="6">
-        <f>IF($C69="","",$C69-MOD(WEEKDAY($C69,3)-4,7))</f>
+        <f>IF($C69="","",$C69-MOD(WEEKDAY($C69,3)-5,7))</f>
         <v/>
       </c>
       <c r="E69" s="5" t="n"/>
@@ -2407,7 +2407,7 @@
       <c r="B70" s="6" t="n"/>
       <c r="C70" s="6" t="n"/>
       <c r="D70" s="6">
-        <f>IF($C70="","",$C70-MOD(WEEKDAY($C70,3)-4,7))</f>
+        <f>IF($C70="","",$C70-MOD(WEEKDAY($C70,3)-5,7))</f>
         <v/>
       </c>
       <c r="E70" s="5" t="n"/>
@@ -2429,7 +2429,7 @@
       <c r="B71" s="6" t="n"/>
       <c r="C71" s="6" t="n"/>
       <c r="D71" s="6">
-        <f>IF($C71="","",$C71-MOD(WEEKDAY($C71,3)-4,7))</f>
+        <f>IF($C71="","",$C71-MOD(WEEKDAY($C71,3)-5,7))</f>
         <v/>
       </c>
       <c r="E71" s="5" t="n"/>
@@ -2451,7 +2451,7 @@
       <c r="B72" s="6" t="n"/>
       <c r="C72" s="6" t="n"/>
       <c r="D72" s="6">
-        <f>IF($C72="","",$C72-MOD(WEEKDAY($C72,3)-4,7))</f>
+        <f>IF($C72="","",$C72-MOD(WEEKDAY($C72,3)-5,7))</f>
         <v/>
       </c>
       <c r="E72" s="5" t="n"/>
@@ -2473,7 +2473,7 @@
       <c r="B73" s="6" t="n"/>
       <c r="C73" s="6" t="n"/>
       <c r="D73" s="6">
-        <f>IF($C73="","",$C73-MOD(WEEKDAY($C73,3)-4,7))</f>
+        <f>IF($C73="","",$C73-MOD(WEEKDAY($C73,3)-5,7))</f>
         <v/>
       </c>
       <c r="E73" s="5" t="n"/>
@@ -2495,7 +2495,7 @@
       <c r="B74" s="6" t="n"/>
       <c r="C74" s="6" t="n"/>
       <c r="D74" s="6">
-        <f>IF($C74="","",$C74-MOD(WEEKDAY($C74,3)-4,7))</f>
+        <f>IF($C74="","",$C74-MOD(WEEKDAY($C74,3)-5,7))</f>
         <v/>
       </c>
       <c r="E74" s="5" t="n"/>
@@ -2517,7 +2517,7 @@
       <c r="B75" s="6" t="n"/>
       <c r="C75" s="6" t="n"/>
       <c r="D75" s="6">
-        <f>IF($C75="","",$C75-MOD(WEEKDAY($C75,3)-4,7))</f>
+        <f>IF($C75="","",$C75-MOD(WEEKDAY($C75,3)-5,7))</f>
         <v/>
       </c>
       <c r="E75" s="5" t="n"/>
@@ -2539,7 +2539,7 @@
       <c r="B76" s="6" t="n"/>
       <c r="C76" s="6" t="n"/>
       <c r="D76" s="6">
-        <f>IF($C76="","",$C76-MOD(WEEKDAY($C76,3)-4,7))</f>
+        <f>IF($C76="","",$C76-MOD(WEEKDAY($C76,3)-5,7))</f>
         <v/>
       </c>
       <c r="E76" s="5" t="n"/>
@@ -2561,7 +2561,7 @@
       <c r="B77" s="6" t="n"/>
       <c r="C77" s="6" t="n"/>
       <c r="D77" s="6">
-        <f>IF($C77="","",$C77-MOD(WEEKDAY($C77,3)-4,7))</f>
+        <f>IF($C77="","",$C77-MOD(WEEKDAY($C77,3)-5,7))</f>
         <v/>
       </c>
       <c r="E77" s="5" t="n"/>
@@ -2583,7 +2583,7 @@
       <c r="B78" s="6" t="n"/>
       <c r="C78" s="6" t="n"/>
       <c r="D78" s="6">
-        <f>IF($C78="","",$C78-MOD(WEEKDAY($C78,3)-4,7))</f>
+        <f>IF($C78="","",$C78-MOD(WEEKDAY($C78,3)-5,7))</f>
         <v/>
       </c>
       <c r="E78" s="5" t="n"/>
@@ -2605,7 +2605,7 @@
       <c r="B79" s="6" t="n"/>
       <c r="C79" s="6" t="n"/>
       <c r="D79" s="6">
-        <f>IF($C79="","",$C79-MOD(WEEKDAY($C79,3)-4,7))</f>
+        <f>IF($C79="","",$C79-MOD(WEEKDAY($C79,3)-5,7))</f>
         <v/>
       </c>
       <c r="E79" s="5" t="n"/>
@@ -2627,7 +2627,7 @@
       <c r="B80" s="6" t="n"/>
       <c r="C80" s="6" t="n"/>
       <c r="D80" s="6">
-        <f>IF($C80="","",$C80-MOD(WEEKDAY($C80,3)-4,7))</f>
+        <f>IF($C80="","",$C80-MOD(WEEKDAY($C80,3)-5,7))</f>
         <v/>
       </c>
       <c r="E80" s="5" t="n"/>
@@ -2649,7 +2649,7 @@
       <c r="B81" s="6" t="n"/>
       <c r="C81" s="6" t="n"/>
       <c r="D81" s="6">
-        <f>IF($C81="","",$C81-MOD(WEEKDAY($C81,3)-4,7))</f>
+        <f>IF($C81="","",$C81-MOD(WEEKDAY($C81,3)-5,7))</f>
         <v/>
       </c>
       <c r="E81" s="5" t="n"/>
@@ -2671,7 +2671,7 @@
       <c r="B82" s="6" t="n"/>
       <c r="C82" s="6" t="n"/>
       <c r="D82" s="6">
-        <f>IF($C82="","",$C82-MOD(WEEKDAY($C82,3)-4,7))</f>
+        <f>IF($C82="","",$C82-MOD(WEEKDAY($C82,3)-5,7))</f>
         <v/>
       </c>
       <c r="E82" s="5" t="n"/>
@@ -2693,7 +2693,7 @@
       <c r="B83" s="6" t="n"/>
       <c r="C83" s="6" t="n"/>
       <c r="D83" s="6">
-        <f>IF($C83="","",$C83-MOD(WEEKDAY($C83,3)-4,7))</f>
+        <f>IF($C83="","",$C83-MOD(WEEKDAY($C83,3)-5,7))</f>
         <v/>
       </c>
       <c r="E83" s="5" t="n"/>
@@ -2715,7 +2715,7 @@
       <c r="B84" s="6" t="n"/>
       <c r="C84" s="6" t="n"/>
       <c r="D84" s="6">
-        <f>IF($C84="","",$C84-MOD(WEEKDAY($C84,3)-4,7))</f>
+        <f>IF($C84="","",$C84-MOD(WEEKDAY($C84,3)-5,7))</f>
         <v/>
       </c>
       <c r="E84" s="5" t="n"/>
@@ -2737,7 +2737,7 @@
       <c r="B85" s="6" t="n"/>
       <c r="C85" s="6" t="n"/>
       <c r="D85" s="6">
-        <f>IF($C85="","",$C85-MOD(WEEKDAY($C85,3)-4,7))</f>
+        <f>IF($C85="","",$C85-MOD(WEEKDAY($C85,3)-5,7))</f>
         <v/>
       </c>
       <c r="E85" s="5" t="n"/>
@@ -2759,7 +2759,7 @@
       <c r="B86" s="6" t="n"/>
       <c r="C86" s="6" t="n"/>
       <c r="D86" s="6">
-        <f>IF($C86="","",$C86-MOD(WEEKDAY($C86,3)-4,7))</f>
+        <f>IF($C86="","",$C86-MOD(WEEKDAY($C86,3)-5,7))</f>
         <v/>
       </c>
       <c r="E86" s="5" t="n"/>
@@ -2781,7 +2781,7 @@
       <c r="B87" s="6" t="n"/>
       <c r="C87" s="6" t="n"/>
       <c r="D87" s="6">
-        <f>IF($C87="","",$C87-MOD(WEEKDAY($C87,3)-4,7))</f>
+        <f>IF($C87="","",$C87-MOD(WEEKDAY($C87,3)-5,7))</f>
         <v/>
       </c>
       <c r="E87" s="5" t="n"/>
@@ -2803,7 +2803,7 @@
       <c r="B88" s="6" t="n"/>
       <c r="C88" s="6" t="n"/>
       <c r="D88" s="6">
-        <f>IF($C88="","",$C88-MOD(WEEKDAY($C88,3)-4,7))</f>
+        <f>IF($C88="","",$C88-MOD(WEEKDAY($C88,3)-5,7))</f>
         <v/>
       </c>
       <c r="E88" s="5" t="n"/>
@@ -2825,7 +2825,7 @@
       <c r="B89" s="6" t="n"/>
       <c r="C89" s="6" t="n"/>
       <c r="D89" s="6">
-        <f>IF($C89="","",$C89-MOD(WEEKDAY($C89,3)-4,7))</f>
+        <f>IF($C89="","",$C89-MOD(WEEKDAY($C89,3)-5,7))</f>
         <v/>
       </c>
       <c r="E89" s="5" t="n"/>
@@ -2847,7 +2847,7 @@
       <c r="B90" s="6" t="n"/>
       <c r="C90" s="6" t="n"/>
       <c r="D90" s="6">
-        <f>IF($C90="","",$C90-MOD(WEEKDAY($C90,3)-4,7))</f>
+        <f>IF($C90="","",$C90-MOD(WEEKDAY($C90,3)-5,7))</f>
         <v/>
       </c>
       <c r="E90" s="5" t="n"/>
@@ -2869,7 +2869,7 @@
       <c r="B91" s="6" t="n"/>
       <c r="C91" s="6" t="n"/>
       <c r="D91" s="6">
-        <f>IF($C91="","",$C91-MOD(WEEKDAY($C91,3)-4,7))</f>
+        <f>IF($C91="","",$C91-MOD(WEEKDAY($C91,3)-5,7))</f>
         <v/>
       </c>
       <c r="E91" s="5" t="n"/>
@@ -2891,7 +2891,7 @@
       <c r="B92" s="6" t="n"/>
       <c r="C92" s="6" t="n"/>
       <c r="D92" s="6">
-        <f>IF($C92="","",$C92-MOD(WEEKDAY($C92,3)-4,7))</f>
+        <f>IF($C92="","",$C92-MOD(WEEKDAY($C92,3)-5,7))</f>
         <v/>
       </c>
       <c r="E92" s="5" t="n"/>
@@ -2913,7 +2913,7 @@
       <c r="B93" s="6" t="n"/>
       <c r="C93" s="6" t="n"/>
       <c r="D93" s="6">
-        <f>IF($C93="","",$C93-MOD(WEEKDAY($C93,3)-4,7))</f>
+        <f>IF($C93="","",$C93-MOD(WEEKDAY($C93,3)-5,7))</f>
         <v/>
       </c>
       <c r="E93" s="5" t="n"/>
@@ -2935,7 +2935,7 @@
       <c r="B94" s="6" t="n"/>
       <c r="C94" s="6" t="n"/>
       <c r="D94" s="6">
-        <f>IF($C94="","",$C94-MOD(WEEKDAY($C94,3)-4,7))</f>
+        <f>IF($C94="","",$C94-MOD(WEEKDAY($C94,3)-5,7))</f>
         <v/>
       </c>
       <c r="E94" s="5" t="n"/>
@@ -2957,7 +2957,7 @@
       <c r="B95" s="6" t="n"/>
       <c r="C95" s="6" t="n"/>
       <c r="D95" s="6">
-        <f>IF($C95="","",$C95-MOD(WEEKDAY($C95,3)-4,7))</f>
+        <f>IF($C95="","",$C95-MOD(WEEKDAY($C95,3)-5,7))</f>
         <v/>
       </c>
       <c r="E95" s="5" t="n"/>
@@ -2979,7 +2979,7 @@
       <c r="B96" s="6" t="n"/>
       <c r="C96" s="6" t="n"/>
       <c r="D96" s="6">
-        <f>IF($C96="","",$C96-MOD(WEEKDAY($C96,3)-4,7))</f>
+        <f>IF($C96="","",$C96-MOD(WEEKDAY($C96,3)-5,7))</f>
         <v/>
       </c>
       <c r="E96" s="5" t="n"/>
@@ -3001,7 +3001,7 @@
       <c r="B97" s="6" t="n"/>
       <c r="C97" s="6" t="n"/>
       <c r="D97" s="6">
-        <f>IF($C97="","",$C97-MOD(WEEKDAY($C97,3)-4,7))</f>
+        <f>IF($C97="","",$C97-MOD(WEEKDAY($C97,3)-5,7))</f>
         <v/>
       </c>
       <c r="E97" s="5" t="n"/>
@@ -3023,7 +3023,7 @@
       <c r="B98" s="6" t="n"/>
       <c r="C98" s="6" t="n"/>
       <c r="D98" s="6">
-        <f>IF($C98="","",$C98-MOD(WEEKDAY($C98,3)-4,7))</f>
+        <f>IF($C98="","",$C98-MOD(WEEKDAY($C98,3)-5,7))</f>
         <v/>
       </c>
       <c r="E98" s="5" t="n"/>
@@ -3045,7 +3045,7 @@
       <c r="B99" s="6" t="n"/>
       <c r="C99" s="6" t="n"/>
       <c r="D99" s="6">
-        <f>IF($C99="","",$C99-MOD(WEEKDAY($C99,3)-4,7))</f>
+        <f>IF($C99="","",$C99-MOD(WEEKDAY($C99,3)-5,7))</f>
         <v/>
       </c>
       <c r="E99" s="5" t="n"/>
@@ -3067,7 +3067,7 @@
       <c r="B100" s="6" t="n"/>
       <c r="C100" s="6" t="n"/>
       <c r="D100" s="6">
-        <f>IF($C100="","",$C100-MOD(WEEKDAY($C100,3)-4,7))</f>
+        <f>IF($C100="","",$C100-MOD(WEEKDAY($C100,3)-5,7))</f>
         <v/>
       </c>
       <c r="E100" s="5" t="n"/>
@@ -3089,7 +3089,7 @@
       <c r="B101" s="6" t="n"/>
       <c r="C101" s="6" t="n"/>
       <c r="D101" s="6">
-        <f>IF($C101="","",$C101-MOD(WEEKDAY($C101,3)-4,7))</f>
+        <f>IF($C101="","",$C101-MOD(WEEKDAY($C101,3)-5,7))</f>
         <v/>
       </c>
       <c r="E101" s="5" t="n"/>
@@ -3111,7 +3111,7 @@
       <c r="B102" s="6" t="n"/>
       <c r="C102" s="6" t="n"/>
       <c r="D102" s="6">
-        <f>IF($C102="","",$C102-MOD(WEEKDAY($C102,3)-4,7))</f>
+        <f>IF($C102="","",$C102-MOD(WEEKDAY($C102,3)-5,7))</f>
         <v/>
       </c>
       <c r="E102" s="5" t="n"/>
@@ -3133,7 +3133,7 @@
       <c r="B103" s="6" t="n"/>
       <c r="C103" s="6" t="n"/>
       <c r="D103" s="6">
-        <f>IF($C103="","",$C103-MOD(WEEKDAY($C103,3)-4,7))</f>
+        <f>IF($C103="","",$C103-MOD(WEEKDAY($C103,3)-5,7))</f>
         <v/>
       </c>
       <c r="E103" s="5" t="n"/>
@@ -3155,7 +3155,7 @@
       <c r="B104" s="6" t="n"/>
       <c r="C104" s="6" t="n"/>
       <c r="D104" s="6">
-        <f>IF($C104="","",$C104-MOD(WEEKDAY($C104,3)-4,7))</f>
+        <f>IF($C104="","",$C104-MOD(WEEKDAY($C104,3)-5,7))</f>
         <v/>
       </c>
       <c r="E104" s="5" t="n"/>
@@ -3177,7 +3177,7 @@
       <c r="B105" s="6" t="n"/>
       <c r="C105" s="6" t="n"/>
       <c r="D105" s="6">
-        <f>IF($C105="","",$C105-MOD(WEEKDAY($C105,3)-4,7))</f>
+        <f>IF($C105="","",$C105-MOD(WEEKDAY($C105,3)-5,7))</f>
         <v/>
       </c>
       <c r="E105" s="5" t="n"/>
@@ -3199,7 +3199,7 @@
       <c r="B106" s="6" t="n"/>
       <c r="C106" s="6" t="n"/>
       <c r="D106" s="6">
-        <f>IF($C106="","",$C106-MOD(WEEKDAY($C106,3)-4,7))</f>
+        <f>IF($C106="","",$C106-MOD(WEEKDAY($C106,3)-5,7))</f>
         <v/>
       </c>
       <c r="E106" s="5" t="n"/>
@@ -3221,7 +3221,7 @@
       <c r="B107" s="6" t="n"/>
       <c r="C107" s="6" t="n"/>
       <c r="D107" s="6">
-        <f>IF($C107="","",$C107-MOD(WEEKDAY($C107,3)-4,7))</f>
+        <f>IF($C107="","",$C107-MOD(WEEKDAY($C107,3)-5,7))</f>
         <v/>
       </c>
       <c r="E107" s="5" t="n"/>
@@ -3243,7 +3243,7 @@
       <c r="B108" s="6" t="n"/>
       <c r="C108" s="6" t="n"/>
       <c r="D108" s="6">
-        <f>IF($C108="","",$C108-MOD(WEEKDAY($C108,3)-4,7))</f>
+        <f>IF($C108="","",$C108-MOD(WEEKDAY($C108,3)-5,7))</f>
         <v/>
       </c>
       <c r="E108" s="5" t="n"/>
@@ -3265,7 +3265,7 @@
       <c r="B109" s="6" t="n"/>
       <c r="C109" s="6" t="n"/>
       <c r="D109" s="6">
-        <f>IF($C109="","",$C109-MOD(WEEKDAY($C109,3)-4,7))</f>
+        <f>IF($C109="","",$C109-MOD(WEEKDAY($C109,3)-5,7))</f>
         <v/>
       </c>
       <c r="E109" s="5" t="n"/>
@@ -3287,7 +3287,7 @@
       <c r="B110" s="6" t="n"/>
       <c r="C110" s="6" t="n"/>
       <c r="D110" s="6">
-        <f>IF($C110="","",$C110-MOD(WEEKDAY($C110,3)-4,7))</f>
+        <f>IF($C110="","",$C110-MOD(WEEKDAY($C110,3)-5,7))</f>
         <v/>
       </c>
       <c r="E110" s="5" t="n"/>
@@ -3309,7 +3309,7 @@
       <c r="B111" s="6" t="n"/>
       <c r="C111" s="6" t="n"/>
       <c r="D111" s="6">
-        <f>IF($C111="","",$C111-MOD(WEEKDAY($C111,3)-4,7))</f>
+        <f>IF($C111="","",$C111-MOD(WEEKDAY($C111,3)-5,7))</f>
         <v/>
       </c>
       <c r="E111" s="5" t="n"/>
@@ -3331,7 +3331,7 @@
       <c r="B112" s="6" t="n"/>
       <c r="C112" s="6" t="n"/>
       <c r="D112" s="6">
-        <f>IF($C112="","",$C112-MOD(WEEKDAY($C112,3)-4,7))</f>
+        <f>IF($C112="","",$C112-MOD(WEEKDAY($C112,3)-5,7))</f>
         <v/>
       </c>
       <c r="E112" s="5" t="n"/>
@@ -3353,7 +3353,7 @@
       <c r="B113" s="6" t="n"/>
       <c r="C113" s="6" t="n"/>
       <c r="D113" s="6">
-        <f>IF($C113="","",$C113-MOD(WEEKDAY($C113,3)-4,7))</f>
+        <f>IF($C113="","",$C113-MOD(WEEKDAY($C113,3)-5,7))</f>
         <v/>
       </c>
       <c r="E113" s="5" t="n"/>
@@ -3375,7 +3375,7 @@
       <c r="B114" s="6" t="n"/>
       <c r="C114" s="6" t="n"/>
       <c r="D114" s="6">
-        <f>IF($C114="","",$C114-MOD(WEEKDAY($C114,3)-4,7))</f>
+        <f>IF($C114="","",$C114-MOD(WEEKDAY($C114,3)-5,7))</f>
         <v/>
       </c>
       <c r="E114" s="5" t="n"/>
@@ -3397,7 +3397,7 @@
       <c r="B115" s="6" t="n"/>
       <c r="C115" s="6" t="n"/>
       <c r="D115" s="6">
-        <f>IF($C115="","",$C115-MOD(WEEKDAY($C115,3)-4,7))</f>
+        <f>IF($C115="","",$C115-MOD(WEEKDAY($C115,3)-5,7))</f>
         <v/>
       </c>
       <c r="E115" s="5" t="n"/>
@@ -3419,7 +3419,7 @@
       <c r="B116" s="6" t="n"/>
       <c r="C116" s="6" t="n"/>
       <c r="D116" s="6">
-        <f>IF($C116="","",$C116-MOD(WEEKDAY($C116,3)-4,7))</f>
+        <f>IF($C116="","",$C116-MOD(WEEKDAY($C116,3)-5,7))</f>
         <v/>
       </c>
       <c r="E116" s="5" t="n"/>
@@ -3441,7 +3441,7 @@
       <c r="B117" s="6" t="n"/>
       <c r="C117" s="6" t="n"/>
       <c r="D117" s="6">
-        <f>IF($C117="","",$C117-MOD(WEEKDAY($C117,3)-4,7))</f>
+        <f>IF($C117="","",$C117-MOD(WEEKDAY($C117,3)-5,7))</f>
         <v/>
       </c>
       <c r="E117" s="5" t="n"/>
@@ -3463,7 +3463,7 @@
       <c r="B118" s="6" t="n"/>
       <c r="C118" s="6" t="n"/>
       <c r="D118" s="6">
-        <f>IF($C118="","",$C118-MOD(WEEKDAY($C118,3)-4,7))</f>
+        <f>IF($C118="","",$C118-MOD(WEEKDAY($C118,3)-5,7))</f>
         <v/>
       </c>
       <c r="E118" s="5" t="n"/>
@@ -3485,7 +3485,7 @@
       <c r="B119" s="6" t="n"/>
       <c r="C119" s="6" t="n"/>
       <c r="D119" s="6">
-        <f>IF($C119="","",$C119-MOD(WEEKDAY($C119,3)-4,7))</f>
+        <f>IF($C119="","",$C119-MOD(WEEKDAY($C119,3)-5,7))</f>
         <v/>
       </c>
       <c r="E119" s="5" t="n"/>
@@ -3507,7 +3507,7 @@
       <c r="B120" s="6" t="n"/>
       <c r="C120" s="6" t="n"/>
       <c r="D120" s="6">
-        <f>IF($C120="","",$C120-MOD(WEEKDAY($C120,3)-4,7))</f>
+        <f>IF($C120="","",$C120-MOD(WEEKDAY($C120,3)-5,7))</f>
         <v/>
       </c>
       <c r="E120" s="5" t="n"/>
@@ -3529,7 +3529,7 @@
       <c r="B121" s="6" t="n"/>
       <c r="C121" s="6" t="n"/>
       <c r="D121" s="6">
-        <f>IF($C121="","",$C121-MOD(WEEKDAY($C121,3)-4,7))</f>
+        <f>IF($C121="","",$C121-MOD(WEEKDAY($C121,3)-5,7))</f>
         <v/>
       </c>
       <c r="E121" s="5" t="n"/>
@@ -3551,7 +3551,7 @@
       <c r="B122" s="6" t="n"/>
       <c r="C122" s="6" t="n"/>
       <c r="D122" s="6">
-        <f>IF($C122="","",$C122-MOD(WEEKDAY($C122,3)-4,7))</f>
+        <f>IF($C122="","",$C122-MOD(WEEKDAY($C122,3)-5,7))</f>
         <v/>
       </c>
       <c r="E122" s="5" t="n"/>
@@ -3573,7 +3573,7 @@
       <c r="B123" s="6" t="n"/>
       <c r="C123" s="6" t="n"/>
       <c r="D123" s="6">
-        <f>IF($C123="","",$C123-MOD(WEEKDAY($C123,3)-4,7))</f>
+        <f>IF($C123="","",$C123-MOD(WEEKDAY($C123,3)-5,7))</f>
         <v/>
       </c>
       <c r="E123" s="5" t="n"/>
@@ -3595,7 +3595,7 @@
       <c r="B124" s="6" t="n"/>
       <c r="C124" s="6" t="n"/>
       <c r="D124" s="6">
-        <f>IF($C124="","",$C124-MOD(WEEKDAY($C124,3)-4,7))</f>
+        <f>IF($C124="","",$C124-MOD(WEEKDAY($C124,3)-5,7))</f>
         <v/>
       </c>
       <c r="E124" s="5" t="n"/>
@@ -3617,7 +3617,7 @@
       <c r="B125" s="6" t="n"/>
       <c r="C125" s="6" t="n"/>
       <c r="D125" s="6">
-        <f>IF($C125="","",$C125-MOD(WEEKDAY($C125,3)-4,7))</f>
+        <f>IF($C125="","",$C125-MOD(WEEKDAY($C125,3)-5,7))</f>
         <v/>
       </c>
       <c r="E125" s="5" t="n"/>
@@ -3639,7 +3639,7 @@
       <c r="B126" s="6" t="n"/>
       <c r="C126" s="6" t="n"/>
       <c r="D126" s="6">
-        <f>IF($C126="","",$C126-MOD(WEEKDAY($C126,3)-4,7))</f>
+        <f>IF($C126="","",$C126-MOD(WEEKDAY($C126,3)-5,7))</f>
         <v/>
       </c>
       <c r="E126" s="5" t="n"/>
@@ -3661,7 +3661,7 @@
       <c r="B127" s="6" t="n"/>
       <c r="C127" s="6" t="n"/>
       <c r="D127" s="6">
-        <f>IF($C127="","",$C127-MOD(WEEKDAY($C127,3)-4,7))</f>
+        <f>IF($C127="","",$C127-MOD(WEEKDAY($C127,3)-5,7))</f>
         <v/>
       </c>
       <c r="E127" s="5" t="n"/>
@@ -3683,7 +3683,7 @@
       <c r="B128" s="6" t="n"/>
       <c r="C128" s="6" t="n"/>
       <c r="D128" s="6">
-        <f>IF($C128="","",$C128-MOD(WEEKDAY($C128,3)-4,7))</f>
+        <f>IF($C128="","",$C128-MOD(WEEKDAY($C128,3)-5,7))</f>
         <v/>
       </c>
       <c r="E128" s="5" t="n"/>
@@ -3705,7 +3705,7 @@
       <c r="B129" s="6" t="n"/>
       <c r="C129" s="6" t="n"/>
       <c r="D129" s="6">
-        <f>IF($C129="","",$C129-MOD(WEEKDAY($C129,3)-4,7))</f>
+        <f>IF($C129="","",$C129-MOD(WEEKDAY($C129,3)-5,7))</f>
         <v/>
       </c>
       <c r="E129" s="5" t="n"/>
@@ -3727,7 +3727,7 @@
       <c r="B130" s="6" t="n"/>
       <c r="C130" s="6" t="n"/>
       <c r="D130" s="6">
-        <f>IF($C130="","",$C130-MOD(WEEKDAY($C130,3)-4,7))</f>
+        <f>IF($C130="","",$C130-MOD(WEEKDAY($C130,3)-5,7))</f>
         <v/>
       </c>
       <c r="E130" s="5" t="n"/>
@@ -3749,7 +3749,7 @@
       <c r="B131" s="6" t="n"/>
       <c r="C131" s="6" t="n"/>
       <c r="D131" s="6">
-        <f>IF($C131="","",$C131-MOD(WEEKDAY($C131,3)-4,7))</f>
+        <f>IF($C131="","",$C131-MOD(WEEKDAY($C131,3)-5,7))</f>
         <v/>
       </c>
       <c r="E131" s="5" t="n"/>
@@ -3771,7 +3771,7 @@
       <c r="B132" s="6" t="n"/>
       <c r="C132" s="6" t="n"/>
       <c r="D132" s="6">
-        <f>IF($C132="","",$C132-MOD(WEEKDAY($C132,3)-4,7))</f>
+        <f>IF($C132="","",$C132-MOD(WEEKDAY($C132,3)-5,7))</f>
         <v/>
       </c>
       <c r="E132" s="5" t="n"/>
@@ -3793,7 +3793,7 @@
       <c r="B133" s="6" t="n"/>
       <c r="C133" s="6" t="n"/>
       <c r="D133" s="6">
-        <f>IF($C133="","",$C133-MOD(WEEKDAY($C133,3)-4,7))</f>
+        <f>IF($C133="","",$C133-MOD(WEEKDAY($C133,3)-5,7))</f>
         <v/>
       </c>
       <c r="E133" s="5" t="n"/>
@@ -3815,7 +3815,7 @@
       <c r="B134" s="6" t="n"/>
       <c r="C134" s="6" t="n"/>
       <c r="D134" s="6">
-        <f>IF($C134="","",$C134-MOD(WEEKDAY($C134,3)-4,7))</f>
+        <f>IF($C134="","",$C134-MOD(WEEKDAY($C134,3)-5,7))</f>
         <v/>
       </c>
       <c r="E134" s="5" t="n"/>
@@ -3837,7 +3837,7 @@
       <c r="B135" s="6" t="n"/>
       <c r="C135" s="6" t="n"/>
       <c r="D135" s="6">
-        <f>IF($C135="","",$C135-MOD(WEEKDAY($C135,3)-4,7))</f>
+        <f>IF($C135="","",$C135-MOD(WEEKDAY($C135,3)-5,7))</f>
         <v/>
       </c>
       <c r="E135" s="5" t="n"/>
@@ -3859,7 +3859,7 @@
       <c r="B136" s="6" t="n"/>
       <c r="C136" s="6" t="n"/>
       <c r="D136" s="6">
-        <f>IF($C136="","",$C136-MOD(WEEKDAY($C136,3)-4,7))</f>
+        <f>IF($C136="","",$C136-MOD(WEEKDAY($C136,3)-5,7))</f>
         <v/>
       </c>
       <c r="E136" s="5" t="n"/>
@@ -3881,7 +3881,7 @@
       <c r="B137" s="6" t="n"/>
       <c r="C137" s="6" t="n"/>
       <c r="D137" s="6">
-        <f>IF($C137="","",$C137-MOD(WEEKDAY($C137,3)-4,7))</f>
+        <f>IF($C137="","",$C137-MOD(WEEKDAY($C137,3)-5,7))</f>
         <v/>
       </c>
       <c r="E137" s="5" t="n"/>
@@ -3903,7 +3903,7 @@
       <c r="B138" s="6" t="n"/>
       <c r="C138" s="6" t="n"/>
       <c r="D138" s="6">
-        <f>IF($C138="","",$C138-MOD(WEEKDAY($C138,3)-4,7))</f>
+        <f>IF($C138="","",$C138-MOD(WEEKDAY($C138,3)-5,7))</f>
         <v/>
       </c>
       <c r="E138" s="5" t="n"/>
@@ -3925,7 +3925,7 @@
       <c r="B139" s="6" t="n"/>
       <c r="C139" s="6" t="n"/>
       <c r="D139" s="6">
-        <f>IF($C139="","",$C139-MOD(WEEKDAY($C139,3)-4,7))</f>
+        <f>IF($C139="","",$C139-MOD(WEEKDAY($C139,3)-5,7))</f>
         <v/>
       </c>
       <c r="E139" s="5" t="n"/>
@@ -3947,7 +3947,7 @@
       <c r="B140" s="6" t="n"/>
       <c r="C140" s="6" t="n"/>
       <c r="D140" s="6">
-        <f>IF($C140="","",$C140-MOD(WEEKDAY($C140,3)-4,7))</f>
+        <f>IF($C140="","",$C140-MOD(WEEKDAY($C140,3)-5,7))</f>
         <v/>
       </c>
       <c r="E140" s="5" t="n"/>
@@ -3969,7 +3969,7 @@
       <c r="B141" s="6" t="n"/>
       <c r="C141" s="6" t="n"/>
       <c r="D141" s="6">
-        <f>IF($C141="","",$C141-MOD(WEEKDAY($C141,3)-4,7))</f>
+        <f>IF($C141="","",$C141-MOD(WEEKDAY($C141,3)-5,7))</f>
         <v/>
       </c>
       <c r="E141" s="5" t="n"/>
@@ -3991,7 +3991,7 @@
       <c r="B142" s="6" t="n"/>
       <c r="C142" s="6" t="n"/>
       <c r="D142" s="6">
-        <f>IF($C142="","",$C142-MOD(WEEKDAY($C142,3)-4,7))</f>
+        <f>IF($C142="","",$C142-MOD(WEEKDAY($C142,3)-5,7))</f>
         <v/>
       </c>
       <c r="E142" s="5" t="n"/>
@@ -4013,7 +4013,7 @@
       <c r="B143" s="6" t="n"/>
       <c r="C143" s="6" t="n"/>
       <c r="D143" s="6">
-        <f>IF($C143="","",$C143-MOD(WEEKDAY($C143,3)-4,7))</f>
+        <f>IF($C143="","",$C143-MOD(WEEKDAY($C143,3)-5,7))</f>
         <v/>
       </c>
       <c r="E143" s="5" t="n"/>
@@ -4035,7 +4035,7 @@
       <c r="B144" s="6" t="n"/>
       <c r="C144" s="6" t="n"/>
       <c r="D144" s="6">
-        <f>IF($C144="","",$C144-MOD(WEEKDAY($C144,3)-4,7))</f>
+        <f>IF($C144="","",$C144-MOD(WEEKDAY($C144,3)-5,7))</f>
         <v/>
       </c>
       <c r="E144" s="5" t="n"/>
@@ -4057,7 +4057,7 @@
       <c r="B145" s="6" t="n"/>
       <c r="C145" s="6" t="n"/>
       <c r="D145" s="6">
-        <f>IF($C145="","",$C145-MOD(WEEKDAY($C145,3)-4,7))</f>
+        <f>IF($C145="","",$C145-MOD(WEEKDAY($C145,3)-5,7))</f>
         <v/>
       </c>
       <c r="E145" s="5" t="n"/>
@@ -4079,7 +4079,7 @@
       <c r="B146" s="6" t="n"/>
       <c r="C146" s="6" t="n"/>
       <c r="D146" s="6">
-        <f>IF($C146="","",$C146-MOD(WEEKDAY($C146,3)-4,7))</f>
+        <f>IF($C146="","",$C146-MOD(WEEKDAY($C146,3)-5,7))</f>
         <v/>
       </c>
       <c r="E146" s="5" t="n"/>
@@ -4101,7 +4101,7 @@
       <c r="B147" s="6" t="n"/>
       <c r="C147" s="6" t="n"/>
       <c r="D147" s="6">
-        <f>IF($C147="","",$C147-MOD(WEEKDAY($C147,3)-4,7))</f>
+        <f>IF($C147="","",$C147-MOD(WEEKDAY($C147,3)-5,7))</f>
         <v/>
       </c>
       <c r="E147" s="5" t="n"/>
@@ -4123,7 +4123,7 @@
       <c r="B148" s="6" t="n"/>
       <c r="C148" s="6" t="n"/>
       <c r="D148" s="6">
-        <f>IF($C148="","",$C148-MOD(WEEKDAY($C148,3)-4,7))</f>
+        <f>IF($C148="","",$C148-MOD(WEEKDAY($C148,3)-5,7))</f>
         <v/>
       </c>
       <c r="E148" s="5" t="n"/>
@@ -4145,7 +4145,7 @@
       <c r="B149" s="6" t="n"/>
       <c r="C149" s="6" t="n"/>
       <c r="D149" s="6">
-        <f>IF($C149="","",$C149-MOD(WEEKDAY($C149,3)-4,7))</f>
+        <f>IF($C149="","",$C149-MOD(WEEKDAY($C149,3)-5,7))</f>
         <v/>
       </c>
       <c r="E149" s="5" t="n"/>
@@ -4167,7 +4167,7 @@
       <c r="B150" s="6" t="n"/>
       <c r="C150" s="6" t="n"/>
       <c r="D150" s="6">
-        <f>IF($C150="","",$C150-MOD(WEEKDAY($C150,3)-4,7))</f>
+        <f>IF($C150="","",$C150-MOD(WEEKDAY($C150,3)-5,7))</f>
         <v/>
       </c>
       <c r="E150" s="5" t="n"/>
@@ -4189,7 +4189,7 @@
       <c r="B151" s="6" t="n"/>
       <c r="C151" s="6" t="n"/>
       <c r="D151" s="6">
-        <f>IF($C151="","",$C151-MOD(WEEKDAY($C151,3)-4,7))</f>
+        <f>IF($C151="","",$C151-MOD(WEEKDAY($C151,3)-5,7))</f>
         <v/>
       </c>
       <c r="E151" s="5" t="n"/>
@@ -4211,7 +4211,7 @@
       <c r="B152" s="6" t="n"/>
       <c r="C152" s="6" t="n"/>
       <c r="D152" s="6">
-        <f>IF($C152="","",$C152-MOD(WEEKDAY($C152,3)-4,7))</f>
+        <f>IF($C152="","",$C152-MOD(WEEKDAY($C152,3)-5,7))</f>
         <v/>
       </c>
       <c r="E152" s="5" t="n"/>
@@ -4233,7 +4233,7 @@
       <c r="B153" s="6" t="n"/>
       <c r="C153" s="6" t="n"/>
       <c r="D153" s="6">
-        <f>IF($C153="","",$C153-MOD(WEEKDAY($C153,3)-4,7))</f>
+        <f>IF($C153="","",$C153-MOD(WEEKDAY($C153,3)-5,7))</f>
         <v/>
       </c>
       <c r="E153" s="5" t="n"/>
@@ -4255,7 +4255,7 @@
       <c r="B154" s="6" t="n"/>
       <c r="C154" s="6" t="n"/>
       <c r="D154" s="6">
-        <f>IF($C154="","",$C154-MOD(WEEKDAY($C154,3)-4,7))</f>
+        <f>IF($C154="","",$C154-MOD(WEEKDAY($C154,3)-5,7))</f>
         <v/>
       </c>
       <c r="E154" s="5" t="n"/>
@@ -4277,7 +4277,7 @@
       <c r="B155" s="6" t="n"/>
       <c r="C155" s="6" t="n"/>
       <c r="D155" s="6">
-        <f>IF($C155="","",$C155-MOD(WEEKDAY($C155,3)-4,7))</f>
+        <f>IF($C155="","",$C155-MOD(WEEKDAY($C155,3)-5,7))</f>
         <v/>
       </c>
       <c r="E155" s="5" t="n"/>
@@ -4299,7 +4299,7 @@
       <c r="B156" s="6" t="n"/>
       <c r="C156" s="6" t="n"/>
       <c r="D156" s="6">
-        <f>IF($C156="","",$C156-MOD(WEEKDAY($C156,3)-4,7))</f>
+        <f>IF($C156="","",$C156-MOD(WEEKDAY($C156,3)-5,7))</f>
         <v/>
       </c>
       <c r="E156" s="5" t="n"/>
@@ -4321,7 +4321,7 @@
       <c r="B157" s="6" t="n"/>
       <c r="C157" s="6" t="n"/>
       <c r="D157" s="6">
-        <f>IF($C157="","",$C157-MOD(WEEKDAY($C157,3)-4,7))</f>
+        <f>IF($C157="","",$C157-MOD(WEEKDAY($C157,3)-5,7))</f>
         <v/>
       </c>
       <c r="E157" s="5" t="n"/>
@@ -4343,7 +4343,7 @@
       <c r="B158" s="6" t="n"/>
       <c r="C158" s="6" t="n"/>
       <c r="D158" s="6">
-        <f>IF($C158="","",$C158-MOD(WEEKDAY($C158,3)-4,7))</f>
+        <f>IF($C158="","",$C158-MOD(WEEKDAY($C158,3)-5,7))</f>
         <v/>
       </c>
       <c r="E158" s="5" t="n"/>
@@ -4365,7 +4365,7 @@
       <c r="B159" s="6" t="n"/>
       <c r="C159" s="6" t="n"/>
       <c r="D159" s="6">
-        <f>IF($C159="","",$C159-MOD(WEEKDAY($C159,3)-4,7))</f>
+        <f>IF($C159="","",$C159-MOD(WEEKDAY($C159,3)-5,7))</f>
         <v/>
       </c>
       <c r="E159" s="5" t="n"/>
@@ -4387,7 +4387,7 @@
       <c r="B160" s="6" t="n"/>
       <c r="C160" s="6" t="n"/>
       <c r="D160" s="6">
-        <f>IF($C160="","",$C160-MOD(WEEKDAY($C160,3)-4,7))</f>
+        <f>IF($C160="","",$C160-MOD(WEEKDAY($C160,3)-5,7))</f>
         <v/>
       </c>
       <c r="E160" s="5" t="n"/>
@@ -4409,7 +4409,7 @@
       <c r="B161" s="6" t="n"/>
       <c r="C161" s="6" t="n"/>
       <c r="D161" s="6">
-        <f>IF($C161="","",$C161-MOD(WEEKDAY($C161,3)-4,7))</f>
+        <f>IF($C161="","",$C161-MOD(WEEKDAY($C161,3)-5,7))</f>
         <v/>
       </c>
       <c r="E161" s="5" t="n"/>
@@ -4431,7 +4431,7 @@
       <c r="B162" s="6" t="n"/>
       <c r="C162" s="6" t="n"/>
       <c r="D162" s="6">
-        <f>IF($C162="","",$C162-MOD(WEEKDAY($C162,3)-4,7))</f>
+        <f>IF($C162="","",$C162-MOD(WEEKDAY($C162,3)-5,7))</f>
         <v/>
       </c>
       <c r="E162" s="5" t="n"/>
@@ -4453,7 +4453,7 @@
       <c r="B163" s="6" t="n"/>
       <c r="C163" s="6" t="n"/>
       <c r="D163" s="6">
-        <f>IF($C163="","",$C163-MOD(WEEKDAY($C163,3)-4,7))</f>
+        <f>IF($C163="","",$C163-MOD(WEEKDAY($C163,3)-5,7))</f>
         <v/>
       </c>
       <c r="E163" s="5" t="n"/>
@@ -4475,7 +4475,7 @@
       <c r="B164" s="6" t="n"/>
       <c r="C164" s="6" t="n"/>
       <c r="D164" s="6">
-        <f>IF($C164="","",$C164-MOD(WEEKDAY($C164,3)-4,7))</f>
+        <f>IF($C164="","",$C164-MOD(WEEKDAY($C164,3)-5,7))</f>
         <v/>
       </c>
       <c r="E164" s="5" t="n"/>
@@ -4497,7 +4497,7 @@
       <c r="B165" s="6" t="n"/>
       <c r="C165" s="6" t="n"/>
       <c r="D165" s="6">
-        <f>IF($C165="","",$C165-MOD(WEEKDAY($C165,3)-4,7))</f>
+        <f>IF($C165="","",$C165-MOD(WEEKDAY($C165,3)-5,7))</f>
         <v/>
       </c>
       <c r="E165" s="5" t="n"/>
@@ -4519,7 +4519,7 @@
       <c r="B166" s="6" t="n"/>
       <c r="C166" s="6" t="n"/>
       <c r="D166" s="6">
-        <f>IF($C166="","",$C166-MOD(WEEKDAY($C166,3)-4,7))</f>
+        <f>IF($C166="","",$C166-MOD(WEEKDAY($C166,3)-5,7))</f>
         <v/>
       </c>
       <c r="E166" s="5" t="n"/>
@@ -4541,7 +4541,7 @@
       <c r="B167" s="6" t="n"/>
       <c r="C167" s="6" t="n"/>
       <c r="D167" s="6">
-        <f>IF($C167="","",$C167-MOD(WEEKDAY($C167,3)-4,7))</f>
+        <f>IF($C167="","",$C167-MOD(WEEKDAY($C167,3)-5,7))</f>
         <v/>
       </c>
       <c r="E167" s="5" t="n"/>
@@ -4563,7 +4563,7 @@
       <c r="B168" s="6" t="n"/>
       <c r="C168" s="6" t="n"/>
       <c r="D168" s="6">
-        <f>IF($C168="","",$C168-MOD(WEEKDAY($C168,3)-4,7))</f>
+        <f>IF($C168="","",$C168-MOD(WEEKDAY($C168,3)-5,7))</f>
         <v/>
       </c>
       <c r="E168" s="5" t="n"/>
@@ -4585,7 +4585,7 @@
       <c r="B169" s="6" t="n"/>
       <c r="C169" s="6" t="n"/>
       <c r="D169" s="6">
-        <f>IF($C169="","",$C169-MOD(WEEKDAY($C169,3)-4,7))</f>
+        <f>IF($C169="","",$C169-MOD(WEEKDAY($C169,3)-5,7))</f>
         <v/>
       </c>
       <c r="E169" s="5" t="n"/>
@@ -4607,7 +4607,7 @@
       <c r="B170" s="6" t="n"/>
       <c r="C170" s="6" t="n"/>
       <c r="D170" s="6">
-        <f>IF($C170="","",$C170-MOD(WEEKDAY($C170,3)-4,7))</f>
+        <f>IF($C170="","",$C170-MOD(WEEKDAY($C170,3)-5,7))</f>
         <v/>
       </c>
       <c r="E170" s="5" t="n"/>
@@ -4629,7 +4629,7 @@
       <c r="B171" s="6" t="n"/>
       <c r="C171" s="6" t="n"/>
       <c r="D171" s="6">
-        <f>IF($C171="","",$C171-MOD(WEEKDAY($C171,3)-4,7))</f>
+        <f>IF($C171="","",$C171-MOD(WEEKDAY($C171,3)-5,7))</f>
         <v/>
       </c>
       <c r="E171" s="5" t="n"/>
@@ -4651,7 +4651,7 @@
       <c r="B172" s="6" t="n"/>
       <c r="C172" s="6" t="n"/>
       <c r="D172" s="6">
-        <f>IF($C172="","",$C172-MOD(WEEKDAY($C172,3)-4,7))</f>
+        <f>IF($C172="","",$C172-MOD(WEEKDAY($C172,3)-5,7))</f>
         <v/>
       </c>
       <c r="E172" s="5" t="n"/>
@@ -4673,7 +4673,7 @@
       <c r="B173" s="6" t="n"/>
       <c r="C173" s="6" t="n"/>
       <c r="D173" s="6">
-        <f>IF($C173="","",$C173-MOD(WEEKDAY($C173,3)-4,7))</f>
+        <f>IF($C173="","",$C173-MOD(WEEKDAY($C173,3)-5,7))</f>
         <v/>
       </c>
       <c r="E173" s="5" t="n"/>
@@ -4695,7 +4695,7 @@
       <c r="B174" s="6" t="n"/>
       <c r="C174" s="6" t="n"/>
       <c r="D174" s="6">
-        <f>IF($C174="","",$C174-MOD(WEEKDAY($C174,3)-4,7))</f>
+        <f>IF($C174="","",$C174-MOD(WEEKDAY($C174,3)-5,7))</f>
         <v/>
       </c>
       <c r="E174" s="5" t="n"/>
@@ -4717,7 +4717,7 @@
       <c r="B175" s="6" t="n"/>
       <c r="C175" s="6" t="n"/>
       <c r="D175" s="6">
-        <f>IF($C175="","",$C175-MOD(WEEKDAY($C175,3)-4,7))</f>
+        <f>IF($C175="","",$C175-MOD(WEEKDAY($C175,3)-5,7))</f>
         <v/>
       </c>
       <c r="E175" s="5" t="n"/>
@@ -4739,7 +4739,7 @@
       <c r="B176" s="6" t="n"/>
       <c r="C176" s="6" t="n"/>
       <c r="D176" s="6">
-        <f>IF($C176="","",$C176-MOD(WEEKDAY($C176,3)-4,7))</f>
+        <f>IF($C176="","",$C176-MOD(WEEKDAY($C176,3)-5,7))</f>
         <v/>
       </c>
       <c r="E176" s="5" t="n"/>
@@ -4761,7 +4761,7 @@
       <c r="B177" s="6" t="n"/>
       <c r="C177" s="6" t="n"/>
       <c r="D177" s="6">
-        <f>IF($C177="","",$C177-MOD(WEEKDAY($C177,3)-4,7))</f>
+        <f>IF($C177="","",$C177-MOD(WEEKDAY($C177,3)-5,7))</f>
         <v/>
       </c>
       <c r="E177" s="5" t="n"/>
@@ -4783,7 +4783,7 @@
       <c r="B178" s="6" t="n"/>
       <c r="C178" s="6" t="n"/>
       <c r="D178" s="6">
-        <f>IF($C178="","",$C178-MOD(WEEKDAY($C178,3)-4,7))</f>
+        <f>IF($C178="","",$C178-MOD(WEEKDAY($C178,3)-5,7))</f>
         <v/>
       </c>
       <c r="E178" s="5" t="n"/>
@@ -4805,7 +4805,7 @@
       <c r="B179" s="6" t="n"/>
       <c r="C179" s="6" t="n"/>
       <c r="D179" s="6">
-        <f>IF($C179="","",$C179-MOD(WEEKDAY($C179,3)-4,7))</f>
+        <f>IF($C179="","",$C179-MOD(WEEKDAY($C179,3)-5,7))</f>
         <v/>
       </c>
       <c r="E179" s="5" t="n"/>
@@ -4827,7 +4827,7 @@
       <c r="B180" s="6" t="n"/>
       <c r="C180" s="6" t="n"/>
       <c r="D180" s="6">
-        <f>IF($C180="","",$C180-MOD(WEEKDAY($C180,3)-4,7))</f>
+        <f>IF($C180="","",$C180-MOD(WEEKDAY($C180,3)-5,7))</f>
         <v/>
       </c>
       <c r="E180" s="5" t="n"/>
@@ -4849,7 +4849,7 @@
       <c r="B181" s="6" t="n"/>
       <c r="C181" s="6" t="n"/>
       <c r="D181" s="6">
-        <f>IF($C181="","",$C181-MOD(WEEKDAY($C181,3)-4,7))</f>
+        <f>IF($C181="","",$C181-MOD(WEEKDAY($C181,3)-5,7))</f>
         <v/>
       </c>
       <c r="E181" s="5" t="n"/>
@@ -4871,7 +4871,7 @@
       <c r="B182" s="6" t="n"/>
       <c r="C182" s="6" t="n"/>
       <c r="D182" s="6">
-        <f>IF($C182="","",$C182-MOD(WEEKDAY($C182,3)-4,7))</f>
+        <f>IF($C182="","",$C182-MOD(WEEKDAY($C182,3)-5,7))</f>
         <v/>
       </c>
       <c r="E182" s="5" t="n"/>
@@ -4893,7 +4893,7 @@
       <c r="B183" s="6" t="n"/>
       <c r="C183" s="6" t="n"/>
       <c r="D183" s="6">
-        <f>IF($C183="","",$C183-MOD(WEEKDAY($C183,3)-4,7))</f>
+        <f>IF($C183="","",$C183-MOD(WEEKDAY($C183,3)-5,7))</f>
         <v/>
       </c>
       <c r="E183" s="5" t="n"/>
@@ -4915,7 +4915,7 @@
       <c r="B184" s="6" t="n"/>
       <c r="C184" s="6" t="n"/>
       <c r="D184" s="6">
-        <f>IF($C184="","",$C184-MOD(WEEKDAY($C184,3)-4,7))</f>
+        <f>IF($C184="","",$C184-MOD(WEEKDAY($C184,3)-5,7))</f>
         <v/>
       </c>
       <c r="E184" s="5" t="n"/>
@@ -4937,7 +4937,7 @@
       <c r="B185" s="6" t="n"/>
       <c r="C185" s="6" t="n"/>
       <c r="D185" s="6">
-        <f>IF($C185="","",$C185-MOD(WEEKDAY($C185,3)-4,7))</f>
+        <f>IF($C185="","",$C185-MOD(WEEKDAY($C185,3)-5,7))</f>
         <v/>
       </c>
       <c r="E185" s="5" t="n"/>
@@ -4959,7 +4959,7 @@
       <c r="B186" s="6" t="n"/>
       <c r="C186" s="6" t="n"/>
       <c r="D186" s="6">
-        <f>IF($C186="","",$C186-MOD(WEEKDAY($C186,3)-4,7))</f>
+        <f>IF($C186="","",$C186-MOD(WEEKDAY($C186,3)-5,7))</f>
         <v/>
       </c>
       <c r="E186" s="5" t="n"/>
@@ -4981,7 +4981,7 @@
       <c r="B187" s="6" t="n"/>
       <c r="C187" s="6" t="n"/>
       <c r="D187" s="6">
-        <f>IF($C187="","",$C187-MOD(WEEKDAY($C187,3)-4,7))</f>
+        <f>IF($C187="","",$C187-MOD(WEEKDAY($C187,3)-5,7))</f>
         <v/>
       </c>
       <c r="E187" s="5" t="n"/>
@@ -5003,7 +5003,7 @@
       <c r="B188" s="6" t="n"/>
       <c r="C188" s="6" t="n"/>
       <c r="D188" s="6">
-        <f>IF($C188="","",$C188-MOD(WEEKDAY($C188,3)-4,7))</f>
+        <f>IF($C188="","",$C188-MOD(WEEKDAY($C188,3)-5,7))</f>
         <v/>
       </c>
       <c r="E188" s="5" t="n"/>
@@ -5025,7 +5025,7 @@
       <c r="B189" s="6" t="n"/>
       <c r="C189" s="6" t="n"/>
       <c r="D189" s="6">
-        <f>IF($C189="","",$C189-MOD(WEEKDAY($C189,3)-4,7))</f>
+        <f>IF($C189="","",$C189-MOD(WEEKDAY($C189,3)-5,7))</f>
         <v/>
       </c>
       <c r="E189" s="5" t="n"/>
@@ -5047,7 +5047,7 @@
       <c r="B190" s="6" t="n"/>
       <c r="C190" s="6" t="n"/>
       <c r="D190" s="6">
-        <f>IF($C190="","",$C190-MOD(WEEKDAY($C190,3)-4,7))</f>
+        <f>IF($C190="","",$C190-MOD(WEEKDAY($C190,3)-5,7))</f>
         <v/>
       </c>
       <c r="E190" s="5" t="n"/>
@@ -5069,7 +5069,7 @@
       <c r="B191" s="6" t="n"/>
       <c r="C191" s="6" t="n"/>
       <c r="D191" s="6">
-        <f>IF($C191="","",$C191-MOD(WEEKDAY($C191,3)-4,7))</f>
+        <f>IF($C191="","",$C191-MOD(WEEKDAY($C191,3)-5,7))</f>
         <v/>
       </c>
       <c r="E191" s="5" t="n"/>
@@ -5091,7 +5091,7 @@
       <c r="B192" s="6" t="n"/>
       <c r="C192" s="6" t="n"/>
       <c r="D192" s="6">
-        <f>IF($C192="","",$C192-MOD(WEEKDAY($C192,3)-4,7))</f>
+        <f>IF($C192="","",$C192-MOD(WEEKDAY($C192,3)-5,7))</f>
         <v/>
       </c>
       <c r="E192" s="5" t="n"/>
@@ -5113,7 +5113,7 @@
       <c r="B193" s="6" t="n"/>
       <c r="C193" s="6" t="n"/>
       <c r="D193" s="6">
-        <f>IF($C193="","",$C193-MOD(WEEKDAY($C193,3)-4,7))</f>
+        <f>IF($C193="","",$C193-MOD(WEEKDAY($C193,3)-5,7))</f>
         <v/>
       </c>
       <c r="E193" s="5" t="n"/>
@@ -5135,7 +5135,7 @@
       <c r="B194" s="6" t="n"/>
       <c r="C194" s="6" t="n"/>
       <c r="D194" s="6">
-        <f>IF($C194="","",$C194-MOD(WEEKDAY($C194,3)-4,7))</f>
+        <f>IF($C194="","",$C194-MOD(WEEKDAY($C194,3)-5,7))</f>
         <v/>
       </c>
       <c r="E194" s="5" t="n"/>
@@ -5157,7 +5157,7 @@
       <c r="B195" s="6" t="n"/>
       <c r="C195" s="6" t="n"/>
       <c r="D195" s="6">
-        <f>IF($C195="","",$C195-MOD(WEEKDAY($C195,3)-4,7))</f>
+        <f>IF($C195="","",$C195-MOD(WEEKDAY($C195,3)-5,7))</f>
         <v/>
       </c>
       <c r="E195" s="5" t="n"/>
@@ -5179,7 +5179,7 @@
       <c r="B196" s="6" t="n"/>
       <c r="C196" s="6" t="n"/>
       <c r="D196" s="6">
-        <f>IF($C196="","",$C196-MOD(WEEKDAY($C196,3)-4,7))</f>
+        <f>IF($C196="","",$C196-MOD(WEEKDAY($C196,3)-5,7))</f>
         <v/>
       </c>
       <c r="E196" s="5" t="n"/>
@@ -5201,7 +5201,7 @@
       <c r="B197" s="6" t="n"/>
       <c r="C197" s="6" t="n"/>
       <c r="D197" s="6">
-        <f>IF($C197="","",$C197-MOD(WEEKDAY($C197,3)-4,7))</f>
+        <f>IF($C197="","",$C197-MOD(WEEKDAY($C197,3)-5,7))</f>
         <v/>
       </c>
       <c r="E197" s="5" t="n"/>
@@ -5223,7 +5223,7 @@
       <c r="B198" s="6" t="n"/>
       <c r="C198" s="6" t="n"/>
       <c r="D198" s="6">
-        <f>IF($C198="","",$C198-MOD(WEEKDAY($C198,3)-4,7))</f>
+        <f>IF($C198="","",$C198-MOD(WEEKDAY($C198,3)-5,7))</f>
         <v/>
       </c>
       <c r="E198" s="5" t="n"/>
@@ -5245,7 +5245,7 @@
       <c r="B199" s="6" t="n"/>
       <c r="C199" s="6" t="n"/>
       <c r="D199" s="6">
-        <f>IF($C199="","",$C199-MOD(WEEKDAY($C199,3)-4,7))</f>
+        <f>IF($C199="","",$C199-MOD(WEEKDAY($C199,3)-5,7))</f>
         <v/>
       </c>
       <c r="E199" s="5" t="n"/>
@@ -5267,7 +5267,7 @@
       <c r="B200" s="6" t="n"/>
       <c r="C200" s="6" t="n"/>
       <c r="D200" s="6">
-        <f>IF($C200="","",$C200-MOD(WEEKDAY($C200,3)-4,7))</f>
+        <f>IF($C200="","",$C200-MOD(WEEKDAY($C200,3)-5,7))</f>
         <v/>
       </c>
       <c r="E200" s="5" t="n"/>
@@ -5289,7 +5289,7 @@
       <c r="B201" s="6" t="n"/>
       <c r="C201" s="6" t="n"/>
       <c r="D201" s="6">
-        <f>IF($C201="","",$C201-MOD(WEEKDAY($C201,3)-4,7))</f>
+        <f>IF($C201="","",$C201-MOD(WEEKDAY($C201,3)-5,7))</f>
         <v/>
       </c>
       <c r="E201" s="5" t="n"/>
@@ -5311,7 +5311,7 @@
       <c r="B202" s="6" t="n"/>
       <c r="C202" s="6" t="n"/>
       <c r="D202" s="6">
-        <f>IF($C202="","",$C202-MOD(WEEKDAY($C202,3)-4,7))</f>
+        <f>IF($C202="","",$C202-MOD(WEEKDAY($C202,3)-5,7))</f>
         <v/>
       </c>
       <c r="E202" s="5" t="n"/>
@@ -5333,7 +5333,7 @@
       <c r="B203" s="6" t="n"/>
       <c r="C203" s="6" t="n"/>
       <c r="D203" s="6">
-        <f>IF($C203="","",$C203-MOD(WEEKDAY($C203,3)-4,7))</f>
+        <f>IF($C203="","",$C203-MOD(WEEKDAY($C203,3)-5,7))</f>
         <v/>
       </c>
       <c r="E203" s="5" t="n"/>
@@ -5355,7 +5355,7 @@
       <c r="B204" s="6" t="n"/>
       <c r="C204" s="6" t="n"/>
       <c r="D204" s="6">
-        <f>IF($C204="","",$C204-MOD(WEEKDAY($C204,3)-4,7))</f>
+        <f>IF($C204="","",$C204-MOD(WEEKDAY($C204,3)-5,7))</f>
         <v/>
       </c>
       <c r="E204" s="5" t="n"/>
@@ -5377,7 +5377,7 @@
       <c r="B205" s="6" t="n"/>
       <c r="C205" s="6" t="n"/>
       <c r="D205" s="6">
-        <f>IF($C205="","",$C205-MOD(WEEKDAY($C205,3)-4,7))</f>
+        <f>IF($C205="","",$C205-MOD(WEEKDAY($C205,3)-5,7))</f>
         <v/>
       </c>
       <c r="E205" s="5" t="n"/>
@@ -5399,7 +5399,7 @@
       <c r="B206" s="6" t="n"/>
       <c r="C206" s="6" t="n"/>
       <c r="D206" s="6">
-        <f>IF($C206="","",$C206-MOD(WEEKDAY($C206,3)-4,7))</f>
+        <f>IF($C206="","",$C206-MOD(WEEKDAY($C206,3)-5,7))</f>
         <v/>
       </c>
       <c r="E206" s="5" t="n"/>
@@ -5421,7 +5421,7 @@
       <c r="B207" s="6" t="n"/>
       <c r="C207" s="6" t="n"/>
       <c r="D207" s="6">
-        <f>IF($C207="","",$C207-MOD(WEEKDAY($C207,3)-4,7))</f>
+        <f>IF($C207="","",$C207-MOD(WEEKDAY($C207,3)-5,7))</f>
         <v/>
       </c>
       <c r="E207" s="5" t="n"/>
@@ -5443,7 +5443,7 @@
       <c r="B208" s="6" t="n"/>
       <c r="C208" s="6" t="n"/>
       <c r="D208" s="6">
-        <f>IF($C208="","",$C208-MOD(WEEKDAY($C208,3)-4,7))</f>
+        <f>IF($C208="","",$C208-MOD(WEEKDAY($C208,3)-5,7))</f>
         <v/>
       </c>
       <c r="E208" s="5" t="n"/>
@@ -5465,7 +5465,7 @@
       <c r="B209" s="6" t="n"/>
       <c r="C209" s="6" t="n"/>
       <c r="D209" s="6">
-        <f>IF($C209="","",$C209-MOD(WEEKDAY($C209,3)-4,7))</f>
+        <f>IF($C209="","",$C209-MOD(WEEKDAY($C209,3)-5,7))</f>
         <v/>
       </c>
       <c r="E209" s="5" t="n"/>
@@ -5487,7 +5487,7 @@
       <c r="B210" s="6" t="n"/>
       <c r="C210" s="6" t="n"/>
       <c r="D210" s="6">
-        <f>IF($C210="","",$C210-MOD(WEEKDAY($C210,3)-4,7))</f>
+        <f>IF($C210="","",$C210-MOD(WEEKDAY($C210,3)-5,7))</f>
         <v/>
       </c>
       <c r="E210" s="5" t="n"/>
@@ -5509,7 +5509,7 @@
       <c r="B211" s="6" t="n"/>
       <c r="C211" s="6" t="n"/>
       <c r="D211" s="6">
-        <f>IF($C211="","",$C211-MOD(WEEKDAY($C211,3)-4,7))</f>
+        <f>IF($C211="","",$C211-MOD(WEEKDAY($C211,3)-5,7))</f>
         <v/>
       </c>
       <c r="E211" s="5" t="n"/>
@@ -5531,7 +5531,7 @@
       <c r="B212" s="6" t="n"/>
       <c r="C212" s="6" t="n"/>
       <c r="D212" s="6">
-        <f>IF($C212="","",$C212-MOD(WEEKDAY($C212,3)-4,7))</f>
+        <f>IF($C212="","",$C212-MOD(WEEKDAY($C212,3)-5,7))</f>
         <v/>
       </c>
       <c r="E212" s="5" t="n"/>
@@ -5553,7 +5553,7 @@
       <c r="B213" s="6" t="n"/>
       <c r="C213" s="6" t="n"/>
       <c r="D213" s="6">
-        <f>IF($C213="","",$C213-MOD(WEEKDAY($C213,3)-4,7))</f>
+        <f>IF($C213="","",$C213-MOD(WEEKDAY($C213,3)-5,7))</f>
         <v/>
       </c>
       <c r="E213" s="5" t="n"/>
@@ -5575,7 +5575,7 @@
       <c r="B214" s="6" t="n"/>
       <c r="C214" s="6" t="n"/>
       <c r="D214" s="6">
-        <f>IF($C214="","",$C214-MOD(WEEKDAY($C214,3)-4,7))</f>
+        <f>IF($C214="","",$C214-MOD(WEEKDAY($C214,3)-5,7))</f>
         <v/>
       </c>
       <c r="E214" s="5" t="n"/>
@@ -5597,7 +5597,7 @@
       <c r="B215" s="6" t="n"/>
       <c r="C215" s="6" t="n"/>
       <c r="D215" s="6">
-        <f>IF($C215="","",$C215-MOD(WEEKDAY($C215,3)-4,7))</f>
+        <f>IF($C215="","",$C215-MOD(WEEKDAY($C215,3)-5,7))</f>
         <v/>
       </c>
       <c r="E215" s="5" t="n"/>
@@ -5619,7 +5619,7 @@
       <c r="B216" s="6" t="n"/>
       <c r="C216" s="6" t="n"/>
       <c r="D216" s="6">
-        <f>IF($C216="","",$C216-MOD(WEEKDAY($C216,3)-4,7))</f>
+        <f>IF($C216="","",$C216-MOD(WEEKDAY($C216,3)-5,7))</f>
         <v/>
       </c>
       <c r="E216" s="5" t="n"/>
@@ -5641,7 +5641,7 @@
       <c r="B217" s="6" t="n"/>
       <c r="C217" s="6" t="n"/>
       <c r="D217" s="6">
-        <f>IF($C217="","",$C217-MOD(WEEKDAY($C217,3)-4,7))</f>
+        <f>IF($C217="","",$C217-MOD(WEEKDAY($C217,3)-5,7))</f>
         <v/>
       </c>
       <c r="E217" s="5" t="n"/>
@@ -5663,7 +5663,7 @@
       <c r="B218" s="6" t="n"/>
       <c r="C218" s="6" t="n"/>
       <c r="D218" s="6">
-        <f>IF($C218="","",$C218-MOD(WEEKDAY($C218,3)-4,7))</f>
+        <f>IF($C218="","",$C218-MOD(WEEKDAY($C218,3)-5,7))</f>
         <v/>
       </c>
       <c r="E218" s="5" t="n"/>
@@ -5685,7 +5685,7 @@
       <c r="B219" s="6" t="n"/>
       <c r="C219" s="6" t="n"/>
       <c r="D219" s="6">
-        <f>IF($C219="","",$C219-MOD(WEEKDAY($C219,3)-4,7))</f>
+        <f>IF($C219="","",$C219-MOD(WEEKDAY($C219,3)-5,7))</f>
         <v/>
       </c>
       <c r="E219" s="5" t="n"/>
@@ -5707,7 +5707,7 @@
       <c r="B220" s="6" t="n"/>
       <c r="C220" s="6" t="n"/>
       <c r="D220" s="6">
-        <f>IF($C220="","",$C220-MOD(WEEKDAY($C220,3)-4,7))</f>
+        <f>IF($C220="","",$C220-MOD(WEEKDAY($C220,3)-5,7))</f>
         <v/>
       </c>
       <c r="E220" s="5" t="n"/>
@@ -5729,7 +5729,7 @@
       <c r="B221" s="6" t="n"/>
       <c r="C221" s="6" t="n"/>
       <c r="D221" s="6">
-        <f>IF($C221="","",$C221-MOD(WEEKDAY($C221,3)-4,7))</f>
+        <f>IF($C221="","",$C221-MOD(WEEKDAY($C221,3)-5,7))</f>
         <v/>
       </c>
       <c r="E221" s="5" t="n"/>
@@ -5751,7 +5751,7 @@
       <c r="B222" s="6" t="n"/>
       <c r="C222" s="6" t="n"/>
       <c r="D222" s="6">
-        <f>IF($C222="","",$C222-MOD(WEEKDAY($C222,3)-4,7))</f>
+        <f>IF($C222="","",$C222-MOD(WEEKDAY($C222,3)-5,7))</f>
         <v/>
       </c>
       <c r="E222" s="5" t="n"/>
@@ -5773,7 +5773,7 @@
       <c r="B223" s="6" t="n"/>
       <c r="C223" s="6" t="n"/>
       <c r="D223" s="6">
-        <f>IF($C223="","",$C223-MOD(WEEKDAY($C223,3)-4,7))</f>
+        <f>IF($C223="","",$C223-MOD(WEEKDAY($C223,3)-5,7))</f>
         <v/>
       </c>
       <c r="E223" s="5" t="n"/>
@@ -5795,7 +5795,7 @@
       <c r="B224" s="6" t="n"/>
       <c r="C224" s="6" t="n"/>
       <c r="D224" s="6">
-        <f>IF($C224="","",$C224-MOD(WEEKDAY($C224,3)-4,7))</f>
+        <f>IF($C224="","",$C224-MOD(WEEKDAY($C224,3)-5,7))</f>
         <v/>
       </c>
       <c r="E224" s="5" t="n"/>
@@ -5817,7 +5817,7 @@
       <c r="B225" s="6" t="n"/>
       <c r="C225" s="6" t="n"/>
       <c r="D225" s="6">
-        <f>IF($C225="","",$C225-MOD(WEEKDAY($C225,3)-4,7))</f>
+        <f>IF($C225="","",$C225-MOD(WEEKDAY($C225,3)-5,7))</f>
         <v/>
       </c>
       <c r="E225" s="5" t="n"/>
@@ -5839,7 +5839,7 @@
       <c r="B226" s="6" t="n"/>
       <c r="C226" s="6" t="n"/>
       <c r="D226" s="6">
-        <f>IF($C226="","",$C226-MOD(WEEKDAY($C226,3)-4,7))</f>
+        <f>IF($C226="","",$C226-MOD(WEEKDAY($C226,3)-5,7))</f>
         <v/>
       </c>
       <c r="E226" s="5" t="n"/>
@@ -5861,7 +5861,7 @@
       <c r="B227" s="6" t="n"/>
       <c r="C227" s="6" t="n"/>
       <c r="D227" s="6">
-        <f>IF($C227="","",$C227-MOD(WEEKDAY($C227,3)-4,7))</f>
+        <f>IF($C227="","",$C227-MOD(WEEKDAY($C227,3)-5,7))</f>
         <v/>
       </c>
       <c r="E227" s="5" t="n"/>
@@ -5883,7 +5883,7 @@
       <c r="B228" s="6" t="n"/>
       <c r="C228" s="6" t="n"/>
       <c r="D228" s="6">
-        <f>IF($C228="","",$C228-MOD(WEEKDAY($C228,3)-4,7))</f>
+        <f>IF($C228="","",$C228-MOD(WEEKDAY($C228,3)-5,7))</f>
         <v/>
       </c>
       <c r="E228" s="5" t="n"/>
@@ -5905,7 +5905,7 @@
       <c r="B229" s="6" t="n"/>
       <c r="C229" s="6" t="n"/>
       <c r="D229" s="6">
-        <f>IF($C229="","",$C229-MOD(WEEKDAY($C229,3)-4,7))</f>
+        <f>IF($C229="","",$C229-MOD(WEEKDAY($C229,3)-5,7))</f>
         <v/>
       </c>
       <c r="E229" s="5" t="n"/>
@@ -5927,7 +5927,7 @@
       <c r="B230" s="6" t="n"/>
       <c r="C230" s="6" t="n"/>
       <c r="D230" s="6">
-        <f>IF($C230="","",$C230-MOD(WEEKDAY($C230,3)-4,7))</f>
+        <f>IF($C230="","",$C230-MOD(WEEKDAY($C230,3)-5,7))</f>
         <v/>
       </c>
       <c r="E230" s="5" t="n"/>
@@ -5949,7 +5949,7 @@
       <c r="B231" s="6" t="n"/>
       <c r="C231" s="6" t="n"/>
       <c r="D231" s="6">
-        <f>IF($C231="","",$C231-MOD(WEEKDAY($C231,3)-4,7))</f>
+        <f>IF($C231="","",$C231-MOD(WEEKDAY($C231,3)-5,7))</f>
         <v/>
       </c>
       <c r="E231" s="5" t="n"/>
@@ -5971,7 +5971,7 @@
       <c r="B232" s="6" t="n"/>
       <c r="C232" s="6" t="n"/>
       <c r="D232" s="6">
-        <f>IF($C232="","",$C232-MOD(WEEKDAY($C232,3)-4,7))</f>
+        <f>IF($C232="","",$C232-MOD(WEEKDAY($C232,3)-5,7))</f>
         <v/>
       </c>
       <c r="E232" s="5" t="n"/>
@@ -5993,7 +5993,7 @@
       <c r="B233" s="6" t="n"/>
       <c r="C233" s="6" t="n"/>
       <c r="D233" s="6">
-        <f>IF($C233="","",$C233-MOD(WEEKDAY($C233,3)-4,7))</f>
+        <f>IF($C233="","",$C233-MOD(WEEKDAY($C233,3)-5,7))</f>
         <v/>
       </c>
       <c r="E233" s="5" t="n"/>
@@ -6015,7 +6015,7 @@
       <c r="B234" s="6" t="n"/>
       <c r="C234" s="6" t="n"/>
       <c r="D234" s="6">
-        <f>IF($C234="","",$C234-MOD(WEEKDAY($C234,3)-4,7))</f>
+        <f>IF($C234="","",$C234-MOD(WEEKDAY($C234,3)-5,7))</f>
         <v/>
       </c>
       <c r="E234" s="5" t="n"/>
@@ -6037,7 +6037,7 @@
       <c r="B235" s="6" t="n"/>
       <c r="C235" s="6" t="n"/>
       <c r="D235" s="6">
-        <f>IF($C235="","",$C235-MOD(WEEKDAY($C235,3)-4,7))</f>
+        <f>IF($C235="","",$C235-MOD(WEEKDAY($C235,3)-5,7))</f>
         <v/>
       </c>
       <c r="E235" s="5" t="n"/>
@@ -6059,7 +6059,7 @@
       <c r="B236" s="6" t="n"/>
       <c r="C236" s="6" t="n"/>
       <c r="D236" s="6">
-        <f>IF($C236="","",$C236-MOD(WEEKDAY($C236,3)-4,7))</f>
+        <f>IF($C236="","",$C236-MOD(WEEKDAY($C236,3)-5,7))</f>
         <v/>
       </c>
       <c r="E236" s="5" t="n"/>
@@ -6081,7 +6081,7 @@
       <c r="B237" s="6" t="n"/>
       <c r="C237" s="6" t="n"/>
       <c r="D237" s="6">
-        <f>IF($C237="","",$C237-MOD(WEEKDAY($C237,3)-4,7))</f>
+        <f>IF($C237="","",$C237-MOD(WEEKDAY($C237,3)-5,7))</f>
         <v/>
       </c>
       <c r="E237" s="5" t="n"/>
@@ -6103,7 +6103,7 @@
       <c r="B238" s="6" t="n"/>
       <c r="C238" s="6" t="n"/>
       <c r="D238" s="6">
-        <f>IF($C238="","",$C238-MOD(WEEKDAY($C238,3)-4,7))</f>
+        <f>IF($C238="","",$C238-MOD(WEEKDAY($C238,3)-5,7))</f>
         <v/>
       </c>
       <c r="E238" s="5" t="n"/>
@@ -6125,7 +6125,7 @@
       <c r="B239" s="6" t="n"/>
       <c r="C239" s="6" t="n"/>
       <c r="D239" s="6">
-        <f>IF($C239="","",$C239-MOD(WEEKDAY($C239,3)-4,7))</f>
+        <f>IF($C239="","",$C239-MOD(WEEKDAY($C239,3)-5,7))</f>
         <v/>
       </c>
       <c r="E239" s="5" t="n"/>
@@ -6147,7 +6147,7 @@
       <c r="B240" s="6" t="n"/>
       <c r="C240" s="6" t="n"/>
       <c r="D240" s="6">
-        <f>IF($C240="","",$C240-MOD(WEEKDAY($C240,3)-4,7))</f>
+        <f>IF($C240="","",$C240-MOD(WEEKDAY($C240,3)-5,7))</f>
         <v/>
       </c>
       <c r="E240" s="5" t="n"/>
@@ -6169,7 +6169,7 @@
       <c r="B241" s="6" t="n"/>
       <c r="C241" s="6" t="n"/>
       <c r="D241" s="6">
-        <f>IF($C241="","",$C241-MOD(WEEKDAY($C241,3)-4,7))</f>
+        <f>IF($C241="","",$C241-MOD(WEEKDAY($C241,3)-5,7))</f>
         <v/>
       </c>
       <c r="E241" s="5" t="n"/>
@@ -6191,7 +6191,7 @@
       <c r="B242" s="6" t="n"/>
       <c r="C242" s="6" t="n"/>
       <c r="D242" s="6">
-        <f>IF($C242="","",$C242-MOD(WEEKDAY($C242,3)-4,7))</f>
+        <f>IF($C242="","",$C242-MOD(WEEKDAY($C242,3)-5,7))</f>
         <v/>
       </c>
       <c r="E242" s="5" t="n"/>
@@ -6213,7 +6213,7 @@
       <c r="B243" s="6" t="n"/>
       <c r="C243" s="6" t="n"/>
       <c r="D243" s="6">
-        <f>IF($C243="","",$C243-MOD(WEEKDAY($C243,3)-4,7))</f>
+        <f>IF($C243="","",$C243-MOD(WEEKDAY($C243,3)-5,7))</f>
         <v/>
       </c>
       <c r="E243" s="5" t="n"/>
@@ -6235,7 +6235,7 @@
       <c r="B244" s="6" t="n"/>
       <c r="C244" s="6" t="n"/>
       <c r="D244" s="6">
-        <f>IF($C244="","",$C244-MOD(WEEKDAY($C244,3)-4,7))</f>
+        <f>IF($C244="","",$C244-MOD(WEEKDAY($C244,3)-5,7))</f>
         <v/>
       </c>
       <c r="E244" s="5" t="n"/>
@@ -6257,7 +6257,7 @@
       <c r="B245" s="6" t="n"/>
       <c r="C245" s="6" t="n"/>
       <c r="D245" s="6">
-        <f>IF($C245="","",$C245-MOD(WEEKDAY($C245,3)-4,7))</f>
+        <f>IF($C245="","",$C245-MOD(WEEKDAY($C245,3)-5,7))</f>
         <v/>
       </c>
       <c r="E245" s="5" t="n"/>
@@ -6279,7 +6279,7 @@
       <c r="B246" s="6" t="n"/>
       <c r="C246" s="6" t="n"/>
       <c r="D246" s="6">
-        <f>IF($C246="","",$C246-MOD(WEEKDAY($C246,3)-4,7))</f>
+        <f>IF($C246="","",$C246-MOD(WEEKDAY($C246,3)-5,7))</f>
         <v/>
       </c>
       <c r="E246" s="5" t="n"/>
@@ -6301,7 +6301,7 @@
       <c r="B247" s="6" t="n"/>
       <c r="C247" s="6" t="n"/>
       <c r="D247" s="6">
-        <f>IF($C247="","",$C247-MOD(WEEKDAY($C247,3)-4,7))</f>
+        <f>IF($C247="","",$C247-MOD(WEEKDAY($C247,3)-5,7))</f>
         <v/>
       </c>
       <c r="E247" s="5" t="n"/>
@@ -6323,7 +6323,7 @@
       <c r="B248" s="6" t="n"/>
       <c r="C248" s="6" t="n"/>
       <c r="D248" s="6">
-        <f>IF($C248="","",$C248-MOD(WEEKDAY($C248,3)-4,7))</f>
+        <f>IF($C248="","",$C248-MOD(WEEKDAY($C248,3)-5,7))</f>
         <v/>
       </c>
       <c r="E248" s="5" t="n"/>
@@ -6345,7 +6345,7 @@
       <c r="B249" s="6" t="n"/>
       <c r="C249" s="6" t="n"/>
       <c r="D249" s="6">
-        <f>IF($C249="","",$C249-MOD(WEEKDAY($C249,3)-4,7))</f>
+        <f>IF($C249="","",$C249-MOD(WEEKDAY($C249,3)-5,7))</f>
         <v/>
       </c>
       <c r="E249" s="5" t="n"/>
@@ -6367,7 +6367,7 @@
       <c r="B250" s="6" t="n"/>
       <c r="C250" s="6" t="n"/>
       <c r="D250" s="6">
-        <f>IF($C250="","",$C250-MOD(WEEKDAY($C250,3)-4,7))</f>
+        <f>IF($C250="","",$C250-MOD(WEEKDAY($C250,3)-5,7))</f>
         <v/>
       </c>
       <c r="E250" s="5" t="n"/>

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -776,8 +776,8 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A14:B14"/>
@@ -10989,44 +10989,120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="5" t="n"/>
+      <c r="A2" s="6" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>RK Group</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>ambitionbox: SCOPE: Bengaluru-filtered, not all locations. GENDER SPLIT: women 1.7 (7 reviews) vs men 3.5 (19) - a 1.8 point gap. Skill Development 2.3. | glassdoor: SCOPE: Bangalore-filtered view only, not all locations - 16 reviews is the Bangalore subset. 69% positive business outlook. Glassdoor classifies RK Group as Manufacturing; industry average 3.5. All-locations figure still needed.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="n"/>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="5" t="n"/>
+      <c r="A3" s="6" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>RK World Infocom</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>ambitionbox: All locations. AmbitionBox flags 23% below industry average. Women 3.0 (16) vs men 3.2 (29). Skill Development 3.4; Work Satisfaction 3.1. | glassdoor: 20 written reviews. Diversity and inclusion 3.9; Senior management 3.7. Company size 201-500 employees, private. Employer Profile NOT claimed.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="5" t="n"/>
+      <c r="A4" s="6" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Robust Kommerce</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="5" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="5" t="n"/>
+      <c r="E4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>glassdoor: Listed on Glassdoor as plain 'Robust' (employer id 1882698) - identity still to be confirmed as Robust Kommerce. Diversity and inclusion 4.2; Senior management 3.1. Company size 51-200 employees. Employer Profile NOT claimed.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="5" t="n"/>
+      <c r="A5" s="6" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Westbury Kommerce</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>ambitionbox: All locations. Highly rated for job security; critically rated for promotions, work satisfaction, skill development. 142 salary entries, 14 followers. | glassdoor: Diversity and inclusion 2.0; Senior management 1.0; 'Be the first to recommend' = 0% recommend</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -5,14 +5,14 @@
   <sheets>
     <sheet name="Guide" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Raw_Data_Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Rating_Tracker" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Escalations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Escalations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Rating_Tracker" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Keyword_Matrix" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data_Log'!$A$1:$Q$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rating_Tracker'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Escalations'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data_Log'!$A$1:$V$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Escalations'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rating_Tracker'!$A$1:$Z$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -83,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -110,6 +111,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -797,7 +800,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1000"/>
+  <dimension ref="A1:V1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="3" min="1" max="1"/>
@@ -806,17 +809,22 @@
     <col width="12" customWidth="1" style="3" min="4" max="4"/>
     <col width="18" customWidth="1" style="3" min="5" max="5"/>
     <col width="15" customWidth="1" style="3" min="6" max="6"/>
-    <col width="12" customWidth="1" style="3" min="7" max="7"/>
-    <col width="16" customWidth="1" style="3" min="8" max="8"/>
-    <col width="46" customWidth="1" style="3" min="9" max="9"/>
-    <col width="34" customWidth="1" style="3" min="10" max="10"/>
-    <col width="16" customWidth="1" style="3" min="11" max="11"/>
-    <col width="12" customWidth="1" style="3" min="12" max="12"/>
-    <col width="15" customWidth="1" style="3" min="13" max="13"/>
-    <col width="16" customWidth="1" style="3" min="14" max="14"/>
-    <col width="20" customWidth="1" style="3" min="15" max="15"/>
-    <col width="14" customWidth="1" style="3" min="16" max="16"/>
-    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="20" customWidth="1" style="3" min="7" max="7"/>
+    <col width="12" customWidth="1" style="3" min="8" max="8"/>
+    <col width="16" customWidth="1" style="3" min="9" max="9"/>
+    <col width="30" customWidth="1" style="3" min="10" max="10"/>
+    <col width="46" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="16" customWidth="1" style="3" min="13" max="13"/>
+    <col width="18" customWidth="1" style="3" min="14" max="14"/>
+    <col width="8" customWidth="1" style="3" min="15" max="15"/>
+    <col width="12" customWidth="1" style="3" min="16" max="16"/>
+    <col width="15" customWidth="1" style="3" min="17" max="17"/>
+    <col width="16" customWidth="1" style="3" min="18" max="18"/>
+    <col width="20" customWidth="1" style="3" min="19" max="19"/>
+    <col width="14" customWidth="1" style="3" min="20" max="20"/>
+    <col width="12" customWidth="1" style="3" min="21" max="21"/>
+    <col width="28" customWidth="1" style="3" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="3">
@@ -852,55 +860,80 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Topic Category</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Title / Snippet</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Summary Overview</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Direct Link / URL</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Author Type</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Role / Department</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Stars</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Names Individual</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Red Flag Escalated</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Red Flag Reason</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Logged By</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -924,9 +957,14 @@
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="5" t="n"/>
       <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
+      <c r="O2" s="14" t="n"/>
       <c r="P2" s="5" t="n"/>
       <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="5" t="n"/>
+      <c r="S2" s="5" t="n"/>
+      <c r="T2" s="5" t="n"/>
+      <c r="U2" s="5" t="n"/>
+      <c r="V2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -946,9 +984,14 @@
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="5" t="n"/>
       <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
+      <c r="O3" s="14" t="n"/>
       <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" s="5" t="n"/>
+      <c r="T3" s="5" t="n"/>
+      <c r="U3" s="5" t="n"/>
+      <c r="V3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -968,9 +1011,14 @@
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
       <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
+      <c r="O4" s="14" t="n"/>
       <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
@@ -990,9 +1038,14 @@
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
+      <c r="O5" s="14" t="n"/>
       <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -1012,9 +1065,14 @@
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
+      <c r="O6" s="14" t="n"/>
       <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -1034,9 +1092,14 @@
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="5" t="n"/>
       <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
+      <c r="O7" s="14" t="n"/>
       <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -1056,9 +1119,14 @@
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
+      <c r="O8" s="14" t="n"/>
       <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -1078,9 +1146,14 @@
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
+      <c r="O9" s="14" t="n"/>
       <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -1100,9 +1173,14 @@
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
+      <c r="O10" s="14" t="n"/>
       <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1122,9 +1200,14 @@
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
+      <c r="O11" s="14" t="n"/>
       <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1144,9 +1227,14 @@
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
+      <c r="O12" s="14" t="n"/>
       <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -1166,9 +1254,14 @@
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
+      <c r="O13" s="14" t="n"/>
       <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1188,9 +1281,14 @@
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n"/>
       <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
+      <c r="O14" s="14" t="n"/>
       <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1210,9 +1308,14 @@
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
+      <c r="O15" s="14" t="n"/>
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1232,9 +1335,14 @@
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
+      <c r="O16" s="14" t="n"/>
       <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1254,9 +1362,14 @@
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
+      <c r="O17" s="14" t="n"/>
       <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1276,9 +1389,14 @@
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="5" t="n"/>
       <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
+      <c r="O18" s="14" t="n"/>
       <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -1298,9 +1416,14 @@
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
+      <c r="O19" s="14" t="n"/>
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1320,9 +1443,14 @@
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n"/>
       <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
+      <c r="O20" s="14" t="n"/>
       <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1342,9 +1470,14 @@
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="5" t="n"/>
       <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
+      <c r="O21" s="14" t="n"/>
       <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -1364,9 +1497,14 @@
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="5" t="n"/>
       <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
+      <c r="O22" s="14" t="n"/>
       <c r="P22" s="5" t="n"/>
       <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1386,9 +1524,14 @@
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
+      <c r="O23" s="14" t="n"/>
       <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="5" t="n"/>
+      <c r="V23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1408,9 +1551,14 @@
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="5" t="n"/>
       <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
+      <c r="O24" s="14" t="n"/>
       <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -1430,9 +1578,14 @@
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="5" t="n"/>
       <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
+      <c r="O25" s="14" t="n"/>
       <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -1452,9 +1605,14 @@
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="5" t="n"/>
       <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
+      <c r="O26" s="14" t="n"/>
       <c r="P26" s="5" t="n"/>
       <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1474,9 +1632,14 @@
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="5" t="n"/>
       <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
+      <c r="O27" s="14" t="n"/>
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="5" t="n"/>
+      <c r="V27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -1496,9 +1659,14 @@
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="5" t="n"/>
       <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
+      <c r="O28" s="14" t="n"/>
       <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="5" t="n"/>
+      <c r="U28" s="5" t="n"/>
+      <c r="V28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1518,9 +1686,14 @@
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="5" t="n"/>
       <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
+      <c r="O29" s="14" t="n"/>
       <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" s="5" t="n"/>
+      <c r="T29" s="5" t="n"/>
+      <c r="U29" s="5" t="n"/>
+      <c r="V29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1540,9 +1713,14 @@
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="5" t="n"/>
       <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
+      <c r="O30" s="14" t="n"/>
       <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" s="5" t="n"/>
+      <c r="T30" s="5" t="n"/>
+      <c r="U30" s="5" t="n"/>
+      <c r="V30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -1562,9 +1740,14 @@
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="5" t="n"/>
       <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
+      <c r="O31" s="14" t="n"/>
       <c r="P31" s="5" t="n"/>
       <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" s="5" t="n"/>
+      <c r="T31" s="5" t="n"/>
+      <c r="U31" s="5" t="n"/>
+      <c r="V31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -1584,9 +1767,14 @@
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="5" t="n"/>
       <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
+      <c r="O32" s="14" t="n"/>
       <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="5" t="n"/>
+      <c r="T32" s="5" t="n"/>
+      <c r="U32" s="5" t="n"/>
+      <c r="V32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -1606,9 +1794,14 @@
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="5" t="n"/>
       <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
+      <c r="O33" s="14" t="n"/>
       <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="5" t="n"/>
+      <c r="T33" s="5" t="n"/>
+      <c r="U33" s="5" t="n"/>
+      <c r="V33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -1628,9 +1821,14 @@
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="5" t="n"/>
       <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
+      <c r="O34" s="14" t="n"/>
       <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="5" t="n"/>
+      <c r="T34" s="5" t="n"/>
+      <c r="U34" s="5" t="n"/>
+      <c r="V34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -1650,9 +1848,14 @@
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="5" t="n"/>
       <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
+      <c r="O35" s="14" t="n"/>
       <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" s="5" t="n"/>
+      <c r="T35" s="5" t="n"/>
+      <c r="U35" s="5" t="n"/>
+      <c r="V35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -1672,9 +1875,14 @@
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
+      <c r="O36" s="14" t="n"/>
       <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="n"/>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" s="5" t="n"/>
+      <c r="T36" s="5" t="n"/>
+      <c r="U36" s="5" t="n"/>
+      <c r="V36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -1694,9 +1902,14 @@
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
-      <c r="O37" s="5" t="n"/>
+      <c r="O37" s="14" t="n"/>
       <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="5" t="n"/>
+      <c r="S37" s="5" t="n"/>
+      <c r="T37" s="5" t="n"/>
+      <c r="U37" s="5" t="n"/>
+      <c r="V37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -1716,9 +1929,14 @@
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="5" t="n"/>
       <c r="N38" s="5" t="n"/>
-      <c r="O38" s="5" t="n"/>
+      <c r="O38" s="14" t="n"/>
       <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="n"/>
+      <c r="S38" s="5" t="n"/>
+      <c r="T38" s="5" t="n"/>
+      <c r="U38" s="5" t="n"/>
+      <c r="V38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -1738,9 +1956,14 @@
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="5" t="n"/>
       <c r="N39" s="5" t="n"/>
-      <c r="O39" s="5" t="n"/>
+      <c r="O39" s="14" t="n"/>
       <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="n"/>
+      <c r="R39" s="5" t="n"/>
+      <c r="S39" s="5" t="n"/>
+      <c r="T39" s="5" t="n"/>
+      <c r="U39" s="5" t="n"/>
+      <c r="V39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -1760,9 +1983,14 @@
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="5" t="n"/>
       <c r="N40" s="5" t="n"/>
-      <c r="O40" s="5" t="n"/>
+      <c r="O40" s="14" t="n"/>
       <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="n"/>
+      <c r="R40" s="5" t="n"/>
+      <c r="S40" s="5" t="n"/>
+      <c r="T40" s="5" t="n"/>
+      <c r="U40" s="5" t="n"/>
+      <c r="V40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -1782,9 +2010,14 @@
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="5" t="n"/>
       <c r="N41" s="5" t="n"/>
-      <c r="O41" s="5" t="n"/>
+      <c r="O41" s="14" t="n"/>
       <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="n"/>
+      <c r="R41" s="5" t="n"/>
+      <c r="S41" s="5" t="n"/>
+      <c r="T41" s="5" t="n"/>
+      <c r="U41" s="5" t="n"/>
+      <c r="V41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -1804,9 +2037,14 @@
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="5" t="n"/>
       <c r="N42" s="5" t="n"/>
-      <c r="O42" s="5" t="n"/>
+      <c r="O42" s="14" t="n"/>
       <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="n"/>
+      <c r="R42" s="5" t="n"/>
+      <c r="S42" s="5" t="n"/>
+      <c r="T42" s="5" t="n"/>
+      <c r="U42" s="5" t="n"/>
+      <c r="V42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -1826,9 +2064,14 @@
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="5" t="n"/>
       <c r="N43" s="5" t="n"/>
-      <c r="O43" s="5" t="n"/>
+      <c r="O43" s="14" t="n"/>
       <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="5" t="n"/>
+      <c r="S43" s="5" t="n"/>
+      <c r="T43" s="5" t="n"/>
+      <c r="U43" s="5" t="n"/>
+      <c r="V43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -1848,9 +2091,14 @@
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="5" t="n"/>
       <c r="N44" s="5" t="n"/>
-      <c r="O44" s="5" t="n"/>
+      <c r="O44" s="14" t="n"/>
       <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="n"/>
+      <c r="R44" s="5" t="n"/>
+      <c r="S44" s="5" t="n"/>
+      <c r="T44" s="5" t="n"/>
+      <c r="U44" s="5" t="n"/>
+      <c r="V44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -1870,9 +2118,14 @@
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="5" t="n"/>
       <c r="N45" s="5" t="n"/>
-      <c r="O45" s="5" t="n"/>
+      <c r="O45" s="14" t="n"/>
       <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="n"/>
+      <c r="R45" s="5" t="n"/>
+      <c r="S45" s="5" t="n"/>
+      <c r="T45" s="5" t="n"/>
+      <c r="U45" s="5" t="n"/>
+      <c r="V45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -1892,9 +2145,14 @@
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="5" t="n"/>
       <c r="N46" s="5" t="n"/>
-      <c r="O46" s="5" t="n"/>
+      <c r="O46" s="14" t="n"/>
       <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="n"/>
+      <c r="R46" s="5" t="n"/>
+      <c r="S46" s="5" t="n"/>
+      <c r="T46" s="5" t="n"/>
+      <c r="U46" s="5" t="n"/>
+      <c r="V46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -1914,9 +2172,14 @@
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="5" t="n"/>
       <c r="N47" s="5" t="n"/>
-      <c r="O47" s="5" t="n"/>
+      <c r="O47" s="14" t="n"/>
       <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="n"/>
+      <c r="R47" s="5" t="n"/>
+      <c r="S47" s="5" t="n"/>
+      <c r="T47" s="5" t="n"/>
+      <c r="U47" s="5" t="n"/>
+      <c r="V47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -1936,9 +2199,14 @@
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="5" t="n"/>
       <c r="N48" s="5" t="n"/>
-      <c r="O48" s="5" t="n"/>
+      <c r="O48" s="14" t="n"/>
       <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="5" t="n"/>
+      <c r="S48" s="5" t="n"/>
+      <c r="T48" s="5" t="n"/>
+      <c r="U48" s="5" t="n"/>
+      <c r="V48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -1958,9 +2226,14 @@
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="5" t="n"/>
       <c r="N49" s="5" t="n"/>
-      <c r="O49" s="5" t="n"/>
+      <c r="O49" s="14" t="n"/>
       <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="5" t="n"/>
+      <c r="S49" s="5" t="n"/>
+      <c r="T49" s="5" t="n"/>
+      <c r="U49" s="5" t="n"/>
+      <c r="V49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -1980,9 +2253,14 @@
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="5" t="n"/>
       <c r="N50" s="5" t="n"/>
-      <c r="O50" s="5" t="n"/>
+      <c r="O50" s="14" t="n"/>
       <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="n"/>
+      <c r="R50" s="5" t="n"/>
+      <c r="S50" s="5" t="n"/>
+      <c r="T50" s="5" t="n"/>
+      <c r="U50" s="5" t="n"/>
+      <c r="V50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -2002,9 +2280,14 @@
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="5" t="n"/>
       <c r="N51" s="5" t="n"/>
-      <c r="O51" s="5" t="n"/>
+      <c r="O51" s="14" t="n"/>
       <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="n"/>
+      <c r="R51" s="5" t="n"/>
+      <c r="S51" s="5" t="n"/>
+      <c r="T51" s="5" t="n"/>
+      <c r="U51" s="5" t="n"/>
+      <c r="V51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -2024,9 +2307,14 @@
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="5" t="n"/>
       <c r="N52" s="5" t="n"/>
-      <c r="O52" s="5" t="n"/>
+      <c r="O52" s="14" t="n"/>
       <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="n"/>
+      <c r="R52" s="5" t="n"/>
+      <c r="S52" s="5" t="n"/>
+      <c r="T52" s="5" t="n"/>
+      <c r="U52" s="5" t="n"/>
+      <c r="V52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -2046,9 +2334,14 @@
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="5" t="n"/>
       <c r="N53" s="5" t="n"/>
-      <c r="O53" s="5" t="n"/>
+      <c r="O53" s="14" t="n"/>
       <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="n"/>
+      <c r="R53" s="5" t="n"/>
+      <c r="S53" s="5" t="n"/>
+      <c r="T53" s="5" t="n"/>
+      <c r="U53" s="5" t="n"/>
+      <c r="V53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -2068,9 +2361,14 @@
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="5" t="n"/>
       <c r="N54" s="5" t="n"/>
-      <c r="O54" s="5" t="n"/>
+      <c r="O54" s="14" t="n"/>
       <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="n"/>
+      <c r="R54" s="5" t="n"/>
+      <c r="S54" s="5" t="n"/>
+      <c r="T54" s="5" t="n"/>
+      <c r="U54" s="5" t="n"/>
+      <c r="V54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -2090,9 +2388,14 @@
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="5" t="n"/>
       <c r="N55" s="5" t="n"/>
-      <c r="O55" s="5" t="n"/>
+      <c r="O55" s="14" t="n"/>
       <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="n"/>
+      <c r="R55" s="5" t="n"/>
+      <c r="S55" s="5" t="n"/>
+      <c r="T55" s="5" t="n"/>
+      <c r="U55" s="5" t="n"/>
+      <c r="V55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -2112,9 +2415,14 @@
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="5" t="n"/>
       <c r="N56" s="5" t="n"/>
-      <c r="O56" s="5" t="n"/>
+      <c r="O56" s="14" t="n"/>
       <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="n"/>
+      <c r="R56" s="5" t="n"/>
+      <c r="S56" s="5" t="n"/>
+      <c r="T56" s="5" t="n"/>
+      <c r="U56" s="5" t="n"/>
+      <c r="V56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -2134,9 +2442,14 @@
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="n"/>
-      <c r="O57" s="5" t="n"/>
+      <c r="O57" s="14" t="n"/>
       <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="5" t="n"/>
+      <c r="V57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -2156,9 +2469,14 @@
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="5" t="n"/>
       <c r="N58" s="5" t="n"/>
-      <c r="O58" s="5" t="n"/>
+      <c r="O58" s="14" t="n"/>
       <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="5" t="n"/>
+      <c r="U58" s="5" t="n"/>
+      <c r="V58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -2178,9 +2496,14 @@
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="5" t="n"/>
       <c r="N59" s="5" t="n"/>
-      <c r="O59" s="5" t="n"/>
+      <c r="O59" s="14" t="n"/>
       <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="n"/>
+      <c r="R59" s="5" t="n"/>
+      <c r="S59" s="5" t="n"/>
+      <c r="T59" s="5" t="n"/>
+      <c r="U59" s="5" t="n"/>
+      <c r="V59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -2200,9 +2523,14 @@
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="5" t="n"/>
       <c r="N60" s="5" t="n"/>
-      <c r="O60" s="5" t="n"/>
+      <c r="O60" s="14" t="n"/>
       <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="n"/>
+      <c r="R60" s="5" t="n"/>
+      <c r="S60" s="5" t="n"/>
+      <c r="T60" s="5" t="n"/>
+      <c r="U60" s="5" t="n"/>
+      <c r="V60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -2222,9 +2550,14 @@
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="5" t="n"/>
       <c r="N61" s="5" t="n"/>
-      <c r="O61" s="5" t="n"/>
+      <c r="O61" s="14" t="n"/>
       <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="n"/>
+      <c r="R61" s="5" t="n"/>
+      <c r="S61" s="5" t="n"/>
+      <c r="T61" s="5" t="n"/>
+      <c r="U61" s="5" t="n"/>
+      <c r="V61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -2244,9 +2577,14 @@
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="5" t="n"/>
       <c r="N62" s="5" t="n"/>
-      <c r="O62" s="5" t="n"/>
+      <c r="O62" s="14" t="n"/>
       <c r="P62" s="5" t="n"/>
       <c r="Q62" s="5" t="n"/>
+      <c r="R62" s="5" t="n"/>
+      <c r="S62" s="5" t="n"/>
+      <c r="T62" s="5" t="n"/>
+      <c r="U62" s="5" t="n"/>
+      <c r="V62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -2266,9 +2604,14 @@
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="5" t="n"/>
       <c r="N63" s="5" t="n"/>
-      <c r="O63" s="5" t="n"/>
+      <c r="O63" s="14" t="n"/>
       <c r="P63" s="5" t="n"/>
       <c r="Q63" s="5" t="n"/>
+      <c r="R63" s="5" t="n"/>
+      <c r="S63" s="5" t="n"/>
+      <c r="T63" s="5" t="n"/>
+      <c r="U63" s="5" t="n"/>
+      <c r="V63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -2288,9 +2631,14 @@
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="5" t="n"/>
       <c r="N64" s="5" t="n"/>
-      <c r="O64" s="5" t="n"/>
+      <c r="O64" s="14" t="n"/>
       <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="n"/>
+      <c r="R64" s="5" t="n"/>
+      <c r="S64" s="5" t="n"/>
+      <c r="T64" s="5" t="n"/>
+      <c r="U64" s="5" t="n"/>
+      <c r="V64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -2310,9 +2658,14 @@
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="5" t="n"/>
       <c r="N65" s="5" t="n"/>
-      <c r="O65" s="5" t="n"/>
+      <c r="O65" s="14" t="n"/>
       <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5" t="n"/>
+      <c r="R65" s="5" t="n"/>
+      <c r="S65" s="5" t="n"/>
+      <c r="T65" s="5" t="n"/>
+      <c r="U65" s="5" t="n"/>
+      <c r="V65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -2332,9 +2685,14 @@
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="5" t="n"/>
       <c r="N66" s="5" t="n"/>
-      <c r="O66" s="5" t="n"/>
+      <c r="O66" s="14" t="n"/>
       <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="n"/>
+      <c r="R66" s="5" t="n"/>
+      <c r="S66" s="5" t="n"/>
+      <c r="T66" s="5" t="n"/>
+      <c r="U66" s="5" t="n"/>
+      <c r="V66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -2354,9 +2712,14 @@
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="5" t="n"/>
       <c r="N67" s="5" t="n"/>
-      <c r="O67" s="5" t="n"/>
+      <c r="O67" s="14" t="n"/>
       <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="n"/>
+      <c r="R67" s="5" t="n"/>
+      <c r="S67" s="5" t="n"/>
+      <c r="T67" s="5" t="n"/>
+      <c r="U67" s="5" t="n"/>
+      <c r="V67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
@@ -2376,9 +2739,14 @@
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="5" t="n"/>
       <c r="N68" s="5" t="n"/>
-      <c r="O68" s="5" t="n"/>
+      <c r="O68" s="14" t="n"/>
       <c r="P68" s="5" t="n"/>
       <c r="Q68" s="5" t="n"/>
+      <c r="R68" s="5" t="n"/>
+      <c r="S68" s="5" t="n"/>
+      <c r="T68" s="5" t="n"/>
+      <c r="U68" s="5" t="n"/>
+      <c r="V68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -2398,9 +2766,14 @@
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="5" t="n"/>
       <c r="N69" s="5" t="n"/>
-      <c r="O69" s="5" t="n"/>
+      <c r="O69" s="14" t="n"/>
       <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5" t="n"/>
+      <c r="R69" s="5" t="n"/>
+      <c r="S69" s="5" t="n"/>
+      <c r="T69" s="5" t="n"/>
+      <c r="U69" s="5" t="n"/>
+      <c r="V69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -2420,9 +2793,14 @@
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="5" t="n"/>
       <c r="N70" s="5" t="n"/>
-      <c r="O70" s="5" t="n"/>
+      <c r="O70" s="14" t="n"/>
       <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="n"/>
+      <c r="R70" s="5" t="n"/>
+      <c r="S70" s="5" t="n"/>
+      <c r="T70" s="5" t="n"/>
+      <c r="U70" s="5" t="n"/>
+      <c r="V70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -2442,9 +2820,14 @@
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="5" t="n"/>
       <c r="N71" s="5" t="n"/>
-      <c r="O71" s="5" t="n"/>
+      <c r="O71" s="14" t="n"/>
       <c r="P71" s="5" t="n"/>
       <c r="Q71" s="5" t="n"/>
+      <c r="R71" s="5" t="n"/>
+      <c r="S71" s="5" t="n"/>
+      <c r="T71" s="5" t="n"/>
+      <c r="U71" s="5" t="n"/>
+      <c r="V71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
@@ -2464,9 +2847,14 @@
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="5" t="n"/>
       <c r="N72" s="5" t="n"/>
-      <c r="O72" s="5" t="n"/>
+      <c r="O72" s="14" t="n"/>
       <c r="P72" s="5" t="n"/>
       <c r="Q72" s="5" t="n"/>
+      <c r="R72" s="5" t="n"/>
+      <c r="S72" s="5" t="n"/>
+      <c r="T72" s="5" t="n"/>
+      <c r="U72" s="5" t="n"/>
+      <c r="V72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -2486,9 +2874,14 @@
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="5" t="n"/>
       <c r="N73" s="5" t="n"/>
-      <c r="O73" s="5" t="n"/>
+      <c r="O73" s="14" t="n"/>
       <c r="P73" s="5" t="n"/>
       <c r="Q73" s="5" t="n"/>
+      <c r="R73" s="5" t="n"/>
+      <c r="S73" s="5" t="n"/>
+      <c r="T73" s="5" t="n"/>
+      <c r="U73" s="5" t="n"/>
+      <c r="V73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -2508,9 +2901,14 @@
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="5" t="n"/>
       <c r="N74" s="5" t="n"/>
-      <c r="O74" s="5" t="n"/>
+      <c r="O74" s="14" t="n"/>
       <c r="P74" s="5" t="n"/>
       <c r="Q74" s="5" t="n"/>
+      <c r="R74" s="5" t="n"/>
+      <c r="S74" s="5" t="n"/>
+      <c r="T74" s="5" t="n"/>
+      <c r="U74" s="5" t="n"/>
+      <c r="V74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -2530,9 +2928,14 @@
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="5" t="n"/>
       <c r="N75" s="5" t="n"/>
-      <c r="O75" s="5" t="n"/>
+      <c r="O75" s="14" t="n"/>
       <c r="P75" s="5" t="n"/>
       <c r="Q75" s="5" t="n"/>
+      <c r="R75" s="5" t="n"/>
+      <c r="S75" s="5" t="n"/>
+      <c r="T75" s="5" t="n"/>
+      <c r="U75" s="5" t="n"/>
+      <c r="V75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -2552,9 +2955,14 @@
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="5" t="n"/>
       <c r="N76" s="5" t="n"/>
-      <c r="O76" s="5" t="n"/>
+      <c r="O76" s="14" t="n"/>
       <c r="P76" s="5" t="n"/>
       <c r="Q76" s="5" t="n"/>
+      <c r="R76" s="5" t="n"/>
+      <c r="S76" s="5" t="n"/>
+      <c r="T76" s="5" t="n"/>
+      <c r="U76" s="5" t="n"/>
+      <c r="V76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
@@ -2574,9 +2982,14 @@
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="5" t="n"/>
       <c r="N77" s="5" t="n"/>
-      <c r="O77" s="5" t="n"/>
+      <c r="O77" s="14" t="n"/>
       <c r="P77" s="5" t="n"/>
       <c r="Q77" s="5" t="n"/>
+      <c r="R77" s="5" t="n"/>
+      <c r="S77" s="5" t="n"/>
+      <c r="T77" s="5" t="n"/>
+      <c r="U77" s="5" t="n"/>
+      <c r="V77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -2596,9 +3009,14 @@
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="5" t="n"/>
       <c r="N78" s="5" t="n"/>
-      <c r="O78" s="5" t="n"/>
+      <c r="O78" s="14" t="n"/>
       <c r="P78" s="5" t="n"/>
       <c r="Q78" s="5" t="n"/>
+      <c r="R78" s="5" t="n"/>
+      <c r="S78" s="5" t="n"/>
+      <c r="T78" s="5" t="n"/>
+      <c r="U78" s="5" t="n"/>
+      <c r="V78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -2618,9 +3036,14 @@
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="5" t="n"/>
       <c r="N79" s="5" t="n"/>
-      <c r="O79" s="5" t="n"/>
+      <c r="O79" s="14" t="n"/>
       <c r="P79" s="5" t="n"/>
       <c r="Q79" s="5" t="n"/>
+      <c r="R79" s="5" t="n"/>
+      <c r="S79" s="5" t="n"/>
+      <c r="T79" s="5" t="n"/>
+      <c r="U79" s="5" t="n"/>
+      <c r="V79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
@@ -2640,9 +3063,14 @@
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="5" t="n"/>
       <c r="N80" s="5" t="n"/>
-      <c r="O80" s="5" t="n"/>
+      <c r="O80" s="14" t="n"/>
       <c r="P80" s="5" t="n"/>
       <c r="Q80" s="5" t="n"/>
+      <c r="R80" s="5" t="n"/>
+      <c r="S80" s="5" t="n"/>
+      <c r="T80" s="5" t="n"/>
+      <c r="U80" s="5" t="n"/>
+      <c r="V80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
@@ -2662,9 +3090,14 @@
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="5" t="n"/>
       <c r="N81" s="5" t="n"/>
-      <c r="O81" s="5" t="n"/>
+      <c r="O81" s="14" t="n"/>
       <c r="P81" s="5" t="n"/>
       <c r="Q81" s="5" t="n"/>
+      <c r="R81" s="5" t="n"/>
+      <c r="S81" s="5" t="n"/>
+      <c r="T81" s="5" t="n"/>
+      <c r="U81" s="5" t="n"/>
+      <c r="V81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -2684,9 +3117,14 @@
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="5" t="n"/>
       <c r="N82" s="5" t="n"/>
-      <c r="O82" s="5" t="n"/>
+      <c r="O82" s="14" t="n"/>
       <c r="P82" s="5" t="n"/>
       <c r="Q82" s="5" t="n"/>
+      <c r="R82" s="5" t="n"/>
+      <c r="S82" s="5" t="n"/>
+      <c r="T82" s="5" t="n"/>
+      <c r="U82" s="5" t="n"/>
+      <c r="V82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -2706,9 +3144,14 @@
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="5" t="n"/>
       <c r="N83" s="5" t="n"/>
-      <c r="O83" s="5" t="n"/>
+      <c r="O83" s="14" t="n"/>
       <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="n"/>
+      <c r="R83" s="5" t="n"/>
+      <c r="S83" s="5" t="n"/>
+      <c r="T83" s="5" t="n"/>
+      <c r="U83" s="5" t="n"/>
+      <c r="V83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
@@ -2728,9 +3171,14 @@
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="5" t="n"/>
       <c r="N84" s="5" t="n"/>
-      <c r="O84" s="5" t="n"/>
+      <c r="O84" s="14" t="n"/>
       <c r="P84" s="5" t="n"/>
       <c r="Q84" s="5" t="n"/>
+      <c r="R84" s="5" t="n"/>
+      <c r="S84" s="5" t="n"/>
+      <c r="T84" s="5" t="n"/>
+      <c r="U84" s="5" t="n"/>
+      <c r="V84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -2750,9 +3198,14 @@
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="5" t="n"/>
       <c r="N85" s="5" t="n"/>
-      <c r="O85" s="5" t="n"/>
+      <c r="O85" s="14" t="n"/>
       <c r="P85" s="5" t="n"/>
       <c r="Q85" s="5" t="n"/>
+      <c r="R85" s="5" t="n"/>
+      <c r="S85" s="5" t="n"/>
+      <c r="T85" s="5" t="n"/>
+      <c r="U85" s="5" t="n"/>
+      <c r="V85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
@@ -2772,9 +3225,14 @@
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="5" t="n"/>
       <c r="N86" s="5" t="n"/>
-      <c r="O86" s="5" t="n"/>
+      <c r="O86" s="14" t="n"/>
       <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="n"/>
+      <c r="R86" s="5" t="n"/>
+      <c r="S86" s="5" t="n"/>
+      <c r="T86" s="5" t="n"/>
+      <c r="U86" s="5" t="n"/>
+      <c r="V86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -2794,9 +3252,14 @@
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="5" t="n"/>
       <c r="N87" s="5" t="n"/>
-      <c r="O87" s="5" t="n"/>
+      <c r="O87" s="14" t="n"/>
       <c r="P87" s="5" t="n"/>
       <c r="Q87" s="5" t="n"/>
+      <c r="R87" s="5" t="n"/>
+      <c r="S87" s="5" t="n"/>
+      <c r="T87" s="5" t="n"/>
+      <c r="U87" s="5" t="n"/>
+      <c r="V87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
@@ -2816,9 +3279,14 @@
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="5" t="n"/>
       <c r="N88" s="5" t="n"/>
-      <c r="O88" s="5" t="n"/>
+      <c r="O88" s="14" t="n"/>
       <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="n"/>
+      <c r="R88" s="5" t="n"/>
+      <c r="S88" s="5" t="n"/>
+      <c r="T88" s="5" t="n"/>
+      <c r="U88" s="5" t="n"/>
+      <c r="V88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
@@ -2838,9 +3306,14 @@
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="5" t="n"/>
       <c r="N89" s="5" t="n"/>
-      <c r="O89" s="5" t="n"/>
+      <c r="O89" s="14" t="n"/>
       <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="n"/>
+      <c r="R89" s="5" t="n"/>
+      <c r="S89" s="5" t="n"/>
+      <c r="T89" s="5" t="n"/>
+      <c r="U89" s="5" t="n"/>
+      <c r="V89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
@@ -2860,9 +3333,14 @@
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="5" t="n"/>
       <c r="N90" s="5" t="n"/>
-      <c r="O90" s="5" t="n"/>
+      <c r="O90" s="14" t="n"/>
       <c r="P90" s="5" t="n"/>
       <c r="Q90" s="5" t="n"/>
+      <c r="R90" s="5" t="n"/>
+      <c r="S90" s="5" t="n"/>
+      <c r="T90" s="5" t="n"/>
+      <c r="U90" s="5" t="n"/>
+      <c r="V90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
@@ -2882,9 +3360,14 @@
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="5" t="n"/>
       <c r="N91" s="5" t="n"/>
-      <c r="O91" s="5" t="n"/>
+      <c r="O91" s="14" t="n"/>
       <c r="P91" s="5" t="n"/>
       <c r="Q91" s="5" t="n"/>
+      <c r="R91" s="5" t="n"/>
+      <c r="S91" s="5" t="n"/>
+      <c r="T91" s="5" t="n"/>
+      <c r="U91" s="5" t="n"/>
+      <c r="V91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
@@ -2904,9 +3387,14 @@
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="5" t="n"/>
       <c r="N92" s="5" t="n"/>
-      <c r="O92" s="5" t="n"/>
+      <c r="O92" s="14" t="n"/>
       <c r="P92" s="5" t="n"/>
       <c r="Q92" s="5" t="n"/>
+      <c r="R92" s="5" t="n"/>
+      <c r="S92" s="5" t="n"/>
+      <c r="T92" s="5" t="n"/>
+      <c r="U92" s="5" t="n"/>
+      <c r="V92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -2926,9 +3414,14 @@
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="5" t="n"/>
       <c r="N93" s="5" t="n"/>
-      <c r="O93" s="5" t="n"/>
+      <c r="O93" s="14" t="n"/>
       <c r="P93" s="5" t="n"/>
       <c r="Q93" s="5" t="n"/>
+      <c r="R93" s="5" t="n"/>
+      <c r="S93" s="5" t="n"/>
+      <c r="T93" s="5" t="n"/>
+      <c r="U93" s="5" t="n"/>
+      <c r="V93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
@@ -2948,9 +3441,14 @@
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="5" t="n"/>
       <c r="N94" s="5" t="n"/>
-      <c r="O94" s="5" t="n"/>
+      <c r="O94" s="14" t="n"/>
       <c r="P94" s="5" t="n"/>
       <c r="Q94" s="5" t="n"/>
+      <c r="R94" s="5" t="n"/>
+      <c r="S94" s="5" t="n"/>
+      <c r="T94" s="5" t="n"/>
+      <c r="U94" s="5" t="n"/>
+      <c r="V94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
@@ -2970,9 +3468,14 @@
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="5" t="n"/>
       <c r="N95" s="5" t="n"/>
-      <c r="O95" s="5" t="n"/>
+      <c r="O95" s="14" t="n"/>
       <c r="P95" s="5" t="n"/>
       <c r="Q95" s="5" t="n"/>
+      <c r="R95" s="5" t="n"/>
+      <c r="S95" s="5" t="n"/>
+      <c r="T95" s="5" t="n"/>
+      <c r="U95" s="5" t="n"/>
+      <c r="V95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
@@ -2992,9 +3495,14 @@
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="5" t="n"/>
       <c r="N96" s="5" t="n"/>
-      <c r="O96" s="5" t="n"/>
+      <c r="O96" s="14" t="n"/>
       <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="n"/>
+      <c r="R96" s="5" t="n"/>
+      <c r="S96" s="5" t="n"/>
+      <c r="T96" s="5" t="n"/>
+      <c r="U96" s="5" t="n"/>
+      <c r="V96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
@@ -3014,9 +3522,14 @@
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="5" t="n"/>
       <c r="N97" s="5" t="n"/>
-      <c r="O97" s="5" t="n"/>
+      <c r="O97" s="14" t="n"/>
       <c r="P97" s="5" t="n"/>
       <c r="Q97" s="5" t="n"/>
+      <c r="R97" s="5" t="n"/>
+      <c r="S97" s="5" t="n"/>
+      <c r="T97" s="5" t="n"/>
+      <c r="U97" s="5" t="n"/>
+      <c r="V97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
@@ -3036,9 +3549,14 @@
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="5" t="n"/>
       <c r="N98" s="5" t="n"/>
-      <c r="O98" s="5" t="n"/>
+      <c r="O98" s="14" t="n"/>
       <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="n"/>
+      <c r="R98" s="5" t="n"/>
+      <c r="S98" s="5" t="n"/>
+      <c r="T98" s="5" t="n"/>
+      <c r="U98" s="5" t="n"/>
+      <c r="V98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -3058,9 +3576,14 @@
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="5" t="n"/>
       <c r="N99" s="5" t="n"/>
-      <c r="O99" s="5" t="n"/>
+      <c r="O99" s="14" t="n"/>
       <c r="P99" s="5" t="n"/>
       <c r="Q99" s="5" t="n"/>
+      <c r="R99" s="5" t="n"/>
+      <c r="S99" s="5" t="n"/>
+      <c r="T99" s="5" t="n"/>
+      <c r="U99" s="5" t="n"/>
+      <c r="V99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
@@ -3080,9 +3603,14 @@
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="5" t="n"/>
       <c r="N100" s="5" t="n"/>
-      <c r="O100" s="5" t="n"/>
+      <c r="O100" s="14" t="n"/>
       <c r="P100" s="5" t="n"/>
       <c r="Q100" s="5" t="n"/>
+      <c r="R100" s="5" t="n"/>
+      <c r="S100" s="5" t="n"/>
+      <c r="T100" s="5" t="n"/>
+      <c r="U100" s="5" t="n"/>
+      <c r="V100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
@@ -3102,9 +3630,14 @@
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="5" t="n"/>
       <c r="N101" s="5" t="n"/>
-      <c r="O101" s="5" t="n"/>
+      <c r="O101" s="14" t="n"/>
       <c r="P101" s="5" t="n"/>
       <c r="Q101" s="5" t="n"/>
+      <c r="R101" s="5" t="n"/>
+      <c r="S101" s="5" t="n"/>
+      <c r="T101" s="5" t="n"/>
+      <c r="U101" s="5" t="n"/>
+      <c r="V101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
@@ -3124,9 +3657,14 @@
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="5" t="n"/>
       <c r="N102" s="5" t="n"/>
-      <c r="O102" s="5" t="n"/>
+      <c r="O102" s="14" t="n"/>
       <c r="P102" s="5" t="n"/>
       <c r="Q102" s="5" t="n"/>
+      <c r="R102" s="5" t="n"/>
+      <c r="S102" s="5" t="n"/>
+      <c r="T102" s="5" t="n"/>
+      <c r="U102" s="5" t="n"/>
+      <c r="V102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n"/>
@@ -3146,9 +3684,14 @@
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="5" t="n"/>
       <c r="N103" s="5" t="n"/>
-      <c r="O103" s="5" t="n"/>
+      <c r="O103" s="14" t="n"/>
       <c r="P103" s="5" t="n"/>
       <c r="Q103" s="5" t="n"/>
+      <c r="R103" s="5" t="n"/>
+      <c r="S103" s="5" t="n"/>
+      <c r="T103" s="5" t="n"/>
+      <c r="U103" s="5" t="n"/>
+      <c r="V103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
@@ -3168,9 +3711,14 @@
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="5" t="n"/>
       <c r="N104" s="5" t="n"/>
-      <c r="O104" s="5" t="n"/>
+      <c r="O104" s="14" t="n"/>
       <c r="P104" s="5" t="n"/>
       <c r="Q104" s="5" t="n"/>
+      <c r="R104" s="5" t="n"/>
+      <c r="S104" s="5" t="n"/>
+      <c r="T104" s="5" t="n"/>
+      <c r="U104" s="5" t="n"/>
+      <c r="V104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
@@ -3190,9 +3738,14 @@
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="5" t="n"/>
       <c r="N105" s="5" t="n"/>
-      <c r="O105" s="5" t="n"/>
+      <c r="O105" s="14" t="n"/>
       <c r="P105" s="5" t="n"/>
       <c r="Q105" s="5" t="n"/>
+      <c r="R105" s="5" t="n"/>
+      <c r="S105" s="5" t="n"/>
+      <c r="T105" s="5" t="n"/>
+      <c r="U105" s="5" t="n"/>
+      <c r="V105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
@@ -3212,9 +3765,14 @@
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="5" t="n"/>
       <c r="N106" s="5" t="n"/>
-      <c r="O106" s="5" t="n"/>
+      <c r="O106" s="14" t="n"/>
       <c r="P106" s="5" t="n"/>
       <c r="Q106" s="5" t="n"/>
+      <c r="R106" s="5" t="n"/>
+      <c r="S106" s="5" t="n"/>
+      <c r="T106" s="5" t="n"/>
+      <c r="U106" s="5" t="n"/>
+      <c r="V106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
@@ -3234,9 +3792,14 @@
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="5" t="n"/>
       <c r="N107" s="5" t="n"/>
-      <c r="O107" s="5" t="n"/>
+      <c r="O107" s="14" t="n"/>
       <c r="P107" s="5" t="n"/>
       <c r="Q107" s="5" t="n"/>
+      <c r="R107" s="5" t="n"/>
+      <c r="S107" s="5" t="n"/>
+      <c r="T107" s="5" t="n"/>
+      <c r="U107" s="5" t="n"/>
+      <c r="V107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
@@ -3256,9 +3819,14 @@
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="5" t="n"/>
       <c r="N108" s="5" t="n"/>
-      <c r="O108" s="5" t="n"/>
+      <c r="O108" s="14" t="n"/>
       <c r="P108" s="5" t="n"/>
       <c r="Q108" s="5" t="n"/>
+      <c r="R108" s="5" t="n"/>
+      <c r="S108" s="5" t="n"/>
+      <c r="T108" s="5" t="n"/>
+      <c r="U108" s="5" t="n"/>
+      <c r="V108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
@@ -3278,9 +3846,14 @@
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="5" t="n"/>
       <c r="N109" s="5" t="n"/>
-      <c r="O109" s="5" t="n"/>
+      <c r="O109" s="14" t="n"/>
       <c r="P109" s="5" t="n"/>
       <c r="Q109" s="5" t="n"/>
+      <c r="R109" s="5" t="n"/>
+      <c r="S109" s="5" t="n"/>
+      <c r="T109" s="5" t="n"/>
+      <c r="U109" s="5" t="n"/>
+      <c r="V109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n"/>
@@ -3300,9 +3873,14 @@
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="5" t="n"/>
       <c r="N110" s="5" t="n"/>
-      <c r="O110" s="5" t="n"/>
+      <c r="O110" s="14" t="n"/>
       <c r="P110" s="5" t="n"/>
       <c r="Q110" s="5" t="n"/>
+      <c r="R110" s="5" t="n"/>
+      <c r="S110" s="5" t="n"/>
+      <c r="T110" s="5" t="n"/>
+      <c r="U110" s="5" t="n"/>
+      <c r="V110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n"/>
@@ -3322,9 +3900,14 @@
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="5" t="n"/>
       <c r="N111" s="5" t="n"/>
-      <c r="O111" s="5" t="n"/>
+      <c r="O111" s="14" t="n"/>
       <c r="P111" s="5" t="n"/>
       <c r="Q111" s="5" t="n"/>
+      <c r="R111" s="5" t="n"/>
+      <c r="S111" s="5" t="n"/>
+      <c r="T111" s="5" t="n"/>
+      <c r="U111" s="5" t="n"/>
+      <c r="V111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -3344,9 +3927,14 @@
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="5" t="n"/>
       <c r="N112" s="5" t="n"/>
-      <c r="O112" s="5" t="n"/>
+      <c r="O112" s="14" t="n"/>
       <c r="P112" s="5" t="n"/>
       <c r="Q112" s="5" t="n"/>
+      <c r="R112" s="5" t="n"/>
+      <c r="S112" s="5" t="n"/>
+      <c r="T112" s="5" t="n"/>
+      <c r="U112" s="5" t="n"/>
+      <c r="V112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
@@ -3366,9 +3954,14 @@
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="5" t="n"/>
       <c r="N113" s="5" t="n"/>
-      <c r="O113" s="5" t="n"/>
+      <c r="O113" s="14" t="n"/>
       <c r="P113" s="5" t="n"/>
       <c r="Q113" s="5" t="n"/>
+      <c r="R113" s="5" t="n"/>
+      <c r="S113" s="5" t="n"/>
+      <c r="T113" s="5" t="n"/>
+      <c r="U113" s="5" t="n"/>
+      <c r="V113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n"/>
@@ -3388,9 +3981,14 @@
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="5" t="n"/>
       <c r="N114" s="5" t="n"/>
-      <c r="O114" s="5" t="n"/>
+      <c r="O114" s="14" t="n"/>
       <c r="P114" s="5" t="n"/>
       <c r="Q114" s="5" t="n"/>
+      <c r="R114" s="5" t="n"/>
+      <c r="S114" s="5" t="n"/>
+      <c r="T114" s="5" t="n"/>
+      <c r="U114" s="5" t="n"/>
+      <c r="V114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n"/>
@@ -3410,9 +4008,14 @@
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="5" t="n"/>
       <c r="N115" s="5" t="n"/>
-      <c r="O115" s="5" t="n"/>
+      <c r="O115" s="14" t="n"/>
       <c r="P115" s="5" t="n"/>
       <c r="Q115" s="5" t="n"/>
+      <c r="R115" s="5" t="n"/>
+      <c r="S115" s="5" t="n"/>
+      <c r="T115" s="5" t="n"/>
+      <c r="U115" s="5" t="n"/>
+      <c r="V115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
@@ -3432,9 +4035,14 @@
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="5" t="n"/>
       <c r="N116" s="5" t="n"/>
-      <c r="O116" s="5" t="n"/>
+      <c r="O116" s="14" t="n"/>
       <c r="P116" s="5" t="n"/>
       <c r="Q116" s="5" t="n"/>
+      <c r="R116" s="5" t="n"/>
+      <c r="S116" s="5" t="n"/>
+      <c r="T116" s="5" t="n"/>
+      <c r="U116" s="5" t="n"/>
+      <c r="V116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n"/>
@@ -3454,9 +4062,14 @@
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="5" t="n"/>
       <c r="N117" s="5" t="n"/>
-      <c r="O117" s="5" t="n"/>
+      <c r="O117" s="14" t="n"/>
       <c r="P117" s="5" t="n"/>
       <c r="Q117" s="5" t="n"/>
+      <c r="R117" s="5" t="n"/>
+      <c r="S117" s="5" t="n"/>
+      <c r="T117" s="5" t="n"/>
+      <c r="U117" s="5" t="n"/>
+      <c r="V117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
@@ -3476,9 +4089,14 @@
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="5" t="n"/>
       <c r="N118" s="5" t="n"/>
-      <c r="O118" s="5" t="n"/>
+      <c r="O118" s="14" t="n"/>
       <c r="P118" s="5" t="n"/>
       <c r="Q118" s="5" t="n"/>
+      <c r="R118" s="5" t="n"/>
+      <c r="S118" s="5" t="n"/>
+      <c r="T118" s="5" t="n"/>
+      <c r="U118" s="5" t="n"/>
+      <c r="V118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n"/>
@@ -3498,9 +4116,14 @@
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="5" t="n"/>
       <c r="N119" s="5" t="n"/>
-      <c r="O119" s="5" t="n"/>
+      <c r="O119" s="14" t="n"/>
       <c r="P119" s="5" t="n"/>
       <c r="Q119" s="5" t="n"/>
+      <c r="R119" s="5" t="n"/>
+      <c r="S119" s="5" t="n"/>
+      <c r="T119" s="5" t="n"/>
+      <c r="U119" s="5" t="n"/>
+      <c r="V119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n"/>
@@ -3520,9 +4143,14 @@
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="5" t="n"/>
       <c r="N120" s="5" t="n"/>
-      <c r="O120" s="5" t="n"/>
+      <c r="O120" s="14" t="n"/>
       <c r="P120" s="5" t="n"/>
       <c r="Q120" s="5" t="n"/>
+      <c r="R120" s="5" t="n"/>
+      <c r="S120" s="5" t="n"/>
+      <c r="T120" s="5" t="n"/>
+      <c r="U120" s="5" t="n"/>
+      <c r="V120" s="5" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n"/>
@@ -3542,9 +4170,14 @@
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="5" t="n"/>
       <c r="N121" s="5" t="n"/>
-      <c r="O121" s="5" t="n"/>
+      <c r="O121" s="14" t="n"/>
       <c r="P121" s="5" t="n"/>
       <c r="Q121" s="5" t="n"/>
+      <c r="R121" s="5" t="n"/>
+      <c r="S121" s="5" t="n"/>
+      <c r="T121" s="5" t="n"/>
+      <c r="U121" s="5" t="n"/>
+      <c r="V121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n"/>
@@ -3564,9 +4197,14 @@
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="5" t="n"/>
       <c r="N122" s="5" t="n"/>
-      <c r="O122" s="5" t="n"/>
+      <c r="O122" s="14" t="n"/>
       <c r="P122" s="5" t="n"/>
       <c r="Q122" s="5" t="n"/>
+      <c r="R122" s="5" t="n"/>
+      <c r="S122" s="5" t="n"/>
+      <c r="T122" s="5" t="n"/>
+      <c r="U122" s="5" t="n"/>
+      <c r="V122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n"/>
@@ -3586,9 +4224,14 @@
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="5" t="n"/>
       <c r="N123" s="5" t="n"/>
-      <c r="O123" s="5" t="n"/>
+      <c r="O123" s="14" t="n"/>
       <c r="P123" s="5" t="n"/>
       <c r="Q123" s="5" t="n"/>
+      <c r="R123" s="5" t="n"/>
+      <c r="S123" s="5" t="n"/>
+      <c r="T123" s="5" t="n"/>
+      <c r="U123" s="5" t="n"/>
+      <c r="V123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n"/>
@@ -3608,9 +4251,14 @@
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="5" t="n"/>
       <c r="N124" s="5" t="n"/>
-      <c r="O124" s="5" t="n"/>
+      <c r="O124" s="14" t="n"/>
       <c r="P124" s="5" t="n"/>
       <c r="Q124" s="5" t="n"/>
+      <c r="R124" s="5" t="n"/>
+      <c r="S124" s="5" t="n"/>
+      <c r="T124" s="5" t="n"/>
+      <c r="U124" s="5" t="n"/>
+      <c r="V124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
@@ -3630,9 +4278,14 @@
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="5" t="n"/>
       <c r="N125" s="5" t="n"/>
-      <c r="O125" s="5" t="n"/>
+      <c r="O125" s="14" t="n"/>
       <c r="P125" s="5" t="n"/>
       <c r="Q125" s="5" t="n"/>
+      <c r="R125" s="5" t="n"/>
+      <c r="S125" s="5" t="n"/>
+      <c r="T125" s="5" t="n"/>
+      <c r="U125" s="5" t="n"/>
+      <c r="V125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n"/>
@@ -3652,9 +4305,14 @@
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="5" t="n"/>
       <c r="N126" s="5" t="n"/>
-      <c r="O126" s="5" t="n"/>
+      <c r="O126" s="14" t="n"/>
       <c r="P126" s="5" t="n"/>
       <c r="Q126" s="5" t="n"/>
+      <c r="R126" s="5" t="n"/>
+      <c r="S126" s="5" t="n"/>
+      <c r="T126" s="5" t="n"/>
+      <c r="U126" s="5" t="n"/>
+      <c r="V126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n"/>
@@ -3674,9 +4332,14 @@
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="5" t="n"/>
       <c r="N127" s="5" t="n"/>
-      <c r="O127" s="5" t="n"/>
+      <c r="O127" s="14" t="n"/>
       <c r="P127" s="5" t="n"/>
       <c r="Q127" s="5" t="n"/>
+      <c r="R127" s="5" t="n"/>
+      <c r="S127" s="5" t="n"/>
+      <c r="T127" s="5" t="n"/>
+      <c r="U127" s="5" t="n"/>
+      <c r="V127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n"/>
@@ -3696,9 +4359,14 @@
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="5" t="n"/>
       <c r="N128" s="5" t="n"/>
-      <c r="O128" s="5" t="n"/>
+      <c r="O128" s="14" t="n"/>
       <c r="P128" s="5" t="n"/>
       <c r="Q128" s="5" t="n"/>
+      <c r="R128" s="5" t="n"/>
+      <c r="S128" s="5" t="n"/>
+      <c r="T128" s="5" t="n"/>
+      <c r="U128" s="5" t="n"/>
+      <c r="V128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n"/>
@@ -3718,9 +4386,14 @@
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="5" t="n"/>
       <c r="N129" s="5" t="n"/>
-      <c r="O129" s="5" t="n"/>
+      <c r="O129" s="14" t="n"/>
       <c r="P129" s="5" t="n"/>
       <c r="Q129" s="5" t="n"/>
+      <c r="R129" s="5" t="n"/>
+      <c r="S129" s="5" t="n"/>
+      <c r="T129" s="5" t="n"/>
+      <c r="U129" s="5" t="n"/>
+      <c r="V129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
@@ -3740,9 +4413,14 @@
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="5" t="n"/>
       <c r="N130" s="5" t="n"/>
-      <c r="O130" s="5" t="n"/>
+      <c r="O130" s="14" t="n"/>
       <c r="P130" s="5" t="n"/>
       <c r="Q130" s="5" t="n"/>
+      <c r="R130" s="5" t="n"/>
+      <c r="S130" s="5" t="n"/>
+      <c r="T130" s="5" t="n"/>
+      <c r="U130" s="5" t="n"/>
+      <c r="V130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n"/>
@@ -3762,9 +4440,14 @@
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="5" t="n"/>
       <c r="N131" s="5" t="n"/>
-      <c r="O131" s="5" t="n"/>
+      <c r="O131" s="14" t="n"/>
       <c r="P131" s="5" t="n"/>
       <c r="Q131" s="5" t="n"/>
+      <c r="R131" s="5" t="n"/>
+      <c r="S131" s="5" t="n"/>
+      <c r="T131" s="5" t="n"/>
+      <c r="U131" s="5" t="n"/>
+      <c r="V131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n"/>
@@ -3784,9 +4467,14 @@
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="5" t="n"/>
       <c r="N132" s="5" t="n"/>
-      <c r="O132" s="5" t="n"/>
+      <c r="O132" s="14" t="n"/>
       <c r="P132" s="5" t="n"/>
       <c r="Q132" s="5" t="n"/>
+      <c r="R132" s="5" t="n"/>
+      <c r="S132" s="5" t="n"/>
+      <c r="T132" s="5" t="n"/>
+      <c r="U132" s="5" t="n"/>
+      <c r="V132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n"/>
@@ -3806,9 +4494,14 @@
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="5" t="n"/>
       <c r="N133" s="5" t="n"/>
-      <c r="O133" s="5" t="n"/>
+      <c r="O133" s="14" t="n"/>
       <c r="P133" s="5" t="n"/>
       <c r="Q133" s="5" t="n"/>
+      <c r="R133" s="5" t="n"/>
+      <c r="S133" s="5" t="n"/>
+      <c r="T133" s="5" t="n"/>
+      <c r="U133" s="5" t="n"/>
+      <c r="V133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n"/>
@@ -3828,9 +4521,14 @@
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="5" t="n"/>
       <c r="N134" s="5" t="n"/>
-      <c r="O134" s="5" t="n"/>
+      <c r="O134" s="14" t="n"/>
       <c r="P134" s="5" t="n"/>
       <c r="Q134" s="5" t="n"/>
+      <c r="R134" s="5" t="n"/>
+      <c r="S134" s="5" t="n"/>
+      <c r="T134" s="5" t="n"/>
+      <c r="U134" s="5" t="n"/>
+      <c r="V134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n"/>
@@ -3850,9 +4548,14 @@
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="5" t="n"/>
       <c r="N135" s="5" t="n"/>
-      <c r="O135" s="5" t="n"/>
+      <c r="O135" s="14" t="n"/>
       <c r="P135" s="5" t="n"/>
       <c r="Q135" s="5" t="n"/>
+      <c r="R135" s="5" t="n"/>
+      <c r="S135" s="5" t="n"/>
+      <c r="T135" s="5" t="n"/>
+      <c r="U135" s="5" t="n"/>
+      <c r="V135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n"/>
@@ -3872,9 +4575,14 @@
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="5" t="n"/>
       <c r="N136" s="5" t="n"/>
-      <c r="O136" s="5" t="n"/>
+      <c r="O136" s="14" t="n"/>
       <c r="P136" s="5" t="n"/>
       <c r="Q136" s="5" t="n"/>
+      <c r="R136" s="5" t="n"/>
+      <c r="S136" s="5" t="n"/>
+      <c r="T136" s="5" t="n"/>
+      <c r="U136" s="5" t="n"/>
+      <c r="V136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n"/>
@@ -3894,9 +4602,14 @@
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="5" t="n"/>
       <c r="N137" s="5" t="n"/>
-      <c r="O137" s="5" t="n"/>
+      <c r="O137" s="14" t="n"/>
       <c r="P137" s="5" t="n"/>
       <c r="Q137" s="5" t="n"/>
+      <c r="R137" s="5" t="n"/>
+      <c r="S137" s="5" t="n"/>
+      <c r="T137" s="5" t="n"/>
+      <c r="U137" s="5" t="n"/>
+      <c r="V137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n"/>
@@ -3916,9 +4629,14 @@
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="5" t="n"/>
       <c r="N138" s="5" t="n"/>
-      <c r="O138" s="5" t="n"/>
+      <c r="O138" s="14" t="n"/>
       <c r="P138" s="5" t="n"/>
       <c r="Q138" s="5" t="n"/>
+      <c r="R138" s="5" t="n"/>
+      <c r="S138" s="5" t="n"/>
+      <c r="T138" s="5" t="n"/>
+      <c r="U138" s="5" t="n"/>
+      <c r="V138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
@@ -3938,9 +4656,14 @@
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="5" t="n"/>
       <c r="N139" s="5" t="n"/>
-      <c r="O139" s="5" t="n"/>
+      <c r="O139" s="14" t="n"/>
       <c r="P139" s="5" t="n"/>
       <c r="Q139" s="5" t="n"/>
+      <c r="R139" s="5" t="n"/>
+      <c r="S139" s="5" t="n"/>
+      <c r="T139" s="5" t="n"/>
+      <c r="U139" s="5" t="n"/>
+      <c r="V139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
@@ -3960,9 +4683,14 @@
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="5" t="n"/>
       <c r="N140" s="5" t="n"/>
-      <c r="O140" s="5" t="n"/>
+      <c r="O140" s="14" t="n"/>
       <c r="P140" s="5" t="n"/>
       <c r="Q140" s="5" t="n"/>
+      <c r="R140" s="5" t="n"/>
+      <c r="S140" s="5" t="n"/>
+      <c r="T140" s="5" t="n"/>
+      <c r="U140" s="5" t="n"/>
+      <c r="V140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n"/>
@@ -3982,9 +4710,14 @@
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="5" t="n"/>
       <c r="N141" s="5" t="n"/>
-      <c r="O141" s="5" t="n"/>
+      <c r="O141" s="14" t="n"/>
       <c r="P141" s="5" t="n"/>
       <c r="Q141" s="5" t="n"/>
+      <c r="R141" s="5" t="n"/>
+      <c r="S141" s="5" t="n"/>
+      <c r="T141" s="5" t="n"/>
+      <c r="U141" s="5" t="n"/>
+      <c r="V141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
@@ -4004,9 +4737,14 @@
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="5" t="n"/>
       <c r="N142" s="5" t="n"/>
-      <c r="O142" s="5" t="n"/>
+      <c r="O142" s="14" t="n"/>
       <c r="P142" s="5" t="n"/>
       <c r="Q142" s="5" t="n"/>
+      <c r="R142" s="5" t="n"/>
+      <c r="S142" s="5" t="n"/>
+      <c r="T142" s="5" t="n"/>
+      <c r="U142" s="5" t="n"/>
+      <c r="V142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n"/>
@@ -4026,9 +4764,14 @@
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="5" t="n"/>
       <c r="N143" s="5" t="n"/>
-      <c r="O143" s="5" t="n"/>
+      <c r="O143" s="14" t="n"/>
       <c r="P143" s="5" t="n"/>
       <c r="Q143" s="5" t="n"/>
+      <c r="R143" s="5" t="n"/>
+      <c r="S143" s="5" t="n"/>
+      <c r="T143" s="5" t="n"/>
+      <c r="U143" s="5" t="n"/>
+      <c r="V143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n"/>
@@ -4048,9 +4791,14 @@
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="5" t="n"/>
       <c r="N144" s="5" t="n"/>
-      <c r="O144" s="5" t="n"/>
+      <c r="O144" s="14" t="n"/>
       <c r="P144" s="5" t="n"/>
       <c r="Q144" s="5" t="n"/>
+      <c r="R144" s="5" t="n"/>
+      <c r="S144" s="5" t="n"/>
+      <c r="T144" s="5" t="n"/>
+      <c r="U144" s="5" t="n"/>
+      <c r="V144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n"/>
@@ -4070,9 +4818,14 @@
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="5" t="n"/>
       <c r="N145" s="5" t="n"/>
-      <c r="O145" s="5" t="n"/>
+      <c r="O145" s="14" t="n"/>
       <c r="P145" s="5" t="n"/>
       <c r="Q145" s="5" t="n"/>
+      <c r="R145" s="5" t="n"/>
+      <c r="S145" s="5" t="n"/>
+      <c r="T145" s="5" t="n"/>
+      <c r="U145" s="5" t="n"/>
+      <c r="V145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n"/>
@@ -4092,9 +4845,14 @@
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="5" t="n"/>
       <c r="N146" s="5" t="n"/>
-      <c r="O146" s="5" t="n"/>
+      <c r="O146" s="14" t="n"/>
       <c r="P146" s="5" t="n"/>
       <c r="Q146" s="5" t="n"/>
+      <c r="R146" s="5" t="n"/>
+      <c r="S146" s="5" t="n"/>
+      <c r="T146" s="5" t="n"/>
+      <c r="U146" s="5" t="n"/>
+      <c r="V146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n"/>
@@ -4114,9 +4872,14 @@
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="5" t="n"/>
       <c r="N147" s="5" t="n"/>
-      <c r="O147" s="5" t="n"/>
+      <c r="O147" s="14" t="n"/>
       <c r="P147" s="5" t="n"/>
       <c r="Q147" s="5" t="n"/>
+      <c r="R147" s="5" t="n"/>
+      <c r="S147" s="5" t="n"/>
+      <c r="T147" s="5" t="n"/>
+      <c r="U147" s="5" t="n"/>
+      <c r="V147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n"/>
@@ -4136,9 +4899,14 @@
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="5" t="n"/>
       <c r="N148" s="5" t="n"/>
-      <c r="O148" s="5" t="n"/>
+      <c r="O148" s="14" t="n"/>
       <c r="P148" s="5" t="n"/>
       <c r="Q148" s="5" t="n"/>
+      <c r="R148" s="5" t="n"/>
+      <c r="S148" s="5" t="n"/>
+      <c r="T148" s="5" t="n"/>
+      <c r="U148" s="5" t="n"/>
+      <c r="V148" s="5" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n"/>
@@ -4158,9 +4926,14 @@
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="5" t="n"/>
       <c r="N149" s="5" t="n"/>
-      <c r="O149" s="5" t="n"/>
+      <c r="O149" s="14" t="n"/>
       <c r="P149" s="5" t="n"/>
       <c r="Q149" s="5" t="n"/>
+      <c r="R149" s="5" t="n"/>
+      <c r="S149" s="5" t="n"/>
+      <c r="T149" s="5" t="n"/>
+      <c r="U149" s="5" t="n"/>
+      <c r="V149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n"/>
@@ -4180,9 +4953,14 @@
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="5" t="n"/>
       <c r="N150" s="5" t="n"/>
-      <c r="O150" s="5" t="n"/>
+      <c r="O150" s="14" t="n"/>
       <c r="P150" s="5" t="n"/>
       <c r="Q150" s="5" t="n"/>
+      <c r="R150" s="5" t="n"/>
+      <c r="S150" s="5" t="n"/>
+      <c r="T150" s="5" t="n"/>
+      <c r="U150" s="5" t="n"/>
+      <c r="V150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n"/>
@@ -4202,9 +4980,14 @@
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="5" t="n"/>
       <c r="N151" s="5" t="n"/>
-      <c r="O151" s="5" t="n"/>
+      <c r="O151" s="14" t="n"/>
       <c r="P151" s="5" t="n"/>
       <c r="Q151" s="5" t="n"/>
+      <c r="R151" s="5" t="n"/>
+      <c r="S151" s="5" t="n"/>
+      <c r="T151" s="5" t="n"/>
+      <c r="U151" s="5" t="n"/>
+      <c r="V151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n"/>
@@ -4224,9 +5007,14 @@
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="5" t="n"/>
       <c r="N152" s="5" t="n"/>
-      <c r="O152" s="5" t="n"/>
+      <c r="O152" s="14" t="n"/>
       <c r="P152" s="5" t="n"/>
       <c r="Q152" s="5" t="n"/>
+      <c r="R152" s="5" t="n"/>
+      <c r="S152" s="5" t="n"/>
+      <c r="T152" s="5" t="n"/>
+      <c r="U152" s="5" t="n"/>
+      <c r="V152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n"/>
@@ -4246,9 +5034,14 @@
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="5" t="n"/>
       <c r="N153" s="5" t="n"/>
-      <c r="O153" s="5" t="n"/>
+      <c r="O153" s="14" t="n"/>
       <c r="P153" s="5" t="n"/>
       <c r="Q153" s="5" t="n"/>
+      <c r="R153" s="5" t="n"/>
+      <c r="S153" s="5" t="n"/>
+      <c r="T153" s="5" t="n"/>
+      <c r="U153" s="5" t="n"/>
+      <c r="V153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n"/>
@@ -4268,9 +5061,14 @@
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="5" t="n"/>
       <c r="N154" s="5" t="n"/>
-      <c r="O154" s="5" t="n"/>
+      <c r="O154" s="14" t="n"/>
       <c r="P154" s="5" t="n"/>
       <c r="Q154" s="5" t="n"/>
+      <c r="R154" s="5" t="n"/>
+      <c r="S154" s="5" t="n"/>
+      <c r="T154" s="5" t="n"/>
+      <c r="U154" s="5" t="n"/>
+      <c r="V154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n"/>
@@ -4290,9 +5088,14 @@
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="5" t="n"/>
       <c r="N155" s="5" t="n"/>
-      <c r="O155" s="5" t="n"/>
+      <c r="O155" s="14" t="n"/>
       <c r="P155" s="5" t="n"/>
       <c r="Q155" s="5" t="n"/>
+      <c r="R155" s="5" t="n"/>
+      <c r="S155" s="5" t="n"/>
+      <c r="T155" s="5" t="n"/>
+      <c r="U155" s="5" t="n"/>
+      <c r="V155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n"/>
@@ -4312,9 +5115,14 @@
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="5" t="n"/>
       <c r="N156" s="5" t="n"/>
-      <c r="O156" s="5" t="n"/>
+      <c r="O156" s="14" t="n"/>
       <c r="P156" s="5" t="n"/>
       <c r="Q156" s="5" t="n"/>
+      <c r="R156" s="5" t="n"/>
+      <c r="S156" s="5" t="n"/>
+      <c r="T156" s="5" t="n"/>
+      <c r="U156" s="5" t="n"/>
+      <c r="V156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n"/>
@@ -4334,9 +5142,14 @@
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="5" t="n"/>
       <c r="N157" s="5" t="n"/>
-      <c r="O157" s="5" t="n"/>
+      <c r="O157" s="14" t="n"/>
       <c r="P157" s="5" t="n"/>
       <c r="Q157" s="5" t="n"/>
+      <c r="R157" s="5" t="n"/>
+      <c r="S157" s="5" t="n"/>
+      <c r="T157" s="5" t="n"/>
+      <c r="U157" s="5" t="n"/>
+      <c r="V157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n"/>
@@ -4356,9 +5169,14 @@
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="5" t="n"/>
       <c r="N158" s="5" t="n"/>
-      <c r="O158" s="5" t="n"/>
+      <c r="O158" s="14" t="n"/>
       <c r="P158" s="5" t="n"/>
       <c r="Q158" s="5" t="n"/>
+      <c r="R158" s="5" t="n"/>
+      <c r="S158" s="5" t="n"/>
+      <c r="T158" s="5" t="n"/>
+      <c r="U158" s="5" t="n"/>
+      <c r="V158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n"/>
@@ -4378,9 +5196,14 @@
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="5" t="n"/>
       <c r="N159" s="5" t="n"/>
-      <c r="O159" s="5" t="n"/>
+      <c r="O159" s="14" t="n"/>
       <c r="P159" s="5" t="n"/>
       <c r="Q159" s="5" t="n"/>
+      <c r="R159" s="5" t="n"/>
+      <c r="S159" s="5" t="n"/>
+      <c r="T159" s="5" t="n"/>
+      <c r="U159" s="5" t="n"/>
+      <c r="V159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n"/>
@@ -4400,9 +5223,14 @@
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="5" t="n"/>
       <c r="N160" s="5" t="n"/>
-      <c r="O160" s="5" t="n"/>
+      <c r="O160" s="14" t="n"/>
       <c r="P160" s="5" t="n"/>
       <c r="Q160" s="5" t="n"/>
+      <c r="R160" s="5" t="n"/>
+      <c r="S160" s="5" t="n"/>
+      <c r="T160" s="5" t="n"/>
+      <c r="U160" s="5" t="n"/>
+      <c r="V160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
@@ -4422,9 +5250,14 @@
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="5" t="n"/>
       <c r="N161" s="5" t="n"/>
-      <c r="O161" s="5" t="n"/>
+      <c r="O161" s="14" t="n"/>
       <c r="P161" s="5" t="n"/>
       <c r="Q161" s="5" t="n"/>
+      <c r="R161" s="5" t="n"/>
+      <c r="S161" s="5" t="n"/>
+      <c r="T161" s="5" t="n"/>
+      <c r="U161" s="5" t="n"/>
+      <c r="V161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
@@ -4444,9 +5277,14 @@
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="5" t="n"/>
       <c r="N162" s="5" t="n"/>
-      <c r="O162" s="5" t="n"/>
+      <c r="O162" s="14" t="n"/>
       <c r="P162" s="5" t="n"/>
       <c r="Q162" s="5" t="n"/>
+      <c r="R162" s="5" t="n"/>
+      <c r="S162" s="5" t="n"/>
+      <c r="T162" s="5" t="n"/>
+      <c r="U162" s="5" t="n"/>
+      <c r="V162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n"/>
@@ -4466,9 +5304,14 @@
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="5" t="n"/>
       <c r="N163" s="5" t="n"/>
-      <c r="O163" s="5" t="n"/>
+      <c r="O163" s="14" t="n"/>
       <c r="P163" s="5" t="n"/>
       <c r="Q163" s="5" t="n"/>
+      <c r="R163" s="5" t="n"/>
+      <c r="S163" s="5" t="n"/>
+      <c r="T163" s="5" t="n"/>
+      <c r="U163" s="5" t="n"/>
+      <c r="V163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n"/>
@@ -4488,9 +5331,14 @@
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="5" t="n"/>
       <c r="N164" s="5" t="n"/>
-      <c r="O164" s="5" t="n"/>
+      <c r="O164" s="14" t="n"/>
       <c r="P164" s="5" t="n"/>
       <c r="Q164" s="5" t="n"/>
+      <c r="R164" s="5" t="n"/>
+      <c r="S164" s="5" t="n"/>
+      <c r="T164" s="5" t="n"/>
+      <c r="U164" s="5" t="n"/>
+      <c r="V164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
@@ -4510,9 +5358,14 @@
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="5" t="n"/>
       <c r="N165" s="5" t="n"/>
-      <c r="O165" s="5" t="n"/>
+      <c r="O165" s="14" t="n"/>
       <c r="P165" s="5" t="n"/>
       <c r="Q165" s="5" t="n"/>
+      <c r="R165" s="5" t="n"/>
+      <c r="S165" s="5" t="n"/>
+      <c r="T165" s="5" t="n"/>
+      <c r="U165" s="5" t="n"/>
+      <c r="V165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n"/>
@@ -4532,9 +5385,14 @@
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="5" t="n"/>
       <c r="N166" s="5" t="n"/>
-      <c r="O166" s="5" t="n"/>
+      <c r="O166" s="14" t="n"/>
       <c r="P166" s="5" t="n"/>
       <c r="Q166" s="5" t="n"/>
+      <c r="R166" s="5" t="n"/>
+      <c r="S166" s="5" t="n"/>
+      <c r="T166" s="5" t="n"/>
+      <c r="U166" s="5" t="n"/>
+      <c r="V166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n"/>
@@ -4554,9 +5412,14 @@
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="5" t="n"/>
       <c r="N167" s="5" t="n"/>
-      <c r="O167" s="5" t="n"/>
+      <c r="O167" s="14" t="n"/>
       <c r="P167" s="5" t="n"/>
       <c r="Q167" s="5" t="n"/>
+      <c r="R167" s="5" t="n"/>
+      <c r="S167" s="5" t="n"/>
+      <c r="T167" s="5" t="n"/>
+      <c r="U167" s="5" t="n"/>
+      <c r="V167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
@@ -4576,9 +5439,14 @@
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="5" t="n"/>
       <c r="N168" s="5" t="n"/>
-      <c r="O168" s="5" t="n"/>
+      <c r="O168" s="14" t="n"/>
       <c r="P168" s="5" t="n"/>
       <c r="Q168" s="5" t="n"/>
+      <c r="R168" s="5" t="n"/>
+      <c r="S168" s="5" t="n"/>
+      <c r="T168" s="5" t="n"/>
+      <c r="U168" s="5" t="n"/>
+      <c r="V168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
@@ -4598,9 +5466,14 @@
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="5" t="n"/>
       <c r="N169" s="5" t="n"/>
-      <c r="O169" s="5" t="n"/>
+      <c r="O169" s="14" t="n"/>
       <c r="P169" s="5" t="n"/>
       <c r="Q169" s="5" t="n"/>
+      <c r="R169" s="5" t="n"/>
+      <c r="S169" s="5" t="n"/>
+      <c r="T169" s="5" t="n"/>
+      <c r="U169" s="5" t="n"/>
+      <c r="V169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
@@ -4620,9 +5493,14 @@
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="5" t="n"/>
       <c r="N170" s="5" t="n"/>
-      <c r="O170" s="5" t="n"/>
+      <c r="O170" s="14" t="n"/>
       <c r="P170" s="5" t="n"/>
       <c r="Q170" s="5" t="n"/>
+      <c r="R170" s="5" t="n"/>
+      <c r="S170" s="5" t="n"/>
+      <c r="T170" s="5" t="n"/>
+      <c r="U170" s="5" t="n"/>
+      <c r="V170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n"/>
@@ -4642,9 +5520,14 @@
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="5" t="n"/>
       <c r="N171" s="5" t="n"/>
-      <c r="O171" s="5" t="n"/>
+      <c r="O171" s="14" t="n"/>
       <c r="P171" s="5" t="n"/>
       <c r="Q171" s="5" t="n"/>
+      <c r="R171" s="5" t="n"/>
+      <c r="S171" s="5" t="n"/>
+      <c r="T171" s="5" t="n"/>
+      <c r="U171" s="5" t="n"/>
+      <c r="V171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n"/>
@@ -4664,9 +5547,14 @@
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="5" t="n"/>
       <c r="N172" s="5" t="n"/>
-      <c r="O172" s="5" t="n"/>
+      <c r="O172" s="14" t="n"/>
       <c r="P172" s="5" t="n"/>
       <c r="Q172" s="5" t="n"/>
+      <c r="R172" s="5" t="n"/>
+      <c r="S172" s="5" t="n"/>
+      <c r="T172" s="5" t="n"/>
+      <c r="U172" s="5" t="n"/>
+      <c r="V172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n"/>
@@ -4686,9 +5574,14 @@
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="5" t="n"/>
       <c r="N173" s="5" t="n"/>
-      <c r="O173" s="5" t="n"/>
+      <c r="O173" s="14" t="n"/>
       <c r="P173" s="5" t="n"/>
       <c r="Q173" s="5" t="n"/>
+      <c r="R173" s="5" t="n"/>
+      <c r="S173" s="5" t="n"/>
+      <c r="T173" s="5" t="n"/>
+      <c r="U173" s="5" t="n"/>
+      <c r="V173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n"/>
@@ -4708,9 +5601,14 @@
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="5" t="n"/>
       <c r="N174" s="5" t="n"/>
-      <c r="O174" s="5" t="n"/>
+      <c r="O174" s="14" t="n"/>
       <c r="P174" s="5" t="n"/>
       <c r="Q174" s="5" t="n"/>
+      <c r="R174" s="5" t="n"/>
+      <c r="S174" s="5" t="n"/>
+      <c r="T174" s="5" t="n"/>
+      <c r="U174" s="5" t="n"/>
+      <c r="V174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n"/>
@@ -4730,9 +5628,14 @@
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="5" t="n"/>
       <c r="N175" s="5" t="n"/>
-      <c r="O175" s="5" t="n"/>
+      <c r="O175" s="14" t="n"/>
       <c r="P175" s="5" t="n"/>
       <c r="Q175" s="5" t="n"/>
+      <c r="R175" s="5" t="n"/>
+      <c r="S175" s="5" t="n"/>
+      <c r="T175" s="5" t="n"/>
+      <c r="U175" s="5" t="n"/>
+      <c r="V175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
@@ -4752,9 +5655,14 @@
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="5" t="n"/>
       <c r="N176" s="5" t="n"/>
-      <c r="O176" s="5" t="n"/>
+      <c r="O176" s="14" t="n"/>
       <c r="P176" s="5" t="n"/>
       <c r="Q176" s="5" t="n"/>
+      <c r="R176" s="5" t="n"/>
+      <c r="S176" s="5" t="n"/>
+      <c r="T176" s="5" t="n"/>
+      <c r="U176" s="5" t="n"/>
+      <c r="V176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n"/>
@@ -4774,9 +5682,14 @@
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="5" t="n"/>
       <c r="N177" s="5" t="n"/>
-      <c r="O177" s="5" t="n"/>
+      <c r="O177" s="14" t="n"/>
       <c r="P177" s="5" t="n"/>
       <c r="Q177" s="5" t="n"/>
+      <c r="R177" s="5" t="n"/>
+      <c r="S177" s="5" t="n"/>
+      <c r="T177" s="5" t="n"/>
+      <c r="U177" s="5" t="n"/>
+      <c r="V177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n"/>
@@ -4796,9 +5709,14 @@
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="5" t="n"/>
       <c r="N178" s="5" t="n"/>
-      <c r="O178" s="5" t="n"/>
+      <c r="O178" s="14" t="n"/>
       <c r="P178" s="5" t="n"/>
       <c r="Q178" s="5" t="n"/>
+      <c r="R178" s="5" t="n"/>
+      <c r="S178" s="5" t="n"/>
+      <c r="T178" s="5" t="n"/>
+      <c r="U178" s="5" t="n"/>
+      <c r="V178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
@@ -4818,9 +5736,14 @@
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="5" t="n"/>
       <c r="N179" s="5" t="n"/>
-      <c r="O179" s="5" t="n"/>
+      <c r="O179" s="14" t="n"/>
       <c r="P179" s="5" t="n"/>
       <c r="Q179" s="5" t="n"/>
+      <c r="R179" s="5" t="n"/>
+      <c r="S179" s="5" t="n"/>
+      <c r="T179" s="5" t="n"/>
+      <c r="U179" s="5" t="n"/>
+      <c r="V179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
@@ -4840,9 +5763,14 @@
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="5" t="n"/>
       <c r="N180" s="5" t="n"/>
-      <c r="O180" s="5" t="n"/>
+      <c r="O180" s="14" t="n"/>
       <c r="P180" s="5" t="n"/>
       <c r="Q180" s="5" t="n"/>
+      <c r="R180" s="5" t="n"/>
+      <c r="S180" s="5" t="n"/>
+      <c r="T180" s="5" t="n"/>
+      <c r="U180" s="5" t="n"/>
+      <c r="V180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
@@ -4862,9 +5790,14 @@
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="5" t="n"/>
       <c r="N181" s="5" t="n"/>
-      <c r="O181" s="5" t="n"/>
+      <c r="O181" s="14" t="n"/>
       <c r="P181" s="5" t="n"/>
       <c r="Q181" s="5" t="n"/>
+      <c r="R181" s="5" t="n"/>
+      <c r="S181" s="5" t="n"/>
+      <c r="T181" s="5" t="n"/>
+      <c r="U181" s="5" t="n"/>
+      <c r="V181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
@@ -4884,9 +5817,14 @@
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="5" t="n"/>
       <c r="N182" s="5" t="n"/>
-      <c r="O182" s="5" t="n"/>
+      <c r="O182" s="14" t="n"/>
       <c r="P182" s="5" t="n"/>
       <c r="Q182" s="5" t="n"/>
+      <c r="R182" s="5" t="n"/>
+      <c r="S182" s="5" t="n"/>
+      <c r="T182" s="5" t="n"/>
+      <c r="U182" s="5" t="n"/>
+      <c r="V182" s="5" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
@@ -4906,9 +5844,14 @@
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="5" t="n"/>
       <c r="N183" s="5" t="n"/>
-      <c r="O183" s="5" t="n"/>
+      <c r="O183" s="14" t="n"/>
       <c r="P183" s="5" t="n"/>
       <c r="Q183" s="5" t="n"/>
+      <c r="R183" s="5" t="n"/>
+      <c r="S183" s="5" t="n"/>
+      <c r="T183" s="5" t="n"/>
+      <c r="U183" s="5" t="n"/>
+      <c r="V183" s="5" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
@@ -4928,9 +5871,14 @@
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="5" t="n"/>
       <c r="N184" s="5" t="n"/>
-      <c r="O184" s="5" t="n"/>
+      <c r="O184" s="14" t="n"/>
       <c r="P184" s="5" t="n"/>
       <c r="Q184" s="5" t="n"/>
+      <c r="R184" s="5" t="n"/>
+      <c r="S184" s="5" t="n"/>
+      <c r="T184" s="5" t="n"/>
+      <c r="U184" s="5" t="n"/>
+      <c r="V184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
@@ -4950,9 +5898,14 @@
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="5" t="n"/>
       <c r="N185" s="5" t="n"/>
-      <c r="O185" s="5" t="n"/>
+      <c r="O185" s="14" t="n"/>
       <c r="P185" s="5" t="n"/>
       <c r="Q185" s="5" t="n"/>
+      <c r="R185" s="5" t="n"/>
+      <c r="S185" s="5" t="n"/>
+      <c r="T185" s="5" t="n"/>
+      <c r="U185" s="5" t="n"/>
+      <c r="V185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
@@ -4972,9 +5925,14 @@
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="5" t="n"/>
       <c r="N186" s="5" t="n"/>
-      <c r="O186" s="5" t="n"/>
+      <c r="O186" s="14" t="n"/>
       <c r="P186" s="5" t="n"/>
       <c r="Q186" s="5" t="n"/>
+      <c r="R186" s="5" t="n"/>
+      <c r="S186" s="5" t="n"/>
+      <c r="T186" s="5" t="n"/>
+      <c r="U186" s="5" t="n"/>
+      <c r="V186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
@@ -4994,9 +5952,14 @@
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="5" t="n"/>
       <c r="N187" s="5" t="n"/>
-      <c r="O187" s="5" t="n"/>
+      <c r="O187" s="14" t="n"/>
       <c r="P187" s="5" t="n"/>
       <c r="Q187" s="5" t="n"/>
+      <c r="R187" s="5" t="n"/>
+      <c r="S187" s="5" t="n"/>
+      <c r="T187" s="5" t="n"/>
+      <c r="U187" s="5" t="n"/>
+      <c r="V187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
@@ -5016,9 +5979,14 @@
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="5" t="n"/>
       <c r="N188" s="5" t="n"/>
-      <c r="O188" s="5" t="n"/>
+      <c r="O188" s="14" t="n"/>
       <c r="P188" s="5" t="n"/>
       <c r="Q188" s="5" t="n"/>
+      <c r="R188" s="5" t="n"/>
+      <c r="S188" s="5" t="n"/>
+      <c r="T188" s="5" t="n"/>
+      <c r="U188" s="5" t="n"/>
+      <c r="V188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
@@ -5038,9 +6006,14 @@
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="5" t="n"/>
       <c r="N189" s="5" t="n"/>
-      <c r="O189" s="5" t="n"/>
+      <c r="O189" s="14" t="n"/>
       <c r="P189" s="5" t="n"/>
       <c r="Q189" s="5" t="n"/>
+      <c r="R189" s="5" t="n"/>
+      <c r="S189" s="5" t="n"/>
+      <c r="T189" s="5" t="n"/>
+      <c r="U189" s="5" t="n"/>
+      <c r="V189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
@@ -5060,9 +6033,14 @@
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="5" t="n"/>
       <c r="N190" s="5" t="n"/>
-      <c r="O190" s="5" t="n"/>
+      <c r="O190" s="14" t="n"/>
       <c r="P190" s="5" t="n"/>
       <c r="Q190" s="5" t="n"/>
+      <c r="R190" s="5" t="n"/>
+      <c r="S190" s="5" t="n"/>
+      <c r="T190" s="5" t="n"/>
+      <c r="U190" s="5" t="n"/>
+      <c r="V190" s="5" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
@@ -5082,9 +6060,14 @@
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="5" t="n"/>
       <c r="N191" s="5" t="n"/>
-      <c r="O191" s="5" t="n"/>
+      <c r="O191" s="14" t="n"/>
       <c r="P191" s="5" t="n"/>
       <c r="Q191" s="5" t="n"/>
+      <c r="R191" s="5" t="n"/>
+      <c r="S191" s="5" t="n"/>
+      <c r="T191" s="5" t="n"/>
+      <c r="U191" s="5" t="n"/>
+      <c r="V191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n"/>
@@ -5104,9 +6087,14 @@
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="5" t="n"/>
       <c r="N192" s="5" t="n"/>
-      <c r="O192" s="5" t="n"/>
+      <c r="O192" s="14" t="n"/>
       <c r="P192" s="5" t="n"/>
       <c r="Q192" s="5" t="n"/>
+      <c r="R192" s="5" t="n"/>
+      <c r="S192" s="5" t="n"/>
+      <c r="T192" s="5" t="n"/>
+      <c r="U192" s="5" t="n"/>
+      <c r="V192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
@@ -5126,9 +6114,14 @@
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="5" t="n"/>
       <c r="N193" s="5" t="n"/>
-      <c r="O193" s="5" t="n"/>
+      <c r="O193" s="14" t="n"/>
       <c r="P193" s="5" t="n"/>
       <c r="Q193" s="5" t="n"/>
+      <c r="R193" s="5" t="n"/>
+      <c r="S193" s="5" t="n"/>
+      <c r="T193" s="5" t="n"/>
+      <c r="U193" s="5" t="n"/>
+      <c r="V193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
@@ -5148,9 +6141,14 @@
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="5" t="n"/>
       <c r="N194" s="5" t="n"/>
-      <c r="O194" s="5" t="n"/>
+      <c r="O194" s="14" t="n"/>
       <c r="P194" s="5" t="n"/>
       <c r="Q194" s="5" t="n"/>
+      <c r="R194" s="5" t="n"/>
+      <c r="S194" s="5" t="n"/>
+      <c r="T194" s="5" t="n"/>
+      <c r="U194" s="5" t="n"/>
+      <c r="V194" s="5" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n"/>
@@ -5170,9 +6168,14 @@
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="5" t="n"/>
       <c r="N195" s="5" t="n"/>
-      <c r="O195" s="5" t="n"/>
+      <c r="O195" s="14" t="n"/>
       <c r="P195" s="5" t="n"/>
       <c r="Q195" s="5" t="n"/>
+      <c r="R195" s="5" t="n"/>
+      <c r="S195" s="5" t="n"/>
+      <c r="T195" s="5" t="n"/>
+      <c r="U195" s="5" t="n"/>
+      <c r="V195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n"/>
@@ -5192,9 +6195,14 @@
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="5" t="n"/>
       <c r="N196" s="5" t="n"/>
-      <c r="O196" s="5" t="n"/>
+      <c r="O196" s="14" t="n"/>
       <c r="P196" s="5" t="n"/>
       <c r="Q196" s="5" t="n"/>
+      <c r="R196" s="5" t="n"/>
+      <c r="S196" s="5" t="n"/>
+      <c r="T196" s="5" t="n"/>
+      <c r="U196" s="5" t="n"/>
+      <c r="V196" s="5" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
@@ -5214,9 +6222,14 @@
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="5" t="n"/>
       <c r="N197" s="5" t="n"/>
-      <c r="O197" s="5" t="n"/>
+      <c r="O197" s="14" t="n"/>
       <c r="P197" s="5" t="n"/>
       <c r="Q197" s="5" t="n"/>
+      <c r="R197" s="5" t="n"/>
+      <c r="S197" s="5" t="n"/>
+      <c r="T197" s="5" t="n"/>
+      <c r="U197" s="5" t="n"/>
+      <c r="V197" s="5" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n"/>
@@ -5236,9 +6249,14 @@
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="5" t="n"/>
       <c r="N198" s="5" t="n"/>
-      <c r="O198" s="5" t="n"/>
+      <c r="O198" s="14" t="n"/>
       <c r="P198" s="5" t="n"/>
       <c r="Q198" s="5" t="n"/>
+      <c r="R198" s="5" t="n"/>
+      <c r="S198" s="5" t="n"/>
+      <c r="T198" s="5" t="n"/>
+      <c r="U198" s="5" t="n"/>
+      <c r="V198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
@@ -5258,9 +6276,14 @@
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="5" t="n"/>
       <c r="N199" s="5" t="n"/>
-      <c r="O199" s="5" t="n"/>
+      <c r="O199" s="14" t="n"/>
       <c r="P199" s="5" t="n"/>
       <c r="Q199" s="5" t="n"/>
+      <c r="R199" s="5" t="n"/>
+      <c r="S199" s="5" t="n"/>
+      <c r="T199" s="5" t="n"/>
+      <c r="U199" s="5" t="n"/>
+      <c r="V199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
@@ -5280,9 +6303,14 @@
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="5" t="n"/>
       <c r="N200" s="5" t="n"/>
-      <c r="O200" s="5" t="n"/>
+      <c r="O200" s="14" t="n"/>
       <c r="P200" s="5" t="n"/>
       <c r="Q200" s="5" t="n"/>
+      <c r="R200" s="5" t="n"/>
+      <c r="S200" s="5" t="n"/>
+      <c r="T200" s="5" t="n"/>
+      <c r="U200" s="5" t="n"/>
+      <c r="V200" s="5" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n"/>
@@ -5302,9 +6330,14 @@
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="5" t="n"/>
       <c r="N201" s="5" t="n"/>
-      <c r="O201" s="5" t="n"/>
+      <c r="O201" s="14" t="n"/>
       <c r="P201" s="5" t="n"/>
       <c r="Q201" s="5" t="n"/>
+      <c r="R201" s="5" t="n"/>
+      <c r="S201" s="5" t="n"/>
+      <c r="T201" s="5" t="n"/>
+      <c r="U201" s="5" t="n"/>
+      <c r="V201" s="5" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n"/>
@@ -5324,9 +6357,14 @@
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="5" t="n"/>
       <c r="N202" s="5" t="n"/>
-      <c r="O202" s="5" t="n"/>
+      <c r="O202" s="14" t="n"/>
       <c r="P202" s="5" t="n"/>
       <c r="Q202" s="5" t="n"/>
+      <c r="R202" s="5" t="n"/>
+      <c r="S202" s="5" t="n"/>
+      <c r="T202" s="5" t="n"/>
+      <c r="U202" s="5" t="n"/>
+      <c r="V202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n"/>
@@ -5346,9 +6384,14 @@
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="5" t="n"/>
       <c r="N203" s="5" t="n"/>
-      <c r="O203" s="5" t="n"/>
+      <c r="O203" s="14" t="n"/>
       <c r="P203" s="5" t="n"/>
       <c r="Q203" s="5" t="n"/>
+      <c r="R203" s="5" t="n"/>
+      <c r="S203" s="5" t="n"/>
+      <c r="T203" s="5" t="n"/>
+      <c r="U203" s="5" t="n"/>
+      <c r="V203" s="5" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n"/>
@@ -5368,9 +6411,14 @@
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="5" t="n"/>
       <c r="N204" s="5" t="n"/>
-      <c r="O204" s="5" t="n"/>
+      <c r="O204" s="14" t="n"/>
       <c r="P204" s="5" t="n"/>
       <c r="Q204" s="5" t="n"/>
+      <c r="R204" s="5" t="n"/>
+      <c r="S204" s="5" t="n"/>
+      <c r="T204" s="5" t="n"/>
+      <c r="U204" s="5" t="n"/>
+      <c r="V204" s="5" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="n"/>
@@ -5390,9 +6438,14 @@
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="5" t="n"/>
       <c r="N205" s="5" t="n"/>
-      <c r="O205" s="5" t="n"/>
+      <c r="O205" s="14" t="n"/>
       <c r="P205" s="5" t="n"/>
       <c r="Q205" s="5" t="n"/>
+      <c r="R205" s="5" t="n"/>
+      <c r="S205" s="5" t="n"/>
+      <c r="T205" s="5" t="n"/>
+      <c r="U205" s="5" t="n"/>
+      <c r="V205" s="5" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="n"/>
@@ -5412,9 +6465,14 @@
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="5" t="n"/>
       <c r="N206" s="5" t="n"/>
-      <c r="O206" s="5" t="n"/>
+      <c r="O206" s="14" t="n"/>
       <c r="P206" s="5" t="n"/>
       <c r="Q206" s="5" t="n"/>
+      <c r="R206" s="5" t="n"/>
+      <c r="S206" s="5" t="n"/>
+      <c r="T206" s="5" t="n"/>
+      <c r="U206" s="5" t="n"/>
+      <c r="V206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="n"/>
@@ -5434,9 +6492,14 @@
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="5" t="n"/>
       <c r="N207" s="5" t="n"/>
-      <c r="O207" s="5" t="n"/>
+      <c r="O207" s="14" t="n"/>
       <c r="P207" s="5" t="n"/>
       <c r="Q207" s="5" t="n"/>
+      <c r="R207" s="5" t="n"/>
+      <c r="S207" s="5" t="n"/>
+      <c r="T207" s="5" t="n"/>
+      <c r="U207" s="5" t="n"/>
+      <c r="V207" s="5" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="n"/>
@@ -5456,9 +6519,14 @@
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="5" t="n"/>
       <c r="N208" s="5" t="n"/>
-      <c r="O208" s="5" t="n"/>
+      <c r="O208" s="14" t="n"/>
       <c r="P208" s="5" t="n"/>
       <c r="Q208" s="5" t="n"/>
+      <c r="R208" s="5" t="n"/>
+      <c r="S208" s="5" t="n"/>
+      <c r="T208" s="5" t="n"/>
+      <c r="U208" s="5" t="n"/>
+      <c r="V208" s="5" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n"/>
@@ -5478,9 +6546,14 @@
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="5" t="n"/>
       <c r="N209" s="5" t="n"/>
-      <c r="O209" s="5" t="n"/>
+      <c r="O209" s="14" t="n"/>
       <c r="P209" s="5" t="n"/>
       <c r="Q209" s="5" t="n"/>
+      <c r="R209" s="5" t="n"/>
+      <c r="S209" s="5" t="n"/>
+      <c r="T209" s="5" t="n"/>
+      <c r="U209" s="5" t="n"/>
+      <c r="V209" s="5" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n"/>
@@ -5500,9 +6573,14 @@
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="5" t="n"/>
       <c r="N210" s="5" t="n"/>
-      <c r="O210" s="5" t="n"/>
+      <c r="O210" s="14" t="n"/>
       <c r="P210" s="5" t="n"/>
       <c r="Q210" s="5" t="n"/>
+      <c r="R210" s="5" t="n"/>
+      <c r="S210" s="5" t="n"/>
+      <c r="T210" s="5" t="n"/>
+      <c r="U210" s="5" t="n"/>
+      <c r="V210" s="5" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n"/>
@@ -5522,9 +6600,14 @@
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="5" t="n"/>
       <c r="N211" s="5" t="n"/>
-      <c r="O211" s="5" t="n"/>
+      <c r="O211" s="14" t="n"/>
       <c r="P211" s="5" t="n"/>
       <c r="Q211" s="5" t="n"/>
+      <c r="R211" s="5" t="n"/>
+      <c r="S211" s="5" t="n"/>
+      <c r="T211" s="5" t="n"/>
+      <c r="U211" s="5" t="n"/>
+      <c r="V211" s="5" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n"/>
@@ -5544,9 +6627,14 @@
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="5" t="n"/>
       <c r="N212" s="5" t="n"/>
-      <c r="O212" s="5" t="n"/>
+      <c r="O212" s="14" t="n"/>
       <c r="P212" s="5" t="n"/>
       <c r="Q212" s="5" t="n"/>
+      <c r="R212" s="5" t="n"/>
+      <c r="S212" s="5" t="n"/>
+      <c r="T212" s="5" t="n"/>
+      <c r="U212" s="5" t="n"/>
+      <c r="V212" s="5" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="n"/>
@@ -5566,9 +6654,14 @@
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="5" t="n"/>
       <c r="N213" s="5" t="n"/>
-      <c r="O213" s="5" t="n"/>
+      <c r="O213" s="14" t="n"/>
       <c r="P213" s="5" t="n"/>
       <c r="Q213" s="5" t="n"/>
+      <c r="R213" s="5" t="n"/>
+      <c r="S213" s="5" t="n"/>
+      <c r="T213" s="5" t="n"/>
+      <c r="U213" s="5" t="n"/>
+      <c r="V213" s="5" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="n"/>
@@ -5588,9 +6681,14 @@
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="5" t="n"/>
       <c r="N214" s="5" t="n"/>
-      <c r="O214" s="5" t="n"/>
+      <c r="O214" s="14" t="n"/>
       <c r="P214" s="5" t="n"/>
       <c r="Q214" s="5" t="n"/>
+      <c r="R214" s="5" t="n"/>
+      <c r="S214" s="5" t="n"/>
+      <c r="T214" s="5" t="n"/>
+      <c r="U214" s="5" t="n"/>
+      <c r="V214" s="5" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="n"/>
@@ -5610,9 +6708,14 @@
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="5" t="n"/>
       <c r="N215" s="5" t="n"/>
-      <c r="O215" s="5" t="n"/>
+      <c r="O215" s="14" t="n"/>
       <c r="P215" s="5" t="n"/>
       <c r="Q215" s="5" t="n"/>
+      <c r="R215" s="5" t="n"/>
+      <c r="S215" s="5" t="n"/>
+      <c r="T215" s="5" t="n"/>
+      <c r="U215" s="5" t="n"/>
+      <c r="V215" s="5" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n"/>
@@ -5632,9 +6735,14 @@
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="5" t="n"/>
       <c r="N216" s="5" t="n"/>
-      <c r="O216" s="5" t="n"/>
+      <c r="O216" s="14" t="n"/>
       <c r="P216" s="5" t="n"/>
       <c r="Q216" s="5" t="n"/>
+      <c r="R216" s="5" t="n"/>
+      <c r="S216" s="5" t="n"/>
+      <c r="T216" s="5" t="n"/>
+      <c r="U216" s="5" t="n"/>
+      <c r="V216" s="5" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n"/>
@@ -5654,9 +6762,14 @@
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="5" t="n"/>
       <c r="N217" s="5" t="n"/>
-      <c r="O217" s="5" t="n"/>
+      <c r="O217" s="14" t="n"/>
       <c r="P217" s="5" t="n"/>
       <c r="Q217" s="5" t="n"/>
+      <c r="R217" s="5" t="n"/>
+      <c r="S217" s="5" t="n"/>
+      <c r="T217" s="5" t="n"/>
+      <c r="U217" s="5" t="n"/>
+      <c r="V217" s="5" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="n"/>
@@ -5676,9 +6789,14 @@
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="5" t="n"/>
       <c r="N218" s="5" t="n"/>
-      <c r="O218" s="5" t="n"/>
+      <c r="O218" s="14" t="n"/>
       <c r="P218" s="5" t="n"/>
       <c r="Q218" s="5" t="n"/>
+      <c r="R218" s="5" t="n"/>
+      <c r="S218" s="5" t="n"/>
+      <c r="T218" s="5" t="n"/>
+      <c r="U218" s="5" t="n"/>
+      <c r="V218" s="5" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="n"/>
@@ -5698,9 +6816,14 @@
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="5" t="n"/>
       <c r="N219" s="5" t="n"/>
-      <c r="O219" s="5" t="n"/>
+      <c r="O219" s="14" t="n"/>
       <c r="P219" s="5" t="n"/>
       <c r="Q219" s="5" t="n"/>
+      <c r="R219" s="5" t="n"/>
+      <c r="S219" s="5" t="n"/>
+      <c r="T219" s="5" t="n"/>
+      <c r="U219" s="5" t="n"/>
+      <c r="V219" s="5" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="n"/>
@@ -5720,9 +6843,14 @@
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="5" t="n"/>
       <c r="N220" s="5" t="n"/>
-      <c r="O220" s="5" t="n"/>
+      <c r="O220" s="14" t="n"/>
       <c r="P220" s="5" t="n"/>
       <c r="Q220" s="5" t="n"/>
+      <c r="R220" s="5" t="n"/>
+      <c r="S220" s="5" t="n"/>
+      <c r="T220" s="5" t="n"/>
+      <c r="U220" s="5" t="n"/>
+      <c r="V220" s="5" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n"/>
@@ -5742,9 +6870,14 @@
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="5" t="n"/>
       <c r="N221" s="5" t="n"/>
-      <c r="O221" s="5" t="n"/>
+      <c r="O221" s="14" t="n"/>
       <c r="P221" s="5" t="n"/>
       <c r="Q221" s="5" t="n"/>
+      <c r="R221" s="5" t="n"/>
+      <c r="S221" s="5" t="n"/>
+      <c r="T221" s="5" t="n"/>
+      <c r="U221" s="5" t="n"/>
+      <c r="V221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n"/>
@@ -5764,9 +6897,14 @@
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="5" t="n"/>
       <c r="N222" s="5" t="n"/>
-      <c r="O222" s="5" t="n"/>
+      <c r="O222" s="14" t="n"/>
       <c r="P222" s="5" t="n"/>
       <c r="Q222" s="5" t="n"/>
+      <c r="R222" s="5" t="n"/>
+      <c r="S222" s="5" t="n"/>
+      <c r="T222" s="5" t="n"/>
+      <c r="U222" s="5" t="n"/>
+      <c r="V222" s="5" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="n"/>
@@ -5786,9 +6924,14 @@
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="5" t="n"/>
       <c r="N223" s="5" t="n"/>
-      <c r="O223" s="5" t="n"/>
+      <c r="O223" s="14" t="n"/>
       <c r="P223" s="5" t="n"/>
       <c r="Q223" s="5" t="n"/>
+      <c r="R223" s="5" t="n"/>
+      <c r="S223" s="5" t="n"/>
+      <c r="T223" s="5" t="n"/>
+      <c r="U223" s="5" t="n"/>
+      <c r="V223" s="5" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n"/>
@@ -5808,9 +6951,14 @@
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="5" t="n"/>
       <c r="N224" s="5" t="n"/>
-      <c r="O224" s="5" t="n"/>
+      <c r="O224" s="14" t="n"/>
       <c r="P224" s="5" t="n"/>
       <c r="Q224" s="5" t="n"/>
+      <c r="R224" s="5" t="n"/>
+      <c r="S224" s="5" t="n"/>
+      <c r="T224" s="5" t="n"/>
+      <c r="U224" s="5" t="n"/>
+      <c r="V224" s="5" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n"/>
@@ -5830,9 +6978,14 @@
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="5" t="n"/>
       <c r="N225" s="5" t="n"/>
-      <c r="O225" s="5" t="n"/>
+      <c r="O225" s="14" t="n"/>
       <c r="P225" s="5" t="n"/>
       <c r="Q225" s="5" t="n"/>
+      <c r="R225" s="5" t="n"/>
+      <c r="S225" s="5" t="n"/>
+      <c r="T225" s="5" t="n"/>
+      <c r="U225" s="5" t="n"/>
+      <c r="V225" s="5" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n"/>
@@ -5852,9 +7005,14 @@
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="5" t="n"/>
       <c r="N226" s="5" t="n"/>
-      <c r="O226" s="5" t="n"/>
+      <c r="O226" s="14" t="n"/>
       <c r="P226" s="5" t="n"/>
       <c r="Q226" s="5" t="n"/>
+      <c r="R226" s="5" t="n"/>
+      <c r="S226" s="5" t="n"/>
+      <c r="T226" s="5" t="n"/>
+      <c r="U226" s="5" t="n"/>
+      <c r="V226" s="5" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="n"/>
@@ -5874,9 +7032,14 @@
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="5" t="n"/>
       <c r="N227" s="5" t="n"/>
-      <c r="O227" s="5" t="n"/>
+      <c r="O227" s="14" t="n"/>
       <c r="P227" s="5" t="n"/>
       <c r="Q227" s="5" t="n"/>
+      <c r="R227" s="5" t="n"/>
+      <c r="S227" s="5" t="n"/>
+      <c r="T227" s="5" t="n"/>
+      <c r="U227" s="5" t="n"/>
+      <c r="V227" s="5" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="n"/>
@@ -5896,9 +7059,14 @@
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="5" t="n"/>
       <c r="N228" s="5" t="n"/>
-      <c r="O228" s="5" t="n"/>
+      <c r="O228" s="14" t="n"/>
       <c r="P228" s="5" t="n"/>
       <c r="Q228" s="5" t="n"/>
+      <c r="R228" s="5" t="n"/>
+      <c r="S228" s="5" t="n"/>
+      <c r="T228" s="5" t="n"/>
+      <c r="U228" s="5" t="n"/>
+      <c r="V228" s="5" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n"/>
@@ -5918,9 +7086,14 @@
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="5" t="n"/>
       <c r="N229" s="5" t="n"/>
-      <c r="O229" s="5" t="n"/>
+      <c r="O229" s="14" t="n"/>
       <c r="P229" s="5" t="n"/>
       <c r="Q229" s="5" t="n"/>
+      <c r="R229" s="5" t="n"/>
+      <c r="S229" s="5" t="n"/>
+      <c r="T229" s="5" t="n"/>
+      <c r="U229" s="5" t="n"/>
+      <c r="V229" s="5" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n"/>
@@ -5940,9 +7113,14 @@
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="5" t="n"/>
       <c r="N230" s="5" t="n"/>
-      <c r="O230" s="5" t="n"/>
+      <c r="O230" s="14" t="n"/>
       <c r="P230" s="5" t="n"/>
       <c r="Q230" s="5" t="n"/>
+      <c r="R230" s="5" t="n"/>
+      <c r="S230" s="5" t="n"/>
+      <c r="T230" s="5" t="n"/>
+      <c r="U230" s="5" t="n"/>
+      <c r="V230" s="5" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="n"/>
@@ -5962,9 +7140,14 @@
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="5" t="n"/>
       <c r="N231" s="5" t="n"/>
-      <c r="O231" s="5" t="n"/>
+      <c r="O231" s="14" t="n"/>
       <c r="P231" s="5" t="n"/>
       <c r="Q231" s="5" t="n"/>
+      <c r="R231" s="5" t="n"/>
+      <c r="S231" s="5" t="n"/>
+      <c r="T231" s="5" t="n"/>
+      <c r="U231" s="5" t="n"/>
+      <c r="V231" s="5" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n"/>
@@ -5984,9 +7167,14 @@
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="5" t="n"/>
       <c r="N232" s="5" t="n"/>
-      <c r="O232" s="5" t="n"/>
+      <c r="O232" s="14" t="n"/>
       <c r="P232" s="5" t="n"/>
       <c r="Q232" s="5" t="n"/>
+      <c r="R232" s="5" t="n"/>
+      <c r="S232" s="5" t="n"/>
+      <c r="T232" s="5" t="n"/>
+      <c r="U232" s="5" t="n"/>
+      <c r="V232" s="5" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n"/>
@@ -6006,9 +7194,14 @@
       <c r="L233" s="5" t="n"/>
       <c r="M233" s="5" t="n"/>
       <c r="N233" s="5" t="n"/>
-      <c r="O233" s="5" t="n"/>
+      <c r="O233" s="14" t="n"/>
       <c r="P233" s="5" t="n"/>
       <c r="Q233" s="5" t="n"/>
+      <c r="R233" s="5" t="n"/>
+      <c r="S233" s="5" t="n"/>
+      <c r="T233" s="5" t="n"/>
+      <c r="U233" s="5" t="n"/>
+      <c r="V233" s="5" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n"/>
@@ -6028,9 +7221,14 @@
       <c r="L234" s="5" t="n"/>
       <c r="M234" s="5" t="n"/>
       <c r="N234" s="5" t="n"/>
-      <c r="O234" s="5" t="n"/>
+      <c r="O234" s="14" t="n"/>
       <c r="P234" s="5" t="n"/>
       <c r="Q234" s="5" t="n"/>
+      <c r="R234" s="5" t="n"/>
+      <c r="S234" s="5" t="n"/>
+      <c r="T234" s="5" t="n"/>
+      <c r="U234" s="5" t="n"/>
+      <c r="V234" s="5" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="n"/>
@@ -6050,9 +7248,14 @@
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="5" t="n"/>
       <c r="N235" s="5" t="n"/>
-      <c r="O235" s="5" t="n"/>
+      <c r="O235" s="14" t="n"/>
       <c r="P235" s="5" t="n"/>
       <c r="Q235" s="5" t="n"/>
+      <c r="R235" s="5" t="n"/>
+      <c r="S235" s="5" t="n"/>
+      <c r="T235" s="5" t="n"/>
+      <c r="U235" s="5" t="n"/>
+      <c r="V235" s="5" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="n"/>
@@ -6072,9 +7275,14 @@
       <c r="L236" s="5" t="n"/>
       <c r="M236" s="5" t="n"/>
       <c r="N236" s="5" t="n"/>
-      <c r="O236" s="5" t="n"/>
+      <c r="O236" s="14" t="n"/>
       <c r="P236" s="5" t="n"/>
       <c r="Q236" s="5" t="n"/>
+      <c r="R236" s="5" t="n"/>
+      <c r="S236" s="5" t="n"/>
+      <c r="T236" s="5" t="n"/>
+      <c r="U236" s="5" t="n"/>
+      <c r="V236" s="5" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="n"/>
@@ -6094,9 +7302,14 @@
       <c r="L237" s="5" t="n"/>
       <c r="M237" s="5" t="n"/>
       <c r="N237" s="5" t="n"/>
-      <c r="O237" s="5" t="n"/>
+      <c r="O237" s="14" t="n"/>
       <c r="P237" s="5" t="n"/>
       <c r="Q237" s="5" t="n"/>
+      <c r="R237" s="5" t="n"/>
+      <c r="S237" s="5" t="n"/>
+      <c r="T237" s="5" t="n"/>
+      <c r="U237" s="5" t="n"/>
+      <c r="V237" s="5" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="n"/>
@@ -6116,9 +7329,14 @@
       <c r="L238" s="5" t="n"/>
       <c r="M238" s="5" t="n"/>
       <c r="N238" s="5" t="n"/>
-      <c r="O238" s="5" t="n"/>
+      <c r="O238" s="14" t="n"/>
       <c r="P238" s="5" t="n"/>
       <c r="Q238" s="5" t="n"/>
+      <c r="R238" s="5" t="n"/>
+      <c r="S238" s="5" t="n"/>
+      <c r="T238" s="5" t="n"/>
+      <c r="U238" s="5" t="n"/>
+      <c r="V238" s="5" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n"/>
@@ -6138,9 +7356,14 @@
       <c r="L239" s="5" t="n"/>
       <c r="M239" s="5" t="n"/>
       <c r="N239" s="5" t="n"/>
-      <c r="O239" s="5" t="n"/>
+      <c r="O239" s="14" t="n"/>
       <c r="P239" s="5" t="n"/>
       <c r="Q239" s="5" t="n"/>
+      <c r="R239" s="5" t="n"/>
+      <c r="S239" s="5" t="n"/>
+      <c r="T239" s="5" t="n"/>
+      <c r="U239" s="5" t="n"/>
+      <c r="V239" s="5" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="n"/>
@@ -6160,9 +7383,14 @@
       <c r="L240" s="5" t="n"/>
       <c r="M240" s="5" t="n"/>
       <c r="N240" s="5" t="n"/>
-      <c r="O240" s="5" t="n"/>
+      <c r="O240" s="14" t="n"/>
       <c r="P240" s="5" t="n"/>
       <c r="Q240" s="5" t="n"/>
+      <c r="R240" s="5" t="n"/>
+      <c r="S240" s="5" t="n"/>
+      <c r="T240" s="5" t="n"/>
+      <c r="U240" s="5" t="n"/>
+      <c r="V240" s="5" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="5" t="n"/>
@@ -6182,9 +7410,14 @@
       <c r="L241" s="5" t="n"/>
       <c r="M241" s="5" t="n"/>
       <c r="N241" s="5" t="n"/>
-      <c r="O241" s="5" t="n"/>
+      <c r="O241" s="14" t="n"/>
       <c r="P241" s="5" t="n"/>
       <c r="Q241" s="5" t="n"/>
+      <c r="R241" s="5" t="n"/>
+      <c r="S241" s="5" t="n"/>
+      <c r="T241" s="5" t="n"/>
+      <c r="U241" s="5" t="n"/>
+      <c r="V241" s="5" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="n"/>
@@ -6204,9 +7437,14 @@
       <c r="L242" s="5" t="n"/>
       <c r="M242" s="5" t="n"/>
       <c r="N242" s="5" t="n"/>
-      <c r="O242" s="5" t="n"/>
+      <c r="O242" s="14" t="n"/>
       <c r="P242" s="5" t="n"/>
       <c r="Q242" s="5" t="n"/>
+      <c r="R242" s="5" t="n"/>
+      <c r="S242" s="5" t="n"/>
+      <c r="T242" s="5" t="n"/>
+      <c r="U242" s="5" t="n"/>
+      <c r="V242" s="5" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="5" t="n"/>
@@ -6226,9 +7464,14 @@
       <c r="L243" s="5" t="n"/>
       <c r="M243" s="5" t="n"/>
       <c r="N243" s="5" t="n"/>
-      <c r="O243" s="5" t="n"/>
+      <c r="O243" s="14" t="n"/>
       <c r="P243" s="5" t="n"/>
       <c r="Q243" s="5" t="n"/>
+      <c r="R243" s="5" t="n"/>
+      <c r="S243" s="5" t="n"/>
+      <c r="T243" s="5" t="n"/>
+      <c r="U243" s="5" t="n"/>
+      <c r="V243" s="5" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="n"/>
@@ -6248,9 +7491,14 @@
       <c r="L244" s="5" t="n"/>
       <c r="M244" s="5" t="n"/>
       <c r="N244" s="5" t="n"/>
-      <c r="O244" s="5" t="n"/>
+      <c r="O244" s="14" t="n"/>
       <c r="P244" s="5" t="n"/>
       <c r="Q244" s="5" t="n"/>
+      <c r="R244" s="5" t="n"/>
+      <c r="S244" s="5" t="n"/>
+      <c r="T244" s="5" t="n"/>
+      <c r="U244" s="5" t="n"/>
+      <c r="V244" s="5" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="n"/>
@@ -6270,9 +7518,14 @@
       <c r="L245" s="5" t="n"/>
       <c r="M245" s="5" t="n"/>
       <c r="N245" s="5" t="n"/>
-      <c r="O245" s="5" t="n"/>
+      <c r="O245" s="14" t="n"/>
       <c r="P245" s="5" t="n"/>
       <c r="Q245" s="5" t="n"/>
+      <c r="R245" s="5" t="n"/>
+      <c r="S245" s="5" t="n"/>
+      <c r="T245" s="5" t="n"/>
+      <c r="U245" s="5" t="n"/>
+      <c r="V245" s="5" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="5" t="n"/>
@@ -6292,9 +7545,14 @@
       <c r="L246" s="5" t="n"/>
       <c r="M246" s="5" t="n"/>
       <c r="N246" s="5" t="n"/>
-      <c r="O246" s="5" t="n"/>
+      <c r="O246" s="14" t="n"/>
       <c r="P246" s="5" t="n"/>
       <c r="Q246" s="5" t="n"/>
+      <c r="R246" s="5" t="n"/>
+      <c r="S246" s="5" t="n"/>
+      <c r="T246" s="5" t="n"/>
+      <c r="U246" s="5" t="n"/>
+      <c r="V246" s="5" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n"/>
@@ -6314,9 +7572,14 @@
       <c r="L247" s="5" t="n"/>
       <c r="M247" s="5" t="n"/>
       <c r="N247" s="5" t="n"/>
-      <c r="O247" s="5" t="n"/>
+      <c r="O247" s="14" t="n"/>
       <c r="P247" s="5" t="n"/>
       <c r="Q247" s="5" t="n"/>
+      <c r="R247" s="5" t="n"/>
+      <c r="S247" s="5" t="n"/>
+      <c r="T247" s="5" t="n"/>
+      <c r="U247" s="5" t="n"/>
+      <c r="V247" s="5" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n"/>
@@ -6336,9 +7599,14 @@
       <c r="L248" s="5" t="n"/>
       <c r="M248" s="5" t="n"/>
       <c r="N248" s="5" t="n"/>
-      <c r="O248" s="5" t="n"/>
+      <c r="O248" s="14" t="n"/>
       <c r="P248" s="5" t="n"/>
       <c r="Q248" s="5" t="n"/>
+      <c r="R248" s="5" t="n"/>
+      <c r="S248" s="5" t="n"/>
+      <c r="T248" s="5" t="n"/>
+      <c r="U248" s="5" t="n"/>
+      <c r="V248" s="5" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="5" t="n"/>
@@ -6358,9 +7626,14 @@
       <c r="L249" s="5" t="n"/>
       <c r="M249" s="5" t="n"/>
       <c r="N249" s="5" t="n"/>
-      <c r="O249" s="5" t="n"/>
+      <c r="O249" s="14" t="n"/>
       <c r="P249" s="5" t="n"/>
       <c r="Q249" s="5" t="n"/>
+      <c r="R249" s="5" t="n"/>
+      <c r="S249" s="5" t="n"/>
+      <c r="T249" s="5" t="n"/>
+      <c r="U249" s="5" t="n"/>
+      <c r="V249" s="5" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="5" t="n"/>
@@ -6380,9 +7653,14 @@
       <c r="L250" s="5" t="n"/>
       <c r="M250" s="5" t="n"/>
       <c r="N250" s="5" t="n"/>
-      <c r="O250" s="5" t="n"/>
+      <c r="O250" s="14" t="n"/>
       <c r="P250" s="5" t="n"/>
       <c r="Q250" s="5" t="n"/>
+      <c r="R250" s="5" t="n"/>
+      <c r="S250" s="5" t="n"/>
+      <c r="T250" s="5" t="n"/>
+      <c r="U250" s="5" t="n"/>
+      <c r="V250" s="5" t="n"/>
     </row>
     <row r="251">
       <c r="C251" s="2" t="n"/>
@@ -10885,13 +12163,27 @@
       <c r="F1000" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:V1"/>
   <conditionalFormatting sqref="A2:Q250">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N2="Yes"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>$P2="Needs Review"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:V250">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
+      <formula>$R2="Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>$T2="Needs Review"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="0">
+      <formula>$R2="Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>$T2="Needs Review"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
@@ -10901,25 +12193,25 @@
     <dataValidation sqref="F2:F250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: AmbitionBox, Glassdoor, LinkedIn, X / Twitter, Reddit, Quora, YouTube, Google Reviews, Indeed" promptTitle="F" prompt="Where it was posted." type="list">
       <formula1>"AmbitionBox,Glassdoor,LinkedIn,X / Twitter,Reddit,Quora,YouTube,Google Reviews,Indeed"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Positive, Neutral, Mixed, Negative" promptTitle="G" prompt="Tag the post, not your view of the company. Mixed = real praise AND a real complaint." type="list">
+    <dataValidation sqref="H2:H250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Positive, Neutral, Mixed, Negative" promptTitle="H" prompt="Tag the post, not your view of the company. Mixed = real praise AND a real complaint." type="list">
       <formula1>"Positive,Neutral,Mixed,Negative"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Culture, Management, Compensation, Appraisals, Payroll Delay, Interviews, Work Hours, Workload, Onboarding, Exits, Layoffs, Safety / Legal, Growth, Facilities, Transparency, Job Security" promptTitle="H" prompt="One topic. See the Guide tab." type="list">
+    <dataValidation sqref="I2:I250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Culture, Management, Compensation, Appraisals, Payroll Delay, Interviews, Work Hours, Workload, Onboarding, Exits, Layoffs, Safety / Legal, Growth, Facilities, Transparency, Job Security" promptTitle="I" prompt="One topic. See the Guide tab." type="list">
       <formula1>"Culture,Management,Compensation,Appraisals,Payroll Delay,Interviews,Work Hours,Workload,Onboarding,Exits,Layoffs,Safety / Legal,Growth,Facilities,Transparency,Job Security"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Current Employee, Ex-Employee, Candidate, Intern, Contractor, Anonymous, Unknown" promptTitle="K" prompt="Only if the post states or clearly implies it." type="list">
+    <dataValidation sqref="M2:M250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Current Employee, Ex-Employee, Candidate, Intern, Contractor, Anonymous, Unknown" promptTitle="M" prompt="Only if the post states or clearly implies it." type="list">
       <formula1>"Current Employee,Ex-Employee,Candidate,Intern,Contractor,Anonymous,Unknown"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Yes, No" promptTitle="M" prompt="Does the post name an individual?" type="list">
+    <dataValidation sqref="Q2:Q250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Yes, No" promptTitle="Q" prompt="Does the post name an individual?" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Yes, No" promptTitle="N" prompt="One of the five triggers on the Guide tab." type="list">
+    <dataValidation sqref="R2:R250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Yes, No" promptTitle="R" prompt="One of the five triggers on the Guide tab." type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Names Individual, Harassment / Safety, Non-payment, Legal / Regulatory, Public Escalation Risk" promptTitle="O" prompt="Which trigger fired." type="list">
+    <dataValidation sqref="S2:S250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Names Individual, Harassment / Safety, Non-payment, Legal / Regulatory, Public Escalation Risk" promptTitle="S" prompt="Which trigger fired." type="list">
       <formula1>"Names Individual,Harassment / Safety,Non-payment,Legal / Regulatory,Public Escalation Risk"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Needs Review, Reviewed, Escalated, Closed, Out of Scope" promptTitle="P" prompt="Needs Review until tagged." type="list">
+    <dataValidation sqref="T2:T250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: Needs Review, Reviewed, Escalated, Closed, Out of Scope" promptTitle="T" prompt="Needs Review until tagged." type="list">
       <formula1>"Needs Review,Reviewed,Escalated,Closed,Out of Scope"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10928,1344 +12220,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H120"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="12" customWidth="1" style="3" min="1" max="1"/>
-    <col width="20" customWidth="1" style="3" min="2" max="2"/>
-    <col width="16" customWidth="1" style="3" min="3" max="3"/>
-    <col width="16" customWidth="1" style="3" min="4" max="4"/>
-    <col width="16" customWidth="1" style="3" min="5" max="5"/>
-    <col width="16" customWidth="1" style="3" min="6" max="6"/>
-    <col width="14" customWidth="1" style="3" min="7" max="7"/>
-    <col width="40" customWidth="1" style="3" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" s="3">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Week Of</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>AmbitionBox Rating</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>AmbitionBox Reviews Count</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Glassdoor Rating</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Glassdoor Reviews Count</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Last Checked Date</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>RK Group</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>ambitionbox: SCOPE: Bengaluru-filtered, not all locations. GENDER SPLIT: women 1.7 (7 reviews) vs men 3.5 (19) - a 1.8 point gap. Skill Development 2.3. | glassdoor: SCOPE: Bangalore-filtered view only, not all locations - 16 reviews is the Bangalore subset. 69% positive business outlook. Glassdoor classifies RK Group as Manufacturing; industry average 3.5. All-locations figure still needed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>RK World Infocom</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>ambitionbox: All locations. AmbitionBox flags 23% below industry average. Women 3.0 (16) vs men 3.2 (29). Skill Development 3.4; Work Satisfaction 3.1. | glassdoor: 20 written reviews. Diversity and inclusion 3.9; Senior management 3.7. Company size 201-500 employees, private. Employer Profile NOT claimed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Robust Kommerce</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>glassdoor: Listed on Glassdoor as plain 'Robust' (employer id 1882698) - identity still to be confirmed as Robust Kommerce. Diversity and inclusion 4.2; Senior management 3.1. Company size 51-200 employees. Employer Profile NOT claimed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Westbury Kommerce</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>ambitionbox: All locations. Highly rated for job security; critically rated for promotions, work satisfaction, skill development. 142 salary entries, 14 followers. | glassdoor: Diversity and inclusion 2.0; Senior management 1.0; 'Be the first to recommend' = 0% recommend</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="5" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="5" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="5" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="7" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="5" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="5" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="5" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="7" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="7" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="5" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="7" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="5" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="7" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="5" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="n"/>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="5" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="7" t="n"/>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="5" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="7" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="7" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="5" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="7" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="7" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="5" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="7" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="5" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="7" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="7" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="5" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="7" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="5" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="n"/>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="7" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="5" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="n"/>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="7" t="n"/>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="5" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="n"/>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="6" t="n"/>
-      <c r="H64" s="5" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="n"/>
-      <c r="B65" s="5" t="n"/>
-      <c r="C65" s="7" t="n"/>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="7" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="5" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="n"/>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="7" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="5" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="n"/>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="7" t="n"/>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="6" t="n"/>
-      <c r="H67" s="5" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="n"/>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="7" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="7" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="6" t="n"/>
-      <c r="H68" s="5" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="n"/>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="7" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="5" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="n"/>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="5" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="7" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="7" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="5" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="n"/>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="7" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="7" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="6" t="n"/>
-      <c r="H72" s="5" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="n"/>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="7" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="5" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="n"/>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="7" t="n"/>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="7" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="6" t="n"/>
-      <c r="H74" s="5" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="n"/>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="7" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="6" t="n"/>
-      <c r="H75" s="5" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="n"/>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="7" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="6" t="n"/>
-      <c r="H76" s="5" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="n"/>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="7" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="5" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="n"/>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="7" t="n"/>
-      <c r="D78" s="5" t="n"/>
-      <c r="E78" s="7" t="n"/>
-      <c r="F78" s="5" t="n"/>
-      <c r="G78" s="6" t="n"/>
-      <c r="H78" s="5" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="n"/>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="7" t="n"/>
-      <c r="D79" s="5" t="n"/>
-      <c r="E79" s="7" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="6" t="n"/>
-      <c r="H79" s="5" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="n"/>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="7" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="7" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="6" t="n"/>
-      <c r="H80" s="5" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="n"/>
-      <c r="B81" s="5" t="n"/>
-      <c r="C81" s="7" t="n"/>
-      <c r="D81" s="5" t="n"/>
-      <c r="E81" s="7" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="6" t="n"/>
-      <c r="H81" s="5" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="n"/>
-      <c r="B82" s="5" t="n"/>
-      <c r="C82" s="7" t="n"/>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="6" t="n"/>
-      <c r="H82" s="5" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="n"/>
-      <c r="B83" s="5" t="n"/>
-      <c r="C83" s="7" t="n"/>
-      <c r="D83" s="5" t="n"/>
-      <c r="E83" s="7" t="n"/>
-      <c r="F83" s="5" t="n"/>
-      <c r="G83" s="6" t="n"/>
-      <c r="H83" s="5" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="n"/>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="7" t="n"/>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="7" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="6" t="n"/>
-      <c r="H84" s="5" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="n"/>
-      <c r="B85" s="5" t="n"/>
-      <c r="C85" s="7" t="n"/>
-      <c r="D85" s="5" t="n"/>
-      <c r="E85" s="7" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="G85" s="6" t="n"/>
-      <c r="H85" s="5" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="n"/>
-      <c r="B86" s="5" t="n"/>
-      <c r="C86" s="7" t="n"/>
-      <c r="D86" s="5" t="n"/>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="6" t="n"/>
-      <c r="H86" s="5" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="n"/>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="7" t="n"/>
-      <c r="D87" s="5" t="n"/>
-      <c r="E87" s="7" t="n"/>
-      <c r="F87" s="5" t="n"/>
-      <c r="G87" s="6" t="n"/>
-      <c r="H87" s="5" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="n"/>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="7" t="n"/>
-      <c r="D88" s="5" t="n"/>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="6" t="n"/>
-      <c r="H88" s="5" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="n"/>
-      <c r="B89" s="5" t="n"/>
-      <c r="C89" s="7" t="n"/>
-      <c r="D89" s="5" t="n"/>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="5" t="n"/>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="5" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="n"/>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="7" t="n"/>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="7" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="6" t="n"/>
-      <c r="H90" s="5" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="n"/>
-      <c r="B91" s="5" t="n"/>
-      <c r="C91" s="7" t="n"/>
-      <c r="D91" s="5" t="n"/>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="5" t="n"/>
-      <c r="G91" s="6" t="n"/>
-      <c r="H91" s="5" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="5" t="n"/>
-      <c r="C92" s="7" t="n"/>
-      <c r="D92" s="5" t="n"/>
-      <c r="E92" s="7" t="n"/>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="6" t="n"/>
-      <c r="H92" s="5" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="n"/>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="7" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="7" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="6" t="n"/>
-      <c r="H93" s="5" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="n"/>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="7" t="n"/>
-      <c r="D94" s="5" t="n"/>
-      <c r="E94" s="7" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="6" t="n"/>
-      <c r="H94" s="5" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="n"/>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="7" t="n"/>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="7" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="6" t="n"/>
-      <c r="H95" s="5" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="n"/>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="7" t="n"/>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="7" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="6" t="n"/>
-      <c r="H96" s="5" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="n"/>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="7" t="n"/>
-      <c r="D97" s="5" t="n"/>
-      <c r="E97" s="7" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="6" t="n"/>
-      <c r="H97" s="5" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="n"/>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="7" t="n"/>
-      <c r="D98" s="5" t="n"/>
-      <c r="E98" s="7" t="n"/>
-      <c r="F98" s="5" t="n"/>
-      <c r="G98" s="6" t="n"/>
-      <c r="H98" s="5" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="n"/>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="7" t="n"/>
-      <c r="D99" s="5" t="n"/>
-      <c r="E99" s="7" t="n"/>
-      <c r="F99" s="5" t="n"/>
-      <c r="G99" s="6" t="n"/>
-      <c r="H99" s="5" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="n"/>
-      <c r="B100" s="5" t="n"/>
-      <c r="C100" s="7" t="n"/>
-      <c r="D100" s="5" t="n"/>
-      <c r="E100" s="7" t="n"/>
-      <c r="F100" s="5" t="n"/>
-      <c r="G100" s="6" t="n"/>
-      <c r="H100" s="5" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="n"/>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="7" t="n"/>
-      <c r="D101" s="5" t="n"/>
-      <c r="E101" s="7" t="n"/>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="6" t="n"/>
-      <c r="H101" s="5" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="n"/>
-      <c r="B102" s="5" t="n"/>
-      <c r="C102" s="7" t="n"/>
-      <c r="D102" s="5" t="n"/>
-      <c r="E102" s="7" t="n"/>
-      <c r="F102" s="5" t="n"/>
-      <c r="G102" s="6" t="n"/>
-      <c r="H102" s="5" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="n"/>
-      <c r="B103" s="5" t="n"/>
-      <c r="C103" s="7" t="n"/>
-      <c r="D103" s="5" t="n"/>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="5" t="n"/>
-      <c r="G103" s="6" t="n"/>
-      <c r="H103" s="5" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="n"/>
-      <c r="B104" s="5" t="n"/>
-      <c r="C104" s="7" t="n"/>
-      <c r="D104" s="5" t="n"/>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="6" t="n"/>
-      <c r="H104" s="5" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="n"/>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="7" t="n"/>
-      <c r="D105" s="5" t="n"/>
-      <c r="E105" s="7" t="n"/>
-      <c r="F105" s="5" t="n"/>
-      <c r="G105" s="6" t="n"/>
-      <c r="H105" s="5" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="n"/>
-      <c r="B106" s="5" t="n"/>
-      <c r="C106" s="7" t="n"/>
-      <c r="D106" s="5" t="n"/>
-      <c r="E106" s="7" t="n"/>
-      <c r="F106" s="5" t="n"/>
-      <c r="G106" s="6" t="n"/>
-      <c r="H106" s="5" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="n"/>
-      <c r="B107" s="5" t="n"/>
-      <c r="C107" s="7" t="n"/>
-      <c r="D107" s="5" t="n"/>
-      <c r="E107" s="7" t="n"/>
-      <c r="F107" s="5" t="n"/>
-      <c r="G107" s="6" t="n"/>
-      <c r="H107" s="5" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="n"/>
-      <c r="B108" s="5" t="n"/>
-      <c r="C108" s="7" t="n"/>
-      <c r="D108" s="5" t="n"/>
-      <c r="E108" s="7" t="n"/>
-      <c r="F108" s="5" t="n"/>
-      <c r="G108" s="6" t="n"/>
-      <c r="H108" s="5" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="n"/>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="7" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="7" t="n"/>
-      <c r="F109" s="5" t="n"/>
-      <c r="G109" s="6" t="n"/>
-      <c r="H109" s="5" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="n"/>
-      <c r="B110" s="5" t="n"/>
-      <c r="C110" s="7" t="n"/>
-      <c r="D110" s="5" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="5" t="n"/>
-      <c r="G110" s="6" t="n"/>
-      <c r="H110" s="5" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="n"/>
-      <c r="B111" s="5" t="n"/>
-      <c r="C111" s="7" t="n"/>
-      <c r="D111" s="5" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="5" t="n"/>
-      <c r="G111" s="6" t="n"/>
-      <c r="H111" s="5" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="6" t="n"/>
-      <c r="B112" s="5" t="n"/>
-      <c r="C112" s="7" t="n"/>
-      <c r="D112" s="5" t="n"/>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="5" t="n"/>
-      <c r="G112" s="6" t="n"/>
-      <c r="H112" s="5" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="n"/>
-      <c r="B113" s="5" t="n"/>
-      <c r="C113" s="7" t="n"/>
-      <c r="D113" s="5" t="n"/>
-      <c r="E113" s="7" t="n"/>
-      <c r="F113" s="5" t="n"/>
-      <c r="G113" s="6" t="n"/>
-      <c r="H113" s="5" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="n"/>
-      <c r="B114" s="5" t="n"/>
-      <c r="C114" s="7" t="n"/>
-      <c r="D114" s="5" t="n"/>
-      <c r="E114" s="7" t="n"/>
-      <c r="F114" s="5" t="n"/>
-      <c r="G114" s="6" t="n"/>
-      <c r="H114" s="5" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="n"/>
-      <c r="B115" s="5" t="n"/>
-      <c r="C115" s="7" t="n"/>
-      <c r="D115" s="5" t="n"/>
-      <c r="E115" s="7" t="n"/>
-      <c r="F115" s="5" t="n"/>
-      <c r="G115" s="6" t="n"/>
-      <c r="H115" s="5" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="6" t="n"/>
-      <c r="B116" s="5" t="n"/>
-      <c r="C116" s="7" t="n"/>
-      <c r="D116" s="5" t="n"/>
-      <c r="E116" s="7" t="n"/>
-      <c r="F116" s="5" t="n"/>
-      <c r="G116" s="6" t="n"/>
-      <c r="H116" s="5" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="n"/>
-      <c r="B117" s="5" t="n"/>
-      <c r="C117" s="7" t="n"/>
-      <c r="D117" s="5" t="n"/>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="5" t="n"/>
-      <c r="G117" s="6" t="n"/>
-      <c r="H117" s="5" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="n"/>
-      <c r="B118" s="5" t="n"/>
-      <c r="C118" s="7" t="n"/>
-      <c r="D118" s="5" t="n"/>
-      <c r="E118" s="7" t="n"/>
-      <c r="F118" s="5" t="n"/>
-      <c r="G118" s="6" t="n"/>
-      <c r="H118" s="5" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="n"/>
-      <c r="B119" s="5" t="n"/>
-      <c r="C119" s="7" t="n"/>
-      <c r="D119" s="5" t="n"/>
-      <c r="E119" s="7" t="n"/>
-      <c r="F119" s="5" t="n"/>
-      <c r="G119" s="6" t="n"/>
-      <c r="H119" s="5" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="n"/>
-      <c r="B120" s="5" t="n"/>
-      <c r="C120" s="7" t="n"/>
-      <c r="D120" s="5" t="n"/>
-      <c r="E120" s="7" t="n"/>
-      <c r="F120" s="5" t="n"/>
-      <c r="G120" s="6" t="n"/>
-      <c r="H120" s="5" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H1"/>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="B" prompt="One row per entity per week. APPEND, never overwrite." type="list">
-      <formula1>"RK Group,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14414,6 +14368,3710 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z120"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="12" customWidth="1" style="3" min="1" max="1"/>
+    <col width="20" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
+    <col width="15" customWidth="1" style="3" min="5" max="5"/>
+    <col width="14" customWidth="1" style="3" min="6" max="6"/>
+    <col width="13" customWidth="1" style="3" min="7" max="7"/>
+    <col width="14" customWidth="1" style="3" min="8" max="8"/>
+    <col width="13" customWidth="1" style="3" min="9" max="9"/>
+    <col width="13" customWidth="1" style="3" min="10" max="10"/>
+    <col width="30" customWidth="1" style="3" min="11" max="11"/>
+    <col width="44" customWidth="1" style="3" min="12" max="12"/>
+    <col width="14" customWidth="1" style="3" min="13" max="13"/>
+    <col width="14" customWidth="1" style="3" min="14" max="14"/>
+    <col width="15" customWidth="1" style="3" min="15" max="15"/>
+    <col width="16" customWidth="1" style="3" min="16" max="16"/>
+    <col width="14" customWidth="1" style="3" min="17" max="17"/>
+    <col width="15" customWidth="1" style="3" min="18" max="18"/>
+    <col width="14" customWidth="1" style="3" min="19" max="19"/>
+    <col width="16" customWidth="1" style="3" min="20" max="20"/>
+    <col width="13" customWidth="1" style="3" min="21" max="21"/>
+    <col width="30" customWidth="1" style="3" min="22" max="22"/>
+    <col width="44" customWidth="1" style="3" min="23" max="23"/>
+    <col width="14" customWidth="1" style="3" min="24" max="24"/>
+    <col width="12" customWidth="1" style="3" min="25" max="25"/>
+    <col width="30" customWidth="1" style="3" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Week Of</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox Rating</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox Reviews Count</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox Recommend %</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox Work-Life</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox Salary</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox Job Security</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox Growth</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox Culture</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox URL</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>AmbitionBox Notes</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor Rating</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor Reviews Count</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor Recommend %</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor CEO Approval %</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor Work-Life</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor Compensation</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor Job Security</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor Career Opportunities</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor Culture</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor URL</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Glassdoor Notes</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Last Checked Date</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>Checked By</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>RK Group</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/reviews/r-dot-k-dot-group-reviews</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>SCOPE: Bengaluru-filtered, not all locations. GENDER SPLIT: women 1.7 (7 reviews) vs men 3.5 (19) - a 1.8 point gap. Skill Development 2.3.</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N2" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="O2" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="P2" s="15" t="n"/>
+      <c r="Q2" s="7" t="n"/>
+      <c r="R2" s="7" t="n"/>
+      <c r="S2" s="7" t="n"/>
+      <c r="T2" s="7" t="n"/>
+      <c r="U2" s="7" t="n"/>
+      <c r="V2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Reviews/RK-Group-Reviews-E653077.htm</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>SCOPE: Bangalore-filtered view only, not all locations - 16 reviews is the Bangalore subset. 69% positive business outlook. Glassdoor classifies RK Group as Manufacturing; industry average 3.5. All-locations figure still needed.</t>
+        </is>
+      </c>
+      <c r="X2" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>RK World Infocom</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/reviews/r-k-world-infocom-reviews</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>All locations. AmbitionBox flags 23% below industry average. Women 3.0 (16) vs men 3.2 (29). Skill Development 3.4; Work Satisfaction 3.1.</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="P3" s="15" t="n"/>
+      <c r="Q3" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R3" s="7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S3" s="7" t="n"/>
+      <c r="T3" s="7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U3" s="7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Reviews/Rk-Worldinfocom-Reviews-E8268877.htm</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>20 written reviews. Diversity and inclusion 3.9; Senior management 3.7. Company size 201-500 employees, private. Employer Profile NOT claimed.</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Robust Kommerce</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="O4" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="P4" s="15" t="n"/>
+      <c r="Q4" s="7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" s="7" t="n"/>
+      <c r="T4" s="7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U4" s="7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Reviews/Robust-Reviews-E1882698.htm</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Listed on Glassdoor as plain 'Robust' (employer id 1882698) - identity still to be confirmed as Robust Kommerce. Diversity and inclusion 4.2; Senior management 3.1. Company size 51-200 employees. Employer Profile NOT claimed.</t>
+        </is>
+      </c>
+      <c r="X4" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Westbury Kommerce</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/reviews/westbury-kommerce-reviews</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>All locations. Highly rated for job security; critically rated for promotions, work satisfaction, skill development. 142 salary entries, 14 followers.</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="15" t="n"/>
+      <c r="Q5" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S5" s="7" t="n"/>
+      <c r="T5" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Reviews/Westbury-Kommerce-Reviews-E6166527.htm</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>Diversity and inclusion 2.0; Senior management 1.0; 'Be the first to recommend' = 0% recommend</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="15" t="n"/>
+      <c r="O6" s="15" t="n"/>
+      <c r="P6" s="15" t="n"/>
+      <c r="Q6" s="7" t="n"/>
+      <c r="R6" s="7" t="n"/>
+      <c r="S6" s="7" t="n"/>
+      <c r="T6" s="7" t="n"/>
+      <c r="U6" s="7" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="5" t="n"/>
+      <c r="Z6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="15" t="n"/>
+      <c r="O7" s="15" t="n"/>
+      <c r="P7" s="15" t="n"/>
+      <c r="Q7" s="7" t="n"/>
+      <c r="R7" s="7" t="n"/>
+      <c r="S7" s="7" t="n"/>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="5" t="n"/>
+      <c r="Z7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="15" t="n"/>
+      <c r="O8" s="15" t="n"/>
+      <c r="P8" s="15" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="7" t="n"/>
+      <c r="T8" s="7" t="n"/>
+      <c r="U8" s="7" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="5" t="n"/>
+      <c r="Z8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="15" t="n"/>
+      <c r="O9" s="15" t="n"/>
+      <c r="P9" s="15" t="n"/>
+      <c r="Q9" s="7" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="7" t="n"/>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="6" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="6" t="n"/>
+      <c r="Y9" s="5" t="n"/>
+      <c r="Z9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="15" t="n"/>
+      <c r="O10" s="15" t="n"/>
+      <c r="P10" s="15" t="n"/>
+      <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="7" t="n"/>
+      <c r="T10" s="7" t="n"/>
+      <c r="U10" s="7" t="n"/>
+      <c r="V10" s="6" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="6" t="n"/>
+      <c r="Y10" s="5" t="n"/>
+      <c r="Z10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="15" t="n"/>
+      <c r="O11" s="15" t="n"/>
+      <c r="P11" s="15" t="n"/>
+      <c r="Q11" s="7" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="7" t="n"/>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="5" t="n"/>
+      <c r="Z11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="15" t="n"/>
+      <c r="P12" s="15" t="n"/>
+      <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="S12" s="7" t="n"/>
+      <c r="T12" s="7" t="n"/>
+      <c r="U12" s="7" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="5" t="n"/>
+      <c r="Z12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="15" t="n"/>
+      <c r="O13" s="15" t="n"/>
+      <c r="P13" s="15" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="7" t="n"/>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="6" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="6" t="n"/>
+      <c r="Y13" s="5" t="n"/>
+      <c r="Z13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="15" t="n"/>
+      <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="7" t="n"/>
+      <c r="T14" s="7" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="6" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="6" t="n"/>
+      <c r="Y14" s="5" t="n"/>
+      <c r="Z14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="15" t="n"/>
+      <c r="O15" s="15" t="n"/>
+      <c r="P15" s="15" t="n"/>
+      <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="7" t="n"/>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="7" t="n"/>
+      <c r="T16" s="7" t="n"/>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="6" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="5" t="n"/>
+      <c r="Z16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="7" t="n"/>
+      <c r="R17" s="7" t="n"/>
+      <c r="S17" s="7" t="n"/>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="5" t="n"/>
+      <c r="Z17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="7" t="n"/>
+      <c r="T18" s="7" t="n"/>
+      <c r="U18" s="7" t="n"/>
+      <c r="V18" s="6" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="5" t="n"/>
+      <c r="Z18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="15" t="n"/>
+      <c r="Q19" s="7" t="n"/>
+      <c r="R19" s="7" t="n"/>
+      <c r="S19" s="7" t="n"/>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="5" t="n"/>
+      <c r="Z19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="7" t="n"/>
+      <c r="R20" s="7" t="n"/>
+      <c r="S20" s="7" t="n"/>
+      <c r="T20" s="7" t="n"/>
+      <c r="U20" s="7" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="5" t="n"/>
+      <c r="Z20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="15" t="n"/>
+      <c r="Q21" s="7" t="n"/>
+      <c r="R21" s="7" t="n"/>
+      <c r="S21" s="7" t="n"/>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="7" t="n"/>
+      <c r="R22" s="7" t="n"/>
+      <c r="S22" s="7" t="n"/>
+      <c r="T22" s="7" t="n"/>
+      <c r="U22" s="7" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="5" t="n"/>
+      <c r="Z22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="15" t="n"/>
+      <c r="Q23" s="7" t="n"/>
+      <c r="R23" s="7" t="n"/>
+      <c r="S23" s="7" t="n"/>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="6" t="n"/>
+      <c r="Y23" s="5" t="n"/>
+      <c r="Z23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="15" t="n"/>
+      <c r="Q24" s="7" t="n"/>
+      <c r="R24" s="7" t="n"/>
+      <c r="S24" s="7" t="n"/>
+      <c r="T24" s="7" t="n"/>
+      <c r="U24" s="7" t="n"/>
+      <c r="V24" s="6" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="6" t="n"/>
+      <c r="Y24" s="5" t="n"/>
+      <c r="Z24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="15" t="n"/>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="15" t="n"/>
+      <c r="Q25" s="7" t="n"/>
+      <c r="R25" s="7" t="n"/>
+      <c r="S25" s="7" t="n"/>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="6" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="6" t="n"/>
+      <c r="Y25" s="5" t="n"/>
+      <c r="Z25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
+      <c r="N26" s="15" t="n"/>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="15" t="n"/>
+      <c r="Q26" s="7" t="n"/>
+      <c r="R26" s="7" t="n"/>
+      <c r="S26" s="7" t="n"/>
+      <c r="T26" s="7" t="n"/>
+      <c r="U26" s="7" t="n"/>
+      <c r="V26" s="6" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="6" t="n"/>
+      <c r="Y26" s="5" t="n"/>
+      <c r="Z26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="15" t="n"/>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="15" t="n"/>
+      <c r="Q27" s="7" t="n"/>
+      <c r="R27" s="7" t="n"/>
+      <c r="S27" s="7" t="n"/>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="6" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="6" t="n"/>
+      <c r="Y27" s="5" t="n"/>
+      <c r="Z27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+      <c r="N28" s="15" t="n"/>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="15" t="n"/>
+      <c r="Q28" s="7" t="n"/>
+      <c r="R28" s="7" t="n"/>
+      <c r="S28" s="7" t="n"/>
+      <c r="T28" s="7" t="n"/>
+      <c r="U28" s="7" t="n"/>
+      <c r="V28" s="6" t="n"/>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="6" t="n"/>
+      <c r="Y28" s="5" t="n"/>
+      <c r="Z28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
+      <c r="N29" s="15" t="n"/>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="15" t="n"/>
+      <c r="Q29" s="7" t="n"/>
+      <c r="R29" s="7" t="n"/>
+      <c r="S29" s="7" t="n"/>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="6" t="n"/>
+      <c r="W29" s="5" t="n"/>
+      <c r="X29" s="6" t="n"/>
+      <c r="Y29" s="5" t="n"/>
+      <c r="Z29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
+      <c r="N30" s="15" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="15" t="n"/>
+      <c r="Q30" s="7" t="n"/>
+      <c r="R30" s="7" t="n"/>
+      <c r="S30" s="7" t="n"/>
+      <c r="T30" s="7" t="n"/>
+      <c r="U30" s="7" t="n"/>
+      <c r="V30" s="6" t="n"/>
+      <c r="W30" s="5" t="n"/>
+      <c r="X30" s="6" t="n"/>
+      <c r="Y30" s="5" t="n"/>
+      <c r="Z30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="15" t="n"/>
+      <c r="O31" s="15" t="n"/>
+      <c r="P31" s="15" t="n"/>
+      <c r="Q31" s="7" t="n"/>
+      <c r="R31" s="7" t="n"/>
+      <c r="S31" s="7" t="n"/>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="6" t="n"/>
+      <c r="W31" s="5" t="n"/>
+      <c r="X31" s="6" t="n"/>
+      <c r="Y31" s="5" t="n"/>
+      <c r="Z31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="15" t="n"/>
+      <c r="O32" s="15" t="n"/>
+      <c r="P32" s="15" t="n"/>
+      <c r="Q32" s="7" t="n"/>
+      <c r="R32" s="7" t="n"/>
+      <c r="S32" s="7" t="n"/>
+      <c r="T32" s="7" t="n"/>
+      <c r="U32" s="7" t="n"/>
+      <c r="V32" s="6" t="n"/>
+      <c r="W32" s="5" t="n"/>
+      <c r="X32" s="6" t="n"/>
+      <c r="Y32" s="5" t="n"/>
+      <c r="Z32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="7" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="15" t="n"/>
+      <c r="O33" s="15" t="n"/>
+      <c r="P33" s="15" t="n"/>
+      <c r="Q33" s="7" t="n"/>
+      <c r="R33" s="7" t="n"/>
+      <c r="S33" s="7" t="n"/>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="6" t="n"/>
+      <c r="W33" s="5" t="n"/>
+      <c r="X33" s="6" t="n"/>
+      <c r="Y33" s="5" t="n"/>
+      <c r="Z33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="15" t="n"/>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="15" t="n"/>
+      <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="7" t="n"/>
+      <c r="S34" s="7" t="n"/>
+      <c r="T34" s="7" t="n"/>
+      <c r="U34" s="7" t="n"/>
+      <c r="V34" s="6" t="n"/>
+      <c r="W34" s="5" t="n"/>
+      <c r="X34" s="6" t="n"/>
+      <c r="Y34" s="5" t="n"/>
+      <c r="Z34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="7" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="15" t="n"/>
+      <c r="O35" s="15" t="n"/>
+      <c r="P35" s="15" t="n"/>
+      <c r="Q35" s="7" t="n"/>
+      <c r="R35" s="7" t="n"/>
+      <c r="S35" s="7" t="n"/>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="6" t="n"/>
+      <c r="W35" s="5" t="n"/>
+      <c r="X35" s="6" t="n"/>
+      <c r="Y35" s="5" t="n"/>
+      <c r="Z35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="15" t="n"/>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="15" t="n"/>
+      <c r="Q36" s="7" t="n"/>
+      <c r="R36" s="7" t="n"/>
+      <c r="S36" s="7" t="n"/>
+      <c r="T36" s="7" t="n"/>
+      <c r="U36" s="7" t="n"/>
+      <c r="V36" s="6" t="n"/>
+      <c r="W36" s="5" t="n"/>
+      <c r="X36" s="6" t="n"/>
+      <c r="Y36" s="5" t="n"/>
+      <c r="Z36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="7" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="15" t="n"/>
+      <c r="O37" s="15" t="n"/>
+      <c r="P37" s="15" t="n"/>
+      <c r="Q37" s="7" t="n"/>
+      <c r="R37" s="7" t="n"/>
+      <c r="S37" s="7" t="n"/>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="6" t="n"/>
+      <c r="W37" s="5" t="n"/>
+      <c r="X37" s="6" t="n"/>
+      <c r="Y37" s="5" t="n"/>
+      <c r="Z37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="7" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="15" t="n"/>
+      <c r="O38" s="15" t="n"/>
+      <c r="P38" s="15" t="n"/>
+      <c r="Q38" s="7" t="n"/>
+      <c r="R38" s="7" t="n"/>
+      <c r="S38" s="7" t="n"/>
+      <c r="T38" s="7" t="n"/>
+      <c r="U38" s="7" t="n"/>
+      <c r="V38" s="6" t="n"/>
+      <c r="W38" s="5" t="n"/>
+      <c r="X38" s="6" t="n"/>
+      <c r="Y38" s="5" t="n"/>
+      <c r="Z38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="7" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="15" t="n"/>
+      <c r="O39" s="15" t="n"/>
+      <c r="P39" s="15" t="n"/>
+      <c r="Q39" s="7" t="n"/>
+      <c r="R39" s="7" t="n"/>
+      <c r="S39" s="7" t="n"/>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="6" t="n"/>
+      <c r="W39" s="5" t="n"/>
+      <c r="X39" s="6" t="n"/>
+      <c r="Y39" s="5" t="n"/>
+      <c r="Z39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="7" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
+      <c r="N40" s="15" t="n"/>
+      <c r="O40" s="15" t="n"/>
+      <c r="P40" s="15" t="n"/>
+      <c r="Q40" s="7" t="n"/>
+      <c r="R40" s="7" t="n"/>
+      <c r="S40" s="7" t="n"/>
+      <c r="T40" s="7" t="n"/>
+      <c r="U40" s="7" t="n"/>
+      <c r="V40" s="6" t="n"/>
+      <c r="W40" s="5" t="n"/>
+      <c r="X40" s="6" t="n"/>
+      <c r="Y40" s="5" t="n"/>
+      <c r="Z40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="7" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="15" t="n"/>
+      <c r="O41" s="15" t="n"/>
+      <c r="P41" s="15" t="n"/>
+      <c r="Q41" s="7" t="n"/>
+      <c r="R41" s="7" t="n"/>
+      <c r="S41" s="7" t="n"/>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="6" t="n"/>
+      <c r="W41" s="5" t="n"/>
+      <c r="X41" s="6" t="n"/>
+      <c r="Y41" s="5" t="n"/>
+      <c r="Z41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
+      <c r="N42" s="15" t="n"/>
+      <c r="O42" s="15" t="n"/>
+      <c r="P42" s="15" t="n"/>
+      <c r="Q42" s="7" t="n"/>
+      <c r="R42" s="7" t="n"/>
+      <c r="S42" s="7" t="n"/>
+      <c r="T42" s="7" t="n"/>
+      <c r="U42" s="7" t="n"/>
+      <c r="V42" s="6" t="n"/>
+      <c r="W42" s="5" t="n"/>
+      <c r="X42" s="6" t="n"/>
+      <c r="Y42" s="5" t="n"/>
+      <c r="Z42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
+      <c r="J43" s="7" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="15" t="n"/>
+      <c r="O43" s="15" t="n"/>
+      <c r="P43" s="15" t="n"/>
+      <c r="Q43" s="7" t="n"/>
+      <c r="R43" s="7" t="n"/>
+      <c r="S43" s="7" t="n"/>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="6" t="n"/>
+      <c r="W43" s="5" t="n"/>
+      <c r="X43" s="6" t="n"/>
+      <c r="Y43" s="5" t="n"/>
+      <c r="Z43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="15" t="n"/>
+      <c r="O44" s="15" t="n"/>
+      <c r="P44" s="15" t="n"/>
+      <c r="Q44" s="7" t="n"/>
+      <c r="R44" s="7" t="n"/>
+      <c r="S44" s="7" t="n"/>
+      <c r="T44" s="7" t="n"/>
+      <c r="U44" s="7" t="n"/>
+      <c r="V44" s="6" t="n"/>
+      <c r="W44" s="5" t="n"/>
+      <c r="X44" s="6" t="n"/>
+      <c r="Y44" s="5" t="n"/>
+      <c r="Z44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="15" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="7" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="15" t="n"/>
+      <c r="O45" s="15" t="n"/>
+      <c r="P45" s="15" t="n"/>
+      <c r="Q45" s="7" t="n"/>
+      <c r="R45" s="7" t="n"/>
+      <c r="S45" s="7" t="n"/>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="6" t="n"/>
+      <c r="W45" s="5" t="n"/>
+      <c r="X45" s="6" t="n"/>
+      <c r="Y45" s="5" t="n"/>
+      <c r="Z45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
+      <c r="J46" s="7" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="15" t="n"/>
+      <c r="O46" s="15" t="n"/>
+      <c r="P46" s="15" t="n"/>
+      <c r="Q46" s="7" t="n"/>
+      <c r="R46" s="7" t="n"/>
+      <c r="S46" s="7" t="n"/>
+      <c r="T46" s="7" t="n"/>
+      <c r="U46" s="7" t="n"/>
+      <c r="V46" s="6" t="n"/>
+      <c r="W46" s="5" t="n"/>
+      <c r="X46" s="6" t="n"/>
+      <c r="Y46" s="5" t="n"/>
+      <c r="Z46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="15" t="n"/>
+      <c r="O47" s="15" t="n"/>
+      <c r="P47" s="15" t="n"/>
+      <c r="Q47" s="7" t="n"/>
+      <c r="R47" s="7" t="n"/>
+      <c r="S47" s="7" t="n"/>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="6" t="n"/>
+      <c r="W47" s="5" t="n"/>
+      <c r="X47" s="6" t="n"/>
+      <c r="Y47" s="5" t="n"/>
+      <c r="Z47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+      <c r="J48" s="7" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
+      <c r="N48" s="15" t="n"/>
+      <c r="O48" s="15" t="n"/>
+      <c r="P48" s="15" t="n"/>
+      <c r="Q48" s="7" t="n"/>
+      <c r="R48" s="7" t="n"/>
+      <c r="S48" s="7" t="n"/>
+      <c r="T48" s="7" t="n"/>
+      <c r="U48" s="7" t="n"/>
+      <c r="V48" s="6" t="n"/>
+      <c r="W48" s="5" t="n"/>
+      <c r="X48" s="6" t="n"/>
+      <c r="Y48" s="5" t="n"/>
+      <c r="Z48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+      <c r="J49" s="7" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
+      <c r="N49" s="15" t="n"/>
+      <c r="O49" s="15" t="n"/>
+      <c r="P49" s="15" t="n"/>
+      <c r="Q49" s="7" t="n"/>
+      <c r="R49" s="7" t="n"/>
+      <c r="S49" s="7" t="n"/>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="6" t="n"/>
+      <c r="W49" s="5" t="n"/>
+      <c r="X49" s="6" t="n"/>
+      <c r="Y49" s="5" t="n"/>
+      <c r="Z49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="15" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="7" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
+      <c r="N50" s="15" t="n"/>
+      <c r="O50" s="15" t="n"/>
+      <c r="P50" s="15" t="n"/>
+      <c r="Q50" s="7" t="n"/>
+      <c r="R50" s="7" t="n"/>
+      <c r="S50" s="7" t="n"/>
+      <c r="T50" s="7" t="n"/>
+      <c r="U50" s="7" t="n"/>
+      <c r="V50" s="6" t="n"/>
+      <c r="W50" s="5" t="n"/>
+      <c r="X50" s="6" t="n"/>
+      <c r="Y50" s="5" t="n"/>
+      <c r="Z50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
+      <c r="N51" s="15" t="n"/>
+      <c r="O51" s="15" t="n"/>
+      <c r="P51" s="15" t="n"/>
+      <c r="Q51" s="7" t="n"/>
+      <c r="R51" s="7" t="n"/>
+      <c r="S51" s="7" t="n"/>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="6" t="n"/>
+      <c r="W51" s="5" t="n"/>
+      <c r="X51" s="6" t="n"/>
+      <c r="Y51" s="5" t="n"/>
+      <c r="Z51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+      <c r="J52" s="7" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="7" t="n"/>
+      <c r="M52" s="7" t="n"/>
+      <c r="N52" s="15" t="n"/>
+      <c r="O52" s="15" t="n"/>
+      <c r="P52" s="15" t="n"/>
+      <c r="Q52" s="7" t="n"/>
+      <c r="R52" s="7" t="n"/>
+      <c r="S52" s="7" t="n"/>
+      <c r="T52" s="7" t="n"/>
+      <c r="U52" s="7" t="n"/>
+      <c r="V52" s="6" t="n"/>
+      <c r="W52" s="5" t="n"/>
+      <c r="X52" s="6" t="n"/>
+      <c r="Y52" s="5" t="n"/>
+      <c r="Z52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="15" t="n"/>
+      <c r="F53" s="7" t="n"/>
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
+      <c r="J53" s="7" t="n"/>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="7" t="n"/>
+      <c r="M53" s="7" t="n"/>
+      <c r="N53" s="15" t="n"/>
+      <c r="O53" s="15" t="n"/>
+      <c r="P53" s="15" t="n"/>
+      <c r="Q53" s="7" t="n"/>
+      <c r="R53" s="7" t="n"/>
+      <c r="S53" s="7" t="n"/>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="6" t="n"/>
+      <c r="W53" s="5" t="n"/>
+      <c r="X53" s="6" t="n"/>
+      <c r="Y53" s="5" t="n"/>
+      <c r="Z53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="15" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
+      <c r="J54" s="7" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="7" t="n"/>
+      <c r="M54" s="7" t="n"/>
+      <c r="N54" s="15" t="n"/>
+      <c r="O54" s="15" t="n"/>
+      <c r="P54" s="15" t="n"/>
+      <c r="Q54" s="7" t="n"/>
+      <c r="R54" s="7" t="n"/>
+      <c r="S54" s="7" t="n"/>
+      <c r="T54" s="7" t="n"/>
+      <c r="U54" s="7" t="n"/>
+      <c r="V54" s="6" t="n"/>
+      <c r="W54" s="5" t="n"/>
+      <c r="X54" s="6" t="n"/>
+      <c r="Y54" s="5" t="n"/>
+      <c r="Z54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="7" t="n"/>
+      <c r="G55" s="7" t="n"/>
+      <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
+      <c r="J55" s="7" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="7" t="n"/>
+      <c r="M55" s="7" t="n"/>
+      <c r="N55" s="15" t="n"/>
+      <c r="O55" s="15" t="n"/>
+      <c r="P55" s="15" t="n"/>
+      <c r="Q55" s="7" t="n"/>
+      <c r="R55" s="7" t="n"/>
+      <c r="S55" s="7" t="n"/>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="6" t="n"/>
+      <c r="W55" s="5" t="n"/>
+      <c r="X55" s="6" t="n"/>
+      <c r="Y55" s="5" t="n"/>
+      <c r="Z55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="15" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+      <c r="J56" s="7" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="7" t="n"/>
+      <c r="M56" s="7" t="n"/>
+      <c r="N56" s="15" t="n"/>
+      <c r="O56" s="15" t="n"/>
+      <c r="P56" s="15" t="n"/>
+      <c r="Q56" s="7" t="n"/>
+      <c r="R56" s="7" t="n"/>
+      <c r="S56" s="7" t="n"/>
+      <c r="T56" s="7" t="n"/>
+      <c r="U56" s="7" t="n"/>
+      <c r="V56" s="6" t="n"/>
+      <c r="W56" s="5" t="n"/>
+      <c r="X56" s="6" t="n"/>
+      <c r="Y56" s="5" t="n"/>
+      <c r="Z56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="15" t="n"/>
+      <c r="F57" s="7" t="n"/>
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
+      <c r="J57" s="7" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="7" t="n"/>
+      <c r="M57" s="7" t="n"/>
+      <c r="N57" s="15" t="n"/>
+      <c r="O57" s="15" t="n"/>
+      <c r="P57" s="15" t="n"/>
+      <c r="Q57" s="7" t="n"/>
+      <c r="R57" s="7" t="n"/>
+      <c r="S57" s="7" t="n"/>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="6" t="n"/>
+      <c r="W57" s="5" t="n"/>
+      <c r="X57" s="6" t="n"/>
+      <c r="Y57" s="5" t="n"/>
+      <c r="Z57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="15" t="n"/>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+      <c r="J58" s="7" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="7" t="n"/>
+      <c r="M58" s="7" t="n"/>
+      <c r="N58" s="15" t="n"/>
+      <c r="O58" s="15" t="n"/>
+      <c r="P58" s="15" t="n"/>
+      <c r="Q58" s="7" t="n"/>
+      <c r="R58" s="7" t="n"/>
+      <c r="S58" s="7" t="n"/>
+      <c r="T58" s="7" t="n"/>
+      <c r="U58" s="7" t="n"/>
+      <c r="V58" s="6" t="n"/>
+      <c r="W58" s="5" t="n"/>
+      <c r="X58" s="6" t="n"/>
+      <c r="Y58" s="5" t="n"/>
+      <c r="Z58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="15" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
+      <c r="J59" s="7" t="n"/>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="7" t="n"/>
+      <c r="M59" s="7" t="n"/>
+      <c r="N59" s="15" t="n"/>
+      <c r="O59" s="15" t="n"/>
+      <c r="P59" s="15" t="n"/>
+      <c r="Q59" s="7" t="n"/>
+      <c r="R59" s="7" t="n"/>
+      <c r="S59" s="7" t="n"/>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="6" t="n"/>
+      <c r="W59" s="5" t="n"/>
+      <c r="X59" s="6" t="n"/>
+      <c r="Y59" s="5" t="n"/>
+      <c r="Z59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="15" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
+      <c r="N60" s="15" t="n"/>
+      <c r="O60" s="15" t="n"/>
+      <c r="P60" s="15" t="n"/>
+      <c r="Q60" s="7" t="n"/>
+      <c r="R60" s="7" t="n"/>
+      <c r="S60" s="7" t="n"/>
+      <c r="T60" s="7" t="n"/>
+      <c r="U60" s="7" t="n"/>
+      <c r="V60" s="6" t="n"/>
+      <c r="W60" s="5" t="n"/>
+      <c r="X60" s="6" t="n"/>
+      <c r="Y60" s="5" t="n"/>
+      <c r="Z60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="15" t="n"/>
+      <c r="F61" s="7" t="n"/>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+      <c r="J61" s="7" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="7" t="n"/>
+      <c r="M61" s="7" t="n"/>
+      <c r="N61" s="15" t="n"/>
+      <c r="O61" s="15" t="n"/>
+      <c r="P61" s="15" t="n"/>
+      <c r="Q61" s="7" t="n"/>
+      <c r="R61" s="7" t="n"/>
+      <c r="S61" s="7" t="n"/>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="6" t="n"/>
+      <c r="W61" s="5" t="n"/>
+      <c r="X61" s="6" t="n"/>
+      <c r="Y61" s="5" t="n"/>
+      <c r="Z61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="7" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+      <c r="J62" s="7" t="n"/>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
+      <c r="N62" s="15" t="n"/>
+      <c r="O62" s="15" t="n"/>
+      <c r="P62" s="15" t="n"/>
+      <c r="Q62" s="7" t="n"/>
+      <c r="R62" s="7" t="n"/>
+      <c r="S62" s="7" t="n"/>
+      <c r="T62" s="7" t="n"/>
+      <c r="U62" s="7" t="n"/>
+      <c r="V62" s="6" t="n"/>
+      <c r="W62" s="5" t="n"/>
+      <c r="X62" s="6" t="n"/>
+      <c r="Y62" s="5" t="n"/>
+      <c r="Z62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="15" t="n"/>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+      <c r="J63" s="7" t="n"/>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="7" t="n"/>
+      <c r="M63" s="7" t="n"/>
+      <c r="N63" s="15" t="n"/>
+      <c r="O63" s="15" t="n"/>
+      <c r="P63" s="15" t="n"/>
+      <c r="Q63" s="7" t="n"/>
+      <c r="R63" s="7" t="n"/>
+      <c r="S63" s="7" t="n"/>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="6" t="n"/>
+      <c r="W63" s="5" t="n"/>
+      <c r="X63" s="6" t="n"/>
+      <c r="Y63" s="5" t="n"/>
+      <c r="Z63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="15" t="n"/>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+      <c r="J64" s="7" t="n"/>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="7" t="n"/>
+      <c r="M64" s="7" t="n"/>
+      <c r="N64" s="15" t="n"/>
+      <c r="O64" s="15" t="n"/>
+      <c r="P64" s="15" t="n"/>
+      <c r="Q64" s="7" t="n"/>
+      <c r="R64" s="7" t="n"/>
+      <c r="S64" s="7" t="n"/>
+      <c r="T64" s="7" t="n"/>
+      <c r="U64" s="7" t="n"/>
+      <c r="V64" s="6" t="n"/>
+      <c r="W64" s="5" t="n"/>
+      <c r="X64" s="6" t="n"/>
+      <c r="Y64" s="5" t="n"/>
+      <c r="Z64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="15" t="n"/>
+      <c r="F65" s="7" t="n"/>
+      <c r="G65" s="7" t="n"/>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
+      <c r="J65" s="7" t="n"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="7" t="n"/>
+      <c r="M65" s="7" t="n"/>
+      <c r="N65" s="15" t="n"/>
+      <c r="O65" s="15" t="n"/>
+      <c r="P65" s="15" t="n"/>
+      <c r="Q65" s="7" t="n"/>
+      <c r="R65" s="7" t="n"/>
+      <c r="S65" s="7" t="n"/>
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="6" t="n"/>
+      <c r="W65" s="5" t="n"/>
+      <c r="X65" s="6" t="n"/>
+      <c r="Y65" s="5" t="n"/>
+      <c r="Z65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="15" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="7" t="n"/>
+      <c r="M66" s="7" t="n"/>
+      <c r="N66" s="15" t="n"/>
+      <c r="O66" s="15" t="n"/>
+      <c r="P66" s="15" t="n"/>
+      <c r="Q66" s="7" t="n"/>
+      <c r="R66" s="7" t="n"/>
+      <c r="S66" s="7" t="n"/>
+      <c r="T66" s="7" t="n"/>
+      <c r="U66" s="7" t="n"/>
+      <c r="V66" s="6" t="n"/>
+      <c r="W66" s="5" t="n"/>
+      <c r="X66" s="6" t="n"/>
+      <c r="Y66" s="5" t="n"/>
+      <c r="Z66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n"/>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="15" t="n"/>
+      <c r="F67" s="7" t="n"/>
+      <c r="G67" s="7" t="n"/>
+      <c r="H67" s="7" t="n"/>
+      <c r="I67" s="7" t="n"/>
+      <c r="J67" s="7" t="n"/>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="7" t="n"/>
+      <c r="M67" s="7" t="n"/>
+      <c r="N67" s="15" t="n"/>
+      <c r="O67" s="15" t="n"/>
+      <c r="P67" s="15" t="n"/>
+      <c r="Q67" s="7" t="n"/>
+      <c r="R67" s="7" t="n"/>
+      <c r="S67" s="7" t="n"/>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="6" t="n"/>
+      <c r="W67" s="5" t="n"/>
+      <c r="X67" s="6" t="n"/>
+      <c r="Y67" s="5" t="n"/>
+      <c r="Z67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="15" t="n"/>
+      <c r="F68" s="7" t="n"/>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+      <c r="J68" s="7" t="n"/>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="7" t="n"/>
+      <c r="M68" s="7" t="n"/>
+      <c r="N68" s="15" t="n"/>
+      <c r="O68" s="15" t="n"/>
+      <c r="P68" s="15" t="n"/>
+      <c r="Q68" s="7" t="n"/>
+      <c r="R68" s="7" t="n"/>
+      <c r="S68" s="7" t="n"/>
+      <c r="T68" s="7" t="n"/>
+      <c r="U68" s="7" t="n"/>
+      <c r="V68" s="6" t="n"/>
+      <c r="W68" s="5" t="n"/>
+      <c r="X68" s="6" t="n"/>
+      <c r="Y68" s="5" t="n"/>
+      <c r="Z68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n"/>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="15" t="n"/>
+      <c r="F69" s="7" t="n"/>
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
+      <c r="J69" s="7" t="n"/>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="7" t="n"/>
+      <c r="M69" s="7" t="n"/>
+      <c r="N69" s="15" t="n"/>
+      <c r="O69" s="15" t="n"/>
+      <c r="P69" s="15" t="n"/>
+      <c r="Q69" s="7" t="n"/>
+      <c r="R69" s="7" t="n"/>
+      <c r="S69" s="7" t="n"/>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="6" t="n"/>
+      <c r="W69" s="5" t="n"/>
+      <c r="X69" s="6" t="n"/>
+      <c r="Y69" s="5" t="n"/>
+      <c r="Z69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n"/>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="15" t="n"/>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="7" t="n"/>
+      <c r="H70" s="7" t="n"/>
+      <c r="I70" s="7" t="n"/>
+      <c r="J70" s="7" t="n"/>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="7" t="n"/>
+      <c r="M70" s="7" t="n"/>
+      <c r="N70" s="15" t="n"/>
+      <c r="O70" s="15" t="n"/>
+      <c r="P70" s="15" t="n"/>
+      <c r="Q70" s="7" t="n"/>
+      <c r="R70" s="7" t="n"/>
+      <c r="S70" s="7" t="n"/>
+      <c r="T70" s="7" t="n"/>
+      <c r="U70" s="7" t="n"/>
+      <c r="V70" s="6" t="n"/>
+      <c r="W70" s="5" t="n"/>
+      <c r="X70" s="6" t="n"/>
+      <c r="Y70" s="5" t="n"/>
+      <c r="Z70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="15" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
+      <c r="J71" s="7" t="n"/>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="7" t="n"/>
+      <c r="M71" s="7" t="n"/>
+      <c r="N71" s="15" t="n"/>
+      <c r="O71" s="15" t="n"/>
+      <c r="P71" s="15" t="n"/>
+      <c r="Q71" s="7" t="n"/>
+      <c r="R71" s="7" t="n"/>
+      <c r="S71" s="7" t="n"/>
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="6" t="n"/>
+      <c r="W71" s="5" t="n"/>
+      <c r="X71" s="6" t="n"/>
+      <c r="Y71" s="5" t="n"/>
+      <c r="Z71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="15" t="n"/>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="7" t="n"/>
+      <c r="I72" s="7" t="n"/>
+      <c r="J72" s="7" t="n"/>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="7" t="n"/>
+      <c r="M72" s="7" t="n"/>
+      <c r="N72" s="15" t="n"/>
+      <c r="O72" s="15" t="n"/>
+      <c r="P72" s="15" t="n"/>
+      <c r="Q72" s="7" t="n"/>
+      <c r="R72" s="7" t="n"/>
+      <c r="S72" s="7" t="n"/>
+      <c r="T72" s="7" t="n"/>
+      <c r="U72" s="7" t="n"/>
+      <c r="V72" s="6" t="n"/>
+      <c r="W72" s="5" t="n"/>
+      <c r="X72" s="6" t="n"/>
+      <c r="Y72" s="5" t="n"/>
+      <c r="Z72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="15" t="n"/>
+      <c r="F73" s="7" t="n"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+      <c r="J73" s="7" t="n"/>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="7" t="n"/>
+      <c r="M73" s="7" t="n"/>
+      <c r="N73" s="15" t="n"/>
+      <c r="O73" s="15" t="n"/>
+      <c r="P73" s="15" t="n"/>
+      <c r="Q73" s="7" t="n"/>
+      <c r="R73" s="7" t="n"/>
+      <c r="S73" s="7" t="n"/>
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="6" t="n"/>
+      <c r="W73" s="5" t="n"/>
+      <c r="X73" s="6" t="n"/>
+      <c r="Y73" s="5" t="n"/>
+      <c r="Z73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="15" t="n"/>
+      <c r="F74" s="7" t="n"/>
+      <c r="G74" s="7" t="n"/>
+      <c r="H74" s="7" t="n"/>
+      <c r="I74" s="7" t="n"/>
+      <c r="J74" s="7" t="n"/>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="7" t="n"/>
+      <c r="M74" s="7" t="n"/>
+      <c r="N74" s="15" t="n"/>
+      <c r="O74" s="15" t="n"/>
+      <c r="P74" s="15" t="n"/>
+      <c r="Q74" s="7" t="n"/>
+      <c r="R74" s="7" t="n"/>
+      <c r="S74" s="7" t="n"/>
+      <c r="T74" s="7" t="n"/>
+      <c r="U74" s="7" t="n"/>
+      <c r="V74" s="6" t="n"/>
+      <c r="W74" s="5" t="n"/>
+      <c r="X74" s="6" t="n"/>
+      <c r="Y74" s="5" t="n"/>
+      <c r="Z74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="15" t="n"/>
+      <c r="F75" s="7" t="n"/>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
+      <c r="J75" s="7" t="n"/>
+      <c r="K75" s="5" t="n"/>
+      <c r="L75" s="7" t="n"/>
+      <c r="M75" s="7" t="n"/>
+      <c r="N75" s="15" t="n"/>
+      <c r="O75" s="15" t="n"/>
+      <c r="P75" s="15" t="n"/>
+      <c r="Q75" s="7" t="n"/>
+      <c r="R75" s="7" t="n"/>
+      <c r="S75" s="7" t="n"/>
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="6" t="n"/>
+      <c r="W75" s="5" t="n"/>
+      <c r="X75" s="6" t="n"/>
+      <c r="Y75" s="5" t="n"/>
+      <c r="Z75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="15" t="n"/>
+      <c r="F76" s="7" t="n"/>
+      <c r="G76" s="7" t="n"/>
+      <c r="H76" s="7" t="n"/>
+      <c r="I76" s="7" t="n"/>
+      <c r="J76" s="7" t="n"/>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="7" t="n"/>
+      <c r="M76" s="7" t="n"/>
+      <c r="N76" s="15" t="n"/>
+      <c r="O76" s="15" t="n"/>
+      <c r="P76" s="15" t="n"/>
+      <c r="Q76" s="7" t="n"/>
+      <c r="R76" s="7" t="n"/>
+      <c r="S76" s="7" t="n"/>
+      <c r="T76" s="7" t="n"/>
+      <c r="U76" s="7" t="n"/>
+      <c r="V76" s="6" t="n"/>
+      <c r="W76" s="5" t="n"/>
+      <c r="X76" s="6" t="n"/>
+      <c r="Y76" s="5" t="n"/>
+      <c r="Z76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n"/>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="15" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="7" t="n"/>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+      <c r="J77" s="7" t="n"/>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="7" t="n"/>
+      <c r="M77" s="7" t="n"/>
+      <c r="N77" s="15" t="n"/>
+      <c r="O77" s="15" t="n"/>
+      <c r="P77" s="15" t="n"/>
+      <c r="Q77" s="7" t="n"/>
+      <c r="R77" s="7" t="n"/>
+      <c r="S77" s="7" t="n"/>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="6" t="n"/>
+      <c r="W77" s="5" t="n"/>
+      <c r="X77" s="6" t="n"/>
+      <c r="Y77" s="5" t="n"/>
+      <c r="Z77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n"/>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="7" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="15" t="n"/>
+      <c r="F78" s="7" t="n"/>
+      <c r="G78" s="7" t="n"/>
+      <c r="H78" s="7" t="n"/>
+      <c r="I78" s="7" t="n"/>
+      <c r="J78" s="7" t="n"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="7" t="n"/>
+      <c r="M78" s="7" t="n"/>
+      <c r="N78" s="15" t="n"/>
+      <c r="O78" s="15" t="n"/>
+      <c r="P78" s="15" t="n"/>
+      <c r="Q78" s="7" t="n"/>
+      <c r="R78" s="7" t="n"/>
+      <c r="S78" s="7" t="n"/>
+      <c r="T78" s="7" t="n"/>
+      <c r="U78" s="7" t="n"/>
+      <c r="V78" s="6" t="n"/>
+      <c r="W78" s="5" t="n"/>
+      <c r="X78" s="6" t="n"/>
+      <c r="Y78" s="5" t="n"/>
+      <c r="Z78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n"/>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="15" t="n"/>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="7" t="n"/>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="7" t="n"/>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="7" t="n"/>
+      <c r="M79" s="7" t="n"/>
+      <c r="N79" s="15" t="n"/>
+      <c r="O79" s="15" t="n"/>
+      <c r="P79" s="15" t="n"/>
+      <c r="Q79" s="7" t="n"/>
+      <c r="R79" s="7" t="n"/>
+      <c r="S79" s="7" t="n"/>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="6" t="n"/>
+      <c r="W79" s="5" t="n"/>
+      <c r="X79" s="6" t="n"/>
+      <c r="Y79" s="5" t="n"/>
+      <c r="Z79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n"/>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="15" t="n"/>
+      <c r="F80" s="7" t="n"/>
+      <c r="G80" s="7" t="n"/>
+      <c r="H80" s="7" t="n"/>
+      <c r="I80" s="7" t="n"/>
+      <c r="J80" s="7" t="n"/>
+      <c r="K80" s="5" t="n"/>
+      <c r="L80" s="7" t="n"/>
+      <c r="M80" s="7" t="n"/>
+      <c r="N80" s="15" t="n"/>
+      <c r="O80" s="15" t="n"/>
+      <c r="P80" s="15" t="n"/>
+      <c r="Q80" s="7" t="n"/>
+      <c r="R80" s="7" t="n"/>
+      <c r="S80" s="7" t="n"/>
+      <c r="T80" s="7" t="n"/>
+      <c r="U80" s="7" t="n"/>
+      <c r="V80" s="6" t="n"/>
+      <c r="W80" s="5" t="n"/>
+      <c r="X80" s="6" t="n"/>
+      <c r="Y80" s="5" t="n"/>
+      <c r="Z80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n"/>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="15" t="n"/>
+      <c r="F81" s="7" t="n"/>
+      <c r="G81" s="7" t="n"/>
+      <c r="H81" s="7" t="n"/>
+      <c r="I81" s="7" t="n"/>
+      <c r="J81" s="7" t="n"/>
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="7" t="n"/>
+      <c r="M81" s="7" t="n"/>
+      <c r="N81" s="15" t="n"/>
+      <c r="O81" s="15" t="n"/>
+      <c r="P81" s="15" t="n"/>
+      <c r="Q81" s="7" t="n"/>
+      <c r="R81" s="7" t="n"/>
+      <c r="S81" s="7" t="n"/>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="6" t="n"/>
+      <c r="W81" s="5" t="n"/>
+      <c r="X81" s="6" t="n"/>
+      <c r="Y81" s="5" t="n"/>
+      <c r="Z81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n"/>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="15" t="n"/>
+      <c r="F82" s="7" t="n"/>
+      <c r="G82" s="7" t="n"/>
+      <c r="H82" s="7" t="n"/>
+      <c r="I82" s="7" t="n"/>
+      <c r="J82" s="7" t="n"/>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="7" t="n"/>
+      <c r="M82" s="7" t="n"/>
+      <c r="N82" s="15" t="n"/>
+      <c r="O82" s="15" t="n"/>
+      <c r="P82" s="15" t="n"/>
+      <c r="Q82" s="7" t="n"/>
+      <c r="R82" s="7" t="n"/>
+      <c r="S82" s="7" t="n"/>
+      <c r="T82" s="7" t="n"/>
+      <c r="U82" s="7" t="n"/>
+      <c r="V82" s="6" t="n"/>
+      <c r="W82" s="5" t="n"/>
+      <c r="X82" s="6" t="n"/>
+      <c r="Y82" s="5" t="n"/>
+      <c r="Z82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n"/>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="15" t="n"/>
+      <c r="F83" s="7" t="n"/>
+      <c r="G83" s="7" t="n"/>
+      <c r="H83" s="7" t="n"/>
+      <c r="I83" s="7" t="n"/>
+      <c r="J83" s="7" t="n"/>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="7" t="n"/>
+      <c r="M83" s="7" t="n"/>
+      <c r="N83" s="15" t="n"/>
+      <c r="O83" s="15" t="n"/>
+      <c r="P83" s="15" t="n"/>
+      <c r="Q83" s="7" t="n"/>
+      <c r="R83" s="7" t="n"/>
+      <c r="S83" s="7" t="n"/>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="6" t="n"/>
+      <c r="W83" s="5" t="n"/>
+      <c r="X83" s="6" t="n"/>
+      <c r="Y83" s="5" t="n"/>
+      <c r="Z83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n"/>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="7" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="15" t="n"/>
+      <c r="F84" s="7" t="n"/>
+      <c r="G84" s="7" t="n"/>
+      <c r="H84" s="7" t="n"/>
+      <c r="I84" s="7" t="n"/>
+      <c r="J84" s="7" t="n"/>
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="7" t="n"/>
+      <c r="M84" s="7" t="n"/>
+      <c r="N84" s="15" t="n"/>
+      <c r="O84" s="15" t="n"/>
+      <c r="P84" s="15" t="n"/>
+      <c r="Q84" s="7" t="n"/>
+      <c r="R84" s="7" t="n"/>
+      <c r="S84" s="7" t="n"/>
+      <c r="T84" s="7" t="n"/>
+      <c r="U84" s="7" t="n"/>
+      <c r="V84" s="6" t="n"/>
+      <c r="W84" s="5" t="n"/>
+      <c r="X84" s="6" t="n"/>
+      <c r="Y84" s="5" t="n"/>
+      <c r="Z84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n"/>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="15" t="n"/>
+      <c r="F85" s="7" t="n"/>
+      <c r="G85" s="7" t="n"/>
+      <c r="H85" s="7" t="n"/>
+      <c r="I85" s="7" t="n"/>
+      <c r="J85" s="7" t="n"/>
+      <c r="K85" s="5" t="n"/>
+      <c r="L85" s="7" t="n"/>
+      <c r="M85" s="7" t="n"/>
+      <c r="N85" s="15" t="n"/>
+      <c r="O85" s="15" t="n"/>
+      <c r="P85" s="15" t="n"/>
+      <c r="Q85" s="7" t="n"/>
+      <c r="R85" s="7" t="n"/>
+      <c r="S85" s="7" t="n"/>
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="6" t="n"/>
+      <c r="W85" s="5" t="n"/>
+      <c r="X85" s="6" t="n"/>
+      <c r="Y85" s="5" t="n"/>
+      <c r="Z85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n"/>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="7" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="15" t="n"/>
+      <c r="F86" s="7" t="n"/>
+      <c r="G86" s="7" t="n"/>
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
+      <c r="J86" s="7" t="n"/>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="7" t="n"/>
+      <c r="M86" s="7" t="n"/>
+      <c r="N86" s="15" t="n"/>
+      <c r="O86" s="15" t="n"/>
+      <c r="P86" s="15" t="n"/>
+      <c r="Q86" s="7" t="n"/>
+      <c r="R86" s="7" t="n"/>
+      <c r="S86" s="7" t="n"/>
+      <c r="T86" s="7" t="n"/>
+      <c r="U86" s="7" t="n"/>
+      <c r="V86" s="6" t="n"/>
+      <c r="W86" s="5" t="n"/>
+      <c r="X86" s="6" t="n"/>
+      <c r="Y86" s="5" t="n"/>
+      <c r="Z86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n"/>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="15" t="n"/>
+      <c r="F87" s="7" t="n"/>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
+      <c r="J87" s="7" t="n"/>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="7" t="n"/>
+      <c r="M87" s="7" t="n"/>
+      <c r="N87" s="15" t="n"/>
+      <c r="O87" s="15" t="n"/>
+      <c r="P87" s="15" t="n"/>
+      <c r="Q87" s="7" t="n"/>
+      <c r="R87" s="7" t="n"/>
+      <c r="S87" s="7" t="n"/>
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="6" t="n"/>
+      <c r="W87" s="5" t="n"/>
+      <c r="X87" s="6" t="n"/>
+      <c r="Y87" s="5" t="n"/>
+      <c r="Z87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n"/>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="15" t="n"/>
+      <c r="F88" s="7" t="n"/>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+      <c r="J88" s="7" t="n"/>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="7" t="n"/>
+      <c r="M88" s="7" t="n"/>
+      <c r="N88" s="15" t="n"/>
+      <c r="O88" s="15" t="n"/>
+      <c r="P88" s="15" t="n"/>
+      <c r="Q88" s="7" t="n"/>
+      <c r="R88" s="7" t="n"/>
+      <c r="S88" s="7" t="n"/>
+      <c r="T88" s="7" t="n"/>
+      <c r="U88" s="7" t="n"/>
+      <c r="V88" s="6" t="n"/>
+      <c r="W88" s="5" t="n"/>
+      <c r="X88" s="6" t="n"/>
+      <c r="Y88" s="5" t="n"/>
+      <c r="Z88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n"/>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="15" t="n"/>
+      <c r="F89" s="7" t="n"/>
+      <c r="G89" s="7" t="n"/>
+      <c r="H89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
+      <c r="J89" s="7" t="n"/>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="7" t="n"/>
+      <c r="M89" s="7" t="n"/>
+      <c r="N89" s="15" t="n"/>
+      <c r="O89" s="15" t="n"/>
+      <c r="P89" s="15" t="n"/>
+      <c r="Q89" s="7" t="n"/>
+      <c r="R89" s="7" t="n"/>
+      <c r="S89" s="7" t="n"/>
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="6" t="n"/>
+      <c r="W89" s="5" t="n"/>
+      <c r="X89" s="6" t="n"/>
+      <c r="Y89" s="5" t="n"/>
+      <c r="Z89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n"/>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="7" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="15" t="n"/>
+      <c r="F90" s="7" t="n"/>
+      <c r="G90" s="7" t="n"/>
+      <c r="H90" s="7" t="n"/>
+      <c r="I90" s="7" t="n"/>
+      <c r="J90" s="7" t="n"/>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="7" t="n"/>
+      <c r="M90" s="7" t="n"/>
+      <c r="N90" s="15" t="n"/>
+      <c r="O90" s="15" t="n"/>
+      <c r="P90" s="15" t="n"/>
+      <c r="Q90" s="7" t="n"/>
+      <c r="R90" s="7" t="n"/>
+      <c r="S90" s="7" t="n"/>
+      <c r="T90" s="7" t="n"/>
+      <c r="U90" s="7" t="n"/>
+      <c r="V90" s="6" t="n"/>
+      <c r="W90" s="5" t="n"/>
+      <c r="X90" s="6" t="n"/>
+      <c r="Y90" s="5" t="n"/>
+      <c r="Z90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n"/>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="15" t="n"/>
+      <c r="F91" s="7" t="n"/>
+      <c r="G91" s="7" t="n"/>
+      <c r="H91" s="7" t="n"/>
+      <c r="I91" s="7" t="n"/>
+      <c r="J91" s="7" t="n"/>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="7" t="n"/>
+      <c r="M91" s="7" t="n"/>
+      <c r="N91" s="15" t="n"/>
+      <c r="O91" s="15" t="n"/>
+      <c r="P91" s="15" t="n"/>
+      <c r="Q91" s="7" t="n"/>
+      <c r="R91" s="7" t="n"/>
+      <c r="S91" s="7" t="n"/>
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="6" t="n"/>
+      <c r="W91" s="5" t="n"/>
+      <c r="X91" s="6" t="n"/>
+      <c r="Y91" s="5" t="n"/>
+      <c r="Z91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n"/>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="7" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="15" t="n"/>
+      <c r="F92" s="7" t="n"/>
+      <c r="G92" s="7" t="n"/>
+      <c r="H92" s="7" t="n"/>
+      <c r="I92" s="7" t="n"/>
+      <c r="J92" s="7" t="n"/>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="7" t="n"/>
+      <c r="M92" s="7" t="n"/>
+      <c r="N92" s="15" t="n"/>
+      <c r="O92" s="15" t="n"/>
+      <c r="P92" s="15" t="n"/>
+      <c r="Q92" s="7" t="n"/>
+      <c r="R92" s="7" t="n"/>
+      <c r="S92" s="7" t="n"/>
+      <c r="T92" s="7" t="n"/>
+      <c r="U92" s="7" t="n"/>
+      <c r="V92" s="6" t="n"/>
+      <c r="W92" s="5" t="n"/>
+      <c r="X92" s="6" t="n"/>
+      <c r="Y92" s="5" t="n"/>
+      <c r="Z92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="15" t="n"/>
+      <c r="F93" s="7" t="n"/>
+      <c r="G93" s="7" t="n"/>
+      <c r="H93" s="7" t="n"/>
+      <c r="I93" s="7" t="n"/>
+      <c r="J93" s="7" t="n"/>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="7" t="n"/>
+      <c r="M93" s="7" t="n"/>
+      <c r="N93" s="15" t="n"/>
+      <c r="O93" s="15" t="n"/>
+      <c r="P93" s="15" t="n"/>
+      <c r="Q93" s="7" t="n"/>
+      <c r="R93" s="7" t="n"/>
+      <c r="S93" s="7" t="n"/>
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="6" t="n"/>
+      <c r="W93" s="5" t="n"/>
+      <c r="X93" s="6" t="n"/>
+      <c r="Y93" s="5" t="n"/>
+      <c r="Z93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n"/>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="7" t="n"/>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="15" t="n"/>
+      <c r="F94" s="7" t="n"/>
+      <c r="G94" s="7" t="n"/>
+      <c r="H94" s="7" t="n"/>
+      <c r="I94" s="7" t="n"/>
+      <c r="J94" s="7" t="n"/>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="7" t="n"/>
+      <c r="M94" s="7" t="n"/>
+      <c r="N94" s="15" t="n"/>
+      <c r="O94" s="15" t="n"/>
+      <c r="P94" s="15" t="n"/>
+      <c r="Q94" s="7" t="n"/>
+      <c r="R94" s="7" t="n"/>
+      <c r="S94" s="7" t="n"/>
+      <c r="T94" s="7" t="n"/>
+      <c r="U94" s="7" t="n"/>
+      <c r="V94" s="6" t="n"/>
+      <c r="W94" s="5" t="n"/>
+      <c r="X94" s="6" t="n"/>
+      <c r="Y94" s="5" t="n"/>
+      <c r="Z94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n"/>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="15" t="n"/>
+      <c r="F95" s="7" t="n"/>
+      <c r="G95" s="7" t="n"/>
+      <c r="H95" s="7" t="n"/>
+      <c r="I95" s="7" t="n"/>
+      <c r="J95" s="7" t="n"/>
+      <c r="K95" s="5" t="n"/>
+      <c r="L95" s="7" t="n"/>
+      <c r="M95" s="7" t="n"/>
+      <c r="N95" s="15" t="n"/>
+      <c r="O95" s="15" t="n"/>
+      <c r="P95" s="15" t="n"/>
+      <c r="Q95" s="7" t="n"/>
+      <c r="R95" s="7" t="n"/>
+      <c r="S95" s="7" t="n"/>
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="6" t="n"/>
+      <c r="W95" s="5" t="n"/>
+      <c r="X95" s="6" t="n"/>
+      <c r="Y95" s="5" t="n"/>
+      <c r="Z95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n"/>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="7" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="15" t="n"/>
+      <c r="F96" s="7" t="n"/>
+      <c r="G96" s="7" t="n"/>
+      <c r="H96" s="7" t="n"/>
+      <c r="I96" s="7" t="n"/>
+      <c r="J96" s="7" t="n"/>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="7" t="n"/>
+      <c r="M96" s="7" t="n"/>
+      <c r="N96" s="15" t="n"/>
+      <c r="O96" s="15" t="n"/>
+      <c r="P96" s="15" t="n"/>
+      <c r="Q96" s="7" t="n"/>
+      <c r="R96" s="7" t="n"/>
+      <c r="S96" s="7" t="n"/>
+      <c r="T96" s="7" t="n"/>
+      <c r="U96" s="7" t="n"/>
+      <c r="V96" s="6" t="n"/>
+      <c r="W96" s="5" t="n"/>
+      <c r="X96" s="6" t="n"/>
+      <c r="Y96" s="5" t="n"/>
+      <c r="Z96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="15" t="n"/>
+      <c r="F97" s="7" t="n"/>
+      <c r="G97" s="7" t="n"/>
+      <c r="H97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
+      <c r="J97" s="7" t="n"/>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="7" t="n"/>
+      <c r="M97" s="7" t="n"/>
+      <c r="N97" s="15" t="n"/>
+      <c r="O97" s="15" t="n"/>
+      <c r="P97" s="15" t="n"/>
+      <c r="Q97" s="7" t="n"/>
+      <c r="R97" s="7" t="n"/>
+      <c r="S97" s="7" t="n"/>
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="6" t="n"/>
+      <c r="W97" s="5" t="n"/>
+      <c r="X97" s="6" t="n"/>
+      <c r="Y97" s="5" t="n"/>
+      <c r="Z97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n"/>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="15" t="n"/>
+      <c r="F98" s="7" t="n"/>
+      <c r="G98" s="7" t="n"/>
+      <c r="H98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
+      <c r="J98" s="7" t="n"/>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="7" t="n"/>
+      <c r="M98" s="7" t="n"/>
+      <c r="N98" s="15" t="n"/>
+      <c r="O98" s="15" t="n"/>
+      <c r="P98" s="15" t="n"/>
+      <c r="Q98" s="7" t="n"/>
+      <c r="R98" s="7" t="n"/>
+      <c r="S98" s="7" t="n"/>
+      <c r="T98" s="7" t="n"/>
+      <c r="U98" s="7" t="n"/>
+      <c r="V98" s="6" t="n"/>
+      <c r="W98" s="5" t="n"/>
+      <c r="X98" s="6" t="n"/>
+      <c r="Y98" s="5" t="n"/>
+      <c r="Z98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n"/>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="15" t="n"/>
+      <c r="F99" s="7" t="n"/>
+      <c r="G99" s="7" t="n"/>
+      <c r="H99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
+      <c r="J99" s="7" t="n"/>
+      <c r="K99" s="5" t="n"/>
+      <c r="L99" s="7" t="n"/>
+      <c r="M99" s="7" t="n"/>
+      <c r="N99" s="15" t="n"/>
+      <c r="O99" s="15" t="n"/>
+      <c r="P99" s="15" t="n"/>
+      <c r="Q99" s="7" t="n"/>
+      <c r="R99" s="7" t="n"/>
+      <c r="S99" s="7" t="n"/>
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="6" t="n"/>
+      <c r="W99" s="5" t="n"/>
+      <c r="X99" s="6" t="n"/>
+      <c r="Y99" s="5" t="n"/>
+      <c r="Z99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n"/>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="7" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="15" t="n"/>
+      <c r="F100" s="7" t="n"/>
+      <c r="G100" s="7" t="n"/>
+      <c r="H100" s="7" t="n"/>
+      <c r="I100" s="7" t="n"/>
+      <c r="J100" s="7" t="n"/>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="7" t="n"/>
+      <c r="M100" s="7" t="n"/>
+      <c r="N100" s="15" t="n"/>
+      <c r="O100" s="15" t="n"/>
+      <c r="P100" s="15" t="n"/>
+      <c r="Q100" s="7" t="n"/>
+      <c r="R100" s="7" t="n"/>
+      <c r="S100" s="7" t="n"/>
+      <c r="T100" s="7" t="n"/>
+      <c r="U100" s="7" t="n"/>
+      <c r="V100" s="6" t="n"/>
+      <c r="W100" s="5" t="n"/>
+      <c r="X100" s="6" t="n"/>
+      <c r="Y100" s="5" t="n"/>
+      <c r="Z100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n"/>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="15" t="n"/>
+      <c r="F101" s="7" t="n"/>
+      <c r="G101" s="7" t="n"/>
+      <c r="H101" s="7" t="n"/>
+      <c r="I101" s="7" t="n"/>
+      <c r="J101" s="7" t="n"/>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="7" t="n"/>
+      <c r="M101" s="7" t="n"/>
+      <c r="N101" s="15" t="n"/>
+      <c r="O101" s="15" t="n"/>
+      <c r="P101" s="15" t="n"/>
+      <c r="Q101" s="7" t="n"/>
+      <c r="R101" s="7" t="n"/>
+      <c r="S101" s="7" t="n"/>
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="6" t="n"/>
+      <c r="W101" s="5" t="n"/>
+      <c r="X101" s="6" t="n"/>
+      <c r="Y101" s="5" t="n"/>
+      <c r="Z101" s="5" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n"/>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="7" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="15" t="n"/>
+      <c r="F102" s="7" t="n"/>
+      <c r="G102" s="7" t="n"/>
+      <c r="H102" s="7" t="n"/>
+      <c r="I102" s="7" t="n"/>
+      <c r="J102" s="7" t="n"/>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="7" t="n"/>
+      <c r="M102" s="7" t="n"/>
+      <c r="N102" s="15" t="n"/>
+      <c r="O102" s="15" t="n"/>
+      <c r="P102" s="15" t="n"/>
+      <c r="Q102" s="7" t="n"/>
+      <c r="R102" s="7" t="n"/>
+      <c r="S102" s="7" t="n"/>
+      <c r="T102" s="7" t="n"/>
+      <c r="U102" s="7" t="n"/>
+      <c r="V102" s="6" t="n"/>
+      <c r="W102" s="5" t="n"/>
+      <c r="X102" s="6" t="n"/>
+      <c r="Y102" s="5" t="n"/>
+      <c r="Z102" s="5" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="7" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="15" t="n"/>
+      <c r="F103" s="7" t="n"/>
+      <c r="G103" s="7" t="n"/>
+      <c r="H103" s="7" t="n"/>
+      <c r="I103" s="7" t="n"/>
+      <c r="J103" s="7" t="n"/>
+      <c r="K103" s="5" t="n"/>
+      <c r="L103" s="7" t="n"/>
+      <c r="M103" s="7" t="n"/>
+      <c r="N103" s="15" t="n"/>
+      <c r="O103" s="15" t="n"/>
+      <c r="P103" s="15" t="n"/>
+      <c r="Q103" s="7" t="n"/>
+      <c r="R103" s="7" t="n"/>
+      <c r="S103" s="7" t="n"/>
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="6" t="n"/>
+      <c r="W103" s="5" t="n"/>
+      <c r="X103" s="6" t="n"/>
+      <c r="Y103" s="5" t="n"/>
+      <c r="Z103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="7" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="15" t="n"/>
+      <c r="F104" s="7" t="n"/>
+      <c r="G104" s="7" t="n"/>
+      <c r="H104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
+      <c r="J104" s="7" t="n"/>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="7" t="n"/>
+      <c r="M104" s="7" t="n"/>
+      <c r="N104" s="15" t="n"/>
+      <c r="O104" s="15" t="n"/>
+      <c r="P104" s="15" t="n"/>
+      <c r="Q104" s="7" t="n"/>
+      <c r="R104" s="7" t="n"/>
+      <c r="S104" s="7" t="n"/>
+      <c r="T104" s="7" t="n"/>
+      <c r="U104" s="7" t="n"/>
+      <c r="V104" s="6" t="n"/>
+      <c r="W104" s="5" t="n"/>
+      <c r="X104" s="6" t="n"/>
+      <c r="Y104" s="5" t="n"/>
+      <c r="Z104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n"/>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="7" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="15" t="n"/>
+      <c r="F105" s="7" t="n"/>
+      <c r="G105" s="7" t="n"/>
+      <c r="H105" s="7" t="n"/>
+      <c r="I105" s="7" t="n"/>
+      <c r="J105" s="7" t="n"/>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="7" t="n"/>
+      <c r="M105" s="7" t="n"/>
+      <c r="N105" s="15" t="n"/>
+      <c r="O105" s="15" t="n"/>
+      <c r="P105" s="15" t="n"/>
+      <c r="Q105" s="7" t="n"/>
+      <c r="R105" s="7" t="n"/>
+      <c r="S105" s="7" t="n"/>
+      <c r="T105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="6" t="n"/>
+      <c r="W105" s="5" t="n"/>
+      <c r="X105" s="6" t="n"/>
+      <c r="Y105" s="5" t="n"/>
+      <c r="Z105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n"/>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="7" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="15" t="n"/>
+      <c r="F106" s="7" t="n"/>
+      <c r="G106" s="7" t="n"/>
+      <c r="H106" s="7" t="n"/>
+      <c r="I106" s="7" t="n"/>
+      <c r="J106" s="7" t="n"/>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="7" t="n"/>
+      <c r="M106" s="7" t="n"/>
+      <c r="N106" s="15" t="n"/>
+      <c r="O106" s="15" t="n"/>
+      <c r="P106" s="15" t="n"/>
+      <c r="Q106" s="7" t="n"/>
+      <c r="R106" s="7" t="n"/>
+      <c r="S106" s="7" t="n"/>
+      <c r="T106" s="7" t="n"/>
+      <c r="U106" s="7" t="n"/>
+      <c r="V106" s="6" t="n"/>
+      <c r="W106" s="5" t="n"/>
+      <c r="X106" s="6" t="n"/>
+      <c r="Y106" s="5" t="n"/>
+      <c r="Z106" s="5" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="n"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="15" t="n"/>
+      <c r="F107" s="7" t="n"/>
+      <c r="G107" s="7" t="n"/>
+      <c r="H107" s="7" t="n"/>
+      <c r="I107" s="7" t="n"/>
+      <c r="J107" s="7" t="n"/>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="7" t="n"/>
+      <c r="M107" s="7" t="n"/>
+      <c r="N107" s="15" t="n"/>
+      <c r="O107" s="15" t="n"/>
+      <c r="P107" s="15" t="n"/>
+      <c r="Q107" s="7" t="n"/>
+      <c r="R107" s="7" t="n"/>
+      <c r="S107" s="7" t="n"/>
+      <c r="T107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="6" t="n"/>
+      <c r="W107" s="5" t="n"/>
+      <c r="X107" s="6" t="n"/>
+      <c r="Y107" s="5" t="n"/>
+      <c r="Z107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="n"/>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="7" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="7" t="n"/>
+      <c r="G108" s="7" t="n"/>
+      <c r="H108" s="7" t="n"/>
+      <c r="I108" s="7" t="n"/>
+      <c r="J108" s="7" t="n"/>
+      <c r="K108" s="5" t="n"/>
+      <c r="L108" s="7" t="n"/>
+      <c r="M108" s="7" t="n"/>
+      <c r="N108" s="15" t="n"/>
+      <c r="O108" s="15" t="n"/>
+      <c r="P108" s="15" t="n"/>
+      <c r="Q108" s="7" t="n"/>
+      <c r="R108" s="7" t="n"/>
+      <c r="S108" s="7" t="n"/>
+      <c r="T108" s="7" t="n"/>
+      <c r="U108" s="7" t="n"/>
+      <c r="V108" s="6" t="n"/>
+      <c r="W108" s="5" t="n"/>
+      <c r="X108" s="6" t="n"/>
+      <c r="Y108" s="5" t="n"/>
+      <c r="Z108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="n"/>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="7" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="15" t="n"/>
+      <c r="F109" s="7" t="n"/>
+      <c r="G109" s="7" t="n"/>
+      <c r="H109" s="7" t="n"/>
+      <c r="I109" s="7" t="n"/>
+      <c r="J109" s="7" t="n"/>
+      <c r="K109" s="5" t="n"/>
+      <c r="L109" s="7" t="n"/>
+      <c r="M109" s="7" t="n"/>
+      <c r="N109" s="15" t="n"/>
+      <c r="O109" s="15" t="n"/>
+      <c r="P109" s="15" t="n"/>
+      <c r="Q109" s="7" t="n"/>
+      <c r="R109" s="7" t="n"/>
+      <c r="S109" s="7" t="n"/>
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="6" t="n"/>
+      <c r="W109" s="5" t="n"/>
+      <c r="X109" s="6" t="n"/>
+      <c r="Y109" s="5" t="n"/>
+      <c r="Z109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n"/>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="7" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="15" t="n"/>
+      <c r="F110" s="7" t="n"/>
+      <c r="G110" s="7" t="n"/>
+      <c r="H110" s="7" t="n"/>
+      <c r="I110" s="7" t="n"/>
+      <c r="J110" s="7" t="n"/>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="7" t="n"/>
+      <c r="M110" s="7" t="n"/>
+      <c r="N110" s="15" t="n"/>
+      <c r="O110" s="15" t="n"/>
+      <c r="P110" s="15" t="n"/>
+      <c r="Q110" s="7" t="n"/>
+      <c r="R110" s="7" t="n"/>
+      <c r="S110" s="7" t="n"/>
+      <c r="T110" s="7" t="n"/>
+      <c r="U110" s="7" t="n"/>
+      <c r="V110" s="6" t="n"/>
+      <c r="W110" s="5" t="n"/>
+      <c r="X110" s="6" t="n"/>
+      <c r="Y110" s="5" t="n"/>
+      <c r="Z110" s="5" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="n"/>
+      <c r="B111" s="5" t="n"/>
+      <c r="C111" s="7" t="n"/>
+      <c r="D111" s="5" t="n"/>
+      <c r="E111" s="15" t="n"/>
+      <c r="F111" s="7" t="n"/>
+      <c r="G111" s="7" t="n"/>
+      <c r="H111" s="7" t="n"/>
+      <c r="I111" s="7" t="n"/>
+      <c r="J111" s="7" t="n"/>
+      <c r="K111" s="5" t="n"/>
+      <c r="L111" s="7" t="n"/>
+      <c r="M111" s="7" t="n"/>
+      <c r="N111" s="15" t="n"/>
+      <c r="O111" s="15" t="n"/>
+      <c r="P111" s="15" t="n"/>
+      <c r="Q111" s="7" t="n"/>
+      <c r="R111" s="7" t="n"/>
+      <c r="S111" s="7" t="n"/>
+      <c r="T111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="6" t="n"/>
+      <c r="W111" s="5" t="n"/>
+      <c r="X111" s="6" t="n"/>
+      <c r="Y111" s="5" t="n"/>
+      <c r="Z111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n"/>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="15" t="n"/>
+      <c r="F112" s="7" t="n"/>
+      <c r="G112" s="7" t="n"/>
+      <c r="H112" s="7" t="n"/>
+      <c r="I112" s="7" t="n"/>
+      <c r="J112" s="7" t="n"/>
+      <c r="K112" s="5" t="n"/>
+      <c r="L112" s="7" t="n"/>
+      <c r="M112" s="7" t="n"/>
+      <c r="N112" s="15" t="n"/>
+      <c r="O112" s="15" t="n"/>
+      <c r="P112" s="15" t="n"/>
+      <c r="Q112" s="7" t="n"/>
+      <c r="R112" s="7" t="n"/>
+      <c r="S112" s="7" t="n"/>
+      <c r="T112" s="7" t="n"/>
+      <c r="U112" s="7" t="n"/>
+      <c r="V112" s="6" t="n"/>
+      <c r="W112" s="5" t="n"/>
+      <c r="X112" s="6" t="n"/>
+      <c r="Y112" s="5" t="n"/>
+      <c r="Z112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="n"/>
+      <c r="B113" s="5" t="n"/>
+      <c r="C113" s="7" t="n"/>
+      <c r="D113" s="5" t="n"/>
+      <c r="E113" s="15" t="n"/>
+      <c r="F113" s="7" t="n"/>
+      <c r="G113" s="7" t="n"/>
+      <c r="H113" s="7" t="n"/>
+      <c r="I113" s="7" t="n"/>
+      <c r="J113" s="7" t="n"/>
+      <c r="K113" s="5" t="n"/>
+      <c r="L113" s="7" t="n"/>
+      <c r="M113" s="7" t="n"/>
+      <c r="N113" s="15" t="n"/>
+      <c r="O113" s="15" t="n"/>
+      <c r="P113" s="15" t="n"/>
+      <c r="Q113" s="7" t="n"/>
+      <c r="R113" s="7" t="n"/>
+      <c r="S113" s="7" t="n"/>
+      <c r="T113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="6" t="n"/>
+      <c r="W113" s="5" t="n"/>
+      <c r="X113" s="6" t="n"/>
+      <c r="Y113" s="5" t="n"/>
+      <c r="Z113" s="5" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="n"/>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="7" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="15" t="n"/>
+      <c r="F114" s="7" t="n"/>
+      <c r="G114" s="7" t="n"/>
+      <c r="H114" s="7" t="n"/>
+      <c r="I114" s="7" t="n"/>
+      <c r="J114" s="7" t="n"/>
+      <c r="K114" s="5" t="n"/>
+      <c r="L114" s="7" t="n"/>
+      <c r="M114" s="7" t="n"/>
+      <c r="N114" s="15" t="n"/>
+      <c r="O114" s="15" t="n"/>
+      <c r="P114" s="15" t="n"/>
+      <c r="Q114" s="7" t="n"/>
+      <c r="R114" s="7" t="n"/>
+      <c r="S114" s="7" t="n"/>
+      <c r="T114" s="7" t="n"/>
+      <c r="U114" s="7" t="n"/>
+      <c r="V114" s="6" t="n"/>
+      <c r="W114" s="5" t="n"/>
+      <c r="X114" s="6" t="n"/>
+      <c r="Y114" s="5" t="n"/>
+      <c r="Z114" s="5" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="n"/>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="15" t="n"/>
+      <c r="F115" s="7" t="n"/>
+      <c r="G115" s="7" t="n"/>
+      <c r="H115" s="7" t="n"/>
+      <c r="I115" s="7" t="n"/>
+      <c r="J115" s="7" t="n"/>
+      <c r="K115" s="5" t="n"/>
+      <c r="L115" s="7" t="n"/>
+      <c r="M115" s="7" t="n"/>
+      <c r="N115" s="15" t="n"/>
+      <c r="O115" s="15" t="n"/>
+      <c r="P115" s="15" t="n"/>
+      <c r="Q115" s="7" t="n"/>
+      <c r="R115" s="7" t="n"/>
+      <c r="S115" s="7" t="n"/>
+      <c r="T115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="6" t="n"/>
+      <c r="W115" s="5" t="n"/>
+      <c r="X115" s="6" t="n"/>
+      <c r="Y115" s="5" t="n"/>
+      <c r="Z115" s="5" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="n"/>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="D116" s="5" t="n"/>
+      <c r="E116" s="15" t="n"/>
+      <c r="F116" s="7" t="n"/>
+      <c r="G116" s="7" t="n"/>
+      <c r="H116" s="7" t="n"/>
+      <c r="I116" s="7" t="n"/>
+      <c r="J116" s="7" t="n"/>
+      <c r="K116" s="5" t="n"/>
+      <c r="L116" s="7" t="n"/>
+      <c r="M116" s="7" t="n"/>
+      <c r="N116" s="15" t="n"/>
+      <c r="O116" s="15" t="n"/>
+      <c r="P116" s="15" t="n"/>
+      <c r="Q116" s="7" t="n"/>
+      <c r="R116" s="7" t="n"/>
+      <c r="S116" s="7" t="n"/>
+      <c r="T116" s="7" t="n"/>
+      <c r="U116" s="7" t="n"/>
+      <c r="V116" s="6" t="n"/>
+      <c r="W116" s="5" t="n"/>
+      <c r="X116" s="6" t="n"/>
+      <c r="Y116" s="5" t="n"/>
+      <c r="Z116" s="5" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="n"/>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="15" t="n"/>
+      <c r="F117" s="7" t="n"/>
+      <c r="G117" s="7" t="n"/>
+      <c r="H117" s="7" t="n"/>
+      <c r="I117" s="7" t="n"/>
+      <c r="J117" s="7" t="n"/>
+      <c r="K117" s="5" t="n"/>
+      <c r="L117" s="7" t="n"/>
+      <c r="M117" s="7" t="n"/>
+      <c r="N117" s="15" t="n"/>
+      <c r="O117" s="15" t="n"/>
+      <c r="P117" s="15" t="n"/>
+      <c r="Q117" s="7" t="n"/>
+      <c r="R117" s="7" t="n"/>
+      <c r="S117" s="7" t="n"/>
+      <c r="T117" s="7" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="6" t="n"/>
+      <c r="W117" s="5" t="n"/>
+      <c r="X117" s="6" t="n"/>
+      <c r="Y117" s="5" t="n"/>
+      <c r="Z117" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="n"/>
+      <c r="B118" s="5" t="n"/>
+      <c r="C118" s="7" t="n"/>
+      <c r="D118" s="5" t="n"/>
+      <c r="E118" s="15" t="n"/>
+      <c r="F118" s="7" t="n"/>
+      <c r="G118" s="7" t="n"/>
+      <c r="H118" s="7" t="n"/>
+      <c r="I118" s="7" t="n"/>
+      <c r="J118" s="7" t="n"/>
+      <c r="K118" s="5" t="n"/>
+      <c r="L118" s="7" t="n"/>
+      <c r="M118" s="7" t="n"/>
+      <c r="N118" s="15" t="n"/>
+      <c r="O118" s="15" t="n"/>
+      <c r="P118" s="15" t="n"/>
+      <c r="Q118" s="7" t="n"/>
+      <c r="R118" s="7" t="n"/>
+      <c r="S118" s="7" t="n"/>
+      <c r="T118" s="7" t="n"/>
+      <c r="U118" s="7" t="n"/>
+      <c r="V118" s="6" t="n"/>
+      <c r="W118" s="5" t="n"/>
+      <c r="X118" s="6" t="n"/>
+      <c r="Y118" s="5" t="n"/>
+      <c r="Z118" s="5" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="n"/>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="15" t="n"/>
+      <c r="F119" s="7" t="n"/>
+      <c r="G119" s="7" t="n"/>
+      <c r="H119" s="7" t="n"/>
+      <c r="I119" s="7" t="n"/>
+      <c r="J119" s="7" t="n"/>
+      <c r="K119" s="5" t="n"/>
+      <c r="L119" s="7" t="n"/>
+      <c r="M119" s="7" t="n"/>
+      <c r="N119" s="15" t="n"/>
+      <c r="O119" s="15" t="n"/>
+      <c r="P119" s="15" t="n"/>
+      <c r="Q119" s="7" t="n"/>
+      <c r="R119" s="7" t="n"/>
+      <c r="S119" s="7" t="n"/>
+      <c r="T119" s="7" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="6" t="n"/>
+      <c r="W119" s="5" t="n"/>
+      <c r="X119" s="6" t="n"/>
+      <c r="Y119" s="5" t="n"/>
+      <c r="Z119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="n"/>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="7" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="15" t="n"/>
+      <c r="F120" s="7" t="n"/>
+      <c r="G120" s="7" t="n"/>
+      <c r="H120" s="7" t="n"/>
+      <c r="I120" s="7" t="n"/>
+      <c r="J120" s="7" t="n"/>
+      <c r="K120" s="5" t="n"/>
+      <c r="L120" s="7" t="n"/>
+      <c r="M120" s="7" t="n"/>
+      <c r="N120" s="15" t="n"/>
+      <c r="O120" s="15" t="n"/>
+      <c r="P120" s="15" t="n"/>
+      <c r="Q120" s="7" t="n"/>
+      <c r="R120" s="7" t="n"/>
+      <c r="S120" s="7" t="n"/>
+      <c r="T120" s="7" t="n"/>
+      <c r="U120" s="7" t="n"/>
+      <c r="V120" s="6" t="n"/>
+      <c r="W120" s="5" t="n"/>
+      <c r="X120" s="6" t="n"/>
+      <c r="Y120" s="5" t="n"/>
+      <c r="Z120" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Z1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="Pick one of: RK Group, RK World Infocom, Robust Kommerce, Westbury Kommerce" promptTitle="B" prompt="One row per entity per week. APPEND, never overwrite." type="list">
+      <formula1>"RK Group,RK World Infocom,Robust Kommerce,Westbury Kommerce"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -943,10 +943,7 @@
       <c r="A2" s="5" t="n"/>
       <c r="B2" s="6" t="n"/>
       <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6">
-        <f>IF($C2="","",$C2-MOD(WEEKDAY($C2,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D2" s="6" t="n"/>
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="5" t="n"/>
@@ -970,10 +967,7 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6">
-        <f>IF($C3="","",$C3-MOD(WEEKDAY($C3,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D3" s="6" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
@@ -997,10 +991,7 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6">
-        <f>IF($C4="","",$C4-MOD(WEEKDAY($C4,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
@@ -1024,10 +1015,7 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6">
-        <f>IF($C5="","",$C5-MOD(WEEKDAY($C5,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
@@ -1051,10 +1039,7 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6">
-        <f>IF($C6="","",$C6-MOD(WEEKDAY($C6,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
@@ -1078,10 +1063,7 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6">
-        <f>IF($C7="","",$C7-MOD(WEEKDAY($C7,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
@@ -1105,10 +1087,7 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6">
-        <f>IF($C8="","",$C8-MOD(WEEKDAY($C8,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
@@ -1132,10 +1111,7 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6">
-        <f>IF($C9="","",$C9-MOD(WEEKDAY($C9,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
@@ -1159,10 +1135,7 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6">
-        <f>IF($C10="","",$C10-MOD(WEEKDAY($C10,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
@@ -1186,10 +1159,7 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6">
-        <f>IF($C11="","",$C11-MOD(WEEKDAY($C11,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D11" s="6" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
@@ -1213,10 +1183,7 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6">
-        <f>IF($C12="","",$C12-MOD(WEEKDAY($C12,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
@@ -1240,10 +1207,7 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6">
-        <f>IF($C13="","",$C13-MOD(WEEKDAY($C13,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D13" s="6" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
@@ -1267,10 +1231,7 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6">
-        <f>IF($C14="","",$C14-MOD(WEEKDAY($C14,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
@@ -1294,10 +1255,7 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6">
-        <f>IF($C15="","",$C15-MOD(WEEKDAY($C15,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D15" s="6" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
@@ -1321,10 +1279,7 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6">
-        <f>IF($C16="","",$C16-MOD(WEEKDAY($C16,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
@@ -1348,10 +1303,7 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6">
-        <f>IF($C17="","",$C17-MOD(WEEKDAY($C17,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D17" s="6" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
@@ -1375,10 +1327,7 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6">
-        <f>IF($C18="","",$C18-MOD(WEEKDAY($C18,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D18" s="6" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
@@ -1402,10 +1351,7 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6">
-        <f>IF($C19="","",$C19-MOD(WEEKDAY($C19,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D19" s="6" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
@@ -1429,10 +1375,7 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6">
-        <f>IF($C20="","",$C20-MOD(WEEKDAY($C20,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D20" s="6" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
@@ -1456,10 +1399,7 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6">
-        <f>IF($C21="","",$C21-MOD(WEEKDAY($C21,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D21" s="6" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
@@ -1483,10 +1423,7 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6">
-        <f>IF($C22="","",$C22-MOD(WEEKDAY($C22,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D22" s="6" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
@@ -1510,10 +1447,7 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6">
-        <f>IF($C23="","",$C23-MOD(WEEKDAY($C23,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D23" s="6" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
@@ -1537,10 +1471,7 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6">
-        <f>IF($C24="","",$C24-MOD(WEEKDAY($C24,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D24" s="6" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
@@ -1564,10 +1495,7 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6">
-        <f>IF($C25="","",$C25-MOD(WEEKDAY($C25,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D25" s="6" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
@@ -1591,10 +1519,7 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6">
-        <f>IF($C26="","",$C26-MOD(WEEKDAY($C26,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D26" s="6" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
@@ -1618,10 +1543,7 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6">
-        <f>IF($C27="","",$C27-MOD(WEEKDAY($C27,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D27" s="6" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
@@ -1645,10 +1567,7 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6">
-        <f>IF($C28="","",$C28-MOD(WEEKDAY($C28,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D28" s="6" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
@@ -1672,10 +1591,7 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6">
-        <f>IF($C29="","",$C29-MOD(WEEKDAY($C29,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D29" s="6" t="n"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
@@ -1699,10 +1615,7 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6">
-        <f>IF($C30="","",$C30-MOD(WEEKDAY($C30,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D30" s="6" t="n"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
@@ -1726,10 +1639,7 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6">
-        <f>IF($C31="","",$C31-MOD(WEEKDAY($C31,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D31" s="6" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
@@ -1753,10 +1663,7 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6">
-        <f>IF($C32="","",$C32-MOD(WEEKDAY($C32,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D32" s="6" t="n"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
@@ -1780,10 +1687,7 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6">
-        <f>IF($C33="","",$C33-MOD(WEEKDAY($C33,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D33" s="6" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
@@ -1807,10 +1711,7 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6">
-        <f>IF($C34="","",$C34-MOD(WEEKDAY($C34,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D34" s="6" t="n"/>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
@@ -1834,10 +1735,7 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6">
-        <f>IF($C35="","",$C35-MOD(WEEKDAY($C35,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D35" s="6" t="n"/>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
@@ -1861,10 +1759,7 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6">
-        <f>IF($C36="","",$C36-MOD(WEEKDAY($C36,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D36" s="6" t="n"/>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
@@ -1888,10 +1783,7 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6">
-        <f>IF($C37="","",$C37-MOD(WEEKDAY($C37,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D37" s="6" t="n"/>
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
@@ -1915,10 +1807,7 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6">
-        <f>IF($C38="","",$C38-MOD(WEEKDAY($C38,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D38" s="6" t="n"/>
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="5" t="n"/>
@@ -1942,10 +1831,7 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6">
-        <f>IF($C39="","",$C39-MOD(WEEKDAY($C39,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D39" s="6" t="n"/>
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
@@ -1969,10 +1855,7 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6">
-        <f>IF($C40="","",$C40-MOD(WEEKDAY($C40,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D40" s="6" t="n"/>
       <c r="E40" s="5" t="n"/>
       <c r="F40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
@@ -1996,10 +1879,7 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6">
-        <f>IF($C41="","",$C41-MOD(WEEKDAY($C41,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D41" s="6" t="n"/>
       <c r="E41" s="5" t="n"/>
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
@@ -2023,10 +1903,7 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6">
-        <f>IF($C42="","",$C42-MOD(WEEKDAY($C42,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D42" s="6" t="n"/>
       <c r="E42" s="5" t="n"/>
       <c r="F42" s="5" t="n"/>
       <c r="G42" s="5" t="n"/>
@@ -2050,10 +1927,7 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="6" t="n"/>
       <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6">
-        <f>IF($C43="","",$C43-MOD(WEEKDAY($C43,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D43" s="6" t="n"/>
       <c r="E43" s="5" t="n"/>
       <c r="F43" s="5" t="n"/>
       <c r="G43" s="5" t="n"/>
@@ -2077,10 +1951,7 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6">
-        <f>IF($C44="","",$C44-MOD(WEEKDAY($C44,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D44" s="6" t="n"/>
       <c r="E44" s="5" t="n"/>
       <c r="F44" s="5" t="n"/>
       <c r="G44" s="5" t="n"/>
@@ -2104,10 +1975,7 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="6" t="n"/>
       <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6">
-        <f>IF($C45="","",$C45-MOD(WEEKDAY($C45,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D45" s="6" t="n"/>
       <c r="E45" s="5" t="n"/>
       <c r="F45" s="5" t="n"/>
       <c r="G45" s="5" t="n"/>
@@ -2131,10 +1999,7 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6">
-        <f>IF($C46="","",$C46-MOD(WEEKDAY($C46,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D46" s="6" t="n"/>
       <c r="E46" s="5" t="n"/>
       <c r="F46" s="5" t="n"/>
       <c r="G46" s="5" t="n"/>
@@ -2158,10 +2023,7 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="6" t="n"/>
       <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6">
-        <f>IF($C47="","",$C47-MOD(WEEKDAY($C47,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D47" s="6" t="n"/>
       <c r="E47" s="5" t="n"/>
       <c r="F47" s="5" t="n"/>
       <c r="G47" s="5" t="n"/>
@@ -2185,10 +2047,7 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6">
-        <f>IF($C48="","",$C48-MOD(WEEKDAY($C48,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D48" s="6" t="n"/>
       <c r="E48" s="5" t="n"/>
       <c r="F48" s="5" t="n"/>
       <c r="G48" s="5" t="n"/>
@@ -2212,10 +2071,7 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6">
-        <f>IF($C49="","",$C49-MOD(WEEKDAY($C49,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D49" s="6" t="n"/>
       <c r="E49" s="5" t="n"/>
       <c r="F49" s="5" t="n"/>
       <c r="G49" s="5" t="n"/>
@@ -2239,10 +2095,7 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="6" t="n"/>
       <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6">
-        <f>IF($C50="","",$C50-MOD(WEEKDAY($C50,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D50" s="6" t="n"/>
       <c r="E50" s="5" t="n"/>
       <c r="F50" s="5" t="n"/>
       <c r="G50" s="5" t="n"/>
@@ -2266,10 +2119,7 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6">
-        <f>IF($C51="","",$C51-MOD(WEEKDAY($C51,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D51" s="6" t="n"/>
       <c r="E51" s="5" t="n"/>
       <c r="F51" s="5" t="n"/>
       <c r="G51" s="5" t="n"/>
@@ -2293,10 +2143,7 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6">
-        <f>IF($C52="","",$C52-MOD(WEEKDAY($C52,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D52" s="6" t="n"/>
       <c r="E52" s="5" t="n"/>
       <c r="F52" s="5" t="n"/>
       <c r="G52" s="5" t="n"/>
@@ -2320,10 +2167,7 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="6" t="n"/>
       <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6">
-        <f>IF($C53="","",$C53-MOD(WEEKDAY($C53,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D53" s="6" t="n"/>
       <c r="E53" s="5" t="n"/>
       <c r="F53" s="5" t="n"/>
       <c r="G53" s="5" t="n"/>
@@ -2347,10 +2191,7 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="6" t="n"/>
       <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6">
-        <f>IF($C54="","",$C54-MOD(WEEKDAY($C54,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D54" s="6" t="n"/>
       <c r="E54" s="5" t="n"/>
       <c r="F54" s="5" t="n"/>
       <c r="G54" s="5" t="n"/>
@@ -2374,10 +2215,7 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6">
-        <f>IF($C55="","",$C55-MOD(WEEKDAY($C55,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D55" s="6" t="n"/>
       <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="n"/>
       <c r="G55" s="5" t="n"/>
@@ -2401,10 +2239,7 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6">
-        <f>IF($C56="","",$C56-MOD(WEEKDAY($C56,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D56" s="6" t="n"/>
       <c r="E56" s="5" t="n"/>
       <c r="F56" s="5" t="n"/>
       <c r="G56" s="5" t="n"/>
@@ -2428,10 +2263,7 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6">
-        <f>IF($C57="","",$C57-MOD(WEEKDAY($C57,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D57" s="6" t="n"/>
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="n"/>
       <c r="G57" s="5" t="n"/>
@@ -2455,10 +2287,7 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="6" t="n"/>
       <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6">
-        <f>IF($C58="","",$C58-MOD(WEEKDAY($C58,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D58" s="6" t="n"/>
       <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="n"/>
       <c r="G58" s="5" t="n"/>
@@ -2482,10 +2311,7 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="6" t="n"/>
       <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6">
-        <f>IF($C59="","",$C59-MOD(WEEKDAY($C59,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D59" s="6" t="n"/>
       <c r="E59" s="5" t="n"/>
       <c r="F59" s="5" t="n"/>
       <c r="G59" s="5" t="n"/>
@@ -2509,10 +2335,7 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="6" t="n"/>
       <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6">
-        <f>IF($C60="","",$C60-MOD(WEEKDAY($C60,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D60" s="6" t="n"/>
       <c r="E60" s="5" t="n"/>
       <c r="F60" s="5" t="n"/>
       <c r="G60" s="5" t="n"/>
@@ -2536,10 +2359,7 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6">
-        <f>IF($C61="","",$C61-MOD(WEEKDAY($C61,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D61" s="6" t="n"/>
       <c r="E61" s="5" t="n"/>
       <c r="F61" s="5" t="n"/>
       <c r="G61" s="5" t="n"/>
@@ -2563,10 +2383,7 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6">
-        <f>IF($C62="","",$C62-MOD(WEEKDAY($C62,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D62" s="6" t="n"/>
       <c r="E62" s="5" t="n"/>
       <c r="F62" s="5" t="n"/>
       <c r="G62" s="5" t="n"/>
@@ -2590,10 +2407,7 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="6" t="n"/>
       <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6">
-        <f>IF($C63="","",$C63-MOD(WEEKDAY($C63,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D63" s="6" t="n"/>
       <c r="E63" s="5" t="n"/>
       <c r="F63" s="5" t="n"/>
       <c r="G63" s="5" t="n"/>
@@ -2617,10 +2431,7 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="6" t="n"/>
       <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6">
-        <f>IF($C64="","",$C64-MOD(WEEKDAY($C64,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D64" s="6" t="n"/>
       <c r="E64" s="5" t="n"/>
       <c r="F64" s="5" t="n"/>
       <c r="G64" s="5" t="n"/>
@@ -2644,10 +2455,7 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="6" t="n"/>
-      <c r="D65" s="6">
-        <f>IF($C65="","",$C65-MOD(WEEKDAY($C65,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D65" s="6" t="n"/>
       <c r="E65" s="5" t="n"/>
       <c r="F65" s="5" t="n"/>
       <c r="G65" s="5" t="n"/>
@@ -2671,10 +2479,7 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="6" t="n"/>
       <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6">
-        <f>IF($C66="","",$C66-MOD(WEEKDAY($C66,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D66" s="6" t="n"/>
       <c r="E66" s="5" t="n"/>
       <c r="F66" s="5" t="n"/>
       <c r="G66" s="5" t="n"/>
@@ -2698,10 +2503,7 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="6" t="n"/>
       <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6">
-        <f>IF($C67="","",$C67-MOD(WEEKDAY($C67,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D67" s="6" t="n"/>
       <c r="E67" s="5" t="n"/>
       <c r="F67" s="5" t="n"/>
       <c r="G67" s="5" t="n"/>
@@ -2725,10 +2527,7 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="6" t="n"/>
       <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6">
-        <f>IF($C68="","",$C68-MOD(WEEKDAY($C68,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D68" s="6" t="n"/>
       <c r="E68" s="5" t="n"/>
       <c r="F68" s="5" t="n"/>
       <c r="G68" s="5" t="n"/>
@@ -2752,10 +2551,7 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="6" t="n"/>
       <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6">
-        <f>IF($C69="","",$C69-MOD(WEEKDAY($C69,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D69" s="6" t="n"/>
       <c r="E69" s="5" t="n"/>
       <c r="F69" s="5" t="n"/>
       <c r="G69" s="5" t="n"/>
@@ -2779,10 +2575,7 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="6" t="n"/>
       <c r="C70" s="6" t="n"/>
-      <c r="D70" s="6">
-        <f>IF($C70="","",$C70-MOD(WEEKDAY($C70,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D70" s="6" t="n"/>
       <c r="E70" s="5" t="n"/>
       <c r="F70" s="5" t="n"/>
       <c r="G70" s="5" t="n"/>
@@ -2806,10 +2599,7 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="6" t="n"/>
       <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6">
-        <f>IF($C71="","",$C71-MOD(WEEKDAY($C71,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D71" s="6" t="n"/>
       <c r="E71" s="5" t="n"/>
       <c r="F71" s="5" t="n"/>
       <c r="G71" s="5" t="n"/>
@@ -2833,10 +2623,7 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="6" t="n"/>
       <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6">
-        <f>IF($C72="","",$C72-MOD(WEEKDAY($C72,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D72" s="6" t="n"/>
       <c r="E72" s="5" t="n"/>
       <c r="F72" s="5" t="n"/>
       <c r="G72" s="5" t="n"/>
@@ -2860,10 +2647,7 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="6" t="n"/>
       <c r="C73" s="6" t="n"/>
-      <c r="D73" s="6">
-        <f>IF($C73="","",$C73-MOD(WEEKDAY($C73,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D73" s="6" t="n"/>
       <c r="E73" s="5" t="n"/>
       <c r="F73" s="5" t="n"/>
       <c r="G73" s="5" t="n"/>
@@ -2887,10 +2671,7 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="6" t="n"/>
       <c r="C74" s="6" t="n"/>
-      <c r="D74" s="6">
-        <f>IF($C74="","",$C74-MOD(WEEKDAY($C74,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D74" s="6" t="n"/>
       <c r="E74" s="5" t="n"/>
       <c r="F74" s="5" t="n"/>
       <c r="G74" s="5" t="n"/>
@@ -2914,10 +2695,7 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="6" t="n"/>
       <c r="C75" s="6" t="n"/>
-      <c r="D75" s="6">
-        <f>IF($C75="","",$C75-MOD(WEEKDAY($C75,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D75" s="6" t="n"/>
       <c r="E75" s="5" t="n"/>
       <c r="F75" s="5" t="n"/>
       <c r="G75" s="5" t="n"/>
@@ -2941,10 +2719,7 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="6" t="n"/>
       <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6">
-        <f>IF($C76="","",$C76-MOD(WEEKDAY($C76,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D76" s="6" t="n"/>
       <c r="E76" s="5" t="n"/>
       <c r="F76" s="5" t="n"/>
       <c r="G76" s="5" t="n"/>
@@ -2968,10 +2743,7 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="6" t="n"/>
       <c r="C77" s="6" t="n"/>
-      <c r="D77" s="6">
-        <f>IF($C77="","",$C77-MOD(WEEKDAY($C77,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D77" s="6" t="n"/>
       <c r="E77" s="5" t="n"/>
       <c r="F77" s="5" t="n"/>
       <c r="G77" s="5" t="n"/>
@@ -2995,10 +2767,7 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="6" t="n"/>
       <c r="C78" s="6" t="n"/>
-      <c r="D78" s="6">
-        <f>IF($C78="","",$C78-MOD(WEEKDAY($C78,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D78" s="6" t="n"/>
       <c r="E78" s="5" t="n"/>
       <c r="F78" s="5" t="n"/>
       <c r="G78" s="5" t="n"/>
@@ -3022,10 +2791,7 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="6" t="n"/>
       <c r="C79" s="6" t="n"/>
-      <c r="D79" s="6">
-        <f>IF($C79="","",$C79-MOD(WEEKDAY($C79,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D79" s="6" t="n"/>
       <c r="E79" s="5" t="n"/>
       <c r="F79" s="5" t="n"/>
       <c r="G79" s="5" t="n"/>
@@ -3049,10 +2815,7 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="6" t="n"/>
       <c r="C80" s="6" t="n"/>
-      <c r="D80" s="6">
-        <f>IF($C80="","",$C80-MOD(WEEKDAY($C80,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D80" s="6" t="n"/>
       <c r="E80" s="5" t="n"/>
       <c r="F80" s="5" t="n"/>
       <c r="G80" s="5" t="n"/>
@@ -3076,10 +2839,7 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="6" t="n"/>
       <c r="C81" s="6" t="n"/>
-      <c r="D81" s="6">
-        <f>IF($C81="","",$C81-MOD(WEEKDAY($C81,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D81" s="6" t="n"/>
       <c r="E81" s="5" t="n"/>
       <c r="F81" s="5" t="n"/>
       <c r="G81" s="5" t="n"/>
@@ -3103,10 +2863,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="6" t="n"/>
       <c r="C82" s="6" t="n"/>
-      <c r="D82" s="6">
-        <f>IF($C82="","",$C82-MOD(WEEKDAY($C82,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D82" s="6" t="n"/>
       <c r="E82" s="5" t="n"/>
       <c r="F82" s="5" t="n"/>
       <c r="G82" s="5" t="n"/>
@@ -3130,10 +2887,7 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="6" t="n"/>
       <c r="C83" s="6" t="n"/>
-      <c r="D83" s="6">
-        <f>IF($C83="","",$C83-MOD(WEEKDAY($C83,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D83" s="6" t="n"/>
       <c r="E83" s="5" t="n"/>
       <c r="F83" s="5" t="n"/>
       <c r="G83" s="5" t="n"/>
@@ -3157,10 +2911,7 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="6" t="n"/>
       <c r="C84" s="6" t="n"/>
-      <c r="D84" s="6">
-        <f>IF($C84="","",$C84-MOD(WEEKDAY($C84,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D84" s="6" t="n"/>
       <c r="E84" s="5" t="n"/>
       <c r="F84" s="5" t="n"/>
       <c r="G84" s="5" t="n"/>
@@ -3184,10 +2935,7 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="6" t="n"/>
       <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6">
-        <f>IF($C85="","",$C85-MOD(WEEKDAY($C85,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D85" s="6" t="n"/>
       <c r="E85" s="5" t="n"/>
       <c r="F85" s="5" t="n"/>
       <c r="G85" s="5" t="n"/>
@@ -3211,10 +2959,7 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="6" t="n"/>
       <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6">
-        <f>IF($C86="","",$C86-MOD(WEEKDAY($C86,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D86" s="6" t="n"/>
       <c r="E86" s="5" t="n"/>
       <c r="F86" s="5" t="n"/>
       <c r="G86" s="5" t="n"/>
@@ -3238,10 +2983,7 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="6" t="n"/>
       <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6">
-        <f>IF($C87="","",$C87-MOD(WEEKDAY($C87,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D87" s="6" t="n"/>
       <c r="E87" s="5" t="n"/>
       <c r="F87" s="5" t="n"/>
       <c r="G87" s="5" t="n"/>
@@ -3265,10 +3007,7 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="6" t="n"/>
       <c r="C88" s="6" t="n"/>
-      <c r="D88" s="6">
-        <f>IF($C88="","",$C88-MOD(WEEKDAY($C88,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D88" s="6" t="n"/>
       <c r="E88" s="5" t="n"/>
       <c r="F88" s="5" t="n"/>
       <c r="G88" s="5" t="n"/>
@@ -3292,10 +3031,7 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="6" t="n"/>
       <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6">
-        <f>IF($C89="","",$C89-MOD(WEEKDAY($C89,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D89" s="6" t="n"/>
       <c r="E89" s="5" t="n"/>
       <c r="F89" s="5" t="n"/>
       <c r="G89" s="5" t="n"/>
@@ -3319,10 +3055,7 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="6" t="n"/>
       <c r="C90" s="6" t="n"/>
-      <c r="D90" s="6">
-        <f>IF($C90="","",$C90-MOD(WEEKDAY($C90,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D90" s="6" t="n"/>
       <c r="E90" s="5" t="n"/>
       <c r="F90" s="5" t="n"/>
       <c r="G90" s="5" t="n"/>
@@ -3346,10 +3079,7 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="6" t="n"/>
       <c r="C91" s="6" t="n"/>
-      <c r="D91" s="6">
-        <f>IF($C91="","",$C91-MOD(WEEKDAY($C91,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D91" s="6" t="n"/>
       <c r="E91" s="5" t="n"/>
       <c r="F91" s="5" t="n"/>
       <c r="G91" s="5" t="n"/>
@@ -3373,10 +3103,7 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="6" t="n"/>
       <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6">
-        <f>IF($C92="","",$C92-MOD(WEEKDAY($C92,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D92" s="6" t="n"/>
       <c r="E92" s="5" t="n"/>
       <c r="F92" s="5" t="n"/>
       <c r="G92" s="5" t="n"/>
@@ -3400,10 +3127,7 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="6" t="n"/>
       <c r="C93" s="6" t="n"/>
-      <c r="D93" s="6">
-        <f>IF($C93="","",$C93-MOD(WEEKDAY($C93,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D93" s="6" t="n"/>
       <c r="E93" s="5" t="n"/>
       <c r="F93" s="5" t="n"/>
       <c r="G93" s="5" t="n"/>
@@ -3427,10 +3151,7 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="6" t="n"/>
       <c r="C94" s="6" t="n"/>
-      <c r="D94" s="6">
-        <f>IF($C94="","",$C94-MOD(WEEKDAY($C94,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D94" s="6" t="n"/>
       <c r="E94" s="5" t="n"/>
       <c r="F94" s="5" t="n"/>
       <c r="G94" s="5" t="n"/>
@@ -3454,10 +3175,7 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="6" t="n"/>
       <c r="C95" s="6" t="n"/>
-      <c r="D95" s="6">
-        <f>IF($C95="","",$C95-MOD(WEEKDAY($C95,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D95" s="6" t="n"/>
       <c r="E95" s="5" t="n"/>
       <c r="F95" s="5" t="n"/>
       <c r="G95" s="5" t="n"/>
@@ -3481,10 +3199,7 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="6" t="n"/>
       <c r="C96" s="6" t="n"/>
-      <c r="D96" s="6">
-        <f>IF($C96="","",$C96-MOD(WEEKDAY($C96,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D96" s="6" t="n"/>
       <c r="E96" s="5" t="n"/>
       <c r="F96" s="5" t="n"/>
       <c r="G96" s="5" t="n"/>
@@ -3508,10 +3223,7 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="6" t="n"/>
       <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6">
-        <f>IF($C97="","",$C97-MOD(WEEKDAY($C97,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D97" s="6" t="n"/>
       <c r="E97" s="5" t="n"/>
       <c r="F97" s="5" t="n"/>
       <c r="G97" s="5" t="n"/>
@@ -3535,10 +3247,7 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="6" t="n"/>
       <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6">
-        <f>IF($C98="","",$C98-MOD(WEEKDAY($C98,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D98" s="6" t="n"/>
       <c r="E98" s="5" t="n"/>
       <c r="F98" s="5" t="n"/>
       <c r="G98" s="5" t="n"/>
@@ -3562,10 +3271,7 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="6" t="n"/>
       <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6">
-        <f>IF($C99="","",$C99-MOD(WEEKDAY($C99,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D99" s="6" t="n"/>
       <c r="E99" s="5" t="n"/>
       <c r="F99" s="5" t="n"/>
       <c r="G99" s="5" t="n"/>
@@ -3589,10 +3295,7 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="6" t="n"/>
       <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6">
-        <f>IF($C100="","",$C100-MOD(WEEKDAY($C100,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D100" s="6" t="n"/>
       <c r="E100" s="5" t="n"/>
       <c r="F100" s="5" t="n"/>
       <c r="G100" s="5" t="n"/>
@@ -3616,10 +3319,7 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="6" t="n"/>
       <c r="C101" s="6" t="n"/>
-      <c r="D101" s="6">
-        <f>IF($C101="","",$C101-MOD(WEEKDAY($C101,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D101" s="6" t="n"/>
       <c r="E101" s="5" t="n"/>
       <c r="F101" s="5" t="n"/>
       <c r="G101" s="5" t="n"/>
@@ -3643,10 +3343,7 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="6" t="n"/>
       <c r="C102" s="6" t="n"/>
-      <c r="D102" s="6">
-        <f>IF($C102="","",$C102-MOD(WEEKDAY($C102,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D102" s="6" t="n"/>
       <c r="E102" s="5" t="n"/>
       <c r="F102" s="5" t="n"/>
       <c r="G102" s="5" t="n"/>
@@ -3670,10 +3367,7 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="6" t="n"/>
       <c r="C103" s="6" t="n"/>
-      <c r="D103" s="6">
-        <f>IF($C103="","",$C103-MOD(WEEKDAY($C103,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D103" s="6" t="n"/>
       <c r="E103" s="5" t="n"/>
       <c r="F103" s="5" t="n"/>
       <c r="G103" s="5" t="n"/>
@@ -3697,10 +3391,7 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="6" t="n"/>
       <c r="C104" s="6" t="n"/>
-      <c r="D104" s="6">
-        <f>IF($C104="","",$C104-MOD(WEEKDAY($C104,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D104" s="6" t="n"/>
       <c r="E104" s="5" t="n"/>
       <c r="F104" s="5" t="n"/>
       <c r="G104" s="5" t="n"/>
@@ -3724,10 +3415,7 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="6" t="n"/>
       <c r="C105" s="6" t="n"/>
-      <c r="D105" s="6">
-        <f>IF($C105="","",$C105-MOD(WEEKDAY($C105,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D105" s="6" t="n"/>
       <c r="E105" s="5" t="n"/>
       <c r="F105" s="5" t="n"/>
       <c r="G105" s="5" t="n"/>
@@ -3751,10 +3439,7 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="6" t="n"/>
       <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6">
-        <f>IF($C106="","",$C106-MOD(WEEKDAY($C106,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D106" s="6" t="n"/>
       <c r="E106" s="5" t="n"/>
       <c r="F106" s="5" t="n"/>
       <c r="G106" s="5" t="n"/>
@@ -3778,10 +3463,7 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="6" t="n"/>
       <c r="C107" s="6" t="n"/>
-      <c r="D107" s="6">
-        <f>IF($C107="","",$C107-MOD(WEEKDAY($C107,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D107" s="6" t="n"/>
       <c r="E107" s="5" t="n"/>
       <c r="F107" s="5" t="n"/>
       <c r="G107" s="5" t="n"/>
@@ -3805,10 +3487,7 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="6" t="n"/>
       <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6">
-        <f>IF($C108="","",$C108-MOD(WEEKDAY($C108,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D108" s="6" t="n"/>
       <c r="E108" s="5" t="n"/>
       <c r="F108" s="5" t="n"/>
       <c r="G108" s="5" t="n"/>
@@ -3832,10 +3511,7 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="6" t="n"/>
       <c r="C109" s="6" t="n"/>
-      <c r="D109" s="6">
-        <f>IF($C109="","",$C109-MOD(WEEKDAY($C109,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D109" s="6" t="n"/>
       <c r="E109" s="5" t="n"/>
       <c r="F109" s="5" t="n"/>
       <c r="G109" s="5" t="n"/>
@@ -3859,10 +3535,7 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="6" t="n"/>
       <c r="C110" s="6" t="n"/>
-      <c r="D110" s="6">
-        <f>IF($C110="","",$C110-MOD(WEEKDAY($C110,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D110" s="6" t="n"/>
       <c r="E110" s="5" t="n"/>
       <c r="F110" s="5" t="n"/>
       <c r="G110" s="5" t="n"/>
@@ -3886,10 +3559,7 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="6" t="n"/>
       <c r="C111" s="6" t="n"/>
-      <c r="D111" s="6">
-        <f>IF($C111="","",$C111-MOD(WEEKDAY($C111,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D111" s="6" t="n"/>
       <c r="E111" s="5" t="n"/>
       <c r="F111" s="5" t="n"/>
       <c r="G111" s="5" t="n"/>
@@ -3913,10 +3583,7 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="6" t="n"/>
       <c r="C112" s="6" t="n"/>
-      <c r="D112" s="6">
-        <f>IF($C112="","",$C112-MOD(WEEKDAY($C112,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D112" s="6" t="n"/>
       <c r="E112" s="5" t="n"/>
       <c r="F112" s="5" t="n"/>
       <c r="G112" s="5" t="n"/>
@@ -3940,10 +3607,7 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="6" t="n"/>
       <c r="C113" s="6" t="n"/>
-      <c r="D113" s="6">
-        <f>IF($C113="","",$C113-MOD(WEEKDAY($C113,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D113" s="6" t="n"/>
       <c r="E113" s="5" t="n"/>
       <c r="F113" s="5" t="n"/>
       <c r="G113" s="5" t="n"/>
@@ -3967,10 +3631,7 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="6" t="n"/>
       <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6">
-        <f>IF($C114="","",$C114-MOD(WEEKDAY($C114,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D114" s="6" t="n"/>
       <c r="E114" s="5" t="n"/>
       <c r="F114" s="5" t="n"/>
       <c r="G114" s="5" t="n"/>
@@ -3994,10 +3655,7 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="6" t="n"/>
       <c r="C115" s="6" t="n"/>
-      <c r="D115" s="6">
-        <f>IF($C115="","",$C115-MOD(WEEKDAY($C115,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D115" s="6" t="n"/>
       <c r="E115" s="5" t="n"/>
       <c r="F115" s="5" t="n"/>
       <c r="G115" s="5" t="n"/>
@@ -4021,10 +3679,7 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="6" t="n"/>
       <c r="C116" s="6" t="n"/>
-      <c r="D116" s="6">
-        <f>IF($C116="","",$C116-MOD(WEEKDAY($C116,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D116" s="6" t="n"/>
       <c r="E116" s="5" t="n"/>
       <c r="F116" s="5" t="n"/>
       <c r="G116" s="5" t="n"/>
@@ -4048,10 +3703,7 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="6" t="n"/>
       <c r="C117" s="6" t="n"/>
-      <c r="D117" s="6">
-        <f>IF($C117="","",$C117-MOD(WEEKDAY($C117,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D117" s="6" t="n"/>
       <c r="E117" s="5" t="n"/>
       <c r="F117" s="5" t="n"/>
       <c r="G117" s="5" t="n"/>
@@ -4075,10 +3727,7 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="6" t="n"/>
       <c r="C118" s="6" t="n"/>
-      <c r="D118" s="6">
-        <f>IF($C118="","",$C118-MOD(WEEKDAY($C118,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D118" s="6" t="n"/>
       <c r="E118" s="5" t="n"/>
       <c r="F118" s="5" t="n"/>
       <c r="G118" s="5" t="n"/>
@@ -4102,10 +3751,7 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="6" t="n"/>
       <c r="C119" s="6" t="n"/>
-      <c r="D119" s="6">
-        <f>IF($C119="","",$C119-MOD(WEEKDAY($C119,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D119" s="6" t="n"/>
       <c r="E119" s="5" t="n"/>
       <c r="F119" s="5" t="n"/>
       <c r="G119" s="5" t="n"/>
@@ -4129,10 +3775,7 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="6" t="n"/>
       <c r="C120" s="6" t="n"/>
-      <c r="D120" s="6">
-        <f>IF($C120="","",$C120-MOD(WEEKDAY($C120,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D120" s="6" t="n"/>
       <c r="E120" s="5" t="n"/>
       <c r="F120" s="5" t="n"/>
       <c r="G120" s="5" t="n"/>
@@ -4156,10 +3799,7 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="6" t="n"/>
       <c r="C121" s="6" t="n"/>
-      <c r="D121" s="6">
-        <f>IF($C121="","",$C121-MOD(WEEKDAY($C121,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D121" s="6" t="n"/>
       <c r="E121" s="5" t="n"/>
       <c r="F121" s="5" t="n"/>
       <c r="G121" s="5" t="n"/>
@@ -4183,10 +3823,7 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="6" t="n"/>
       <c r="C122" s="6" t="n"/>
-      <c r="D122" s="6">
-        <f>IF($C122="","",$C122-MOD(WEEKDAY($C122,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D122" s="6" t="n"/>
       <c r="E122" s="5" t="n"/>
       <c r="F122" s="5" t="n"/>
       <c r="G122" s="5" t="n"/>
@@ -4210,10 +3847,7 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="6" t="n"/>
       <c r="C123" s="6" t="n"/>
-      <c r="D123" s="6">
-        <f>IF($C123="","",$C123-MOD(WEEKDAY($C123,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D123" s="6" t="n"/>
       <c r="E123" s="5" t="n"/>
       <c r="F123" s="5" t="n"/>
       <c r="G123" s="5" t="n"/>
@@ -4237,10 +3871,7 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="6" t="n"/>
       <c r="C124" s="6" t="n"/>
-      <c r="D124" s="6">
-        <f>IF($C124="","",$C124-MOD(WEEKDAY($C124,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D124" s="6" t="n"/>
       <c r="E124" s="5" t="n"/>
       <c r="F124" s="5" t="n"/>
       <c r="G124" s="5" t="n"/>
@@ -4264,10 +3895,7 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="6" t="n"/>
       <c r="C125" s="6" t="n"/>
-      <c r="D125" s="6">
-        <f>IF($C125="","",$C125-MOD(WEEKDAY($C125,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D125" s="6" t="n"/>
       <c r="E125" s="5" t="n"/>
       <c r="F125" s="5" t="n"/>
       <c r="G125" s="5" t="n"/>
@@ -4291,10 +3919,7 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="6" t="n"/>
       <c r="C126" s="6" t="n"/>
-      <c r="D126" s="6">
-        <f>IF($C126="","",$C126-MOD(WEEKDAY($C126,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D126" s="6" t="n"/>
       <c r="E126" s="5" t="n"/>
       <c r="F126" s="5" t="n"/>
       <c r="G126" s="5" t="n"/>
@@ -4318,10 +3943,7 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="6" t="n"/>
       <c r="C127" s="6" t="n"/>
-      <c r="D127" s="6">
-        <f>IF($C127="","",$C127-MOD(WEEKDAY($C127,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D127" s="6" t="n"/>
       <c r="E127" s="5" t="n"/>
       <c r="F127" s="5" t="n"/>
       <c r="G127" s="5" t="n"/>
@@ -4345,10 +3967,7 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="6" t="n"/>
       <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6">
-        <f>IF($C128="","",$C128-MOD(WEEKDAY($C128,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D128" s="6" t="n"/>
       <c r="E128" s="5" t="n"/>
       <c r="F128" s="5" t="n"/>
       <c r="G128" s="5" t="n"/>
@@ -4372,10 +3991,7 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="6" t="n"/>
       <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6">
-        <f>IF($C129="","",$C129-MOD(WEEKDAY($C129,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D129" s="6" t="n"/>
       <c r="E129" s="5" t="n"/>
       <c r="F129" s="5" t="n"/>
       <c r="G129" s="5" t="n"/>
@@ -4399,10 +4015,7 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="6" t="n"/>
       <c r="C130" s="6" t="n"/>
-      <c r="D130" s="6">
-        <f>IF($C130="","",$C130-MOD(WEEKDAY($C130,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D130" s="6" t="n"/>
       <c r="E130" s="5" t="n"/>
       <c r="F130" s="5" t="n"/>
       <c r="G130" s="5" t="n"/>
@@ -4426,10 +4039,7 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="6" t="n"/>
       <c r="C131" s="6" t="n"/>
-      <c r="D131" s="6">
-        <f>IF($C131="","",$C131-MOD(WEEKDAY($C131,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D131" s="6" t="n"/>
       <c r="E131" s="5" t="n"/>
       <c r="F131" s="5" t="n"/>
       <c r="G131" s="5" t="n"/>
@@ -4453,10 +4063,7 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="6" t="n"/>
       <c r="C132" s="6" t="n"/>
-      <c r="D132" s="6">
-        <f>IF($C132="","",$C132-MOD(WEEKDAY($C132,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D132" s="6" t="n"/>
       <c r="E132" s="5" t="n"/>
       <c r="F132" s="5" t="n"/>
       <c r="G132" s="5" t="n"/>
@@ -4480,10 +4087,7 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="6" t="n"/>
       <c r="C133" s="6" t="n"/>
-      <c r="D133" s="6">
-        <f>IF($C133="","",$C133-MOD(WEEKDAY($C133,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D133" s="6" t="n"/>
       <c r="E133" s="5" t="n"/>
       <c r="F133" s="5" t="n"/>
       <c r="G133" s="5" t="n"/>
@@ -4507,10 +4111,7 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="6" t="n"/>
       <c r="C134" s="6" t="n"/>
-      <c r="D134" s="6">
-        <f>IF($C134="","",$C134-MOD(WEEKDAY($C134,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D134" s="6" t="n"/>
       <c r="E134" s="5" t="n"/>
       <c r="F134" s="5" t="n"/>
       <c r="G134" s="5" t="n"/>
@@ -4534,10 +4135,7 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="6" t="n"/>
       <c r="C135" s="6" t="n"/>
-      <c r="D135" s="6">
-        <f>IF($C135="","",$C135-MOD(WEEKDAY($C135,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D135" s="6" t="n"/>
       <c r="E135" s="5" t="n"/>
       <c r="F135" s="5" t="n"/>
       <c r="G135" s="5" t="n"/>
@@ -4561,10 +4159,7 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="6" t="n"/>
       <c r="C136" s="6" t="n"/>
-      <c r="D136" s="6">
-        <f>IF($C136="","",$C136-MOD(WEEKDAY($C136,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D136" s="6" t="n"/>
       <c r="E136" s="5" t="n"/>
       <c r="F136" s="5" t="n"/>
       <c r="G136" s="5" t="n"/>
@@ -4588,10 +4183,7 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="6" t="n"/>
       <c r="C137" s="6" t="n"/>
-      <c r="D137" s="6">
-        <f>IF($C137="","",$C137-MOD(WEEKDAY($C137,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D137" s="6" t="n"/>
       <c r="E137" s="5" t="n"/>
       <c r="F137" s="5" t="n"/>
       <c r="G137" s="5" t="n"/>
@@ -4615,10 +4207,7 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="6" t="n"/>
       <c r="C138" s="6" t="n"/>
-      <c r="D138" s="6">
-        <f>IF($C138="","",$C138-MOD(WEEKDAY($C138,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D138" s="6" t="n"/>
       <c r="E138" s="5" t="n"/>
       <c r="F138" s="5" t="n"/>
       <c r="G138" s="5" t="n"/>
@@ -4642,10 +4231,7 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="6" t="n"/>
       <c r="C139" s="6" t="n"/>
-      <c r="D139" s="6">
-        <f>IF($C139="","",$C139-MOD(WEEKDAY($C139,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D139" s="6" t="n"/>
       <c r="E139" s="5" t="n"/>
       <c r="F139" s="5" t="n"/>
       <c r="G139" s="5" t="n"/>
@@ -4669,10 +4255,7 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="6" t="n"/>
       <c r="C140" s="6" t="n"/>
-      <c r="D140" s="6">
-        <f>IF($C140="","",$C140-MOD(WEEKDAY($C140,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D140" s="6" t="n"/>
       <c r="E140" s="5" t="n"/>
       <c r="F140" s="5" t="n"/>
       <c r="G140" s="5" t="n"/>
@@ -4696,10 +4279,7 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="6" t="n"/>
       <c r="C141" s="6" t="n"/>
-      <c r="D141" s="6">
-        <f>IF($C141="","",$C141-MOD(WEEKDAY($C141,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D141" s="6" t="n"/>
       <c r="E141" s="5" t="n"/>
       <c r="F141" s="5" t="n"/>
       <c r="G141" s="5" t="n"/>
@@ -4723,10 +4303,7 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="6" t="n"/>
       <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6">
-        <f>IF($C142="","",$C142-MOD(WEEKDAY($C142,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D142" s="6" t="n"/>
       <c r="E142" s="5" t="n"/>
       <c r="F142" s="5" t="n"/>
       <c r="G142" s="5" t="n"/>
@@ -4750,10 +4327,7 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="6" t="n"/>
       <c r="C143" s="6" t="n"/>
-      <c r="D143" s="6">
-        <f>IF($C143="","",$C143-MOD(WEEKDAY($C143,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D143" s="6" t="n"/>
       <c r="E143" s="5" t="n"/>
       <c r="F143" s="5" t="n"/>
       <c r="G143" s="5" t="n"/>
@@ -4777,10 +4351,7 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="6" t="n"/>
       <c r="C144" s="6" t="n"/>
-      <c r="D144" s="6">
-        <f>IF($C144="","",$C144-MOD(WEEKDAY($C144,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D144" s="6" t="n"/>
       <c r="E144" s="5" t="n"/>
       <c r="F144" s="5" t="n"/>
       <c r="G144" s="5" t="n"/>
@@ -4804,10 +4375,7 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="6" t="n"/>
       <c r="C145" s="6" t="n"/>
-      <c r="D145" s="6">
-        <f>IF($C145="","",$C145-MOD(WEEKDAY($C145,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D145" s="6" t="n"/>
       <c r="E145" s="5" t="n"/>
       <c r="F145" s="5" t="n"/>
       <c r="G145" s="5" t="n"/>
@@ -4831,10 +4399,7 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="6" t="n"/>
       <c r="C146" s="6" t="n"/>
-      <c r="D146" s="6">
-        <f>IF($C146="","",$C146-MOD(WEEKDAY($C146,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D146" s="6" t="n"/>
       <c r="E146" s="5" t="n"/>
       <c r="F146" s="5" t="n"/>
       <c r="G146" s="5" t="n"/>
@@ -4858,10 +4423,7 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="6" t="n"/>
       <c r="C147" s="6" t="n"/>
-      <c r="D147" s="6">
-        <f>IF($C147="","",$C147-MOD(WEEKDAY($C147,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D147" s="6" t="n"/>
       <c r="E147" s="5" t="n"/>
       <c r="F147" s="5" t="n"/>
       <c r="G147" s="5" t="n"/>
@@ -4885,10 +4447,7 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="6" t="n"/>
       <c r="C148" s="6" t="n"/>
-      <c r="D148" s="6">
-        <f>IF($C148="","",$C148-MOD(WEEKDAY($C148,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D148" s="6" t="n"/>
       <c r="E148" s="5" t="n"/>
       <c r="F148" s="5" t="n"/>
       <c r="G148" s="5" t="n"/>
@@ -4912,10 +4471,7 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="6" t="n"/>
       <c r="C149" s="6" t="n"/>
-      <c r="D149" s="6">
-        <f>IF($C149="","",$C149-MOD(WEEKDAY($C149,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D149" s="6" t="n"/>
       <c r="E149" s="5" t="n"/>
       <c r="F149" s="5" t="n"/>
       <c r="G149" s="5" t="n"/>
@@ -4939,10 +4495,7 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="6" t="n"/>
       <c r="C150" s="6" t="n"/>
-      <c r="D150" s="6">
-        <f>IF($C150="","",$C150-MOD(WEEKDAY($C150,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D150" s="6" t="n"/>
       <c r="E150" s="5" t="n"/>
       <c r="F150" s="5" t="n"/>
       <c r="G150" s="5" t="n"/>
@@ -4966,10 +4519,7 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="6" t="n"/>
       <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6">
-        <f>IF($C151="","",$C151-MOD(WEEKDAY($C151,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D151" s="6" t="n"/>
       <c r="E151" s="5" t="n"/>
       <c r="F151" s="5" t="n"/>
       <c r="G151" s="5" t="n"/>
@@ -4993,10 +4543,7 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="6" t="n"/>
       <c r="C152" s="6" t="n"/>
-      <c r="D152" s="6">
-        <f>IF($C152="","",$C152-MOD(WEEKDAY($C152,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D152" s="6" t="n"/>
       <c r="E152" s="5" t="n"/>
       <c r="F152" s="5" t="n"/>
       <c r="G152" s="5" t="n"/>
@@ -5020,10 +4567,7 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="6" t="n"/>
       <c r="C153" s="6" t="n"/>
-      <c r="D153" s="6">
-        <f>IF($C153="","",$C153-MOD(WEEKDAY($C153,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D153" s="6" t="n"/>
       <c r="E153" s="5" t="n"/>
       <c r="F153" s="5" t="n"/>
       <c r="G153" s="5" t="n"/>
@@ -5047,10 +4591,7 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="6" t="n"/>
       <c r="C154" s="6" t="n"/>
-      <c r="D154" s="6">
-        <f>IF($C154="","",$C154-MOD(WEEKDAY($C154,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D154" s="6" t="n"/>
       <c r="E154" s="5" t="n"/>
       <c r="F154" s="5" t="n"/>
       <c r="G154" s="5" t="n"/>
@@ -5074,10 +4615,7 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="6" t="n"/>
       <c r="C155" s="6" t="n"/>
-      <c r="D155" s="6">
-        <f>IF($C155="","",$C155-MOD(WEEKDAY($C155,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D155" s="6" t="n"/>
       <c r="E155" s="5" t="n"/>
       <c r="F155" s="5" t="n"/>
       <c r="G155" s="5" t="n"/>
@@ -5101,10 +4639,7 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="6" t="n"/>
       <c r="C156" s="6" t="n"/>
-      <c r="D156" s="6">
-        <f>IF($C156="","",$C156-MOD(WEEKDAY($C156,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D156" s="6" t="n"/>
       <c r="E156" s="5" t="n"/>
       <c r="F156" s="5" t="n"/>
       <c r="G156" s="5" t="n"/>
@@ -5128,10 +4663,7 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="6" t="n"/>
       <c r="C157" s="6" t="n"/>
-      <c r="D157" s="6">
-        <f>IF($C157="","",$C157-MOD(WEEKDAY($C157,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D157" s="6" t="n"/>
       <c r="E157" s="5" t="n"/>
       <c r="F157" s="5" t="n"/>
       <c r="G157" s="5" t="n"/>
@@ -5155,10 +4687,7 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="6" t="n"/>
       <c r="C158" s="6" t="n"/>
-      <c r="D158" s="6">
-        <f>IF($C158="","",$C158-MOD(WEEKDAY($C158,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D158" s="6" t="n"/>
       <c r="E158" s="5" t="n"/>
       <c r="F158" s="5" t="n"/>
       <c r="G158" s="5" t="n"/>
@@ -5182,10 +4711,7 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="6" t="n"/>
       <c r="C159" s="6" t="n"/>
-      <c r="D159" s="6">
-        <f>IF($C159="","",$C159-MOD(WEEKDAY($C159,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D159" s="6" t="n"/>
       <c r="E159" s="5" t="n"/>
       <c r="F159" s="5" t="n"/>
       <c r="G159" s="5" t="n"/>
@@ -5209,10 +4735,7 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="6" t="n"/>
       <c r="C160" s="6" t="n"/>
-      <c r="D160" s="6">
-        <f>IF($C160="","",$C160-MOD(WEEKDAY($C160,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D160" s="6" t="n"/>
       <c r="E160" s="5" t="n"/>
       <c r="F160" s="5" t="n"/>
       <c r="G160" s="5" t="n"/>
@@ -5236,10 +4759,7 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="6" t="n"/>
       <c r="C161" s="6" t="n"/>
-      <c r="D161" s="6">
-        <f>IF($C161="","",$C161-MOD(WEEKDAY($C161,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D161" s="6" t="n"/>
       <c r="E161" s="5" t="n"/>
       <c r="F161" s="5" t="n"/>
       <c r="G161" s="5" t="n"/>
@@ -5263,10 +4783,7 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="6" t="n"/>
       <c r="C162" s="6" t="n"/>
-      <c r="D162" s="6">
-        <f>IF($C162="","",$C162-MOD(WEEKDAY($C162,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D162" s="6" t="n"/>
       <c r="E162" s="5" t="n"/>
       <c r="F162" s="5" t="n"/>
       <c r="G162" s="5" t="n"/>
@@ -5290,10 +4807,7 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="6" t="n"/>
       <c r="C163" s="6" t="n"/>
-      <c r="D163" s="6">
-        <f>IF($C163="","",$C163-MOD(WEEKDAY($C163,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D163" s="6" t="n"/>
       <c r="E163" s="5" t="n"/>
       <c r="F163" s="5" t="n"/>
       <c r="G163" s="5" t="n"/>
@@ -5317,10 +4831,7 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="6" t="n"/>
       <c r="C164" s="6" t="n"/>
-      <c r="D164" s="6">
-        <f>IF($C164="","",$C164-MOD(WEEKDAY($C164,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D164" s="6" t="n"/>
       <c r="E164" s="5" t="n"/>
       <c r="F164" s="5" t="n"/>
       <c r="G164" s="5" t="n"/>
@@ -5344,10 +4855,7 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="6" t="n"/>
       <c r="C165" s="6" t="n"/>
-      <c r="D165" s="6">
-        <f>IF($C165="","",$C165-MOD(WEEKDAY($C165,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D165" s="6" t="n"/>
       <c r="E165" s="5" t="n"/>
       <c r="F165" s="5" t="n"/>
       <c r="G165" s="5" t="n"/>
@@ -5371,10 +4879,7 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="6" t="n"/>
       <c r="C166" s="6" t="n"/>
-      <c r="D166" s="6">
-        <f>IF($C166="","",$C166-MOD(WEEKDAY($C166,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D166" s="6" t="n"/>
       <c r="E166" s="5" t="n"/>
       <c r="F166" s="5" t="n"/>
       <c r="G166" s="5" t="n"/>
@@ -5398,10 +4903,7 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="6" t="n"/>
       <c r="C167" s="6" t="n"/>
-      <c r="D167" s="6">
-        <f>IF($C167="","",$C167-MOD(WEEKDAY($C167,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D167" s="6" t="n"/>
       <c r="E167" s="5" t="n"/>
       <c r="F167" s="5" t="n"/>
       <c r="G167" s="5" t="n"/>
@@ -5425,10 +4927,7 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="6" t="n"/>
       <c r="C168" s="6" t="n"/>
-      <c r="D168" s="6">
-        <f>IF($C168="","",$C168-MOD(WEEKDAY($C168,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D168" s="6" t="n"/>
       <c r="E168" s="5" t="n"/>
       <c r="F168" s="5" t="n"/>
       <c r="G168" s="5" t="n"/>
@@ -5452,10 +4951,7 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="6" t="n"/>
       <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6">
-        <f>IF($C169="","",$C169-MOD(WEEKDAY($C169,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D169" s="6" t="n"/>
       <c r="E169" s="5" t="n"/>
       <c r="F169" s="5" t="n"/>
       <c r="G169" s="5" t="n"/>
@@ -5479,10 +4975,7 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="6" t="n"/>
       <c r="C170" s="6" t="n"/>
-      <c r="D170" s="6">
-        <f>IF($C170="","",$C170-MOD(WEEKDAY($C170,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D170" s="6" t="n"/>
       <c r="E170" s="5" t="n"/>
       <c r="F170" s="5" t="n"/>
       <c r="G170" s="5" t="n"/>
@@ -5506,10 +4999,7 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="6" t="n"/>
       <c r="C171" s="6" t="n"/>
-      <c r="D171" s="6">
-        <f>IF($C171="","",$C171-MOD(WEEKDAY($C171,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D171" s="6" t="n"/>
       <c r="E171" s="5" t="n"/>
       <c r="F171" s="5" t="n"/>
       <c r="G171" s="5" t="n"/>
@@ -5533,10 +5023,7 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="6" t="n"/>
       <c r="C172" s="6" t="n"/>
-      <c r="D172" s="6">
-        <f>IF($C172="","",$C172-MOD(WEEKDAY($C172,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D172" s="6" t="n"/>
       <c r="E172" s="5" t="n"/>
       <c r="F172" s="5" t="n"/>
       <c r="G172" s="5" t="n"/>
@@ -5560,10 +5047,7 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="6" t="n"/>
       <c r="C173" s="6" t="n"/>
-      <c r="D173" s="6">
-        <f>IF($C173="","",$C173-MOD(WEEKDAY($C173,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D173" s="6" t="n"/>
       <c r="E173" s="5" t="n"/>
       <c r="F173" s="5" t="n"/>
       <c r="G173" s="5" t="n"/>
@@ -5587,10 +5071,7 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="6" t="n"/>
       <c r="C174" s="6" t="n"/>
-      <c r="D174" s="6">
-        <f>IF($C174="","",$C174-MOD(WEEKDAY($C174,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D174" s="6" t="n"/>
       <c r="E174" s="5" t="n"/>
       <c r="F174" s="5" t="n"/>
       <c r="G174" s="5" t="n"/>
@@ -5614,10 +5095,7 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="6" t="n"/>
       <c r="C175" s="6" t="n"/>
-      <c r="D175" s="6">
-        <f>IF($C175="","",$C175-MOD(WEEKDAY($C175,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D175" s="6" t="n"/>
       <c r="E175" s="5" t="n"/>
       <c r="F175" s="5" t="n"/>
       <c r="G175" s="5" t="n"/>
@@ -5641,10 +5119,7 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="6" t="n"/>
       <c r="C176" s="6" t="n"/>
-      <c r="D176" s="6">
-        <f>IF($C176="","",$C176-MOD(WEEKDAY($C176,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D176" s="6" t="n"/>
       <c r="E176" s="5" t="n"/>
       <c r="F176" s="5" t="n"/>
       <c r="G176" s="5" t="n"/>
@@ -5668,10 +5143,7 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="6" t="n"/>
       <c r="C177" s="6" t="n"/>
-      <c r="D177" s="6">
-        <f>IF($C177="","",$C177-MOD(WEEKDAY($C177,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D177" s="6" t="n"/>
       <c r="E177" s="5" t="n"/>
       <c r="F177" s="5" t="n"/>
       <c r="G177" s="5" t="n"/>
@@ -5695,10 +5167,7 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="6" t="n"/>
       <c r="C178" s="6" t="n"/>
-      <c r="D178" s="6">
-        <f>IF($C178="","",$C178-MOD(WEEKDAY($C178,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D178" s="6" t="n"/>
       <c r="E178" s="5" t="n"/>
       <c r="F178" s="5" t="n"/>
       <c r="G178" s="5" t="n"/>
@@ -5722,10 +5191,7 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="6" t="n"/>
       <c r="C179" s="6" t="n"/>
-      <c r="D179" s="6">
-        <f>IF($C179="","",$C179-MOD(WEEKDAY($C179,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D179" s="6" t="n"/>
       <c r="E179" s="5" t="n"/>
       <c r="F179" s="5" t="n"/>
       <c r="G179" s="5" t="n"/>
@@ -5749,10 +5215,7 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="6" t="n"/>
       <c r="C180" s="6" t="n"/>
-      <c r="D180" s="6">
-        <f>IF($C180="","",$C180-MOD(WEEKDAY($C180,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D180" s="6" t="n"/>
       <c r="E180" s="5" t="n"/>
       <c r="F180" s="5" t="n"/>
       <c r="G180" s="5" t="n"/>
@@ -5776,10 +5239,7 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="6" t="n"/>
       <c r="C181" s="6" t="n"/>
-      <c r="D181" s="6">
-        <f>IF($C181="","",$C181-MOD(WEEKDAY($C181,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D181" s="6" t="n"/>
       <c r="E181" s="5" t="n"/>
       <c r="F181" s="5" t="n"/>
       <c r="G181" s="5" t="n"/>
@@ -5803,10 +5263,7 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="6" t="n"/>
       <c r="C182" s="6" t="n"/>
-      <c r="D182" s="6">
-        <f>IF($C182="","",$C182-MOD(WEEKDAY($C182,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D182" s="6" t="n"/>
       <c r="E182" s="5" t="n"/>
       <c r="F182" s="5" t="n"/>
       <c r="G182" s="5" t="n"/>
@@ -5830,10 +5287,7 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="6" t="n"/>
       <c r="C183" s="6" t="n"/>
-      <c r="D183" s="6">
-        <f>IF($C183="","",$C183-MOD(WEEKDAY($C183,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D183" s="6" t="n"/>
       <c r="E183" s="5" t="n"/>
       <c r="F183" s="5" t="n"/>
       <c r="G183" s="5" t="n"/>
@@ -5857,10 +5311,7 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="6" t="n"/>
       <c r="C184" s="6" t="n"/>
-      <c r="D184" s="6">
-        <f>IF($C184="","",$C184-MOD(WEEKDAY($C184,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D184" s="6" t="n"/>
       <c r="E184" s="5" t="n"/>
       <c r="F184" s="5" t="n"/>
       <c r="G184" s="5" t="n"/>
@@ -5884,10 +5335,7 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="6" t="n"/>
       <c r="C185" s="6" t="n"/>
-      <c r="D185" s="6">
-        <f>IF($C185="","",$C185-MOD(WEEKDAY($C185,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D185" s="6" t="n"/>
       <c r="E185" s="5" t="n"/>
       <c r="F185" s="5" t="n"/>
       <c r="G185" s="5" t="n"/>
@@ -5911,10 +5359,7 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="6" t="n"/>
       <c r="C186" s="6" t="n"/>
-      <c r="D186" s="6">
-        <f>IF($C186="","",$C186-MOD(WEEKDAY($C186,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D186" s="6" t="n"/>
       <c r="E186" s="5" t="n"/>
       <c r="F186" s="5" t="n"/>
       <c r="G186" s="5" t="n"/>
@@ -5938,10 +5383,7 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="6" t="n"/>
       <c r="C187" s="6" t="n"/>
-      <c r="D187" s="6">
-        <f>IF($C187="","",$C187-MOD(WEEKDAY($C187,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D187" s="6" t="n"/>
       <c r="E187" s="5" t="n"/>
       <c r="F187" s="5" t="n"/>
       <c r="G187" s="5" t="n"/>
@@ -5965,10 +5407,7 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="6" t="n"/>
       <c r="C188" s="6" t="n"/>
-      <c r="D188" s="6">
-        <f>IF($C188="","",$C188-MOD(WEEKDAY($C188,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D188" s="6" t="n"/>
       <c r="E188" s="5" t="n"/>
       <c r="F188" s="5" t="n"/>
       <c r="G188" s="5" t="n"/>
@@ -5992,10 +5431,7 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="6" t="n"/>
       <c r="C189" s="6" t="n"/>
-      <c r="D189" s="6">
-        <f>IF($C189="","",$C189-MOD(WEEKDAY($C189,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D189" s="6" t="n"/>
       <c r="E189" s="5" t="n"/>
       <c r="F189" s="5" t="n"/>
       <c r="G189" s="5" t="n"/>
@@ -6019,10 +5455,7 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="6" t="n"/>
       <c r="C190" s="6" t="n"/>
-      <c r="D190" s="6">
-        <f>IF($C190="","",$C190-MOD(WEEKDAY($C190,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D190" s="6" t="n"/>
       <c r="E190" s="5" t="n"/>
       <c r="F190" s="5" t="n"/>
       <c r="G190" s="5" t="n"/>
@@ -6046,10 +5479,7 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="6" t="n"/>
       <c r="C191" s="6" t="n"/>
-      <c r="D191" s="6">
-        <f>IF($C191="","",$C191-MOD(WEEKDAY($C191,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D191" s="6" t="n"/>
       <c r="E191" s="5" t="n"/>
       <c r="F191" s="5" t="n"/>
       <c r="G191" s="5" t="n"/>
@@ -6073,10 +5503,7 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="6" t="n"/>
       <c r="C192" s="6" t="n"/>
-      <c r="D192" s="6">
-        <f>IF($C192="","",$C192-MOD(WEEKDAY($C192,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D192" s="6" t="n"/>
       <c r="E192" s="5" t="n"/>
       <c r="F192" s="5" t="n"/>
       <c r="G192" s="5" t="n"/>
@@ -6100,10 +5527,7 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="6" t="n"/>
       <c r="C193" s="6" t="n"/>
-      <c r="D193" s="6">
-        <f>IF($C193="","",$C193-MOD(WEEKDAY($C193,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D193" s="6" t="n"/>
       <c r="E193" s="5" t="n"/>
       <c r="F193" s="5" t="n"/>
       <c r="G193" s="5" t="n"/>
@@ -6127,10 +5551,7 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="6" t="n"/>
       <c r="C194" s="6" t="n"/>
-      <c r="D194" s="6">
-        <f>IF($C194="","",$C194-MOD(WEEKDAY($C194,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D194" s="6" t="n"/>
       <c r="E194" s="5" t="n"/>
       <c r="F194" s="5" t="n"/>
       <c r="G194" s="5" t="n"/>
@@ -6154,10 +5575,7 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="6" t="n"/>
       <c r="C195" s="6" t="n"/>
-      <c r="D195" s="6">
-        <f>IF($C195="","",$C195-MOD(WEEKDAY($C195,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D195" s="6" t="n"/>
       <c r="E195" s="5" t="n"/>
       <c r="F195" s="5" t="n"/>
       <c r="G195" s="5" t="n"/>
@@ -6181,10 +5599,7 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="6" t="n"/>
       <c r="C196" s="6" t="n"/>
-      <c r="D196" s="6">
-        <f>IF($C196="","",$C196-MOD(WEEKDAY($C196,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D196" s="6" t="n"/>
       <c r="E196" s="5" t="n"/>
       <c r="F196" s="5" t="n"/>
       <c r="G196" s="5" t="n"/>
@@ -6208,10 +5623,7 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="6" t="n"/>
       <c r="C197" s="6" t="n"/>
-      <c r="D197" s="6">
-        <f>IF($C197="","",$C197-MOD(WEEKDAY($C197,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D197" s="6" t="n"/>
       <c r="E197" s="5" t="n"/>
       <c r="F197" s="5" t="n"/>
       <c r="G197" s="5" t="n"/>
@@ -6235,10 +5647,7 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="6" t="n"/>
       <c r="C198" s="6" t="n"/>
-      <c r="D198" s="6">
-        <f>IF($C198="","",$C198-MOD(WEEKDAY($C198,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D198" s="6" t="n"/>
       <c r="E198" s="5" t="n"/>
       <c r="F198" s="5" t="n"/>
       <c r="G198" s="5" t="n"/>
@@ -6262,10 +5671,7 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="6" t="n"/>
       <c r="C199" s="6" t="n"/>
-      <c r="D199" s="6">
-        <f>IF($C199="","",$C199-MOD(WEEKDAY($C199,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D199" s="6" t="n"/>
       <c r="E199" s="5" t="n"/>
       <c r="F199" s="5" t="n"/>
       <c r="G199" s="5" t="n"/>
@@ -6289,10 +5695,7 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="6" t="n"/>
       <c r="C200" s="6" t="n"/>
-      <c r="D200" s="6">
-        <f>IF($C200="","",$C200-MOD(WEEKDAY($C200,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D200" s="6" t="n"/>
       <c r="E200" s="5" t="n"/>
       <c r="F200" s="5" t="n"/>
       <c r="G200" s="5" t="n"/>
@@ -6316,10 +5719,7 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="6" t="n"/>
       <c r="C201" s="6" t="n"/>
-      <c r="D201" s="6">
-        <f>IF($C201="","",$C201-MOD(WEEKDAY($C201,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D201" s="6" t="n"/>
       <c r="E201" s="5" t="n"/>
       <c r="F201" s="5" t="n"/>
       <c r="G201" s="5" t="n"/>
@@ -6343,10 +5743,7 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="6" t="n"/>
       <c r="C202" s="6" t="n"/>
-      <c r="D202" s="6">
-        <f>IF($C202="","",$C202-MOD(WEEKDAY($C202,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D202" s="6" t="n"/>
       <c r="E202" s="5" t="n"/>
       <c r="F202" s="5" t="n"/>
       <c r="G202" s="5" t="n"/>
@@ -6370,10 +5767,7 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="6" t="n"/>
       <c r="C203" s="6" t="n"/>
-      <c r="D203" s="6">
-        <f>IF($C203="","",$C203-MOD(WEEKDAY($C203,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D203" s="6" t="n"/>
       <c r="E203" s="5" t="n"/>
       <c r="F203" s="5" t="n"/>
       <c r="G203" s="5" t="n"/>
@@ -6397,10 +5791,7 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="6" t="n"/>
       <c r="C204" s="6" t="n"/>
-      <c r="D204" s="6">
-        <f>IF($C204="","",$C204-MOD(WEEKDAY($C204,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D204" s="6" t="n"/>
       <c r="E204" s="5" t="n"/>
       <c r="F204" s="5" t="n"/>
       <c r="G204" s="5" t="n"/>
@@ -6424,10 +5815,7 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="6" t="n"/>
       <c r="C205" s="6" t="n"/>
-      <c r="D205" s="6">
-        <f>IF($C205="","",$C205-MOD(WEEKDAY($C205,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D205" s="6" t="n"/>
       <c r="E205" s="5" t="n"/>
       <c r="F205" s="5" t="n"/>
       <c r="G205" s="5" t="n"/>
@@ -6451,10 +5839,7 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="6" t="n"/>
       <c r="C206" s="6" t="n"/>
-      <c r="D206" s="6">
-        <f>IF($C206="","",$C206-MOD(WEEKDAY($C206,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D206" s="6" t="n"/>
       <c r="E206" s="5" t="n"/>
       <c r="F206" s="5" t="n"/>
       <c r="G206" s="5" t="n"/>
@@ -6478,10 +5863,7 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="6" t="n"/>
       <c r="C207" s="6" t="n"/>
-      <c r="D207" s="6">
-        <f>IF($C207="","",$C207-MOD(WEEKDAY($C207,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D207" s="6" t="n"/>
       <c r="E207" s="5" t="n"/>
       <c r="F207" s="5" t="n"/>
       <c r="G207" s="5" t="n"/>
@@ -6505,10 +5887,7 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="6" t="n"/>
       <c r="C208" s="6" t="n"/>
-      <c r="D208" s="6">
-        <f>IF($C208="","",$C208-MOD(WEEKDAY($C208,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D208" s="6" t="n"/>
       <c r="E208" s="5" t="n"/>
       <c r="F208" s="5" t="n"/>
       <c r="G208" s="5" t="n"/>
@@ -6532,10 +5911,7 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="6" t="n"/>
       <c r="C209" s="6" t="n"/>
-      <c r="D209" s="6">
-        <f>IF($C209="","",$C209-MOD(WEEKDAY($C209,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D209" s="6" t="n"/>
       <c r="E209" s="5" t="n"/>
       <c r="F209" s="5" t="n"/>
       <c r="G209" s="5" t="n"/>
@@ -6559,10 +5935,7 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="6" t="n"/>
       <c r="C210" s="6" t="n"/>
-      <c r="D210" s="6">
-        <f>IF($C210="","",$C210-MOD(WEEKDAY($C210,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D210" s="6" t="n"/>
       <c r="E210" s="5" t="n"/>
       <c r="F210" s="5" t="n"/>
       <c r="G210" s="5" t="n"/>
@@ -6586,10 +5959,7 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="6" t="n"/>
       <c r="C211" s="6" t="n"/>
-      <c r="D211" s="6">
-        <f>IF($C211="","",$C211-MOD(WEEKDAY($C211,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D211" s="6" t="n"/>
       <c r="E211" s="5" t="n"/>
       <c r="F211" s="5" t="n"/>
       <c r="G211" s="5" t="n"/>
@@ -6613,10 +5983,7 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="6" t="n"/>
       <c r="C212" s="6" t="n"/>
-      <c r="D212" s="6">
-        <f>IF($C212="","",$C212-MOD(WEEKDAY($C212,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D212" s="6" t="n"/>
       <c r="E212" s="5" t="n"/>
       <c r="F212" s="5" t="n"/>
       <c r="G212" s="5" t="n"/>
@@ -6640,10 +6007,7 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="6" t="n"/>
       <c r="C213" s="6" t="n"/>
-      <c r="D213" s="6">
-        <f>IF($C213="","",$C213-MOD(WEEKDAY($C213,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D213" s="6" t="n"/>
       <c r="E213" s="5" t="n"/>
       <c r="F213" s="5" t="n"/>
       <c r="G213" s="5" t="n"/>
@@ -6667,10 +6031,7 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="6" t="n"/>
       <c r="C214" s="6" t="n"/>
-      <c r="D214" s="6">
-        <f>IF($C214="","",$C214-MOD(WEEKDAY($C214,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D214" s="6" t="n"/>
       <c r="E214" s="5" t="n"/>
       <c r="F214" s="5" t="n"/>
       <c r="G214" s="5" t="n"/>
@@ -6694,10 +6055,7 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="6" t="n"/>
       <c r="C215" s="6" t="n"/>
-      <c r="D215" s="6">
-        <f>IF($C215="","",$C215-MOD(WEEKDAY($C215,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D215" s="6" t="n"/>
       <c r="E215" s="5" t="n"/>
       <c r="F215" s="5" t="n"/>
       <c r="G215" s="5" t="n"/>
@@ -6721,10 +6079,7 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="6" t="n"/>
       <c r="C216" s="6" t="n"/>
-      <c r="D216" s="6">
-        <f>IF($C216="","",$C216-MOD(WEEKDAY($C216,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D216" s="6" t="n"/>
       <c r="E216" s="5" t="n"/>
       <c r="F216" s="5" t="n"/>
       <c r="G216" s="5" t="n"/>
@@ -6748,10 +6103,7 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="6" t="n"/>
       <c r="C217" s="6" t="n"/>
-      <c r="D217" s="6">
-        <f>IF($C217="","",$C217-MOD(WEEKDAY($C217,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D217" s="6" t="n"/>
       <c r="E217" s="5" t="n"/>
       <c r="F217" s="5" t="n"/>
       <c r="G217" s="5" t="n"/>
@@ -6775,10 +6127,7 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="6" t="n"/>
       <c r="C218" s="6" t="n"/>
-      <c r="D218" s="6">
-        <f>IF($C218="","",$C218-MOD(WEEKDAY($C218,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D218" s="6" t="n"/>
       <c r="E218" s="5" t="n"/>
       <c r="F218" s="5" t="n"/>
       <c r="G218" s="5" t="n"/>
@@ -6802,10 +6151,7 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="6" t="n"/>
       <c r="C219" s="6" t="n"/>
-      <c r="D219" s="6">
-        <f>IF($C219="","",$C219-MOD(WEEKDAY($C219,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D219" s="6" t="n"/>
       <c r="E219" s="5" t="n"/>
       <c r="F219" s="5" t="n"/>
       <c r="G219" s="5" t="n"/>
@@ -6829,10 +6175,7 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="6" t="n"/>
       <c r="C220" s="6" t="n"/>
-      <c r="D220" s="6">
-        <f>IF($C220="","",$C220-MOD(WEEKDAY($C220,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D220" s="6" t="n"/>
       <c r="E220" s="5" t="n"/>
       <c r="F220" s="5" t="n"/>
       <c r="G220" s="5" t="n"/>
@@ -6856,10 +6199,7 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="6" t="n"/>
       <c r="C221" s="6" t="n"/>
-      <c r="D221" s="6">
-        <f>IF($C221="","",$C221-MOD(WEEKDAY($C221,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D221" s="6" t="n"/>
       <c r="E221" s="5" t="n"/>
       <c r="F221" s="5" t="n"/>
       <c r="G221" s="5" t="n"/>
@@ -6883,10 +6223,7 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="6" t="n"/>
       <c r="C222" s="6" t="n"/>
-      <c r="D222" s="6">
-        <f>IF($C222="","",$C222-MOD(WEEKDAY($C222,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D222" s="6" t="n"/>
       <c r="E222" s="5" t="n"/>
       <c r="F222" s="5" t="n"/>
       <c r="G222" s="5" t="n"/>
@@ -6910,10 +6247,7 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="6" t="n"/>
       <c r="C223" s="6" t="n"/>
-      <c r="D223" s="6">
-        <f>IF($C223="","",$C223-MOD(WEEKDAY($C223,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D223" s="6" t="n"/>
       <c r="E223" s="5" t="n"/>
       <c r="F223" s="5" t="n"/>
       <c r="G223" s="5" t="n"/>
@@ -6937,10 +6271,7 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="6" t="n"/>
       <c r="C224" s="6" t="n"/>
-      <c r="D224" s="6">
-        <f>IF($C224="","",$C224-MOD(WEEKDAY($C224,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D224" s="6" t="n"/>
       <c r="E224" s="5" t="n"/>
       <c r="F224" s="5" t="n"/>
       <c r="G224" s="5" t="n"/>
@@ -6964,10 +6295,7 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="6" t="n"/>
       <c r="C225" s="6" t="n"/>
-      <c r="D225" s="6">
-        <f>IF($C225="","",$C225-MOD(WEEKDAY($C225,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D225" s="6" t="n"/>
       <c r="E225" s="5" t="n"/>
       <c r="F225" s="5" t="n"/>
       <c r="G225" s="5" t="n"/>
@@ -6991,10 +6319,7 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="6" t="n"/>
       <c r="C226" s="6" t="n"/>
-      <c r="D226" s="6">
-        <f>IF($C226="","",$C226-MOD(WEEKDAY($C226,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D226" s="6" t="n"/>
       <c r="E226" s="5" t="n"/>
       <c r="F226" s="5" t="n"/>
       <c r="G226" s="5" t="n"/>
@@ -7018,10 +6343,7 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="6" t="n"/>
       <c r="C227" s="6" t="n"/>
-      <c r="D227" s="6">
-        <f>IF($C227="","",$C227-MOD(WEEKDAY($C227,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D227" s="6" t="n"/>
       <c r="E227" s="5" t="n"/>
       <c r="F227" s="5" t="n"/>
       <c r="G227" s="5" t="n"/>
@@ -7045,10 +6367,7 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="6" t="n"/>
       <c r="C228" s="6" t="n"/>
-      <c r="D228" s="6">
-        <f>IF($C228="","",$C228-MOD(WEEKDAY($C228,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D228" s="6" t="n"/>
       <c r="E228" s="5" t="n"/>
       <c r="F228" s="5" t="n"/>
       <c r="G228" s="5" t="n"/>
@@ -7072,10 +6391,7 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="6" t="n"/>
       <c r="C229" s="6" t="n"/>
-      <c r="D229" s="6">
-        <f>IF($C229="","",$C229-MOD(WEEKDAY($C229,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D229" s="6" t="n"/>
       <c r="E229" s="5" t="n"/>
       <c r="F229" s="5" t="n"/>
       <c r="G229" s="5" t="n"/>
@@ -7099,10 +6415,7 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="6" t="n"/>
       <c r="C230" s="6" t="n"/>
-      <c r="D230" s="6">
-        <f>IF($C230="","",$C230-MOD(WEEKDAY($C230,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D230" s="6" t="n"/>
       <c r="E230" s="5" t="n"/>
       <c r="F230" s="5" t="n"/>
       <c r="G230" s="5" t="n"/>
@@ -7126,10 +6439,7 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="6" t="n"/>
       <c r="C231" s="6" t="n"/>
-      <c r="D231" s="6">
-        <f>IF($C231="","",$C231-MOD(WEEKDAY($C231,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D231" s="6" t="n"/>
       <c r="E231" s="5" t="n"/>
       <c r="F231" s="5" t="n"/>
       <c r="G231" s="5" t="n"/>
@@ -7153,10 +6463,7 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="6" t="n"/>
       <c r="C232" s="6" t="n"/>
-      <c r="D232" s="6">
-        <f>IF($C232="","",$C232-MOD(WEEKDAY($C232,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D232" s="6" t="n"/>
       <c r="E232" s="5" t="n"/>
       <c r="F232" s="5" t="n"/>
       <c r="G232" s="5" t="n"/>
@@ -7180,10 +6487,7 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="6" t="n"/>
       <c r="C233" s="6" t="n"/>
-      <c r="D233" s="6">
-        <f>IF($C233="","",$C233-MOD(WEEKDAY($C233,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D233" s="6" t="n"/>
       <c r="E233" s="5" t="n"/>
       <c r="F233" s="5" t="n"/>
       <c r="G233" s="5" t="n"/>
@@ -7207,10 +6511,7 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="6" t="n"/>
       <c r="C234" s="6" t="n"/>
-      <c r="D234" s="6">
-        <f>IF($C234="","",$C234-MOD(WEEKDAY($C234,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D234" s="6" t="n"/>
       <c r="E234" s="5" t="n"/>
       <c r="F234" s="5" t="n"/>
       <c r="G234" s="5" t="n"/>
@@ -7234,10 +6535,7 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="6" t="n"/>
       <c r="C235" s="6" t="n"/>
-      <c r="D235" s="6">
-        <f>IF($C235="","",$C235-MOD(WEEKDAY($C235,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D235" s="6" t="n"/>
       <c r="E235" s="5" t="n"/>
       <c r="F235" s="5" t="n"/>
       <c r="G235" s="5" t="n"/>
@@ -7261,10 +6559,7 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="6" t="n"/>
       <c r="C236" s="6" t="n"/>
-      <c r="D236" s="6">
-        <f>IF($C236="","",$C236-MOD(WEEKDAY($C236,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D236" s="6" t="n"/>
       <c r="E236" s="5" t="n"/>
       <c r="F236" s="5" t="n"/>
       <c r="G236" s="5" t="n"/>
@@ -7288,10 +6583,7 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="6" t="n"/>
       <c r="C237" s="6" t="n"/>
-      <c r="D237" s="6">
-        <f>IF($C237="","",$C237-MOD(WEEKDAY($C237,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D237" s="6" t="n"/>
       <c r="E237" s="5" t="n"/>
       <c r="F237" s="5" t="n"/>
       <c r="G237" s="5" t="n"/>
@@ -7315,10 +6607,7 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="6" t="n"/>
       <c r="C238" s="6" t="n"/>
-      <c r="D238" s="6">
-        <f>IF($C238="","",$C238-MOD(WEEKDAY($C238,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D238" s="6" t="n"/>
       <c r="E238" s="5" t="n"/>
       <c r="F238" s="5" t="n"/>
       <c r="G238" s="5" t="n"/>
@@ -7342,10 +6631,7 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="6" t="n"/>
       <c r="C239" s="6" t="n"/>
-      <c r="D239" s="6">
-        <f>IF($C239="","",$C239-MOD(WEEKDAY($C239,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D239" s="6" t="n"/>
       <c r="E239" s="5" t="n"/>
       <c r="F239" s="5" t="n"/>
       <c r="G239" s="5" t="n"/>
@@ -7369,10 +6655,7 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="6" t="n"/>
       <c r="C240" s="6" t="n"/>
-      <c r="D240" s="6">
-        <f>IF($C240="","",$C240-MOD(WEEKDAY($C240,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D240" s="6" t="n"/>
       <c r="E240" s="5" t="n"/>
       <c r="F240" s="5" t="n"/>
       <c r="G240" s="5" t="n"/>
@@ -7396,10 +6679,7 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="6" t="n"/>
       <c r="C241" s="6" t="n"/>
-      <c r="D241" s="6">
-        <f>IF($C241="","",$C241-MOD(WEEKDAY($C241,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D241" s="6" t="n"/>
       <c r="E241" s="5" t="n"/>
       <c r="F241" s="5" t="n"/>
       <c r="G241" s="5" t="n"/>
@@ -7423,10 +6703,7 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="6" t="n"/>
       <c r="C242" s="6" t="n"/>
-      <c r="D242" s="6">
-        <f>IF($C242="","",$C242-MOD(WEEKDAY($C242,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D242" s="6" t="n"/>
       <c r="E242" s="5" t="n"/>
       <c r="F242" s="5" t="n"/>
       <c r="G242" s="5" t="n"/>
@@ -7450,10 +6727,7 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="6" t="n"/>
       <c r="C243" s="6" t="n"/>
-      <c r="D243" s="6">
-        <f>IF($C243="","",$C243-MOD(WEEKDAY($C243,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D243" s="6" t="n"/>
       <c r="E243" s="5" t="n"/>
       <c r="F243" s="5" t="n"/>
       <c r="G243" s="5" t="n"/>
@@ -7477,10 +6751,7 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="6" t="n"/>
       <c r="C244" s="6" t="n"/>
-      <c r="D244" s="6">
-        <f>IF($C244="","",$C244-MOD(WEEKDAY($C244,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D244" s="6" t="n"/>
       <c r="E244" s="5" t="n"/>
       <c r="F244" s="5" t="n"/>
       <c r="G244" s="5" t="n"/>
@@ -7504,10 +6775,7 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="6" t="n"/>
       <c r="C245" s="6" t="n"/>
-      <c r="D245" s="6">
-        <f>IF($C245="","",$C245-MOD(WEEKDAY($C245,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D245" s="6" t="n"/>
       <c r="E245" s="5" t="n"/>
       <c r="F245" s="5" t="n"/>
       <c r="G245" s="5" t="n"/>
@@ -7531,10 +6799,7 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="6" t="n"/>
       <c r="C246" s="6" t="n"/>
-      <c r="D246" s="6">
-        <f>IF($C246="","",$C246-MOD(WEEKDAY($C246,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D246" s="6" t="n"/>
       <c r="E246" s="5" t="n"/>
       <c r="F246" s="5" t="n"/>
       <c r="G246" s="5" t="n"/>
@@ -7558,10 +6823,7 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="6" t="n"/>
       <c r="C247" s="6" t="n"/>
-      <c r="D247" s="6">
-        <f>IF($C247="","",$C247-MOD(WEEKDAY($C247,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D247" s="6" t="n"/>
       <c r="E247" s="5" t="n"/>
       <c r="F247" s="5" t="n"/>
       <c r="G247" s="5" t="n"/>
@@ -7585,10 +6847,7 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="6" t="n"/>
       <c r="C248" s="6" t="n"/>
-      <c r="D248" s="6">
-        <f>IF($C248="","",$C248-MOD(WEEKDAY($C248,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D248" s="6" t="n"/>
       <c r="E248" s="5" t="n"/>
       <c r="F248" s="5" t="n"/>
       <c r="G248" s="5" t="n"/>
@@ -7612,10 +6871,7 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="6" t="n"/>
       <c r="C249" s="6" t="n"/>
-      <c r="D249" s="6">
-        <f>IF($C249="","",$C249-MOD(WEEKDAY($C249,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D249" s="6" t="n"/>
       <c r="E249" s="5" t="n"/>
       <c r="F249" s="5" t="n"/>
       <c r="G249" s="5" t="n"/>
@@ -7639,10 +6895,7 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="6" t="n"/>
       <c r="C250" s="6" t="n"/>
-      <c r="D250" s="6">
-        <f>IF($C250="","",$C250-MOD(WEEKDAY($C250,3)-5,7))</f>
-        <v/>
-      </c>
+      <c r="D250" s="6" t="n"/>
       <c r="E250" s="5" t="n"/>
       <c r="F250" s="5" t="n"/>
       <c r="G250" s="5" t="n"/>

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -13956,50 +13956,70 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Robust Kommerce</t>
+          <t>Westbury Kommerce</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="C4" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="E4" s="15" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
+      <c r="F4" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>3.8</v>
+      </c>
       <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="7" t="n"/>
+      <c r="J4" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/reviews/westbury-kommerce-reviews</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>All locations. Highly rated for job security; critically rated for promotions, work satisfaction, skill development. 142 salary entries, 14 followers.</t>
+        </is>
+      </c>
       <c r="M4" s="7" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="N4" s="15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P4" s="15" t="n"/>
       <c r="Q4" s="7" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="S4" s="7" t="n"/>
       <c r="T4" s="7" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.co.in/Reviews/Robust-Reviews-E1882698.htm</t>
+          <t>https://www.glassdoor.co.in/Reviews/Westbury-Kommerce-Reviews-E6166527.htm</t>
         </is>
       </c>
       <c r="W4" s="5" t="inlineStr">
         <is>
-          <t>Listed on Glassdoor as plain 'Robust' (employer id 1882698) - identity still to be confirmed as Robust Kommerce. Diversity and inclusion 4.2; Senior management 3.1. Company size 51-200 employees. Employer Profile NOT claimed.</t>
+          <t>Diversity and inclusion 2.0; Senior management 1.0; 'Be the first to recommend' = 0% recommend</t>
         </is>
       </c>
       <c r="X4" s="6" t="n">
@@ -14013,85 +14033,31 @@
       <c r="Z4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Westbury Kommerce</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>18</v>
-      </c>
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="15" t="n"/>
-      <c r="F5" s="7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ambitionbox.com/reviews/westbury-kommerce-reviews</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>All locations. Highly rated for job security; critically rated for promotions, work satisfaction, skill development. 142 salary entries, 14 followers.</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N5" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
+      <c r="N5" s="15" t="n"/>
+      <c r="O5" s="15" t="n"/>
       <c r="P5" s="15" t="n"/>
-      <c r="Q5" s="7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="Q5" s="7" t="n"/>
+      <c r="R5" s="7" t="n"/>
       <c r="S5" s="7" t="n"/>
-      <c r="T5" s="7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V5" s="6" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.co.in/Reviews/Westbury-Kommerce-Reviews-E6166527.htm</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="inlineStr">
-        <is>
-          <t>Diversity and inclusion 2.0; Senior management 1.0; 'Be the first to recommend' = 0% recommend</t>
-        </is>
-      </c>
-      <c r="X5" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="Y5" s="5" t="inlineStr">
-        <is>
-          <t>desk</t>
-        </is>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="5" t="n"/>
       <c r="Z5" s="5" t="n"/>
     </row>
     <row r="6">

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -13956,70 +13956,50 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Westbury Kommerce</t>
+          <t>Robust Kommerce</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>18</v>
-      </c>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="15" t="n"/>
-      <c r="F4" s="7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ambitionbox.com/reviews/westbury-kommerce-reviews</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>All locations. Highly rated for job security; critically rated for promotions, work satisfaction, skill development. 142 salary entries, 14 followers.</t>
-        </is>
-      </c>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="7" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="N4" s="15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P4" s="15" t="n"/>
       <c r="Q4" s="7" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="S4" s="7" t="n"/>
       <c r="T4" s="7" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.co.in/Reviews/Westbury-Kommerce-Reviews-E6166527.htm</t>
+          <t>https://www.glassdoor.co.in/Reviews/Robust-Reviews-E1882698.htm</t>
         </is>
       </c>
       <c r="W4" s="5" t="inlineStr">
         <is>
-          <t>Diversity and inclusion 2.0; Senior management 1.0; 'Be the first to recommend' = 0% recommend</t>
+          <t>Listed on Glassdoor as plain 'Robust' (employer id 1882698); confirmed as Robust Kommerce by the programme owner on 2026-09-21, who supplied the Overview link for this same employer id. Diversity and inclusion 4.2; Senior management 3.1. Company size 51-200 employees. Employer Profile NOT claimed.</t>
         </is>
       </c>
       <c r="X4" s="6" t="n">
@@ -14033,31 +14013,85 @@
       <c r="Z4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="A5" s="6" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Westbury Kommerce</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="E5" s="15" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
+      <c r="F5" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>3.8</v>
+      </c>
       <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="15" t="n"/>
+      <c r="J5" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/reviews/westbury-kommerce-reviews</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>All locations. Highly rated for job security; critically rated for promotions, work satisfaction, skill development. 142 salary entries, 14 followers.</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" s="15" t="n"/>
-      <c r="Q5" s="7" t="n"/>
-      <c r="R5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>2.1</v>
+      </c>
       <c r="S5" s="7" t="n"/>
-      <c r="T5" s="7" t="n"/>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="6" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="6" t="n"/>
-      <c r="Y5" s="5" t="n"/>
+      <c r="T5" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Reviews/Westbury-Kommerce-Reviews-E6166527.htm</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>Diversity and inclusion 2.0; Senior management 1.0; 'Be the first to recommend' = 0% recommend</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
       <c r="Z5" s="5" t="n"/>
     </row>
     <row r="6">

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -940,75 +940,247 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>M-20260808-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>RK World Infocom</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Glassdoor</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Glassdoor</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
       <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>good company to work for</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Reviews/Employee-Review-Rk-Worldinfocom-E8268877-RVW105157672.htm</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Current Employee</t>
+        </is>
+      </c>
       <c r="N2" s="5" t="n"/>
-      <c r="O2" s="14" t="n"/>
+      <c r="O2" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="P2" s="5" t="n"/>
-      <c r="Q2" s="5" t="n"/>
-      <c r="R2" s="5" t="n"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="n"/>
-      <c r="T2" s="5" t="n"/>
-      <c r="U2" s="5" t="n"/>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
       <c r="V2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>M-20260829-001</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>46268</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>46263</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>RK Group</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>AmbitionBox</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>AmbitionBox</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Management | Culture</t>
+        </is>
+      </c>
       <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>There is big politics inside the company old people don't want work according to new guys they always pinch to director or uppper lavel management.7 days (Flexible Timings), This job involves Travel Within Country, Travel Within City.</t>
+        </is>
+      </c>
       <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="N3" s="5" t="n"/>
-      <c r="O3" s="14" t="n"/>
+      <c r="O3" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="P3" s="5" t="n"/>
-      <c r="Q3" s="5" t="n"/>
-      <c r="R3" s="5" t="n"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="n"/>
-      <c r="T3" s="5" t="n"/>
-      <c r="U3" s="5" t="n"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
       <c r="V3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>M-20260905-001</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>46275</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>46270</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>RK World Infocom</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>AmbitionBox</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>AmbitionBox</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Culture | Appraisals</t>
+        </is>
+      </c>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Team Outing, Supportive team members,Salary way below market standard, no promotions,5 days (Strict Timings), This is a desk job, Occasional overtime</t>
+        </is>
+      </c>
       <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Anonymous</t>
+        </is>
+      </c>
       <c r="N4" s="5" t="n"/>
-      <c r="O4" s="14" t="n"/>
+      <c r="O4" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
-      <c r="R4" s="5" t="n"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="S4" s="5" t="n"/>
-      <c r="T4" s="5" t="n"/>
-      <c r="U4" s="5" t="n"/>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
       <c r="V4" s="5" t="n"/>
     </row>
     <row r="5">

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -1055,7 +1055,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -1066,13 +1066,17 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>There is big politics inside the company old people don't want work according to new guys they always pinch to director or uppper lavel management.7 days (Flexible Timings), This job involves Travel Within Country, Travel Within City.</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
+          <t>Describes internal politics, says longer-serving staff escalate to directors rather than work with newer employees</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/reviews/r-dot-k-dot-group-reviews</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Anonymous</t>
         </is>
       </c>
       <c r="N3" s="5" t="n"/>
@@ -1106,7 +1110,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>M-20260905-001</t>
+          <t>M-20260905-002</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -1140,19 +1144,23 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Culture | Appraisals</t>
+          <t>Salary &amp; Appraisals | Growth | Culture</t>
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Team Outing, Supportive team members,Salary way below market standard, no promotions,5 days (Strict Timings), This is a desk job, Occasional overtime</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
+          <t>Praises supportive team and outings, says salary is well below market with no promotions</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/reviews/r-k-world-infocom-reviews</t>
+        </is>
+      </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Anonymous</t>
+          <t>Current Employee</t>
         </is>
       </c>
       <c r="N4" s="5" t="n"/>
@@ -13972,27 +13980,17 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="E2" s="15" t="n"/>
-      <c r="F2" s="7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.ambitionbox.com/reviews/r-dot-k-dot-group-reviews</t>
@@ -14000,7 +13998,7 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>SCOPE: Bengaluru-filtered, not all locations. GENDER SPLIT: women 1.7 (7 reviews) vs men 3.5 (19) - a 1.8 point gap. Skill Development 2.3.</t>
+          <t>ALL LOCATIONS, corrected 2026-09-22. The first reading was the Bengaluru view: 2.70 across 27 reviews, against 3.30 across 151 company-wide - Bengaluru rates the group 0.6 lower than the rest of India. Locations: New Delhi 39, Bengaluru 27, Mumbai 6, Ahmedabad 5, Hyderabad 4, Lucknow 4, Daman &amp; Diu 3, others. Sub-scores cleared: they were Bengaluru-only and would have read as company-wide.</t>
         </is>
       </c>
       <c r="M2" s="7" t="n">

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -14002,13 +14002,13 @@
         </is>
       </c>
       <c r="M2" s="7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N2" s="15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="O2" s="15" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="P2" s="15" t="n"/>
       <c r="Q2" s="7" t="n"/>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="W2" s="5" t="inlineStr">
         <is>
-          <t>SCOPE: Bangalore-filtered view only, not all locations - 16 reviews is the Bangalore subset. 69% positive business outlook. Glassdoor classifies RK Group as Manufacturing; industry average 3.5. All-locations figure still needed.</t>
+          <t>ALL LOCATIONS, corrected 2026-09-22. The first reading was the Bangalore view: 3.60 across 16 reviews, 56% recommend. Company-wide is 3.70 across 30, 64% recommend, 65% positive business outlook - so Bangalore is the weaker half on Glassdoor too, matching AmbitionBox. Glassdoor classifies RK Group as Manufacturing; industry average 3.5. Employer Profile NOT claimed.</t>
         </is>
       </c>
       <c r="X2" s="6" t="n">

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -1055,7 +1055,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -1066,13 +1066,17 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>There is big politics inside the company old people don't want work according to new guys they always pinch to director or uppper lavel management.7 days (Flexible Timings), This job involves Travel Within Country, Travel Within City.</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
+          <t>Describes internal politics, says longer-serving staff escalate to directors rather than work with newer employees</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/reviews/r-dot-k-dot-group-reviews</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Anonymous</t>
         </is>
       </c>
       <c r="N3" s="5" t="n"/>
@@ -1106,7 +1110,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>M-20260905-001</t>
+          <t>M-20260905-002</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -1140,19 +1144,23 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Culture | Appraisals</t>
+          <t>Salary &amp; Appraisals | Growth | Culture</t>
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Team Outing, Supportive team members,Salary way below market standard, no promotions,5 days (Strict Timings), This is a desk job, Occasional overtime</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
+          <t>Praises supportive team and outings, says salary is well below market with no promotions</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/reviews/r-k-world-infocom-reviews</t>
+        </is>
+      </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Anonymous</t>
+          <t>Current Employee</t>
         </is>
       </c>
       <c r="N4" s="5" t="n"/>

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -13980,27 +13980,17 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="E2" s="15" t="n"/>
-      <c r="F2" s="7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.ambitionbox.com/reviews/r-dot-k-dot-group-reviews</t>
@@ -14008,17 +13998,17 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>SCOPE: Bengaluru-filtered, not all locations. GENDER SPLIT: women 1.7 (7 reviews) vs men 3.5 (19) - a 1.8 point gap. Skill Development 2.3.</t>
+          <t>ALL LOCATIONS, corrected 2026-09-22. The first reading was the Bengaluru view: 2.70 across 27 reviews, against 3.30 across 151 company-wide - Bengaluru rates the group 0.6 lower than the rest of India. Locations: New Delhi 39, Bengaluru 27, Mumbai 6, Ahmedabad 5, Hyderabad 4, Lucknow 4, Daman &amp; Diu 3, others. Sub-scores cleared: they were Bengaluru-only and would have read as company-wide.</t>
         </is>
       </c>
       <c r="M2" s="7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N2" s="15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="O2" s="15" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="P2" s="15" t="n"/>
       <c r="Q2" s="7" t="n"/>
@@ -14033,7 +14023,7 @@
       </c>
       <c r="W2" s="5" t="inlineStr">
         <is>
-          <t>SCOPE: Bangalore-filtered view only, not all locations - 16 reviews is the Bangalore subset. 69% positive business outlook. Glassdoor classifies RK Group as Manufacturing; industry average 3.5. All-locations figure still needed.</t>
+          <t>ALL LOCATIONS, corrected 2026-09-22. The first reading was the Bangalore view: 3.60 across 16 reviews, 56% recommend. Company-wide is 3.70 across 30, 64% recommend, 65% positive business outlook - so Bangalore is the weaker half on Glassdoor too, matching AmbitionBox. Glassdoor classifies RK Group as Manufacturing; industry average 3.5. Employer Profile NOT claimed.</t>
         </is>
       </c>
       <c r="X2" s="6" t="n">

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -13985,7 +13985,11 @@
       <c r="D2" s="5" t="n">
         <v>151</v>
       </c>
-      <c r="E2" s="15" t="n"/>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F2" s="7" t="n"/>
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="7" t="n"/>
@@ -14010,7 +14014,11 @@
       <c r="O2" s="15" t="n">
         <v>64</v>
       </c>
-      <c r="P2" s="15" t="n"/>
+      <c r="P2" s="15" t="inlineStr">
+        <is>
+          <t>not shown</t>
+        </is>
+      </c>
       <c r="Q2" s="7" t="n"/>
       <c r="R2" s="7" t="n"/>
       <c r="S2" s="7" t="n"/>
@@ -14051,7 +14059,11 @@
       <c r="D3" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="E3" s="15" t="n"/>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F3" s="7" t="n">
         <v>3.2</v>
       </c>
@@ -14086,7 +14098,11 @@
       <c r="O3" s="15" t="n">
         <v>78</v>
       </c>
-      <c r="P3" s="15" t="n"/>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>not shown</t>
+        </is>
+      </c>
       <c r="Q3" s="7" t="n">
         <v>3.5</v>
       </c>
@@ -14148,7 +14164,11 @@
       <c r="O4" s="15" t="n">
         <v>75</v>
       </c>
-      <c r="P4" s="15" t="n"/>
+      <c r="P4" s="15" t="inlineStr">
+        <is>
+          <t>not shown</t>
+        </is>
+      </c>
       <c r="Q4" s="7" t="n">
         <v>3.9</v>
       </c>
@@ -14197,7 +14217,11 @@
       <c r="D5" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="E5" s="15" t="n"/>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="n">
         <v>3.6</v>
       </c>
@@ -14230,7 +14254,11 @@
       <c r="O5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="15" t="n"/>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>not shown</t>
+        </is>
+      </c>
       <c r="Q5" s="7" t="n">
         <v>3.3</v>
       </c>

--- a/templates/HR_Intelligence_Master_Tracker.xlsx
+++ b/templates/HR_Intelligence_Master_Tracker.xlsx
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1000"/>
+  <dimension ref="A1:W1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="3" min="1" max="1"/>
@@ -815,7 +815,7 @@
     <col width="30" customWidth="1" style="3" min="10" max="10"/>
     <col width="46" customWidth="1" style="3" min="11" max="11"/>
     <col width="34" customWidth="1" style="3" min="12" max="12"/>
-    <col width="16" customWidth="1" style="3" min="13" max="13"/>
+    <col width="18" customWidth="1" style="3" min="13" max="13"/>
     <col width="18" customWidth="1" style="3" min="14" max="14"/>
     <col width="8" customWidth="1" style="3" min="15" max="15"/>
     <col width="12" customWidth="1" style="3" min="16" max="16"/>
@@ -890,50 +890,55 @@
       </c>
       <c r="M1" s="4" t="inlineStr">
         <is>
+          <t>Item Type</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
           <t>Author Type</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Role / Department</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Stars</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Names Individual</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Red Flag Escalated</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Red Flag Reason</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Logged By</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -992,36 +997,41 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
           <t>Current Employee</t>
         </is>
       </c>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="14" t="n">
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="5" t="n"/>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="S2" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" s="5" t="n"/>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="T2" s="5" t="n"/>
+      <c r="U2" s="5" t="inlineStr">
         <is>
           <t>Reviewed</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>desk</t>
         </is>
       </c>
-      <c r="V2" s="5" t="n"/>
+      <c r="W2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1076,36 +1086,41 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="14" t="n">
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="P3" s="5" t="n"/>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" s="5" t="n"/>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="T3" s="5" t="n"/>
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>Reviewed</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>desk</t>
         </is>
       </c>
-      <c r="V3" s="5" t="n"/>
+      <c r="W3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1160,36 +1175,41 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
           <t>Current Employee</t>
         </is>
       </c>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="14" t="n">
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" s="5" t="n"/>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>Reviewed</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>desk</t>
         </is>
       </c>
-      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
@@ -1204,16 +1224,16 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="n"/>
       <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
-      <c r="O5" s="14" t="n"/>
-      <c r="P5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="14" t="n"/>
       <c r="Q5" s="5" t="n"/>
       <c r="R5" s="5" t="n"/>
       <c r="S5" s="5" t="n"/>
       <c r="T5" s="5" t="n"/>
       <c r="U5" s="5" t="n"/>
       <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -1228,16 +1248,16 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="n"/>
       <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
-      <c r="O6" s="14" t="n"/>
-      <c r="P6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="14" t="n"/>
       <c r="Q6" s="5" t="n"/>
       <c r="R6" s="5" t="n"/>
       <c r="S6" s="5" t="n"/>
       <c r="T6" s="5" t="n"/>
       <c r="U6" s="5" t="n"/>
       <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -1252,16 +1272,16 @@
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="n"/>
       <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
       <c r="N7" s="5" t="n"/>
-      <c r="O7" s="14" t="n"/>
-      <c r="P7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="14" t="n"/>
       <c r="Q7" s="5" t="n"/>
       <c r="R7" s="5" t="n"/>
       <c r="S7" s="5" t="n"/>
       <c r="T7" s="5" t="n"/>
       <c r="U7" s="5" t="n"/>
       <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -1276,16 +1296,16 @@
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="n"/>
       <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
-      <c r="O8" s="14" t="n"/>
-      <c r="P8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="14" t="n"/>
       <c r="Q8" s="5" t="n"/>
       <c r="R8" s="5" t="n"/>
       <c r="S8" s="5" t="n"/>
       <c r="T8" s="5" t="n"/>
       <c r="U8" s="5" t="n"/>
       <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -1300,16 +1320,16 @@
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="5" t="n"/>
       <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="14" t="n"/>
       <c r="Q9" s="5" t="n"/>
       <c r="R9" s="5" t="n"/>
       <c r="S9" s="5" t="n"/>
       <c r="T9" s="5" t="n"/>
       <c r="U9" s="5" t="n"/>
       <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -1324,16 +1344,16 @@
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="n"/>
       <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="n"/>
-      <c r="O10" s="14" t="n"/>
-      <c r="P10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="14" t="n"/>
       <c r="Q10" s="5" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="S10" s="5" t="n"/>
       <c r="T10" s="5" t="n"/>
       <c r="U10" s="5" t="n"/>
       <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1348,16 +1368,16 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
       <c r="N11" s="5" t="n"/>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="14" t="n"/>
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
       <c r="T11" s="5" t="n"/>
       <c r="U11" s="5" t="n"/>
       <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1372,16 +1392,16 @@
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="n"/>
       <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
-      <c r="O12" s="14" t="n"/>
-      <c r="P12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="14" t="n"/>
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
       <c r="T12" s="5" t="n"/>
       <c r="U12" s="5" t="n"/>
       <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -1396,16 +1416,16 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
-      <c r="O13" s="14" t="n"/>
-      <c r="P13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="14" t="n"/>
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
       <c r="T13" s="5" t="n"/>
       <c r="U13" s="5" t="n"/>
       <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1420,16 +1440,16 @@
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
       <c r="N14" s="5" t="n"/>
-      <c r="O14" s="14" t="n"/>
-      <c r="P14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="14" t="n"/>
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
       <c r="T14" s="5" t="n"/>
       <c r="U14" s="5" t="n"/>
       <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1444,16 +1464,16 @@
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
-      <c r="O15" s="14" t="n"/>
-      <c r="P15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="14" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
       <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1468,16 +1488,16 @@
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="14" t="n"/>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
       <c r="T16" s="5" t="n"/>
       <c r="U16" s="5" t="n"/>
       <c r="V16" s="5" t="n"/>
+      <c r="W16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1492,16 +1512,16 @@
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
       <c r="N17" s="5" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="14" t="n"/>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="5" t="n"/>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
       <c r="V17" s="5" t="n"/>
+      <c r="W17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1516,16 +1536,16 @@
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
       <c r="N18" s="5" t="n"/>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="14" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
       <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -1540,16 +1560,16 @@
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="14" t="n"/>
       <c r="Q19" s="5" t="n"/>
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5" t="n"/>
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5" t="n"/>
       <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1564,16 +1584,16 @@
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
       <c r="N20" s="5" t="n"/>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="14" t="n"/>
       <c r="Q20" s="5" t="n"/>
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5" t="n"/>
       <c r="T20" s="5" t="n"/>
       <c r="U20" s="5" t="n"/>
       <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1588,16 +1608,16 @@
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
       <c r="N21" s="5" t="n"/>
-      <c r="O21" s="14" t="n"/>
-      <c r="P21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="14" t="n"/>
       <c r="Q21" s="5" t="n"/>
       <c r="R21" s="5" t="n"/>
       <c r="S21" s="5" t="n"/>
       <c r="T21" s="5" t="n"/>
       <c r="U21" s="5" t="n"/>
       <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -1612,16 +1632,16 @@
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
       <c r="N22" s="5" t="n"/>
-      <c r="O22" s="14" t="n"/>
-      <c r="P22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="14" t="n"/>
       <c r="Q22" s="5" t="n"/>
       <c r="R22" s="5" t="n"/>
       <c r="S22" s="5" t="n"/>
       <c r="T22" s="5" t="n"/>
       <c r="U22" s="5" t="n"/>
       <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1636,16 +1656,16 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="5" t="n"/>
       <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n"/>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="14" t="n"/>
       <c r="Q23" s="5" t="n"/>
       <c r="R23" s="5" t="n"/>
       <c r="S23" s="5" t="n"/>
       <c r="T23" s="5" t="n"/>
       <c r="U23" s="5" t="n"/>
       <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1660,16 +1680,16 @@
       <c r="J24" s="5" t="n"/>
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
       <c r="N24" s="5" t="n"/>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="14" t="n"/>
       <c r="Q24" s="5" t="n"/>
       <c r="R24" s="5" t="n"/>
       <c r="S24" s="5" t="n"/>
       <c r="T24" s="5" t="n"/>
       <c r="U24" s="5" t="n"/>
       <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -1684,16 +1704,16 @@
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
       <c r="N25" s="5" t="n"/>
-      <c r="O25" s="14" t="n"/>
-      <c r="P25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="14" t="n"/>
       <c r="Q25" s="5" t="n"/>
       <c r="R25" s="5" t="n"/>
       <c r="S25" s="5" t="n"/>
       <c r="T25" s="5" t="n"/>
       <c r="U25" s="5" t="n"/>
       <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -1708,16 +1728,16 @@
       <c r="J26" s="5" t="n"/>
       <c r="K26" s="5" t="n"/>
       <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
       <c r="N26" s="5" t="n"/>
-      <c r="O26" s="14" t="n"/>
-      <c r="P26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="14" t="n"/>
       <c r="Q26" s="5" t="n"/>
       <c r="R26" s="5" t="n"/>
       <c r="S26" s="5" t="n"/>
       <c r="T26" s="5" t="n"/>
       <c r="U26" s="5" t="n"/>
       <c r="V26" s="5" t="n"/>
+      <c r="W26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1732,16 +1752,16 @@
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="5" t="n"/>
       <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
       <c r="N27" s="5" t="n"/>
-      <c r="O27" s="14" t="n"/>
-      <c r="P27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="14" t="n"/>
       <c r="Q27" s="5" t="n"/>
       <c r="R27" s="5" t="n"/>
       <c r="S27" s="5" t="n"/>
       <c r="T27" s="5" t="n"/>
       <c r="U27" s="5" t="n"/>
       <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -1756,16 +1776,16 @@
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="5" t="n"/>
       <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
       <c r="N28" s="5" t="n"/>
-      <c r="O28" s="14" t="n"/>
-      <c r="P28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="14" t="n"/>
       <c r="Q28" s="5" t="n"/>
       <c r="R28" s="5" t="n"/>
       <c r="S28" s="5" t="n"/>
       <c r="T28" s="5" t="n"/>
       <c r="U28" s="5" t="n"/>
       <c r="V28" s="5" t="n"/>
+      <c r="W28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1780,16 +1800,16 @@
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="5" t="n"/>
       <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
       <c r="N29" s="5" t="n"/>
-      <c r="O29" s="14" t="n"/>
-      <c r="P29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="14" t="n"/>
       <c r="Q29" s="5" t="n"/>
       <c r="R29" s="5" t="n"/>
       <c r="S29" s="5" t="n"/>
       <c r="T29" s="5" t="n"/>
       <c r="U29" s="5" t="n"/>
       <c r="V29" s="5" t="n"/>
+      <c r="W29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1804,16 +1824,16 @@
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="5" t="n"/>
       <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
       <c r="N30" s="5" t="n"/>
-      <c r="O30" s="14" t="n"/>
-      <c r="P30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="14" t="n"/>
       <c r="Q30" s="5" t="n"/>
       <c r="R30" s="5" t="n"/>
       <c r="S30" s="5" t="n"/>
       <c r="T30" s="5" t="n"/>
       <c r="U30" s="5" t="n"/>
       <c r="V30" s="5" t="n"/>
+      <c r="W30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -1828,16 +1848,16 @@
       <c r="J31" s="5" t="n"/>
       <c r="K31" s="5" t="n"/>
       <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
       <c r="N31" s="5" t="n"/>
-      <c r="O31" s="14" t="n"/>
-      <c r="P31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="14" t="n"/>
       <c r="Q31" s="5" t="n"/>
       <c r="R31" s="5" t="n"/>
       <c r="S31" s="5" t="n"/>
       <c r="T31" s="5" t="n"/>
       <c r="U31" s="5" t="n"/>
       <c r="V31" s="5" t="n"/>
+      <c r="W31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -1852,16 +1872,16 @@
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="5" t="n"/>
       <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
       <c r="N32" s="5" t="n"/>
-      <c r="O32" s="14" t="n"/>
-      <c r="P32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="14" t="n"/>
       <c r="Q32" s="5" t="n"/>
       <c r="R32" s="5" t="n"/>
       <c r="S32" s="5" t="n"/>
       <c r="T32" s="5" t="n"/>
       <c r="U32" s="5" t="n"/>
       <c r="V32" s="5" t="n"/>
+      <c r="W32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -1876,16 +1896,16 @@
       <c r="J33" s="5" t="n"/>
       <c r="K33" s="5" t="n"/>
       <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
       <c r="N33" s="5" t="n"/>
-      <c r="O33" s="14" t="n"/>
-      <c r="P33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="14" t="n"/>
       <c r="Q33" s="5" t="n"/>
       <c r="R33" s="5" t="n"/>
       <c r="S33" s="5" t="n"/>
       <c r="T33" s="5" t="n"/>
       <c r="U33" s="5" t="n"/>
       <c r="V33" s="5" t="n"/>
+      <c r="W33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -1900,16 +1920,16 @@
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="5" t="n"/>
       <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
       <c r="N34" s="5" t="n"/>
-      <c r="O34" s="14" t="n"/>
-      <c r="P34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="14" t="n"/>
       <c r="Q34" s="5" t="n"/>
       <c r="R34" s="5" t="n"/>
       <c r="S34" s="5" t="n"/>
       <c r="T34" s="5" t="n"/>
       <c r="U34" s="5" t="n"/>
       <c r="V34" s="5" t="n"/>
+      <c r="W34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -1924,16 +1944,16 @@
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="5" t="n"/>
       <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
       <c r="N35" s="5" t="n"/>
-      <c r="O35" s="14" t="n"/>
-      <c r="P35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="14" t="n"/>
       <c r="Q35" s="5" t="n"/>
       <c r="R35" s="5" t="n"/>
       <c r="S35" s="5" t="n"/>
       <c r="T35" s="5" t="n"/>
       <c r="U35" s="5" t="n"/>
       <c r="V35" s="5" t="n"/>
+      <c r="W35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -1948,16 +1968,16 @@
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="n"/>
       <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
-      <c r="O36" s="14" t="n"/>
-      <c r="P36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="14" t="n"/>
       <c r="Q36" s="5" t="n"/>
       <c r="R36" s="5" t="n"/>
       <c r="S36" s="5" t="n"/>
       <c r="T36" s="5" t="n"/>
       <c r="U36" s="5" t="n"/>
       <c r="V36" s="5" t="n"/>
+      <c r="W36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -1972,16 +1992,16 @@
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="5" t="n"/>
       <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
-      <c r="O37" s="14" t="n"/>
-      <c r="P37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="14" t="n"/>
       <c r="Q37" s="5" t="n"/>
       <c r="R37" s="5" t="n"/>
       <c r="S37" s="5" t="n"/>
       <c r="T37" s="5" t="n"/>
       <c r="U37" s="5" t="n"/>
       <c r="V37" s="5" t="n"/>
+      <c r="W37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -1996,16 +2016,16 @@
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="5" t="n"/>
       <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
       <c r="N38" s="5" t="n"/>
-      <c r="O38" s="14" t="n"/>
-      <c r="P38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="14" t="n"/>
       <c r="Q38" s="5" t="n"/>
       <c r="R38" s="5" t="n"/>
       <c r="S38" s="5" t="n"/>
       <c r="T38" s="5" t="n"/>
       <c r="U38" s="5" t="n"/>
       <c r="V38" s="5" t="n"/>
+      <c r="W38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -2020,16 +2040,16 @@
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="5" t="n"/>
       <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
       <c r="N39" s="5" t="n"/>
-      <c r="O39" s="14" t="n"/>
-      <c r="P39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="14" t="n"/>
       <c r="Q39" s="5" t="n"/>
       <c r="R39" s="5" t="n"/>
       <c r="S39" s="5" t="n"/>
       <c r="T39" s="5" t="n"/>
       <c r="U39" s="5" t="n"/>
       <c r="V39" s="5" t="n"/>
+      <c r="W39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -2044,16 +2064,16 @@
       <c r="J40" s="5" t="n"/>
       <c r="K40" s="5" t="n"/>
       <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
       <c r="N40" s="5" t="n"/>
-      <c r="O40" s="14" t="n"/>
-      <c r="P40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="14" t="n"/>
       <c r="Q40" s="5" t="n"/>
       <c r="R40" s="5" t="n"/>
       <c r="S40" s="5" t="n"/>
       <c r="T40" s="5" t="n"/>
       <c r="U40" s="5" t="n"/>
       <c r="V40" s="5" t="n"/>
+      <c r="W40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -2068,16 +2088,16 @@
       <c r="J41" s="5" t="n"/>
       <c r="K41" s="5" t="n"/>
       <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
       <c r="N41" s="5" t="n"/>
-      <c r="O41" s="14" t="n"/>
-      <c r="P41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="14" t="n"/>
       <c r="Q41" s="5" t="n"/>
       <c r="R41" s="5" t="n"/>
       <c r="S41" s="5" t="n"/>
       <c r="T41" s="5" t="n"/>
       <c r="U41" s="5" t="n"/>
       <c r="V41" s="5" t="n"/>
+      <c r="W41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -2092,16 +2112,16 @@
       <c r="J42" s="5" t="n"/>
       <c r="K42" s="5" t="n"/>
       <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
       <c r="N42" s="5" t="n"/>
-      <c r="O42" s="14" t="n"/>
-      <c r="P42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="14" t="n"/>
       <c r="Q42" s="5" t="n"/>
       <c r="R42" s="5" t="n"/>
       <c r="S42" s="5" t="n"/>
       <c r="T42" s="5" t="n"/>
       <c r="U42" s="5" t="n"/>
       <c r="V42" s="5" t="n"/>
+      <c r="W42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -2116,16 +2136,16 @@
       <c r="J43" s="5" t="n"/>
       <c r="K43" s="5" t="n"/>
       <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
       <c r="N43" s="5" t="n"/>
-      <c r="O43" s="14" t="n"/>
-      <c r="P43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="14" t="n"/>
       <c r="Q43" s="5" t="n"/>
       <c r="R43" s="5" t="n"/>
       <c r="S43" s="5" t="n"/>
       <c r="T43" s="5" t="n"/>
       <c r="U43" s="5" t="n"/>
       <c r="V43" s="5" t="n"/>
+      <c r="W43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -2140,16 +2160,16 @@
       <c r="J44" s="5" t="n"/>
       <c r="K44" s="5" t="n"/>
       <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
       <c r="N44" s="5" t="n"/>
-      <c r="O44" s="14" t="n"/>
-      <c r="P44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="14" t="n"/>
       <c r="Q44" s="5" t="n"/>
       <c r="R44" s="5" t="n"/>
       <c r="S44" s="5" t="n"/>
       <c r="T44" s="5" t="n"/>
       <c r="U44" s="5" t="n"/>
       <c r="V44" s="5" t="n"/>
+      <c r="W44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -2164,16 +2184,16 @@
       <c r="J45" s="5" t="n"/>
       <c r="K45" s="5" t="n"/>
       <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
       <c r="N45" s="5" t="n"/>
-      <c r="O45" s="14" t="n"/>
-      <c r="P45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="14" t="n"/>
       <c r="Q45" s="5" t="n"/>
       <c r="R45" s="5" t="n"/>
       <c r="S45" s="5" t="n"/>
       <c r="T45" s="5" t="n"/>
       <c r="U45" s="5" t="n"/>
       <c r="V45" s="5" t="n"/>
+      <c r="W45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -2188,16 +2208,16 @@
       <c r="J46" s="5" t="n"/>
       <c r="K46" s="5" t="n"/>
       <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
       <c r="N46" s="5" t="n"/>
-      <c r="O46" s="14" t="n"/>
-      <c r="P46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="14" t="n"/>
       <c r="Q46" s="5" t="n"/>
       <c r="R46" s="5" t="n"/>
       <c r="S46" s="5" t="n"/>
       <c r="T46" s="5" t="n"/>
       <c r="U46" s="5" t="n"/>
       <c r="V46" s="5" t="n"/>
+      <c r="W46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -2212,16 +2232,16 @@
       <c r="J47" s="5" t="n"/>
       <c r="K47" s="5" t="n"/>
       <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
       <c r="N47" s="5" t="n"/>
-      <c r="O47" s="14" t="n"/>
-      <c r="P47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="14" t="n"/>
       <c r="Q47" s="5" t="n"/>
       <c r="R47" s="5" t="n"/>
       <c r="S47" s="5" t="n"/>
       <c r="T47" s="5" t="n"/>
       <c r="U47" s="5" t="n"/>
       <c r="V47" s="5" t="n"/>
+      <c r="W47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -2236,16 +2256,16 @@
       <c r="J48" s="5" t="n"/>
       <c r="K48" s="5" t="n"/>
       <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
       <c r="N48" s="5" t="n"/>
-      <c r="O48" s="14" t="n"/>
-      <c r="P48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="14" t="n"/>
       <c r="Q48" s="5" t="n"/>
       <c r="R48" s="5" t="n"/>
       <c r="S48" s="5" t="n"/>
       <c r="T48" s="5" t="n"/>
       <c r="U48" s="5" t="n"/>
       <c r="V48" s="5" t="n"/>
+      <c r="W48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -2260,16 +2280,16 @@
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="5" t="n"/>
       <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
       <c r="N49" s="5" t="n"/>
-      <c r="O49" s="14" t="n"/>
-      <c r="P49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="14" t="n"/>
       <c r="Q49" s="5" t="n"/>
       <c r="R49" s="5" t="n"/>
       <c r="S49" s="5" t="n"/>
       <c r="T49" s="5" t="n"/>
       <c r="U49" s="5" t="n"/>
       <c r="V49" s="5" t="n"/>
+      <c r="W49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -2284,16 +2304,16 @@
       <c r="J50" s="5" t="n"/>
       <c r="K50" s="5" t="n"/>
       <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
       <c r="N50" s="5" t="n"/>
-      <c r="O50" s="14" t="n"/>
-      <c r="P50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="14" t="n"/>
       <c r="Q50" s="5" t="n"/>
       <c r="R50" s="5" t="n"/>
       <c r="S50" s="5" t="n"/>
       <c r="T50" s="5" t="n"/>
       <c r="U50" s="5" t="n"/>
       <c r="V50" s="5" t="n"/>
+      <c r="W50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -2308,16 +2328,16 @@
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="5" t="n"/>
       <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
       <c r="N51" s="5" t="n"/>
-      <c r="O51" s="14" t="n"/>
-      <c r="P51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="14" t="n"/>
       <c r="Q51" s="5" t="n"/>
       <c r="R51" s="5" t="n"/>
       <c r="S51" s="5" t="n"/>
       <c r="T51" s="5" t="n"/>
       <c r="U51" s="5" t="n"/>
       <c r="V51" s="5" t="n"/>
+      <c r="W51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -2332,16 +2352,16 @@
       <c r="J52" s="5" t="n"/>
       <c r="K52" s="5" t="n"/>
       <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
       <c r="N52" s="5" t="n"/>
-      <c r="O52" s="14" t="n"/>
-      <c r="P52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="14" t="n"/>
       <c r="Q52" s="5" t="n"/>
       <c r="R52" s="5" t="n"/>
       <c r="S52" s="5" t="n"/>
       <c r="T52" s="5" t="n"/>
       <c r="U52" s="5" t="n"/>
       <c r="V52" s="5" t="n"/>
+      <c r="W52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -2356,16 +2376,16 @@
       <c r="J53" s="5" t="n"/>
       <c r="K53" s="5" t="n"/>
       <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
       <c r="N53" s="5" t="n"/>
-      <c r="O53" s="14" t="n"/>
-      <c r="P53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="14" t="n"/>
       <c r="Q53" s="5" t="n"/>
       <c r="R53" s="5" t="n"/>
       <c r="S53" s="5" t="n"/>
       <c r="T53" s="5" t="n"/>
       <c r="U53" s="5" t="n"/>
       <c r="V53" s="5" t="n"/>
+      <c r="W53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -2380,16 +2400,16 @@
       <c r="J54" s="5" t="n"/>
       <c r="K54" s="5" t="n"/>
       <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
       <c r="N54" s="5" t="n"/>
-      <c r="O54" s="14" t="n"/>
-      <c r="P54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="14" t="n"/>
       <c r="Q54" s="5" t="n"/>
       <c r="R54" s="5" t="n"/>
       <c r="S54" s="5" t="n"/>
       <c r="T54" s="5" t="n"/>
       <c r="U54" s="5" t="n"/>
       <c r="V54" s="5" t="n"/>
+      <c r="W54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -2404,16 +2424,16 @@
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="5" t="n"/>
       <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
       <c r="N55" s="5" t="n"/>
-      <c r="O55" s="14" t="n"/>
-      <c r="P55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="14" t="n"/>
       <c r="Q55" s="5" t="n"/>
       <c r="R55" s="5" t="n"/>
       <c r="S55" s="5" t="n"/>
       <c r="T55" s="5" t="n"/>
       <c r="U55" s="5" t="n"/>
       <c r="V55" s="5" t="n"/>
+      <c r="W55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -2428,16 +2448,16 @@
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="n"/>
       <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
       <c r="N56" s="5" t="n"/>
-      <c r="O56" s="14" t="n"/>
-      <c r="P56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="14" t="n"/>
       <c r="Q56" s="5" t="n"/>
       <c r="R56" s="5" t="n"/>
       <c r="S56" s="5" t="n"/>
       <c r="T56" s="5" t="n"/>
       <c r="U56" s="5" t="n"/>
       <c r="V56" s="5" t="n"/>
+      <c r="W56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -2452,16 +2472,16 @@
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="5" t="n"/>
       <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="n"/>
-      <c r="O57" s="14" t="n"/>
-      <c r="P57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="14" t="n"/>
       <c r="Q57" s="5" t="n"/>
       <c r="R57" s="5" t="n"/>
       <c r="S57" s="5" t="n"/>
       <c r="T57" s="5" t="n"/>
       <c r="U57" s="5" t="n"/>
       <c r="V57" s="5" t="n"/>
+      <c r="W57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -2476,16 +2496,16 @@
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="5" t="n"/>
       <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
       <c r="N58" s="5" t="n"/>
-      <c r="O58" s="14" t="n"/>
-      <c r="P58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="14" t="n"/>
       <c r="Q58" s="5" t="n"/>
       <c r="R58" s="5" t="n"/>
       <c r="S58" s="5" t="n"/>
       <c r="T58" s="5" t="n"/>
       <c r="U58" s="5" t="n"/>
       <c r="V58" s="5" t="n"/>
+      <c r="W58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -2500,16 +2520,16 @@
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="5" t="n"/>
       <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
       <c r="N59" s="5" t="n"/>
-      <c r="O59" s="14" t="n"/>
-      <c r="P59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="14" t="n"/>
       <c r="Q59" s="5" t="n"/>
       <c r="R59" s="5" t="n"/>
       <c r="S59" s="5" t="n"/>
       <c r="T59" s="5" t="n"/>
       <c r="U59" s="5" t="n"/>
       <c r="V59" s="5" t="n"/>
+      <c r="W59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -2524,16 +2544,16 @@
       <c r="J60" s="5" t="n"/>
       <c r="K60" s="5" t="n"/>
       <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
       <c r="N60" s="5" t="n"/>
-      <c r="O60" s="14" t="n"/>
-      <c r="P60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="14" t="n"/>
       <c r="Q60" s="5" t="n"/>
       <c r="R60" s="5" t="n"/>
       <c r="S60" s="5" t="n"/>
       <c r="T60" s="5" t="n"/>
       <c r="U60" s="5" t="n"/>
       <c r="V60" s="5" t="n"/>
+      <c r="W60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -2548,16 +2568,16 @@
       <c r="J61" s="5" t="n"/>
       <c r="K61" s="5" t="n"/>
       <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
       <c r="N61" s="5" t="n"/>
-      <c r="O61" s="14" t="n"/>
-      <c r="P61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="14" t="n"/>
       <c r="Q61" s="5" t="n"/>
       <c r="R61" s="5" t="n"/>
       <c r="S61" s="5" t="n"/>
       <c r="T61" s="5" t="n"/>
       <c r="U61" s="5" t="n"/>
       <c r="V61" s="5" t="n"/>
+      <c r="W61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -2572,16 +2592,16 @@
       <c r="J62" s="5" t="n"/>
       <c r="K62" s="5" t="n"/>
       <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
       <c r="N62" s="5" t="n"/>
-      <c r="O62" s="14" t="n"/>
-      <c r="P62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="14" t="n"/>
       <c r="Q62" s="5" t="n"/>
       <c r="R62" s="5" t="n"/>
       <c r="S62" s="5" t="n"/>
       <c r="T62" s="5" t="n"/>
       <c r="U62" s="5" t="n"/>
       <c r="V62" s="5" t="n"/>
+      <c r="W62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -2596,16 +2616,16 @@
       <c r="J63" s="5" t="n"/>
       <c r="K63" s="5" t="n"/>
       <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
       <c r="N63" s="5" t="n"/>
-      <c r="O63" s="14" t="n"/>
-      <c r="P63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="14" t="n"/>
       <c r="Q63" s="5" t="n"/>
       <c r="R63" s="5" t="n"/>
       <c r="S63" s="5" t="n"/>
       <c r="T63" s="5" t="n"/>
       <c r="U63" s="5" t="n"/>
       <c r="V63" s="5" t="n"/>
+      <c r="W63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -2620,16 +2640,16 @@
       <c r="J64" s="5" t="n"/>
       <c r="K64" s="5" t="n"/>
       <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
       <c r="N64" s="5" t="n"/>
-      <c r="O64" s="14" t="n"/>
-      <c r="P64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="14" t="n"/>
       <c r="Q64" s="5" t="n"/>
       <c r="R64" s="5" t="n"/>
       <c r="S64" s="5" t="n"/>
       <c r="T64" s="5" t="n"/>
       <c r="U64" s="5" t="n"/>
       <c r="V64" s="5" t="n"/>
+      <c r="W64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -2644,16 +2664,16 @@
       <c r="J65" s="5" t="n"/>
       <c r="K65" s="5" t="n"/>
       <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
       <c r="N65" s="5" t="n"/>
-      <c r="O65" s="14" t="n"/>
-      <c r="P65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="14" t="n"/>
       <c r="Q65" s="5" t="n"/>
       <c r="R65" s="5" t="n"/>
       <c r="S65" s="5" t="n"/>
       <c r="T65" s="5" t="n"/>
       <c r="U65" s="5" t="n"/>
       <c r="V65" s="5" t="n"/>
+      <c r="W65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -2668,16 +2688,16 @@
       <c r="J66" s="5" t="n"/>
       <c r="K66" s="5" t="n"/>
       <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
       <c r="N66" s="5" t="n"/>
-      <c r="O66" s="14" t="n"/>
-      <c r="P66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="14" t="n"/>
       <c r="Q66" s="5" t="n"/>
       <c r="R66" s="5" t="n"/>
       <c r="S66" s="5" t="n"/>
       <c r="T66" s="5" t="n"/>
       <c r="U66" s="5" t="n"/>
       <c r="V66" s="5" t="n"/>
+      <c r="W66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -2692,16 +2712,16 @@
       <c r="J67" s="5" t="n"/>
       <c r="K67" s="5" t="n"/>
       <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
       <c r="N67" s="5" t="n"/>
-      <c r="O67" s="14" t="n"/>
-      <c r="P67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="14" t="n"/>
       <c r="Q67" s="5" t="n"/>
       <c r="R67" s="5" t="n"/>
       <c r="S67" s="5" t="n"/>
       <c r="T67" s="5" t="n"/>
       <c r="U67" s="5" t="n"/>
       <c r="V67" s="5" t="n"/>
+      <c r="W67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
@@ -2716,16 +2736,16 @@
       <c r="J68" s="5" t="n"/>
       <c r="K68" s="5" t="n"/>
       <c r="L68" s="5" t="n"/>
-      <c r="M68" s="5" t="n"/>
       <c r="N68" s="5" t="n"/>
-      <c r="O68" s="14" t="n"/>
-      <c r="P68" s="5" t="n"/>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="14" t="n"/>
       <c r="Q68" s="5" t="n"/>
       <c r="R68" s="5" t="n"/>
       <c r="S68" s="5" t="n"/>
       <c r="T68" s="5" t="n"/>
       <c r="U68" s="5" t="n"/>
       <c r="V68" s="5" t="n"/>
+      <c r="W68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -2740,16 +2760,16 @@
       <c r="J69" s="5" t="n"/>
       <c r="K69" s="5" t="n"/>
       <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
       <c r="N69" s="5" t="n"/>
-      <c r="O69" s="14" t="n"/>
-      <c r="P69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="14" t="n"/>
       <c r="Q69" s="5" t="n"/>
       <c r="R69" s="5" t="n"/>
       <c r="S69" s="5" t="n"/>
       <c r="T69" s="5" t="n"/>
       <c r="U69" s="5" t="n"/>
       <c r="V69" s="5" t="n"/>
+      <c r="W69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -2764,16 +2784,16 @@
       <c r="J70" s="5" t="n"/>
       <c r="K70" s="5" t="n"/>
       <c r="L70" s="5" t="n"/>
-      <c r="M70" s="5" t="n"/>
       <c r="N70" s="5" t="n"/>
-      <c r="O70" s="14" t="n"/>
-      <c r="P70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="14" t="n"/>
       <c r="Q70" s="5" t="n"/>
       <c r="R70" s="5" t="n"/>
       <c r="S70" s="5" t="n"/>
       <c r="T70" s="5" t="n"/>
       <c r="U70" s="5" t="n"/>
       <c r="V70" s="5" t="n"/>
+      <c r="W70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -2788,16 +2808,16 @@
       <c r="J71" s="5" t="n"/>
       <c r="K71" s="5" t="n"/>
       <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
       <c r="N71" s="5" t="n"/>
-      <c r="O71" s="14" t="n"/>
-      <c r="P71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="14" t="n"/>
       <c r="Q71" s="5" t="n"/>
       <c r="R71" s="5" t="n"/>
       <c r="S71" s="5" t="n"/>
       <c r="T71" s="5" t="n"/>
       <c r="U71" s="5" t="n"/>
       <c r="V71" s="5" t="n"/>
+      <c r="W71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
@@ -2812,16 +2832,16 @@
       <c r="J72" s="5" t="n"/>
       <c r="K72" s="5" t="n"/>
       <c r="L72" s="5" t="n"/>
-      <c r="M72" s="5" t="n"/>
       <c r="N72" s="5" t="n"/>
-      <c r="O72" s="14" t="n"/>
-      <c r="P72" s="5" t="n"/>
+      <c r="O72" s="5" t="n"/>
+      <c r="P72" s="14" t="n"/>
       <c r="Q72" s="5" t="n"/>
       <c r="R72" s="5" t="n"/>
       <c r="S72" s="5" t="n"/>
       <c r="T72" s="5" t="n"/>
       <c r="U72" s="5" t="n"/>
       <c r="V72" s="5" t="n"/>
+      <c r="W72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -2836,16 +2856,16 @@
       <c r="J73" s="5" t="n"/>
       <c r="K73" s="5" t="n"/>
       <c r="L73" s="5" t="n"/>
-      <c r="M73" s="5" t="n"/>
       <c r="N73" s="5" t="n"/>
-      <c r="O73" s="14" t="n"/>
-      <c r="P73" s="5" t="n"/>
+      <c r="O73" s="5" t="n"/>
+      <c r="P73" s="14" t="n"/>
       <c r="Q73" s="5" t="n"/>
       <c r="R73" s="5" t="n"/>
       <c r="S73" s="5" t="n"/>
       <c r="T73" s="5" t="n"/>
       <c r="U73" s="5" t="n"/>
       <c r="V73" s="5" t="n"/>
+      <c r="W73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -2860,16 +2880,16 @@
       <c r="J74" s="5" t="n"/>
       <c r="K74" s="5" t="n"/>
       <c r="L74" s="5" t="n"/>
-      <c r="M74" s="5" t="n"/>
       <c r="N74" s="5" t="n"/>
-      <c r="O74" s="14" t="n"/>
-      <c r="P74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="14" t="n"/>
       <c r="Q74" s="5" t="n"/>
       <c r="R74" s="5" t="n"/>
       <c r="S74" s="5" t="n"/>
       <c r="T74" s="5" t="n"/>
       <c r="U74" s="5" t="n"/>
       <c r="V74" s="5" t="n"/>
+      <c r="W74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -2884,16 +2904,16 @@
       <c r="J75" s="5" t="n"/>
       <c r="K75" s="5" t="n"/>
       <c r="L75" s="5" t="n"/>
-      <c r="M75" s="5" t="n"/>
       <c r="N75" s="5" t="n"/>
-      <c r="O75" s="14" t="n"/>
-      <c r="P75" s="5" t="n"/>
+      <c r="O75" s="5" t="n"/>
+      <c r="P75" s="14" t="n"/>
       <c r="Q75" s="5" t="n"/>
       <c r="R75" s="5" t="n"/>
       <c r="S75" s="5" t="n"/>
       <c r="T75" s="5" t="n"/>
       <c r="U75" s="5" t="n"/>
       <c r="V75" s="5" t="n"/>
+      <c r="W75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -2908,16 +2928,16 @@
       <c r="J76" s="5" t="n"/>
       <c r="K76" s="5" t="n"/>
       <c r="L76" s="5" t="n"/>
-      <c r="M76" s="5" t="n"/>
       <c r="N76" s="5" t="n"/>
-      <c r="O76" s="14" t="n"/>
-      <c r="P76" s="5" t="n"/>
+      <c r="O76" s="5" t="n"/>
+      <c r="P76" s="14" t="n"/>
       <c r="Q76" s="5" t="n"/>
       <c r="R76" s="5" t="n"/>
       <c r="S76" s="5" t="n"/>
       <c r="T76" s="5" t="n"/>
       <c r="U76" s="5" t="n"/>
       <c r="V76" s="5" t="n"/>
+      <c r="W76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
@@ -2932,16 +2952,16 @@
       <c r="J77" s="5" t="n"/>
       <c r="K77" s="5" t="n"/>
       <c r="L77" s="5" t="n"/>
-      <c r="M77" s="5" t="n"/>
       <c r="N77" s="5" t="n"/>
-      <c r="O77" s="14" t="n"/>
-      <c r="P77" s="5" t="n"/>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="14" t="n"/>
       <c r="Q77" s="5" t="n"/>
       <c r="R77" s="5" t="n"/>
       <c r="S77" s="5" t="n"/>
       <c r="T77" s="5" t="n"/>
       <c r="U77" s="5" t="n"/>
       <c r="V77" s="5" t="n"/>
+      <c r="W77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -2956,16 +2976,16 @@
       <c r="J78" s="5" t="n"/>
       <c r="K78" s="5" t="n"/>
       <c r="L78" s="5" t="n"/>
-      <c r="M78" s="5" t="n"/>
       <c r="N78" s="5" t="n"/>
-      <c r="O78" s="14" t="n"/>
-      <c r="P78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="14" t="n"/>
       <c r="Q78" s="5" t="n"/>
       <c r="R78" s="5" t="n"/>
       <c r="S78" s="5" t="n"/>
       <c r="T78" s="5" t="n"/>
       <c r="U78" s="5" t="n"/>
       <c r="V78" s="5" t="n"/>
+      <c r="W78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -2980,16 +3000,16 @@
       <c r="J79" s="5" t="n"/>
       <c r="K79" s="5" t="n"/>
       <c r="L79" s="5" t="n"/>
-      <c r="M79" s="5" t="n"/>
       <c r="N79" s="5" t="n"/>
-      <c r="O79" s="14" t="n"/>
-      <c r="P79" s="5" t="n"/>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="14" t="n"/>
       <c r="Q79" s="5" t="n"/>
       <c r="R79" s="5" t="n"/>
       <c r="S79" s="5" t="n"/>
       <c r="T79" s="5" t="n"/>
       <c r="U79" s="5" t="n"/>
       <c r="V79" s="5" t="n"/>
+      <c r="W79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
@@ -3004,16 +3024,16 @@
       <c r="J80" s="5" t="n"/>
       <c r="K80" s="5" t="n"/>
       <c r="L80" s="5" t="n"/>
-      <c r="M80" s="5" t="n"/>
       <c r="N80" s="5" t="n"/>
-      <c r="O80" s="14" t="n"/>
-      <c r="P80" s="5" t="n"/>
+      <c r="O80" s="5" t="n"/>
+      <c r="P80" s="14" t="n"/>
       <c r="Q80" s="5" t="n"/>
       <c r="R80" s="5" t="n"/>
       <c r="S80" s="5" t="n"/>
       <c r="T80" s="5" t="n"/>
       <c r="U80" s="5" t="n"/>
       <c r="V80" s="5" t="n"/>
+      <c r="W80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
@@ -3028,16 +3048,16 @@
       <c r="J81" s="5" t="n"/>
       <c r="K81" s="5" t="n"/>
       <c r="L81" s="5" t="n"/>
-      <c r="M81" s="5" t="n"/>
       <c r="N81" s="5" t="n"/>
-      <c r="O81" s="14" t="n"/>
-      <c r="P81" s="5" t="n"/>
+      <c r="O81" s="5" t="n"/>
+      <c r="P81" s="14" t="n"/>
       <c r="Q81" s="5" t="n"/>
       <c r="R81" s="5" t="n"/>
       <c r="S81" s="5" t="n"/>
       <c r="T81" s="5" t="n"/>
       <c r="U81" s="5" t="n"/>
       <c r="V81" s="5" t="n"/>
+      <c r="W81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -3052,16 +3072,16 @@
       <c r="J82" s="5" t="n"/>
       <c r="K82" s="5" t="n"/>
       <c r="L82" s="5" t="n"/>
-      <c r="M82" s="5" t="n"/>
       <c r="N82" s="5" t="n"/>
-      <c r="O82" s="14" t="n"/>
-      <c r="P82" s="5" t="n"/>
+      <c r="O82" s="5" t="n"/>
+      <c r="P82" s="14" t="n"/>
       <c r="Q82" s="5" t="n"/>
       <c r="R82" s="5" t="n"/>
       <c r="S82" s="5" t="n"/>
       <c r="T82" s="5" t="n"/>
       <c r="U82" s="5" t="n"/>
       <c r="V82" s="5" t="n"/>
+      <c r="W82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -3076,16 +3096,16 @@
       <c r="J83" s="5" t="n"/>
       <c r="K83" s="5" t="n"/>
       <c r="L83" s="5" t="n"/>
-      <c r="M83" s="5" t="n"/>
       <c r="N83" s="5" t="n"/>
-      <c r="O83" s="14" t="n"/>
-      <c r="P83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="14" t="n"/>
       <c r="Q83" s="5" t="n"/>
       <c r="R83" s="5" t="n"/>
       <c r="S83" s="5" t="n"/>
       <c r="T83" s="5" t="n"/>
       <c r="U83" s="5" t="n"/>
       <c r="V83" s="5" t="n"/>
+      <c r="W83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
@@ -3100,16 +3120,16 @@
       <c r="J84" s="5" t="n"/>
       <c r="K84" s="5" t="n"/>
       <c r="L84" s="5" t="n"/>
-      <c r="M84" s="5" t="n"/>
       <c r="N84" s="5" t="n"/>
-      <c r="O84" s="14" t="n"/>
-      <c r="P84" s="5" t="n"/>
+      <c r="O84" s="5" t="n"/>
+      <c r="P84" s="14" t="n"/>
       <c r="Q84" s="5" t="n"/>
       <c r="R84" s="5" t="n"/>
       <c r="S84" s="5" t="n"/>
       <c r="T84" s="5" t="n"/>
       <c r="U84" s="5" t="n"/>
       <c r="V84" s="5" t="n"/>
+      <c r="W84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -3124,16 +3144,16 @@
       <c r="J85" s="5" t="n"/>
       <c r="K85" s="5" t="n"/>
       <c r="L85" s="5" t="n"/>
-      <c r="M85" s="5" t="n"/>
       <c r="N85" s="5" t="n"/>
-      <c r="O85" s="14" t="n"/>
-      <c r="P85" s="5" t="n"/>
+      <c r="O85" s="5" t="n"/>
+      <c r="P85" s="14" t="n"/>
       <c r="Q85" s="5" t="n"/>
       <c r="R85" s="5" t="n"/>
       <c r="S85" s="5" t="n"/>
       <c r="T85" s="5" t="n"/>
       <c r="U85" s="5" t="n"/>
       <c r="V85" s="5" t="n"/>
+      <c r="W85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
@@ -3148,16 +3168,16 @@
       <c r="J86" s="5" t="n"/>
       <c r="K86" s="5" t="n"/>
       <c r="L86" s="5" t="n"/>
-      <c r="M86" s="5" t="n"/>
       <c r="N86" s="5" t="n"/>
-      <c r="O86" s="14" t="n"/>
-      <c r="P86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="14" t="n"/>
       <c r="Q86" s="5" t="n"/>
       <c r="R86" s="5" t="n"/>
       <c r="S86" s="5" t="n"/>
       <c r="T86" s="5" t="n"/>
       <c r="U86" s="5" t="n"/>
       <c r="V86" s="5" t="n"/>
+      <c r="W86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -3172,16 +3192,16 @@
       <c r="J87" s="5" t="n"/>
       <c r="K87" s="5" t="n"/>
       <c r="L87" s="5" t="n"/>
-      <c r="M87" s="5" t="n"/>
       <c r="N87" s="5" t="n"/>
-      <c r="O87" s="14" t="n"/>
-      <c r="P87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="14" t="n"/>
       <c r="Q87" s="5" t="n"/>
       <c r="R87" s="5" t="n"/>
       <c r="S87" s="5" t="n"/>
       <c r="T87" s="5" t="n"/>
       <c r="U87" s="5" t="n"/>
       <c r="V87" s="5" t="n"/>
+      <c r="W87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
@@ -3196,16 +3216,16 @@
       <c r="J88" s="5" t="n"/>
       <c r="K88" s="5" t="n"/>
       <c r="L88" s="5" t="n"/>
-      <c r="M88" s="5" t="n"/>
       <c r="N88" s="5" t="n"/>
-      <c r="O88" s="14" t="n"/>
-      <c r="P88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="14" t="n"/>
       <c r="Q88" s="5" t="n"/>
       <c r="R88" s="5" t="n"/>
       <c r="S88" s="5" t="n"/>
       <c r="T88" s="5" t="n"/>
       <c r="U88" s="5" t="n"/>
       <c r="V88" s="5" t="n"/>
+      <c r="W88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
@@ -3220,16 +3240,16 @@
       <c r="J89" s="5" t="n"/>
       <c r="K89" s="5" t="n"/>
       <c r="L89" s="5" t="n"/>
-      <c r="M89" s="5" t="n"/>
       <c r="N89" s="5" t="n"/>
-      <c r="O89" s="14" t="n"/>
-      <c r="P89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="14" t="n"/>
       <c r="Q89" s="5" t="n"/>
       <c r="R89" s="5" t="n"/>
       <c r="S89" s="5" t="n"/>
       <c r="T89" s="5" t="n"/>
       <c r="U89" s="5" t="n"/>
       <c r="V89" s="5" t="n"/>
+      <c r="W89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
@@ -3244,16 +3264,16 @@
       <c r="J90" s="5" t="n"/>
       <c r="K90" s="5" t="n"/>
       <c r="L90" s="5" t="n"/>
-      <c r="M90" s="5" t="n"/>
       <c r="N90" s="5" t="n"/>
-      <c r="O90" s="14" t="n"/>
-      <c r="P90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="14" t="n"/>
       <c r="Q90" s="5" t="n"/>
       <c r="R90" s="5" t="n"/>
       <c r="S90" s="5" t="n"/>
       <c r="T90" s="5" t="n"/>
       <c r="U90" s="5" t="n"/>
       <c r="V90" s="5" t="n"/>
+      <c r="W90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
@@ -3268,16 +3288,16 @@
       <c r="J91" s="5" t="n"/>
       <c r="K91" s="5" t="n"/>
       <c r="L91" s="5" t="n"/>
-      <c r="M91" s="5" t="n"/>
       <c r="N91" s="5" t="n"/>
-      <c r="O91" s="14" t="n"/>
-      <c r="P91" s="5" t="n"/>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="14" t="n"/>
       <c r="Q91" s="5" t="n"/>
       <c r="R91" s="5" t="n"/>
       <c r="S91" s="5" t="n"/>
       <c r="T91" s="5" t="n"/>
       <c r="U91" s="5" t="n"/>
       <c r="V91" s="5" t="n"/>
+      <c r="W91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
@@ -3292,16 +3312,16 @@
       <c r="J92" s="5" t="n"/>
       <c r="K92" s="5" t="n"/>
       <c r="L92" s="5" t="n"/>
-      <c r="M92" s="5" t="n"/>
       <c r="N92" s="5" t="n"/>
-      <c r="O92" s="14" t="n"/>
-      <c r="P92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="14" t="n"/>
       <c r="Q92" s="5" t="n"/>
       <c r="R92" s="5" t="n"/>
       <c r="S92" s="5" t="n"/>
       <c r="T92" s="5" t="n"/>
       <c r="U92" s="5" t="n"/>
       <c r="V92" s="5" t="n"/>
+      <c r="W92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -3316,16 +3336,16 @@
       <c r="J93" s="5" t="n"/>
       <c r="K93" s="5" t="n"/>
       <c r="L93" s="5" t="n"/>
-      <c r="M93" s="5" t="n"/>
       <c r="N93" s="5" t="n"/>
-      <c r="O93" s="14" t="n"/>
-      <c r="P93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="14" t="n"/>
       <c r="Q93" s="5" t="n"/>
       <c r="R93" s="5" t="n"/>
       <c r="S93" s="5" t="n"/>
       <c r="T93" s="5" t="n"/>
       <c r="U93" s="5" t="n"/>
       <c r="V93" s="5" t="n"/>
+      <c r="W93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
@@ -3340,16 +3360,16 @@
       <c r="J94" s="5" t="n"/>
       <c r="K94" s="5" t="n"/>
       <c r="L94" s="5" t="n"/>
-      <c r="M94" s="5" t="n"/>
       <c r="N94" s="5" t="n"/>
-      <c r="O94" s="14" t="n"/>
-      <c r="P94" s="5" t="n"/>
+      <c r="O94" s="5" t="n"/>
+      <c r="P94" s="14" t="n"/>
       <c r="Q94" s="5" t="n"/>
       <c r="R94" s="5" t="n"/>
       <c r="S94" s="5" t="n"/>
       <c r="T94" s="5" t="n"/>
       <c r="U94" s="5" t="n"/>
       <c r="V94" s="5" t="n"/>
+      <c r="W94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
@@ -3364,16 +3384,16 @@
       <c r="J95" s="5" t="n"/>
       <c r="K95" s="5" t="n"/>
       <c r="L95" s="5" t="n"/>
-      <c r="M95" s="5" t="n"/>
       <c r="N95" s="5" t="n"/>
-      <c r="O95" s="14" t="n"/>
-      <c r="P95" s="5" t="n"/>
+      <c r="O95" s="5" t="n"/>
+      <c r="P95" s="14" t="n"/>
       <c r="Q95" s="5" t="n"/>
       <c r="R95" s="5" t="n"/>
       <c r="S95" s="5" t="n"/>
       <c r="T95" s="5" t="n"/>
       <c r="U95" s="5" t="n"/>
       <c r="V95" s="5" t="n"/>
+      <c r="W95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
@@ -3388,16 +3408,16 @@
       <c r="J96" s="5" t="n"/>
       <c r="K96" s="5" t="n"/>
       <c r="L96" s="5" t="n"/>
-      <c r="M96" s="5" t="n"/>
       <c r="N96" s="5" t="n"/>
-      <c r="O96" s="14" t="n"/>
-      <c r="P96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="14" t="n"/>
       <c r="Q96" s="5" t="n"/>
       <c r="R96" s="5" t="n"/>
       <c r="S96" s="5" t="n"/>
       <c r="T96" s="5" t="n"/>
       <c r="U96" s="5" t="n"/>
       <c r="V96" s="5" t="n"/>
+      <c r="W96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
@@ -3412,16 +3432,16 @@
       <c r="J97" s="5" t="n"/>
       <c r="K97" s="5" t="n"/>
       <c r="L97" s="5" t="n"/>
-      <c r="M97" s="5" t="n"/>
       <c r="N97" s="5" t="n"/>
-      <c r="O97" s="14" t="n"/>
-      <c r="P97" s="5" t="n"/>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="14" t="n"/>
       <c r="Q97" s="5" t="n"/>
       <c r="R97" s="5" t="n"/>
       <c r="S97" s="5" t="n"/>
       <c r="T97" s="5" t="n"/>
       <c r="U97" s="5" t="n"/>
       <c r="V97" s="5" t="n"/>
+      <c r="W97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
@@ -3436,16 +3456,16 @@
       <c r="J98" s="5" t="n"/>
       <c r="K98" s="5" t="n"/>
       <c r="L98" s="5" t="n"/>
-      <c r="M98" s="5" t="n"/>
       <c r="N98" s="5" t="n"/>
-      <c r="O98" s="14" t="n"/>
-      <c r="P98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="14" t="n"/>
       <c r="Q98" s="5" t="n"/>
       <c r="R98" s="5" t="n"/>
       <c r="S98" s="5" t="n"/>
       <c r="T98" s="5" t="n"/>
       <c r="U98" s="5" t="n"/>
       <c r="V98" s="5" t="n"/>
+      <c r="W98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -3460,16 +3480,16 @@
       <c r="J99" s="5" t="n"/>
       <c r="K99" s="5" t="n"/>
       <c r="L99" s="5" t="n"/>
-      <c r="M99" s="5" t="n"/>
       <c r="N99" s="5" t="n"/>
-      <c r="O99" s="14" t="n"/>
-      <c r="P99" s="5" t="n"/>
+      <c r="O99" s="5" t="n"/>
+      <c r="P99" s="14" t="n"/>
       <c r="Q99" s="5" t="n"/>
       <c r="R99" s="5" t="n"/>
       <c r="S99" s="5" t="n"/>
       <c r="T99" s="5" t="n"/>
       <c r="U99" s="5" t="n"/>
       <c r="V99" s="5" t="n"/>
+      <c r="W99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
@@ -3484,16 +3504,16 @@
       <c r="J100" s="5" t="n"/>
       <c r="K100" s="5" t="n"/>
       <c r="L100" s="5" t="n"/>
-      <c r="M100" s="5" t="n"/>
       <c r="N100" s="5" t="n"/>
-      <c r="O100" s="14" t="n"/>
-      <c r="P100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="14" t="n"/>
       <c r="Q100" s="5" t="n"/>
       <c r="R100" s="5" t="n"/>
       <c r="S100" s="5" t="n"/>
       <c r="T100" s="5" t="n"/>
       <c r="U100" s="5" t="n"/>
       <c r="V100" s="5" t="n"/>
+      <c r="W100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
@@ -3508,16 +3528,16 @@
       <c r="J101" s="5" t="n"/>
       <c r="K101" s="5" t="n"/>
       <c r="L101" s="5" t="n"/>
-      <c r="M101" s="5" t="n"/>
       <c r="N101" s="5" t="n"/>
-      <c r="O101" s="14" t="n"/>
-      <c r="P101" s="5" t="n"/>
+      <c r="O101" s="5" t="n"/>
+      <c r="P101" s="14" t="n"/>
       <c r="Q101" s="5" t="n"/>
       <c r="R101" s="5" t="n"/>
       <c r="S101" s="5" t="n"/>
       <c r="T101" s="5" t="n"/>
       <c r="U101" s="5" t="n"/>
       <c r="V101" s="5" t="n"/>
+      <c r="W101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
@@ -3532,16 +3552,16 @@
       <c r="J102" s="5" t="n"/>
       <c r="K102" s="5" t="n"/>
       <c r="L102" s="5" t="n"/>
-      <c r="M102" s="5" t="n"/>
       <c r="N102" s="5" t="n"/>
-      <c r="O102" s="14" t="n"/>
-      <c r="P102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
+      <c r="P102" s="14" t="n"/>
       <c r="Q102" s="5" t="n"/>
       <c r="R102" s="5" t="n"/>
       <c r="S102" s="5" t="n"/>
       <c r="T102" s="5" t="n"/>
       <c r="U102" s="5" t="n"/>
       <c r="V102" s="5" t="n"/>
+      <c r="W102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n"/>
@@ -3556,16 +3576,16 @@
       <c r="J103" s="5" t="n"/>
       <c r="K103" s="5" t="n"/>
       <c r="L103" s="5" t="n"/>
-      <c r="M103" s="5" t="n"/>
       <c r="N103" s="5" t="n"/>
-      <c r="O103" s="14" t="n"/>
-      <c r="P103" s="5" t="n"/>
+      <c r="O103" s="5" t="n"/>
+      <c r="P103" s="14" t="n"/>
       <c r="Q103" s="5" t="n"/>
       <c r="R103" s="5" t="n"/>
       <c r="S103" s="5" t="n"/>
       <c r="T103" s="5" t="n"/>
       <c r="U103" s="5" t="n"/>
       <c r="V103" s="5" t="n"/>
+      <c r="W103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
@@ -3580,16 +3600,16 @@
       <c r="J104" s="5" t="n"/>
       <c r="K104" s="5" t="n"/>
       <c r="L104" s="5" t="n"/>
-      <c r="M104" s="5" t="n"/>
       <c r="N104" s="5" t="n"/>
-      <c r="O104" s="14" t="n"/>
-      <c r="P104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
+      <c r="P104" s="14" t="n"/>
       <c r="Q104" s="5" t="n"/>
       <c r="R104" s="5" t="n"/>
       <c r="S104" s="5" t="n"/>
       <c r="T104" s="5" t="n"/>
       <c r="U104" s="5" t="n"/>
       <c r="V104" s="5" t="n"/>
+      <c r="W104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
@@ -3604,16 +3624,16 @@
       <c r="J105" s="5" t="n"/>
       <c r="K105" s="5" t="n"/>
       <c r="L105" s="5" t="n"/>
-      <c r="M105" s="5" t="n"/>
       <c r="N105" s="5" t="n"/>
-      <c r="O105" s="14" t="n"/>
-      <c r="P105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="14" t="n"/>
       <c r="Q105" s="5" t="n"/>
       <c r="R105" s="5" t="n"/>
       <c r="S105" s="5" t="n"/>
       <c r="T105" s="5" t="n"/>
       <c r="U105" s="5" t="n"/>
       <c r="V105" s="5" t="n"/>
+      <c r="W105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
@@ -3628,16 +3648,16 @@
       <c r="J106" s="5" t="n"/>
       <c r="K106" s="5" t="n"/>
       <c r="L106" s="5" t="n"/>
-      <c r="M106" s="5" t="n"/>
       <c r="N106" s="5" t="n"/>
-      <c r="O106" s="14" t="n"/>
-      <c r="P106" s="5" t="n"/>
+      <c r="O106" s="5" t="n"/>
+      <c r="P106" s="14" t="n"/>
       <c r="Q106" s="5" t="n"/>
       <c r="R106" s="5" t="n"/>
       <c r="S106" s="5" t="n"/>
       <c r="T106" s="5" t="n"/>
       <c r="U106" s="5" t="n"/>
       <c r="V106" s="5" t="n"/>
+      <c r="W106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
@@ -3652,16 +3672,16 @@
       <c r="J107" s="5" t="n"/>
       <c r="K107" s="5" t="n"/>
       <c r="L107" s="5" t="n"/>
-      <c r="M107" s="5" t="n"/>
       <c r="N107" s="5" t="n"/>
-      <c r="O107" s="14" t="n"/>
-      <c r="P107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="14" t="n"/>
       <c r="Q107" s="5" t="n"/>
       <c r="R107" s="5" t="n"/>
       <c r="S107" s="5" t="n"/>
       <c r="T107" s="5" t="n"/>
       <c r="U107" s="5" t="n"/>
       <c r="V107" s="5" t="n"/>
+      <c r="W107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
@@ -3676,16 +3696,16 @@
       <c r="J108" s="5" t="n"/>
       <c r="K108" s="5" t="n"/>
       <c r="L108" s="5" t="n"/>
-      <c r="M108" s="5" t="n"/>
       <c r="N108" s="5" t="n"/>
-      <c r="O108" s="14" t="n"/>
-      <c r="P108" s="5" t="n"/>
+      <c r="O108" s="5" t="n"/>
+      <c r="P108" s="14" t="n"/>
       <c r="Q108" s="5" t="n"/>
       <c r="R108" s="5" t="n"/>
       <c r="S108" s="5" t="n"/>
       <c r="T108" s="5" t="n"/>
       <c r="U108" s="5" t="n"/>
       <c r="V108" s="5" t="n"/>
+      <c r="W108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
@@ -3700,16 +3720,16 @@
       <c r="J109" s="5" t="n"/>
       <c r="K109" s="5" t="n"/>
       <c r="L109" s="5" t="n"/>
-      <c r="M109" s="5" t="n"/>
       <c r="N109" s="5" t="n"/>
-      <c r="O109" s="14" t="n"/>
-      <c r="P109" s="5" t="n"/>
+      <c r="O109" s="5" t="n"/>
+      <c r="P109" s="14" t="n"/>
       <c r="Q109" s="5" t="n"/>
       <c r="R109" s="5" t="n"/>
       <c r="S109" s="5" t="n"/>
       <c r="T109" s="5" t="n"/>
       <c r="U109" s="5" t="n"/>
       <c r="V109" s="5" t="n"/>
+      <c r="W109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n"/>
@@ -3724,16 +3744,16 @@
       <c r="J110" s="5" t="n"/>
       <c r="K110" s="5" t="n"/>
       <c r="L110" s="5" t="n"/>
-      <c r="M110" s="5" t="n"/>
       <c r="N110" s="5" t="n"/>
-      <c r="O110" s="14" t="n"/>
-      <c r="P110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
+      <c r="P110" s="14" t="n"/>
       <c r="Q110" s="5" t="n"/>
       <c r="R110" s="5" t="n"/>
       <c r="S110" s="5" t="n"/>
       <c r="T110" s="5" t="n"/>
       <c r="U110" s="5" t="n"/>
       <c r="V110" s="5" t="n"/>
+      <c r="W110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n"/>
@@ -3748,16 +3768,16 @@
       <c r="J111" s="5" t="n"/>
       <c r="K111" s="5" t="n"/>
       <c r="L111" s="5" t="n"/>
-      <c r="M111" s="5" t="n"/>
       <c r="N111" s="5" t="n"/>
-      <c r="O111" s="14" t="n"/>
-      <c r="P111" s="5" t="n"/>
+      <c r="O111" s="5" t="n"/>
+      <c r="P111" s="14" t="n"/>
       <c r="Q111" s="5" t="n"/>
       <c r="R111" s="5" t="n"/>
       <c r="S111" s="5" t="n"/>
       <c r="T111" s="5" t="n"/>
       <c r="U111" s="5" t="n"/>
       <c r="V111" s="5" t="n"/>
+      <c r="W111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -3772,16 +3792,16 @@
       <c r="J112" s="5" t="n"/>
       <c r="K112" s="5" t="n"/>
       <c r="L112" s="5" t="n"/>
-      <c r="M112" s="5" t="n"/>
       <c r="N112" s="5" t="n"/>
-      <c r="O112" s="14" t="n"/>
-      <c r="P112" s="5" t="n"/>
+      <c r="O112" s="5" t="n"/>
+      <c r="P112" s="14" t="n"/>
       <c r="Q112" s="5" t="n"/>
       <c r="R112" s="5" t="n"/>
       <c r="S112" s="5" t="n"/>
       <c r="T112" s="5" t="n"/>
       <c r="U112" s="5" t="n"/>
       <c r="V112" s="5" t="n"/>
+      <c r="W112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
@@ -3796,16 +3816,16 @@
       <c r="J113" s="5" t="n"/>
       <c r="K113" s="5" t="n"/>
       <c r="L113" s="5" t="n"/>
-      <c r="M113" s="5" t="n"/>
       <c r="N113" s="5" t="n"/>
-      <c r="O113" s="14" t="n"/>
-      <c r="P113" s="5" t="n"/>
+      <c r="O113" s="5" t="n"/>
+      <c r="P113" s="14" t="n"/>
       <c r="Q113" s="5" t="n"/>
       <c r="R113" s="5" t="n"/>
       <c r="S113" s="5" t="n"/>
       <c r="T113" s="5" t="n"/>
       <c r="U113" s="5" t="n"/>
       <c r="V113" s="5" t="n"/>
+      <c r="W113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n"/>
@@ -3820,16 +3840,16 @@
       <c r="J114" s="5" t="n"/>
       <c r="K114" s="5" t="n"/>
       <c r="L114" s="5" t="n"/>
-      <c r="M114" s="5" t="n"/>
       <c r="N114" s="5" t="n"/>
-      <c r="O114" s="14" t="n"/>
-      <c r="P114" s="5" t="n"/>
+      <c r="O114" s="5" t="n"/>
+      <c r="P114" s="14" t="n"/>
       <c r="Q114" s="5" t="n"/>
       <c r="R114" s="5" t="n"/>
       <c r="S114" s="5" t="n"/>
       <c r="T114" s="5" t="n"/>
       <c r="U114" s="5" t="n"/>
       <c r="V114" s="5" t="n"/>
+      <c r="W114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n"/>
@@ -3844,16 +3864,16 @@
       <c r="J115" s="5" t="n"/>
       <c r="K115" s="5" t="n"/>
       <c r="L115" s="5" t="n"/>
-      <c r="M115" s="5" t="n"/>
       <c r="N115" s="5" t="n"/>
-      <c r="O115" s="14" t="n"/>
-      <c r="P115" s="5" t="n"/>
+      <c r="O115" s="5" t="n"/>
+      <c r="P115" s="14" t="n"/>
       <c r="Q115" s="5" t="n"/>
       <c r="R115" s="5" t="n"/>
       <c r="S115" s="5" t="n"/>
       <c r="T115" s="5" t="n"/>
       <c r="U115" s="5" t="n"/>
       <c r="V115" s="5" t="n"/>
+      <c r="W115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
@@ -3868,16 +3888,16 @@
       <c r="J116" s="5" t="n"/>
       <c r="K116" s="5" t="n"/>
       <c r="L116" s="5" t="n"/>
-      <c r="M116" s="5" t="n"/>
       <c r="N116" s="5" t="n"/>
-      <c r="O116" s="14" t="n"/>
-      <c r="P116" s="5" t="n"/>
+      <c r="O116" s="5" t="n"/>
+      <c r="P116" s="14" t="n"/>
       <c r="Q116" s="5" t="n"/>
       <c r="R116" s="5" t="n"/>
       <c r="S116" s="5" t="n"/>
       <c r="T116" s="5" t="n"/>
       <c r="U116" s="5" t="n"/>
       <c r="V116" s="5" t="n"/>
+      <c r="W116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n"/>
@@ -3892,16 +3912,16 @@
       <c r="J117" s="5" t="n"/>
       <c r="K117" s="5" t="n"/>
       <c r="L117" s="5" t="n"/>
-      <c r="M117" s="5" t="n"/>
       <c r="N117" s="5" t="n"/>
-      <c r="O117" s="14" t="n"/>
-      <c r="P117" s="5" t="n"/>
+      <c r="O117" s="5" t="n"/>
+      <c r="P117" s="14" t="n"/>
       <c r="Q117" s="5" t="n"/>
       <c r="R117" s="5" t="n"/>
       <c r="S117" s="5" t="n"/>
       <c r="T117" s="5" t="n"/>
       <c r="U117" s="5" t="n"/>
       <c r="V117" s="5" t="n"/>
+      <c r="W117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
@@ -3916,16 +3936,16 @@
       <c r="J118" s="5" t="n"/>
       <c r="K118" s="5" t="n"/>
       <c r="L118" s="5" t="n"/>
-      <c r="M118" s="5" t="n"/>
       <c r="N118" s="5" t="n"/>
-      <c r="O118" s="14" t="n"/>
-      <c r="P118" s="5" t="n"/>
+      <c r="O118" s="5" t="n"/>
+      <c r="P118" s="14" t="n"/>
       <c r="Q118" s="5" t="n"/>
       <c r="R118" s="5" t="n"/>
       <c r="S118" s="5" t="n"/>
       <c r="T118" s="5" t="n"/>
       <c r="U118" s="5" t="n"/>
       <c r="V118" s="5" t="n"/>
+      <c r="W118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n"/>
@@ -3940,16 +3960,16 @@
       <c r="J119" s="5" t="n"/>
       <c r="K119" s="5" t="n"/>
       <c r="L119" s="5" t="n"/>
-      <c r="M119" s="5" t="n"/>
       <c r="N119" s="5" t="n"/>
-      <c r="O119" s="14" t="n"/>
-      <c r="P119" s="5" t="n"/>
+      <c r="O119" s="5" t="n"/>
+      <c r="P119" s="14" t="n"/>
       <c r="Q119" s="5" t="n"/>
       <c r="R119" s="5" t="n"/>
       <c r="S119" s="5" t="n"/>
       <c r="T119" s="5" t="n"/>
       <c r="U119" s="5" t="n"/>
       <c r="V119" s="5" t="n"/>
+      <c r="W119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n"/>
@@ -3964,16 +3984,16 @@
       <c r="J120" s="5" t="n"/>
       <c r="K120" s="5" t="n"/>
       <c r="L120" s="5" t="n"/>
-      <c r="M120" s="5" t="n"/>
       <c r="N120" s="5" t="n"/>
-      <c r="O120" s="14" t="n"/>
-      <c r="P120" s="5" t="n"/>
+      <c r="O120" s="5" t="n"/>
+      <c r="P120" s="14" t="n"/>
       <c r="Q120" s="5" t="n"/>
       <c r="R120" s="5" t="n"/>
       <c r="S120" s="5" t="n"/>
       <c r="T120" s="5" t="n"/>
       <c r="U120" s="5" t="n"/>
       <c r="V120" s="5" t="n"/>
+      <c r="W120" s="5" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n"/>
@@ -3988,16 +4008,16 @@
       <c r="J121" s="5" t="n"/>
       <c r="K121" s="5" t="n"/>
       <c r="L121" s="5" t="n"/>
-      <c r="M121" s="5" t="n"/>
       <c r="N121" s="5" t="n"/>
-      <c r="O121" s="14" t="n"/>
-      <c r="P121" s="5" t="n"/>
+      <c r="O121" s="5" t="n"/>
+      <c r="P121" s="14" t="n"/>
       <c r="Q121" s="5" t="n"/>
       <c r="R121" s="5" t="n"/>
       <c r="S121" s="5" t="n"/>
       <c r="T121" s="5" t="n"/>
       <c r="U121" s="5" t="n"/>
       <c r="V121" s="5" t="n"/>
+      <c r="W121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n"/>
@@ -4012,16 +4032,16 @@
       <c r="J122" s="5" t="n"/>
       <c r="K122" s="5" t="n"/>
       <c r="L122" s="5" t="n"/>
-      <c r="M122" s="5" t="n"/>
       <c r="N122" s="5" t="n"/>
-      <c r="O122" s="14" t="n"/>
-      <c r="P122" s="5" t="n"/>
+      <c r="O122" s="5" t="n"/>
+      <c r="P122" s="14" t="n"/>
       <c r="Q122" s="5" t="n"/>
       <c r="R122" s="5" t="n"/>
       <c r="S122" s="5" t="n"/>
       <c r="T122" s="5" t="n"/>
       <c r="U122" s="5" t="n"/>
       <c r="V122" s="5" t="n"/>
+      <c r="W122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n"/>
@@ -4036,16 +4056,16 @@
       <c r="J123" s="5" t="n"/>
       <c r="K123" s="5" t="n"/>
       <c r="L123" s="5" t="n"/>
-      <c r="M123" s="5" t="n"/>
       <c r="N123" s="5" t="n"/>
-      <c r="O123" s="14" t="n"/>
-      <c r="P123" s="5" t="n"/>
+      <c r="O123" s="5" t="n"/>
+      <c r="P123" s="14" t="n"/>
       <c r="Q123" s="5" t="n"/>
       <c r="R123" s="5" t="n"/>
       <c r="S123" s="5" t="n"/>
       <c r="T123" s="5" t="n"/>
       <c r="U123" s="5" t="n"/>
       <c r="V123" s="5" t="n"/>
+      <c r="W123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n"/>
@@ -4060,16 +4080,16 @@
       <c r="J124" s="5" t="n"/>
       <c r="K124" s="5" t="n"/>
       <c r="L124" s="5" t="n"/>
-      <c r="M124" s="5" t="n"/>
       <c r="N124" s="5" t="n"/>
-      <c r="O124" s="14" t="n"/>
-      <c r="P124" s="5" t="n"/>
+      <c r="O124" s="5" t="n"/>
+      <c r="P124" s="14" t="n"/>
       <c r="Q124" s="5" t="n"/>
       <c r="R124" s="5" t="n"/>
       <c r="S124" s="5" t="n"/>
       <c r="T124" s="5" t="n"/>
       <c r="U124" s="5" t="n"/>
       <c r="V124" s="5" t="n"/>
+      <c r="W124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
@@ -4084,16 +4104,16 @@
       <c r="J125" s="5" t="n"/>
       <c r="K125" s="5" t="n"/>
       <c r="L125" s="5" t="n"/>
-      <c r="M125" s="5" t="n"/>
       <c r="N125" s="5" t="n"/>
-      <c r="O125" s="14" t="n"/>
-      <c r="P125" s="5" t="n"/>
+      <c r="O125" s="5" t="n"/>
+      <c r="P125" s="14" t="n"/>
       <c r="Q125" s="5" t="n"/>
       <c r="R125" s="5" t="n"/>
       <c r="S125" s="5" t="n"/>
       <c r="T125" s="5" t="n"/>
       <c r="U125" s="5" t="n"/>
       <c r="V125" s="5" t="n"/>
+      <c r="W125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n"/>
@@ -4108,16 +4128,16 @@
       <c r="J126" s="5" t="n"/>
       <c r="K126" s="5" t="n"/>
       <c r="L126" s="5" t="n"/>
-      <c r="M126" s="5" t="n"/>
       <c r="N126" s="5" t="n"/>
-      <c r="O126" s="14" t="n"/>
-      <c r="P126" s="5" t="n"/>
+      <c r="O126" s="5" t="n"/>
+      <c r="P126" s="14" t="n"/>
       <c r="Q126" s="5" t="n"/>
       <c r="R126" s="5" t="n"/>
       <c r="S126" s="5" t="n"/>
       <c r="T126" s="5" t="n"/>
       <c r="U126" s="5" t="n"/>
       <c r="V126" s="5" t="n"/>
+      <c r="W126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n"/>
@@ -4132,16 +4152,16 @@
       <c r="J127" s="5" t="n"/>
       <c r="K127" s="5" t="n"/>
       <c r="L127" s="5" t="n"/>
-      <c r="M127" s="5" t="n"/>
       <c r="N127" s="5" t="n"/>
-      <c r="O127" s="14" t="n"/>
-      <c r="P127" s="5" t="n"/>
+      <c r="O127" s="5" t="n"/>
+      <c r="P127" s="14" t="n"/>
       <c r="Q127" s="5" t="n"/>
       <c r="R127" s="5" t="n"/>
       <c r="S127" s="5" t="n"/>
       <c r="T127" s="5" t="n"/>
       <c r="U127" s="5" t="n"/>
       <c r="V127" s="5" t="n"/>
+      <c r="W127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n"/>
@@ -4156,16 +4176,16 @@
       <c r="J128" s="5" t="n"/>
       <c r="K128" s="5" t="n"/>
       <c r="L128" s="5" t="n"/>
-      <c r="M128" s="5" t="n"/>
       <c r="N128" s="5" t="n"/>
-      <c r="O128" s="14" t="n"/>
-      <c r="P128" s="5" t="n"/>
+      <c r="O128" s="5" t="n"/>
+      <c r="P128" s="14" t="n"/>
       <c r="Q128" s="5" t="n"/>
       <c r="R128" s="5" t="n"/>
       <c r="S128" s="5" t="n"/>
       <c r="T128" s="5" t="n"/>
       <c r="U128" s="5" t="n"/>
       <c r="V128" s="5" t="n"/>
+      <c r="W128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n"/>
@@ -4180,16 +4200,16 @@
       <c r="J129" s="5" t="n"/>
       <c r="K129" s="5" t="n"/>
       <c r="L129" s="5" t="n"/>
-      <c r="M129" s="5" t="n"/>
       <c r="N129" s="5" t="n"/>
-      <c r="O129" s="14" t="n"/>
-      <c r="P129" s="5" t="n"/>
+      <c r="O129" s="5" t="n"/>
+      <c r="P129" s="14" t="n"/>
       <c r="Q129" s="5" t="n"/>
       <c r="R129" s="5" t="n"/>
       <c r="S129" s="5" t="n"/>
       <c r="T129" s="5" t="n"/>
       <c r="U129" s="5" t="n"/>
       <c r="V129" s="5" t="n"/>
+      <c r="W129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
@@ -4204,16 +4224,16 @@
       <c r="J130" s="5" t="n"/>
       <c r="K130" s="5" t="n"/>
       <c r="L130" s="5" t="n"/>
-      <c r="M130" s="5" t="n"/>
       <c r="N130" s="5" t="n"/>
-      <c r="O130" s="14" t="n"/>
-      <c r="P130" s="5" t="n"/>
+      <c r="O130" s="5" t="n"/>
+      <c r="P130" s="14" t="n"/>
       <c r="Q130" s="5" t="n"/>
       <c r="R130" s="5" t="n"/>
       <c r="S130" s="5" t="n"/>
       <c r="T130" s="5" t="n"/>
       <c r="U130" s="5" t="n"/>
       <c r="V130" s="5" t="n"/>
+      <c r="W130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n"/>
@@ -4228,16 +4248,16 @@
       <c r="J131" s="5" t="n"/>
       <c r="K131" s="5" t="n"/>
       <c r="L131" s="5" t="n"/>
-      <c r="M131" s="5" t="n"/>
       <c r="N131" s="5" t="n"/>
-      <c r="O131" s="14" t="n"/>
-      <c r="P131" s="5" t="n"/>
+      <c r="O131" s="5" t="n"/>
+      <c r="P131" s="14" t="n"/>
       <c r="Q131" s="5" t="n"/>
       <c r="R131" s="5" t="n"/>
       <c r="S131" s="5" t="n"/>
       <c r="T131" s="5" t="n"/>
       <c r="U131" s="5" t="n"/>
       <c r="V131" s="5" t="n"/>
+      <c r="W131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n"/>
@@ -4252,16 +4272,16 @@
       <c r="J132" s="5" t="n"/>
       <c r="K132" s="5" t="n"/>
       <c r="L132" s="5" t="n"/>
-      <c r="M132" s="5" t="n"/>
       <c r="N132" s="5" t="n"/>
-      <c r="O132" s="14" t="n"/>
-      <c r="P132" s="5" t="n"/>
+      <c r="O132" s="5" t="n"/>
+      <c r="P132" s="14" t="n"/>
       <c r="Q132" s="5" t="n"/>
       <c r="R132" s="5" t="n"/>
       <c r="S132" s="5" t="n"/>
       <c r="T132" s="5" t="n"/>
       <c r="U132" s="5" t="n"/>
       <c r="V132" s="5" t="n"/>
+      <c r="W132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n"/>
@@ -4276,16 +4296,16 @@
       <c r="J133" s="5" t="n"/>
       <c r="K133" s="5" t="n"/>
       <c r="L133" s="5" t="n"/>
-      <c r="M133" s="5" t="n"/>
       <c r="N133" s="5" t="n"/>
-      <c r="O133" s="14" t="n"/>
-      <c r="P133" s="5" t="n"/>
+      <c r="O133" s="5" t="n"/>
+      <c r="P133" s="14" t="n"/>
       <c r="Q133" s="5" t="n"/>
       <c r="R133" s="5" t="n"/>
       <c r="S133" s="5" t="n"/>
       <c r="T133" s="5" t="n"/>
       <c r="U133" s="5" t="n"/>
       <c r="V133" s="5" t="n"/>
+      <c r="W133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n"/>
@@ -4300,16 +4320,16 @@
       <c r="J134" s="5" t="n"/>
       <c r="K134" s="5" t="n"/>
       <c r="L134" s="5" t="n"/>
-      <c r="M134" s="5" t="n"/>
       <c r="N134" s="5" t="n"/>
-      <c r="O134" s="14" t="n"/>
-      <c r="P134" s="5" t="n"/>
+      <c r="O134" s="5" t="n"/>
+      <c r="P134" s="14" t="n"/>
       <c r="Q134" s="5" t="n"/>
       <c r="R134" s="5" t="n"/>
       <c r="S134" s="5" t="n"/>
       <c r="T134" s="5" t="n"/>
       <c r="U134" s="5" t="n"/>
       <c r="V134" s="5" t="n"/>
+      <c r="W134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n"/>
@@ -4324,16 +4344,16 @@
       <c r="J135" s="5" t="n"/>
       <c r="K135" s="5" t="n"/>
       <c r="L135" s="5" t="n"/>
-      <c r="M135" s="5" t="n"/>
       <c r="N135" s="5" t="n"/>
-      <c r="O135" s="14" t="n"/>
-      <c r="P135" s="5" t="n"/>
+      <c r="O135" s="5" t="n"/>
+      <c r="P135" s="14" t="n"/>
       <c r="Q135" s="5" t="n"/>
       <c r="R135" s="5" t="n"/>
       <c r="S135" s="5" t="n"/>
       <c r="T135" s="5" t="n"/>
       <c r="U135" s="5" t="n"/>
       <c r="V135" s="5" t="n"/>
+      <c r="W135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n"/>
@@ -4348,16 +4368,16 @@
       <c r="J136" s="5" t="n"/>
       <c r="K136" s="5" t="n"/>
       <c r="L136" s="5" t="n"/>
-      <c r="M136" s="5" t="n"/>
       <c r="N136" s="5" t="n"/>
-      <c r="O136" s="14" t="n"/>
-      <c r="P136" s="5" t="n"/>
+      <c r="O136" s="5" t="n"/>
+      <c r="P136" s="14" t="n"/>
       <c r="Q136" s="5" t="n"/>
       <c r="R136" s="5" t="n"/>
       <c r="S136" s="5" t="n"/>
       <c r="T136" s="5" t="n"/>
       <c r="U136" s="5" t="n"/>
       <c r="V136" s="5" t="n"/>
+      <c r="W136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n"/>
@@ -4372,16 +4392,16 @@
       <c r="J137" s="5" t="n"/>
       <c r="K137" s="5" t="n"/>
       <c r="L137" s="5" t="n"/>
-      <c r="M137" s="5" t="n"/>
       <c r="N137" s="5" t="n"/>
-      <c r="O137" s="14" t="n"/>
-      <c r="P137" s="5" t="n"/>
+      <c r="O137" s="5" t="n"/>
+      <c r="P137" s="14" t="n"/>
       <c r="Q137" s="5" t="n"/>
       <c r="R137" s="5" t="n"/>
       <c r="S137" s="5" t="n"/>
       <c r="T137" s="5" t="n"/>
       <c r="U137" s="5" t="n"/>
       <c r="V137" s="5" t="n"/>
+      <c r="W137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n"/>
@@ -4396,16 +4416,16 @@
       <c r="J138" s="5" t="n"/>
       <c r="K138" s="5" t="n"/>
       <c r="L138" s="5" t="n"/>
-      <c r="M138" s="5" t="n"/>
       <c r="N138" s="5" t="n"/>
-      <c r="O138" s="14" t="n"/>
-      <c r="P138" s="5" t="n"/>
+      <c r="O138" s="5" t="n"/>
+      <c r="P138" s="14" t="n"/>
       <c r="Q138" s="5" t="n"/>
       <c r="R138" s="5" t="n"/>
       <c r="S138" s="5" t="n"/>
       <c r="T138" s="5" t="n"/>
       <c r="U138" s="5" t="n"/>
       <c r="V138" s="5" t="n"/>
+      <c r="W138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
@@ -4420,16 +4440,16 @@
       <c r="J139" s="5" t="n"/>
       <c r="K139" s="5" t="n"/>
       <c r="L139" s="5" t="n"/>
-      <c r="M139" s="5" t="n"/>
       <c r="N139" s="5" t="n"/>
-      <c r="O139" s="14" t="n"/>
-      <c r="P139" s="5" t="n"/>
+      <c r="O139" s="5" t="n"/>
+      <c r="P139" s="14" t="n"/>
       <c r="Q139" s="5" t="n"/>
       <c r="R139" s="5" t="n"/>
       <c r="S139" s="5" t="n"/>
       <c r="T139" s="5" t="n"/>
       <c r="U139" s="5" t="n"/>
       <c r="V139" s="5" t="n"/>
+      <c r="W139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
@@ -4444,16 +4464,16 @@
       <c r="J140" s="5" t="n"/>
       <c r="K140" s="5" t="n"/>
       <c r="L140" s="5" t="n"/>
-      <c r="M140" s="5" t="n"/>
       <c r="N140" s="5" t="n"/>
-      <c r="O140" s="14" t="n"/>
-      <c r="P140" s="5" t="n"/>
+      <c r="O140" s="5" t="n"/>
+      <c r="P140" s="14" t="n"/>
       <c r="Q140" s="5" t="n"/>
       <c r="R140" s="5" t="n"/>
       <c r="S140" s="5" t="n"/>
       <c r="T140" s="5" t="n"/>
       <c r="U140" s="5" t="n"/>
       <c r="V140" s="5" t="n"/>
+      <c r="W140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n"/>
@@ -4468,16 +4488,16 @@
       <c r="J141" s="5" t="n"/>
       <c r="K141" s="5" t="n"/>
       <c r="L141" s="5" t="n"/>
-      <c r="M141" s="5" t="n"/>
       <c r="N141" s="5" t="n"/>
-      <c r="O141" s="14" t="n"/>
-      <c r="P141" s="5" t="n"/>
+      <c r="O141" s="5" t="n"/>
+      <c r="P141" s="14" t="n"/>
       <c r="Q141" s="5" t="n"/>
       <c r="R141" s="5" t="n"/>
       <c r="S141" s="5" t="n"/>
       <c r="T141" s="5" t="n"/>
       <c r="U141" s="5" t="n"/>
       <c r="V141" s="5" t="n"/>
+      <c r="W141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
@@ -4492,16 +4512,16 @@
       <c r="J142" s="5" t="n"/>
       <c r="K142" s="5" t="n"/>
       <c r="L142" s="5" t="n"/>
-      <c r="M142" s="5" t="n"/>
       <c r="N142" s="5" t="n"/>
-      <c r="O142" s="14" t="n"/>
-      <c r="P142" s="5" t="n"/>
+      <c r="O142" s="5" t="n"/>
+      <c r="P142" s="14" t="n"/>
       <c r="Q142" s="5" t="n"/>
       <c r="R142" s="5" t="n"/>
       <c r="S142" s="5" t="n"/>
       <c r="T142" s="5" t="n"/>
       <c r="U142" s="5" t="n"/>
       <c r="V142" s="5" t="n"/>
+      <c r="W142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n"/>
@@ -4516,16 +4536,16 @@
       <c r="J143" s="5" t="n"/>
       <c r="K143" s="5" t="n"/>
       <c r="L143" s="5" t="n"/>
-      <c r="M143" s="5" t="n"/>
       <c r="N143" s="5" t="n"/>
-      <c r="O143" s="14" t="n"/>
-      <c r="P143" s="5" t="n"/>
+      <c r="O143" s="5" t="n"/>
+      <c r="P143" s="14" t="n"/>
       <c r="Q143" s="5" t="n"/>
       <c r="R143" s="5" t="n"/>
       <c r="S143" s="5" t="n"/>
       <c r="T143" s="5" t="n"/>
       <c r="U143" s="5" t="n"/>
       <c r="V143" s="5" t="n"/>
+      <c r="W143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n"/>
@@ -4540,16 +4560,16 @@
       <c r="J144" s="5" t="n"/>
       <c r="K144" s="5" t="n"/>
       <c r="L144" s="5" t="n"/>
-      <c r="M144" s="5" t="n"/>
       <c r="N144" s="5" t="n"/>
-      <c r="O144" s="14" t="n"/>
-      <c r="P144" s="5" t="n"/>
+      <c r="O144" s="5" t="n"/>
+      <c r="P144" s="14" t="n"/>
       <c r="Q144" s="5" t="n"/>
       <c r="R144" s="5" t="n"/>
       <c r="S144" s="5" t="n"/>
       <c r="T144" s="5" t="n"/>
       <c r="U144" s="5" t="n"/>
       <c r="V144" s="5" t="n"/>
+      <c r="W144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n"/>
@@ -4564,16 +4584,16 @@
       <c r="J145" s="5" t="n"/>
       <c r="K145" s="5" t="n"/>
       <c r="L145" s="5" t="n"/>
-      <c r="M145" s="5" t="n"/>
       <c r="N145" s="5" t="n"/>
-      <c r="O145" s="14" t="n"/>
-      <c r="P145" s="5" t="n"/>
+      <c r="O145" s="5" t="n"/>
+      <c r="P145" s="14" t="n"/>
       <c r="Q145" s="5" t="n"/>
       <c r="R145" s="5" t="n"/>
       <c r="S145" s="5" t="n"/>
       <c r="T145" s="5" t="n"/>
       <c r="U145" s="5" t="n"/>
       <c r="V145" s="5" t="n"/>
+      <c r="W145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n"/>
@@ -4588,16 +4608,16 @@
       <c r="J146" s="5" t="n"/>
       <c r="K146" s="5" t="n"/>
       <c r="L146" s="5" t="n"/>
-      <c r="M146" s="5" t="n"/>
       <c r="N146" s="5" t="n"/>
-      <c r="O146" s="14" t="n"/>
-      <c r="P146" s="5" t="n"/>
+      <c r="O146" s="5" t="n"/>
+      <c r="P146" s="14" t="n"/>
       <c r="Q146" s="5" t="n"/>
       <c r="R146" s="5" t="n"/>
       <c r="S146" s="5" t="n"/>
       <c r="T146" s="5" t="n"/>
       <c r="U146" s="5" t="n"/>
       <c r="V146" s="5" t="n"/>
+      <c r="W146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n"/>
@@ -4612,16 +4632,16 @@
       <c r="J147" s="5" t="n"/>
       <c r="K147" s="5" t="n"/>
       <c r="L147" s="5" t="n"/>
-      <c r="M147" s="5" t="n"/>
       <c r="N147" s="5" t="n"/>
-      <c r="O147" s="14" t="n"/>
-      <c r="P147" s="5" t="n"/>
+      <c r="O147" s="5" t="n"/>
+      <c r="P147" s="14" t="n"/>
       <c r="Q147" s="5" t="n"/>
       <c r="R147" s="5" t="n"/>
       <c r="S147" s="5" t="n"/>
       <c r="T147" s="5" t="n"/>
       <c r="U147" s="5" t="n"/>
       <c r="V147" s="5" t="n"/>
+      <c r="W147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n"/>
@@ -4636,16 +4656,16 @@
       <c r="J148" s="5" t="n"/>
       <c r="K148" s="5" t="n"/>
       <c r="L148" s="5" t="n"/>
-      <c r="M148" s="5" t="n"/>
       <c r="N148" s="5" t="n"/>
-      <c r="O148" s="14" t="n"/>
-      <c r="P148" s="5" t="n"/>
+      <c r="O148" s="5" t="n"/>
+      <c r="P148" s="14" t="n"/>
       <c r="Q148" s="5" t="n"/>
       <c r="R148" s="5" t="n"/>
       <c r="S148" s="5" t="n"/>
       <c r="T148" s="5" t="n"/>
       <c r="U148" s="5" t="n"/>
       <c r="V148" s="5" t="n"/>
+      <c r="W148" s="5" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n"/>
@@ -4660,16 +4680,16 @@
       <c r="J149" s="5" t="n"/>
       <c r="K149" s="5" t="n"/>
       <c r="L149" s="5" t="n"/>
-      <c r="M149" s="5" t="n"/>
       <c r="N149" s="5" t="n"/>
-      <c r="O149" s="14" t="n"/>
-      <c r="P149" s="5" t="n"/>
+      <c r="O149" s="5" t="n"/>
+      <c r="P149" s="14" t="n"/>
       <c r="Q149" s="5" t="n"/>
       <c r="R149" s="5" t="n"/>
       <c r="S149" s="5" t="n"/>
       <c r="T149" s="5" t="n"/>
       <c r="U149" s="5" t="n"/>
       <c r="V149" s="5" t="n"/>
+      <c r="W149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n"/>
@@ -4684,16 +4704,16 @@
       <c r="J150" s="5" t="n"/>
       <c r="K150" s="5" t="n"/>
       <c r="L150" s="5" t="n"/>
-      <c r="M150" s="5" t="n"/>
       <c r="N150" s="5" t="n"/>
-      <c r="O150" s="14" t="n"/>
-      <c r="P150" s="5" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="14" t="n"/>
       <c r="Q150" s="5" t="n"/>
       <c r="R150" s="5" t="n"/>
       <c r="S150" s="5" t="n"/>
       <c r="T150" s="5" t="n"/>
       <c r="U150" s="5" t="n"/>
       <c r="V150" s="5" t="n"/>
+      <c r="W150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n"/>
@@ -4708,16 +4728,16 @@
       <c r="J151" s="5" t="n"/>
       <c r="K151" s="5" t="n"/>
       <c r="L151" s="5" t="n"/>
-      <c r="M151" s="5" t="n"/>
       <c r="N151" s="5" t="n"/>
-      <c r="O151" s="14" t="n"/>
-      <c r="P151" s="5" t="n"/>
+      <c r="O151" s="5" t="n"/>
+      <c r="P151" s="14" t="n"/>
       <c r="Q151" s="5" t="n"/>
       <c r="R151" s="5" t="n"/>
       <c r="S151" s="5" t="n"/>
       <c r="T151" s="5" t="n"/>
       <c r="U151" s="5" t="n"/>
       <c r="V151" s="5" t="n"/>
+      <c r="W151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n"/>
@@ -4732,16 +4752,16 @@
       <c r="J152" s="5" t="n"/>
       <c r="K152" s="5" t="n"/>
       <c r="L152" s="5" t="n"/>
-      <c r="M152" s="5" t="n"/>
       <c r="N152" s="5" t="n"/>
-      <c r="O152" s="14" t="n"/>
-      <c r="P152" s="5" t="n"/>
+      <c r="O152" s="5" t="n"/>
+      <c r="P152" s="14" t="n"/>
       <c r="Q152" s="5" t="n"/>
       <c r="R152" s="5" t="n"/>
       <c r="S152" s="5" t="n"/>
       <c r="T152" s="5" t="n"/>
       <c r="U152" s="5" t="n"/>
       <c r="V152" s="5" t="n"/>
+      <c r="W152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n"/>
@@ -4756,16 +4776,16 @@
       <c r="J153" s="5" t="n"/>
       <c r="K153" s="5" t="n"/>
       <c r="L153" s="5" t="n"/>
-      <c r="M153" s="5" t="n"/>
       <c r="N153" s="5" t="n"/>
-      <c r="O153" s="14" t="n"/>
-      <c r="P153" s="5" t="n"/>
+      <c r="O153" s="5" t="n"/>
+      <c r="P153" s="14" t="n"/>
       <c r="Q153" s="5" t="n"/>
       <c r="R153" s="5" t="n"/>
       <c r="S153" s="5" t="n"/>
       <c r="T153" s="5" t="n"/>
       <c r="U153" s="5" t="n"/>
       <c r="V153" s="5" t="n"/>
+      <c r="W153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n"/>
@@ -4780,16 +4800,16 @@
       <c r="J154" s="5" t="n"/>
       <c r="K154" s="5" t="n"/>
       <c r="L154" s="5" t="n"/>
-      <c r="M154" s="5" t="n"/>
       <c r="N154" s="5" t="n"/>
-      <c r="O154" s="14" t="n"/>
-      <c r="P154" s="5" t="n"/>
+      <c r="O154" s="5" t="n"/>
+      <c r="P154" s="14" t="n"/>
       <c r="Q154" s="5" t="n"/>
       <c r="R154" s="5" t="n"/>
       <c r="S154" s="5" t="n"/>
       <c r="T154" s="5" t="n"/>
       <c r="U154" s="5" t="n"/>
       <c r="V154" s="5" t="n"/>
+      <c r="W154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n"/>
@@ -4804,16 +4824,16 @@
       <c r="J155" s="5" t="n"/>
       <c r="K155" s="5" t="n"/>
       <c r="L155" s="5" t="n"/>
-      <c r="M155" s="5" t="n"/>
       <c r="N155" s="5" t="n"/>
-      <c r="O155" s="14" t="n"/>
-      <c r="P155" s="5" t="n"/>
+      <c r="O155" s="5" t="n"/>
+      <c r="P155" s="14" t="n"/>
       <c r="Q155" s="5" t="n"/>
       <c r="R155" s="5" t="n"/>
       <c r="S155" s="5" t="n"/>
       <c r="T155" s="5" t="n"/>
       <c r="U155" s="5" t="n"/>
       <c r="V155" s="5" t="n"/>
+      <c r="W155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n"/>
@@ -4828,16 +4848,16 @@
       <c r="J156" s="5" t="n"/>
       <c r="K156" s="5" t="n"/>
       <c r="L156" s="5" t="n"/>
-      <c r="M156" s="5" t="n"/>
       <c r="N156" s="5" t="n"/>
-      <c r="O156" s="14" t="n"/>
-      <c r="P156" s="5" t="n"/>
+      <c r="O156" s="5" t="n"/>
+      <c r="P156" s="14" t="n"/>
       <c r="Q156" s="5" t="n"/>
       <c r="R156" s="5" t="n"/>
       <c r="S156" s="5" t="n"/>
       <c r="T156" s="5" t="n"/>
       <c r="U156" s="5" t="n"/>
       <c r="V156" s="5" t="n"/>
+      <c r="W156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n"/>
@@ -4852,16 +4872,16 @@
       <c r="J157" s="5" t="n"/>
       <c r="K157" s="5" t="n"/>
       <c r="L157" s="5" t="n"/>
-      <c r="M157" s="5" t="n"/>
       <c r="N157" s="5" t="n"/>
-      <c r="O157" s="14" t="n"/>
-      <c r="P157" s="5" t="n"/>
+      <c r="O157" s="5" t="n"/>
+      <c r="P157" s="14" t="n"/>
       <c r="Q157" s="5" t="n"/>
       <c r="R157" s="5" t="n"/>
       <c r="S157" s="5" t="n"/>
       <c r="T157" s="5" t="n"/>
       <c r="U157" s="5" t="n"/>
       <c r="V157" s="5" t="n"/>
+      <c r="W157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n"/>
@@ -4876,16 +4896,16 @@
       <c r="J158" s="5" t="n"/>
       <c r="K158" s="5" t="n"/>
       <c r="L158" s="5" t="n"/>
-      <c r="M158" s="5" t="n"/>
       <c r="N158" s="5" t="n"/>
-      <c r="O158" s="14" t="n"/>
-      <c r="P158" s="5" t="n"/>
+      <c r="O158" s="5" t="n"/>
+      <c r="P158" s="14" t="n"/>
       <c r="Q158" s="5" t="n"/>
       <c r="R158" s="5" t="n"/>
       <c r="S158" s="5" t="n"/>
       <c r="T158" s="5" t="n"/>
       <c r="U158" s="5" t="n"/>
       <c r="V158" s="5" t="n"/>
+      <c r="W158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n"/>
@@ -4900,16 +4920,16 @@
       <c r="J159" s="5" t="n"/>
       <c r="K159" s="5" t="n"/>
       <c r="L159" s="5" t="n"/>
-      <c r="M159" s="5" t="n"/>
       <c r="N159" s="5" t="n"/>
-      <c r="O159" s="14" t="n"/>
-      <c r="P159" s="5" t="n"/>
+      <c r="O159" s="5" t="n"/>
+      <c r="P159" s="14" t="n"/>
       <c r="Q159" s="5" t="n"/>
       <c r="R159" s="5" t="n"/>
       <c r="S159" s="5" t="n"/>
       <c r="T159" s="5" t="n"/>
       <c r="U159" s="5" t="n"/>
       <c r="V159" s="5" t="n"/>
+      <c r="W159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n"/>
@@ -4924,16 +4944,16 @@
       <c r="J160" s="5" t="n"/>
       <c r="K160" s="5" t="n"/>
       <c r="L160" s="5" t="n"/>
-      <c r="M160" s="5" t="n"/>
       <c r="N160" s="5" t="n"/>
-      <c r="O160" s="14" t="n"/>
-      <c r="P160" s="5" t="n"/>
+      <c r="O160" s="5" t="n"/>
+      <c r="P160" s="14" t="n"/>
       <c r="Q160" s="5" t="n"/>
       <c r="R160" s="5" t="n"/>
       <c r="S160" s="5" t="n"/>
       <c r="T160" s="5" t="n"/>
       <c r="U160" s="5" t="n"/>
       <c r="V160" s="5" t="n"/>
+      <c r="W160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
@@ -4948,16 +4968,16 @@
       <c r="J161" s="5" t="n"/>
       <c r="K161" s="5" t="n"/>
       <c r="L161" s="5" t="n"/>
-      <c r="M161" s="5" t="n"/>
       <c r="N161" s="5" t="n"/>
-      <c r="O161" s="14" t="n"/>
-      <c r="P161" s="5" t="n"/>
+      <c r="O161" s="5" t="n"/>
+      <c r="P161" s="14" t="n"/>
       <c r="Q161" s="5" t="n"/>
       <c r="R161" s="5" t="n"/>
       <c r="S161" s="5" t="n"/>
       <c r="T161" s="5" t="n"/>
       <c r="U161" s="5" t="n"/>
       <c r="V161" s="5" t="n"/>
+      <c r="W161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
@@ -4972,16 +4992,16 @@
       <c r="J162" s="5" t="n"/>
       <c r="K162" s="5" t="n"/>
       <c r="L162" s="5" t="n"/>
-      <c r="M162" s="5" t="n"/>
       <c r="N162" s="5" t="n"/>
-      <c r="O162" s="14" t="n"/>
-      <c r="P162" s="5" t="n"/>
+      <c r="O162" s="5" t="n"/>
+      <c r="P162" s="14" t="n"/>
       <c r="Q162" s="5" t="n"/>
       <c r="R162" s="5" t="n"/>
       <c r="S162" s="5" t="n"/>
       <c r="T162" s="5" t="n"/>
       <c r="U162" s="5" t="n"/>
       <c r="V162" s="5" t="n"/>
+      <c r="W162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n"/>
@@ -4996,16 +5016,16 @@
       <c r="J163" s="5" t="n"/>
       <c r="K163" s="5" t="n"/>
       <c r="L163" s="5" t="n"/>
-      <c r="M163" s="5" t="n"/>
       <c r="N163" s="5" t="n"/>
-      <c r="O163" s="14" t="n"/>
-      <c r="P163" s="5" t="n"/>
+      <c r="O163" s="5" t="n"/>
+      <c r="P163" s="14" t="n"/>
       <c r="Q163" s="5" t="n"/>
       <c r="R163" s="5" t="n"/>
       <c r="S163" s="5" t="n"/>
       <c r="T163" s="5" t="n"/>
       <c r="U163" s="5" t="n"/>
       <c r="V163" s="5" t="n"/>
+      <c r="W163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n"/>
@@ -5020,16 +5040,16 @@
       <c r="J164" s="5" t="n"/>
       <c r="K164" s="5" t="n"/>
       <c r="L164" s="5" t="n"/>
-      <c r="M164" s="5" t="n"/>
       <c r="N164" s="5" t="n"/>
-      <c r="O164" s="14" t="n"/>
-      <c r="P164" s="5" t="n"/>
+      <c r="O164" s="5" t="n"/>
+      <c r="P164" s="14" t="n"/>
       <c r="Q164" s="5" t="n"/>
       <c r="R164" s="5" t="n"/>
       <c r="S164" s="5" t="n"/>
       <c r="T164" s="5" t="n"/>
       <c r="U164" s="5" t="n"/>
       <c r="V164" s="5" t="n"/>
+      <c r="W164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
@@ -5044,16 +5064,16 @@
       <c r="J165" s="5" t="n"/>
       <c r="K165" s="5" t="n"/>
       <c r="L165" s="5" t="n"/>
-      <c r="M165" s="5" t="n"/>
       <c r="N165" s="5" t="n"/>
-      <c r="O165" s="14" t="n"/>
-      <c r="P165" s="5" t="n"/>
+      <c r="O165" s="5" t="n"/>
+      <c r="P165" s="14" t="n"/>
       <c r="Q165" s="5" t="n"/>
       <c r="R165" s="5" t="n"/>
       <c r="S165" s="5" t="n"/>
       <c r="T165" s="5" t="n"/>
       <c r="U165" s="5" t="n"/>
       <c r="V165" s="5" t="n"/>
+      <c r="W165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n"/>
@@ -5068,16 +5088,16 @@
       <c r="J166" s="5" t="n"/>
       <c r="K166" s="5" t="n"/>
       <c r="L166" s="5" t="n"/>
-      <c r="M166" s="5" t="n"/>
       <c r="N166" s="5" t="n"/>
-      <c r="O166" s="14" t="n"/>
-      <c r="P166" s="5" t="n"/>
+      <c r="O166" s="5" t="n"/>
+      <c r="P166" s="14" t="n"/>
       <c r="Q166" s="5" t="n"/>
       <c r="R166" s="5" t="n"/>
       <c r="S166" s="5" t="n"/>
       <c r="T166" s="5" t="n"/>
       <c r="U166" s="5" t="n"/>
       <c r="V166" s="5" t="n"/>
+      <c r="W166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n"/>
@@ -5092,16 +5112,16 @@
       <c r="J167" s="5" t="n"/>
       <c r="K167" s="5" t="n"/>
       <c r="L167" s="5" t="n"/>
-      <c r="M167" s="5" t="n"/>
       <c r="N167" s="5" t="n"/>
-      <c r="O167" s="14" t="n"/>
-      <c r="P167" s="5" t="n"/>
+      <c r="O167" s="5" t="n"/>
+      <c r="P167" s="14" t="n"/>
       <c r="Q167" s="5" t="n"/>
       <c r="R167" s="5" t="n"/>
       <c r="S167" s="5" t="n"/>
       <c r="T167" s="5" t="n"/>
       <c r="U167" s="5" t="n"/>
       <c r="V167" s="5" t="n"/>
+      <c r="W167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
@@ -5116,16 +5136,16 @@
       <c r="J168" s="5" t="n"/>
       <c r="K168" s="5" t="n"/>
       <c r="L168" s="5" t="n"/>
-      <c r="M168" s="5" t="n"/>
       <c r="N168" s="5" t="n"/>
-      <c r="O168" s="14" t="n"/>
-      <c r="P168" s="5" t="n"/>
+      <c r="O168" s="5" t="n"/>
+      <c r="P168" s="14" t="n"/>
       <c r="Q168" s="5" t="n"/>
       <c r="R168" s="5" t="n"/>
       <c r="S168" s="5" t="n"/>
       <c r="T168" s="5" t="n"/>
       <c r="U168" s="5" t="n"/>
       <c r="V168" s="5" t="n"/>
+      <c r="W168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
@@ -5140,16 +5160,16 @@
       <c r="J169" s="5" t="n"/>
       <c r="K169" s="5" t="n"/>
       <c r="L169" s="5" t="n"/>
-      <c r="M169" s="5" t="n"/>
       <c r="N169" s="5" t="n"/>
-      <c r="O169" s="14" t="n"/>
-      <c r="P169" s="5" t="n"/>
+      <c r="O169" s="5" t="n"/>
+      <c r="P169" s="14" t="n"/>
       <c r="Q169" s="5" t="n"/>
       <c r="R169" s="5" t="n"/>
       <c r="S169" s="5" t="n"/>
       <c r="T169" s="5" t="n"/>
       <c r="U169" s="5" t="n"/>
       <c r="V169" s="5" t="n"/>
+      <c r="W169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
@@ -5164,16 +5184,16 @@
       <c r="J170" s="5" t="n"/>
       <c r="K170" s="5" t="n"/>
       <c r="L170" s="5" t="n"/>
-      <c r="M170" s="5" t="n"/>
       <c r="N170" s="5" t="n"/>
-      <c r="O170" s="14" t="n"/>
-      <c r="P170" s="5" t="n"/>
+      <c r="O170" s="5" t="n"/>
+      <c r="P170" s="14" t="n"/>
       <c r="Q170" s="5" t="n"/>
       <c r="R170" s="5" t="n"/>
       <c r="S170" s="5" t="n"/>
       <c r="T170" s="5" t="n"/>
       <c r="U170" s="5" t="n"/>
       <c r="V170" s="5" t="n"/>
+      <c r="W170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n"/>
@@ -5188,16 +5208,16 @@
       <c r="J171" s="5" t="n"/>
       <c r="K171" s="5" t="n"/>
       <c r="L171" s="5" t="n"/>
-      <c r="M171" s="5" t="n"/>
       <c r="N171" s="5" t="n"/>
-      <c r="O171" s="14" t="n"/>
-      <c r="P171" s="5" t="n"/>
+      <c r="O171" s="5" t="n"/>
+      <c r="P171" s="14" t="n"/>
       <c r="Q171" s="5" t="n"/>
       <c r="R171" s="5" t="n"/>
       <c r="S171" s="5" t="n"/>
       <c r="T171" s="5" t="n"/>
       <c r="U171" s="5" t="n"/>
       <c r="V171" s="5" t="n"/>
+      <c r="W171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n"/>
@@ -5212,16 +5232,16 @@
       <c r="J172" s="5" t="n"/>
       <c r="K172" s="5" t="n"/>
       <c r="L172" s="5" t="n"/>
-      <c r="M172" s="5" t="n"/>
       <c r="N172" s="5" t="n"/>
-      <c r="O172" s="14" t="n"/>
-      <c r="P172" s="5" t="n"/>
+      <c r="O172" s="5" t="n"/>
+      <c r="P172" s="14" t="n"/>
       <c r="Q172" s="5" t="n"/>
       <c r="R172" s="5" t="n"/>
       <c r="S172" s="5" t="n"/>
       <c r="T172" s="5" t="n"/>
       <c r="U172" s="5" t="n"/>
       <c r="V172" s="5" t="n"/>
+      <c r="W172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n"/>
@@ -5236,16 +5256,16 @@
       <c r="J173" s="5" t="n"/>
       <c r="K173" s="5" t="n"/>
       <c r="L173" s="5" t="n"/>
-      <c r="M173" s="5" t="n"/>
       <c r="N173" s="5" t="n"/>
-      <c r="O173" s="14" t="n"/>
-      <c r="P173" s="5" t="n"/>
+      <c r="O173" s="5" t="n"/>
+      <c r="P173" s="14" t="n"/>
       <c r="Q173" s="5" t="n"/>
       <c r="R173" s="5" t="n"/>
       <c r="S173" s="5" t="n"/>
       <c r="T173" s="5" t="n"/>
       <c r="U173" s="5" t="n"/>
       <c r="V173" s="5" t="n"/>
+      <c r="W173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n"/>
@@ -5260,16 +5280,16 @@
       <c r="J174" s="5" t="n"/>
       <c r="K174" s="5" t="n"/>
       <c r="L174" s="5" t="n"/>
-      <c r="M174" s="5" t="n"/>
       <c r="N174" s="5" t="n"/>
-      <c r="O174" s="14" t="n"/>
-      <c r="P174" s="5" t="n"/>
+      <c r="O174" s="5" t="n"/>
+      <c r="P174" s="14" t="n"/>
       <c r="Q174" s="5" t="n"/>
       <c r="R174" s="5" t="n"/>
       <c r="S174" s="5" t="n"/>
       <c r="T174" s="5" t="n"/>
       <c r="U174" s="5" t="n"/>
       <c r="V174" s="5" t="n"/>
+      <c r="W174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n"/>
@@ -5284,16 +5304,16 @@
       <c r="J175" s="5" t="n"/>
       <c r="K175" s="5" t="n"/>
       <c r="L175" s="5" t="n"/>
-      <c r="M175" s="5" t="n"/>
       <c r="N175" s="5" t="n"/>
-      <c r="O175" s="14" t="n"/>
-      <c r="P175" s="5" t="n"/>
+      <c r="O175" s="5" t="n"/>
+      <c r="P175" s="14" t="n"/>
       <c r="Q175" s="5" t="n"/>
       <c r="R175" s="5" t="n"/>
       <c r="S175" s="5" t="n"/>
       <c r="T175" s="5" t="n"/>
       <c r="U175" s="5" t="n"/>
       <c r="V175" s="5" t="n"/>
+      <c r="W175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
@@ -5308,16 +5328,16 @@
       <c r="J176" s="5" t="n"/>
       <c r="K176" s="5" t="n"/>
       <c r="L176" s="5" t="n"/>
-      <c r="M176" s="5" t="n"/>
       <c r="N176" s="5" t="n"/>
-      <c r="O176" s="14" t="n"/>
-      <c r="P176" s="5" t="n"/>
+      <c r="O176" s="5" t="n"/>
+      <c r="P176" s="14" t="n"/>
       <c r="Q176" s="5" t="n"/>
       <c r="R176" s="5" t="n"/>
       <c r="S176" s="5" t="n"/>
       <c r="T176" s="5" t="n"/>
       <c r="U176" s="5" t="n"/>
       <c r="V176" s="5" t="n"/>
+      <c r="W176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n"/>
@@ -5332,16 +5352,16 @@
       <c r="J177" s="5" t="n"/>
       <c r="K177" s="5" t="n"/>
       <c r="L177" s="5" t="n"/>
-      <c r="M177" s="5" t="n"/>
       <c r="N177" s="5" t="n"/>
-      <c r="O177" s="14" t="n"/>
-      <c r="P177" s="5" t="n"/>
+      <c r="O177" s="5" t="n"/>
+      <c r="P177" s="14" t="n"/>
       <c r="Q177" s="5" t="n"/>
       <c r="R177" s="5" t="n"/>
       <c r="S177" s="5" t="n"/>
       <c r="T177" s="5" t="n"/>
       <c r="U177" s="5" t="n"/>
       <c r="V177" s="5" t="n"/>
+      <c r="W177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n"/>
@@ -5356,16 +5376,16 @@
       <c r="J178" s="5" t="n"/>
       <c r="K178" s="5" t="n"/>
       <c r="L178" s="5" t="n"/>
-      <c r="M178" s="5" t="n"/>
       <c r="N178" s="5" t="n"/>
-      <c r="O178" s="14" t="n"/>
-      <c r="P178" s="5" t="n"/>
+      <c r="O178" s="5" t="n"/>
+      <c r="P178" s="14" t="n"/>
       <c r="Q178" s="5" t="n"/>
       <c r="R178" s="5" t="n"/>
       <c r="S178" s="5" t="n"/>
       <c r="T178" s="5" t="n"/>
       <c r="U178" s="5" t="n"/>
       <c r="V178" s="5" t="n"/>
+      <c r="W178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
@@ -5380,16 +5400,16 @@
       <c r="J179" s="5" t="n"/>
       <c r="K179" s="5" t="n"/>
       <c r="L179" s="5" t="n"/>
-      <c r="M179" s="5" t="n"/>
       <c r="N179" s="5" t="n"/>
-      <c r="O179" s="14" t="n"/>
-      <c r="P179" s="5" t="n"/>
+      <c r="O179" s="5" t="n"/>
+      <c r="P179" s="14" t="n"/>
       <c r="Q179" s="5" t="n"/>
       <c r="R179" s="5" t="n"/>
       <c r="S179" s="5" t="n"/>
       <c r="T179" s="5" t="n"/>
       <c r="U179" s="5" t="n"/>
       <c r="V179" s="5" t="n"/>
+      <c r="W179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
@@ -5404,16 +5424,16 @@
       <c r="J180" s="5" t="n"/>
       <c r="K180" s="5" t="n"/>
       <c r="L180" s="5" t="n"/>
-      <c r="M180" s="5" t="n"/>
       <c r="N180" s="5" t="n"/>
-      <c r="O180" s="14" t="n"/>
-      <c r="P180" s="5" t="n"/>
+      <c r="O180" s="5" t="n"/>
+      <c r="P180" s="14" t="n"/>
       <c r="Q180" s="5" t="n"/>
       <c r="R180" s="5" t="n"/>
       <c r="S180" s="5" t="n"/>
       <c r="T180" s="5" t="n"/>
       <c r="U180" s="5" t="n"/>
       <c r="V180" s="5" t="n"/>
+      <c r="W180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
@@ -5428,16 +5448,16 @@
       <c r="J181" s="5" t="n"/>
       <c r="K181" s="5" t="n"/>
       <c r="L181" s="5" t="n"/>
-      <c r="M181" s="5" t="n"/>
       <c r="N181" s="5" t="n"/>
-      <c r="O181" s="14" t="n"/>
-      <c r="P181" s="5" t="n"/>
+      <c r="O181" s="5" t="n"/>
+      <c r="P181" s="14" t="n"/>
       <c r="Q181" s="5" t="n"/>
       <c r="R181" s="5" t="n"/>
       <c r="S181" s="5" t="n"/>
       <c r="T181" s="5" t="n"/>
       <c r="U181" s="5" t="n"/>
       <c r="V181" s="5" t="n"/>
+      <c r="W181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
@@ -5452,16 +5472,16 @@
       <c r="J182" s="5" t="n"/>
       <c r="K182" s="5" t="n"/>
       <c r="L182" s="5" t="n"/>
-      <c r="M182" s="5" t="n"/>
       <c r="N182" s="5" t="n"/>
-      <c r="O182" s="14" t="n"/>
-      <c r="P182" s="5" t="n"/>
+      <c r="O182" s="5" t="n"/>
+      <c r="P182" s="14" t="n"/>
       <c r="Q182" s="5" t="n"/>
       <c r="R182" s="5" t="n"/>
       <c r="S182" s="5" t="n"/>
       <c r="T182" s="5" t="n"/>
       <c r="U182" s="5" t="n"/>
       <c r="V182" s="5" t="n"/>
+      <c r="W182" s="5" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
@@ -5476,16 +5496,16 @@
       <c r="J183" s="5" t="n"/>
       <c r="K183" s="5" t="n"/>
       <c r="L183" s="5" t="n"/>
-      <c r="M183" s="5" t="n"/>
       <c r="N183" s="5" t="n"/>
-      <c r="O183" s="14" t="n"/>
-      <c r="P183" s="5" t="n"/>
+      <c r="O183" s="5" t="n"/>
+      <c r="P183" s="14" t="n"/>
       <c r="Q183" s="5" t="n"/>
       <c r="R183" s="5" t="n"/>
       <c r="S183" s="5" t="n"/>
       <c r="T183" s="5" t="n"/>
       <c r="U183" s="5" t="n"/>
       <c r="V183" s="5" t="n"/>
+      <c r="W183" s="5" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
@@ -5500,16 +5520,16 @@
       <c r="J184" s="5" t="n"/>
       <c r="K184" s="5" t="n"/>
       <c r="L184" s="5" t="n"/>
-      <c r="M184" s="5" t="n"/>
       <c r="N184" s="5" t="n"/>
-      <c r="O184" s="14" t="n"/>
-      <c r="P184" s="5" t="n"/>
+      <c r="O184" s="5" t="n"/>
+      <c r="P184" s="14" t="n"/>
       <c r="Q184" s="5" t="n"/>
       <c r="R184" s="5" t="n"/>
       <c r="S184" s="5" t="n"/>
       <c r="T184" s="5" t="n"/>
       <c r="U184" s="5" t="n"/>
       <c r="V184" s="5" t="n"/>
+      <c r="W184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
@@ -5524,16 +5544,16 @@
       <c r="J185" s="5" t="n"/>
       <c r="K185" s="5" t="n"/>
       <c r="L185" s="5" t="n"/>
-      <c r="M185" s="5" t="n"/>
       <c r="N185" s="5" t="n"/>
-      <c r="O185" s="14" t="n"/>
-      <c r="P185" s="5" t="n"/>
+      <c r="O185" s="5" t="n"/>
+      <c r="P185" s="14" t="n"/>
       <c r="Q185" s="5" t="n"/>
       <c r="R185" s="5" t="n"/>
       <c r="S185" s="5" t="n"/>
       <c r="T185" s="5" t="n"/>
       <c r="U185" s="5" t="n"/>
       <c r="V185" s="5" t="n"/>
+      <c r="W185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
@@ -5548,16 +5568,16 @@
       <c r="J186" s="5" t="n"/>
       <c r="K186" s="5" t="n"/>
       <c r="L186" s="5" t="n"/>
-      <c r="M186" s="5" t="n"/>
       <c r="N186" s="5" t="n"/>
-      <c r="O186" s="14" t="n"/>
-      <c r="P186" s="5" t="n"/>
+      <c r="O186" s="5" t="n"/>
+      <c r="P186" s="14" t="n"/>
       <c r="Q186" s="5" t="n"/>
       <c r="R186" s="5" t="n"/>
       <c r="S186" s="5" t="n"/>
       <c r="T186" s="5" t="n"/>
       <c r="U186" s="5" t="n"/>
       <c r="V186" s="5" t="n"/>
+      <c r="W186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
@@ -5572,16 +5592,16 @@
       <c r="J187" s="5" t="n"/>
       <c r="K187" s="5" t="n"/>
       <c r="L187" s="5" t="n"/>
-      <c r="M187" s="5" t="n"/>
       <c r="N187" s="5" t="n"/>
-      <c r="O187" s="14" t="n"/>
-      <c r="P187" s="5" t="n"/>
+      <c r="O187" s="5" t="n"/>
+      <c r="P187" s="14" t="n"/>
       <c r="Q187" s="5" t="n"/>
       <c r="R187" s="5" t="n"/>
       <c r="S187" s="5" t="n"/>
       <c r="T187" s="5" t="n"/>
       <c r="U187" s="5" t="n"/>
       <c r="V187" s="5" t="n"/>
+      <c r="W187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
@@ -5596,16 +5616,16 @@
       <c r="J188" s="5" t="n"/>
       <c r="K188" s="5" t="n"/>
       <c r="L188" s="5" t="n"/>
-      <c r="M188" s="5" t="n"/>
       <c r="N188" s="5" t="n"/>
-      <c r="O188" s="14" t="n"/>
-      <c r="P188" s="5" t="n"/>
+      <c r="O188" s="5" t="n"/>
+      <c r="P188" s="14" t="n"/>
       <c r="Q188" s="5" t="n"/>
       <c r="R188" s="5" t="n"/>
       <c r="S188" s="5" t="n"/>
       <c r="T188" s="5" t="n"/>
       <c r="U188" s="5" t="n"/>
       <c r="V188" s="5" t="n"/>
+      <c r="W188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
@@ -5620,16 +5640,16 @@
       <c r="J189" s="5" t="n"/>
       <c r="K189" s="5" t="n"/>
       <c r="L189" s="5" t="n"/>
-      <c r="M189" s="5" t="n"/>
       <c r="N189" s="5" t="n"/>
-      <c r="O189" s="14" t="n"/>
-      <c r="P189" s="5" t="n"/>
+      <c r="O189" s="5" t="n"/>
+      <c r="P189" s="14" t="n"/>
       <c r="Q189" s="5" t="n"/>
       <c r="R189" s="5" t="n"/>
       <c r="S189" s="5" t="n"/>
       <c r="T189" s="5" t="n"/>
       <c r="U189" s="5" t="n"/>
       <c r="V189" s="5" t="n"/>
+      <c r="W189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
@@ -5644,16 +5664,16 @@
       <c r="J190" s="5" t="n"/>
       <c r="K190" s="5" t="n"/>
       <c r="L190" s="5" t="n"/>
-      <c r="M190" s="5" t="n"/>
       <c r="N190" s="5" t="n"/>
-      <c r="O190" s="14" t="n"/>
-      <c r="P190" s="5" t="n"/>
+      <c r="O190" s="5" t="n"/>
+      <c r="P190" s="14" t="n"/>
       <c r="Q190" s="5" t="n"/>
       <c r="R190" s="5" t="n"/>
       <c r="S190" s="5" t="n"/>
       <c r="T190" s="5" t="n"/>
       <c r="U190" s="5" t="n"/>
       <c r="V190" s="5" t="n"/>
+      <c r="W190" s="5" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
@@ -5668,16 +5688,16 @@
       <c r="J191" s="5" t="n"/>
       <c r="K191" s="5" t="n"/>
       <c r="L191" s="5" t="n"/>
-      <c r="M191" s="5" t="n"/>
       <c r="N191" s="5" t="n"/>
-      <c r="O191" s="14" t="n"/>
-      <c r="P191" s="5" t="n"/>
+      <c r="O191" s="5" t="n"/>
+      <c r="P191" s="14" t="n"/>
       <c r="Q191" s="5" t="n"/>
       <c r="R191" s="5" t="n"/>
       <c r="S191" s="5" t="n"/>
       <c r="T191" s="5" t="n"/>
       <c r="U191" s="5" t="n"/>
       <c r="V191" s="5" t="n"/>
+      <c r="W191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n"/>
@@ -5692,16 +5712,16 @@
       <c r="J192" s="5" t="n"/>
       <c r="K192" s="5" t="n"/>
       <c r="L192" s="5" t="n"/>
-      <c r="M192" s="5" t="n"/>
       <c r="N192" s="5" t="n"/>
-      <c r="O192" s="14" t="n"/>
-      <c r="P192" s="5" t="n"/>
+      <c r="O192" s="5" t="n"/>
+      <c r="P192" s="14" t="n"/>
       <c r="Q192" s="5" t="n"/>
       <c r="R192" s="5" t="n"/>
       <c r="S192" s="5" t="n"/>
       <c r="T192" s="5" t="n"/>
       <c r="U192" s="5" t="n"/>
       <c r="V192" s="5" t="n"/>
+      <c r="W192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
@@ -5716,16 +5736,16 @@
       <c r="J193" s="5" t="n"/>
       <c r="K193" s="5" t="n"/>
       <c r="L193" s="5" t="n"/>
-      <c r="M193" s="5" t="n"/>
       <c r="N193" s="5" t="n"/>
-      <c r="O193" s="14" t="n"/>
-      <c r="P193" s="5" t="n"/>
+      <c r="O193" s="5" t="n"/>
+      <c r="P193" s="14" t="n"/>
       <c r="Q193" s="5" t="n"/>
       <c r="R193" s="5" t="n"/>
       <c r="S193" s="5" t="n"/>
       <c r="T193" s="5" t="n"/>
       <c r="U193" s="5" t="n"/>
       <c r="V193" s="5" t="n"/>
+      <c r="W193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
@@ -5740,16 +5760,16 @@
       <c r="J194" s="5" t="n"/>
       <c r="K194" s="5" t="n"/>
       <c r="L194" s="5" t="n"/>
-      <c r="M194" s="5" t="n"/>
       <c r="N194" s="5" t="n"/>
-      <c r="O194" s="14" t="n"/>
-      <c r="P194" s="5" t="n"/>
+      <c r="O194" s="5" t="n"/>
+      <c r="P194" s="14" t="n"/>
       <c r="Q194" s="5" t="n"/>
       <c r="R194" s="5" t="n"/>
       <c r="S194" s="5" t="n"/>
       <c r="T194" s="5" t="n"/>
       <c r="U194" s="5" t="n"/>
       <c r="V194" s="5" t="n"/>
+      <c r="W194" s="5" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n"/>
@@ -5764,16 +5784,16 @@
       <c r="J195" s="5" t="n"/>
       <c r="K195" s="5" t="n"/>
       <c r="L195" s="5" t="n"/>
-      <c r="M195" s="5" t="n"/>
       <c r="N195" s="5" t="n"/>
-      <c r="O195" s="14" t="n"/>
-      <c r="P195" s="5" t="n"/>
+      <c r="O195" s="5" t="n"/>
+      <c r="P195" s="14" t="n"/>
       <c r="Q195" s="5" t="n"/>
       <c r="R195" s="5" t="n"/>
       <c r="S195" s="5" t="n"/>
       <c r="T195" s="5" t="n"/>
       <c r="U195" s="5" t="n"/>
       <c r="V195" s="5" t="n"/>
+      <c r="W195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n"/>
@@ -5788,16 +5808,16 @@
       <c r="J196" s="5" t="n"/>
       <c r="K196" s="5" t="n"/>
       <c r="L196" s="5" t="n"/>
-      <c r="M196" s="5" t="n"/>
       <c r="N196" s="5" t="n"/>
-      <c r="O196" s="14" t="n"/>
-      <c r="P196" s="5" t="n"/>
+      <c r="O196" s="5" t="n"/>
+      <c r="P196" s="14" t="n"/>
       <c r="Q196" s="5" t="n"/>
       <c r="R196" s="5" t="n"/>
       <c r="S196" s="5" t="n"/>
       <c r="T196" s="5" t="n"/>
       <c r="U196" s="5" t="n"/>
       <c r="V196" s="5" t="n"/>
+      <c r="W196" s="5" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
@@ -5812,16 +5832,16 @@
       <c r="J197" s="5" t="n"/>
       <c r="K197" s="5" t="n"/>
       <c r="L197" s="5" t="n"/>
-      <c r="M197" s="5" t="n"/>
       <c r="N197" s="5" t="n"/>
-      <c r="O197" s="14" t="n"/>
-      <c r="P197" s="5" t="n"/>
+      <c r="O197" s="5" t="n"/>
+      <c r="P197" s="14" t="n"/>
       <c r="Q197" s="5" t="n"/>
       <c r="R197" s="5" t="n"/>
       <c r="S197" s="5" t="n"/>
       <c r="T197" s="5" t="n"/>
       <c r="U197" s="5" t="n"/>
       <c r="V197" s="5" t="n"/>
+      <c r="W197" s="5" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n"/>
@@ -5836,16 +5856,16 @@
       <c r="J198" s="5" t="n"/>
       <c r="K198" s="5" t="n"/>
       <c r="L198" s="5" t="n"/>
-      <c r="M198" s="5" t="n"/>
       <c r="N198" s="5" t="n"/>
-      <c r="O198" s="14" t="n"/>
-      <c r="P198" s="5" t="n"/>
+      <c r="O198" s="5" t="n"/>
+      <c r="P198" s="14" t="n"/>
       <c r="Q198" s="5" t="n"/>
       <c r="R198" s="5" t="n"/>
       <c r="S198" s="5" t="n"/>
       <c r="T198" s="5" t="n"/>
       <c r="U198" s="5" t="n"/>
       <c r="V198" s="5" t="n"/>
+      <c r="W198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
@@ -5860,16 +5880,16 @@
       <c r="J199" s="5" t="n"/>
       <c r="K199" s="5" t="n"/>
       <c r="L199" s="5" t="n"/>
-      <c r="M199" s="5" t="n"/>
       <c r="N199" s="5" t="n"/>
-      <c r="O199" s="14" t="n"/>
-      <c r="P199" s="5" t="n"/>
+      <c r="O199" s="5" t="n"/>
+      <c r="P199" s="14" t="n"/>
       <c r="Q199" s="5" t="n"/>
       <c r="R199" s="5" t="n"/>
       <c r="S199" s="5" t="n"/>
       <c r="T199" s="5" t="n"/>
       <c r="U199" s="5" t="n"/>
       <c r="V199" s="5" t="n"/>
+      <c r="W199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
@@ -5884,16 +5904,16 @@
       <c r="J200" s="5" t="n"/>
       <c r="K200" s="5" t="n"/>
       <c r="L200" s="5" t="n"/>
-      <c r="M200" s="5" t="n"/>
       <c r="N200" s="5" t="n"/>
-      <c r="O200" s="14" t="n"/>
-      <c r="P200" s="5" t="n"/>
+      <c r="O200" s="5" t="n"/>
+      <c r="P200" s="14" t="n"/>
       <c r="Q200" s="5" t="n"/>
       <c r="R200" s="5" t="n"/>
       <c r="S200" s="5" t="n"/>
       <c r="T200" s="5" t="n"/>
       <c r="U200" s="5" t="n"/>
       <c r="V200" s="5" t="n"/>
+      <c r="W200" s="5" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n"/>
@@ -5908,16 +5928,16 @@
       <c r="J201" s="5" t="n"/>
       <c r="K201" s="5" t="n"/>
       <c r="L201" s="5" t="n"/>
-      <c r="M201" s="5" t="n"/>
       <c r="N201" s="5" t="n"/>
-      <c r="O201" s="14" t="n"/>
-      <c r="P201" s="5" t="n"/>
+      <c r="O201" s="5" t="n"/>
+      <c r="P201" s="14" t="n"/>
       <c r="Q201" s="5" t="n"/>
       <c r="R201" s="5" t="n"/>
       <c r="S201" s="5" t="n"/>
       <c r="T201" s="5" t="n"/>
       <c r="U201" s="5" t="n"/>
       <c r="V201" s="5" t="n"/>
+      <c r="W201" s="5" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n"/>
@@ -5932,16 +5952,16 @@
       <c r="J202" s="5" t="n"/>
       <c r="K202" s="5" t="n"/>
       <c r="L202" s="5" t="n"/>
-      <c r="M202" s="5" t="n"/>
       <c r="N202" s="5" t="n"/>
-      <c r="O202" s="14" t="n"/>
-      <c r="P202" s="5" t="n"/>
+      <c r="O202" s="5" t="n"/>
+      <c r="P202" s="14" t="n"/>
       <c r="Q202" s="5" t="n"/>
       <c r="R202" s="5" t="n"/>
       <c r="S202" s="5" t="n"/>
       <c r="T202" s="5" t="n"/>
       <c r="U202" s="5" t="n"/>
       <c r="V202" s="5" t="n"/>
+      <c r="W202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n"/>
@@ -5956,16 +5976,16 @@
       <c r="J203" s="5" t="n"/>
       <c r="K203" s="5" t="n"/>
       <c r="L203" s="5" t="n"/>
-      <c r="M203" s="5" t="n"/>
       <c r="N203" s="5" t="n"/>
-      <c r="O203" s="14" t="n"/>
-      <c r="P203" s="5" t="n"/>
+      <c r="O203" s="5" t="n"/>
+      <c r="P203" s="14" t="n"/>
       <c r="Q203" s="5" t="n"/>
       <c r="R203" s="5" t="n"/>
       <c r="S203" s="5" t="n"/>
       <c r="T203" s="5" t="n"/>
       <c r="U203" s="5" t="n"/>
       <c r="V203" s="5" t="n"/>
+      <c r="W203" s="5" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n"/>
@@ -5980,16 +6000,16 @@
       <c r="J204" s="5" t="n"/>
       <c r="K204" s="5" t="n"/>
       <c r="L204" s="5" t="n"/>
-      <c r="M204" s="5" t="n"/>
       <c r="N204" s="5" t="n"/>
-      <c r="O204" s="14" t="n"/>
-      <c r="P204" s="5" t="n"/>
+      <c r="O204" s="5" t="n"/>
+      <c r="P204" s="14" t="n"/>
       <c r="Q204" s="5" t="n"/>
       <c r="R204" s="5" t="n"/>
       <c r="S204" s="5" t="n"/>
       <c r="T204" s="5" t="n"/>
       <c r="U204" s="5" t="n"/>
       <c r="V204" s="5" t="n"/>
+      <c r="W204" s="5" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="n"/>
@@ -6004,16 +6024,16 @@
       <c r="J205" s="5" t="n"/>
       <c r="K205" s="5" t="n"/>
       <c r="L205" s="5" t="n"/>
-      <c r="M205" s="5" t="n"/>
       <c r="N205" s="5" t="n"/>
-      <c r="O205" s="14" t="n"/>
-      <c r="P205" s="5" t="n"/>
+      <c r="O205" s="5" t="n"/>
+      <c r="P205" s="14" t="n"/>
       <c r="Q205" s="5" t="n"/>
       <c r="R205" s="5" t="n"/>
       <c r="S205" s="5" t="n"/>
       <c r="T205" s="5" t="n"/>
       <c r="U205" s="5" t="n"/>
       <c r="V205" s="5" t="n"/>
+      <c r="W205" s="5" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="n"/>
@@ -6028,16 +6048,16 @@
       <c r="J206" s="5" t="n"/>
       <c r="K206" s="5" t="n"/>
       <c r="L206" s="5" t="n"/>
-      <c r="M206" s="5" t="n"/>
       <c r="N206" s="5" t="n"/>
-      <c r="O206" s="14" t="n"/>
-      <c r="P206" s="5" t="n"/>
+      <c r="O206" s="5" t="n"/>
+      <c r="P206" s="14" t="n"/>
       <c r="Q206" s="5" t="n"/>
       <c r="R206" s="5" t="n"/>
       <c r="S206" s="5" t="n"/>
       <c r="T206" s="5" t="n"/>
       <c r="U206" s="5" t="n"/>
       <c r="V206" s="5" t="n"/>
+      <c r="W206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="n"/>
@@ -6052,16 +6072,16 @@
       <c r="J207" s="5" t="n"/>
       <c r="K207" s="5" t="n"/>
       <c r="L207" s="5" t="n"/>
-      <c r="M207" s="5" t="n"/>
       <c r="N207" s="5" t="n"/>
-      <c r="O207" s="14" t="n"/>
-      <c r="P207" s="5" t="n"/>
+      <c r="O207" s="5" t="n"/>
+      <c r="P207" s="14" t="n"/>
       <c r="Q207" s="5" t="n"/>
       <c r="R207" s="5" t="n"/>
       <c r="S207" s="5" t="n"/>
       <c r="T207" s="5" t="n"/>
       <c r="U207" s="5" t="n"/>
       <c r="V207" s="5" t="n"/>
+      <c r="W207" s="5" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="n"/>
@@ -6076,16 +6096,16 @@
       <c r="J208" s="5" t="n"/>
       <c r="K208" s="5" t="n"/>
       <c r="L208" s="5" t="n"/>
-      <c r="M208" s="5" t="n"/>
       <c r="N208" s="5" t="n"/>
-      <c r="O208" s="14" t="n"/>
-      <c r="P208" s="5" t="n"/>
+      <c r="O208" s="5" t="n"/>
+      <c r="P208" s="14" t="n"/>
       <c r="Q208" s="5" t="n"/>
       <c r="R208" s="5" t="n"/>
       <c r="S208" s="5" t="n"/>
       <c r="T208" s="5" t="n"/>
       <c r="U208" s="5" t="n"/>
       <c r="V208" s="5" t="n"/>
+      <c r="W208" s="5" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n"/>
@@ -6100,16 +6120,16 @@
       <c r="J209" s="5" t="n"/>
       <c r="K209" s="5" t="n"/>
       <c r="L209" s="5" t="n"/>
-      <c r="M209" s="5" t="n"/>
       <c r="N209" s="5" t="n"/>
-      <c r="O209" s="14" t="n"/>
-      <c r="P209" s="5" t="n"/>
+      <c r="O209" s="5" t="n"/>
+      <c r="P209" s="14" t="n"/>
       <c r="Q209" s="5" t="n"/>
       <c r="R209" s="5" t="n"/>
       <c r="S209" s="5" t="n"/>
       <c r="T209" s="5" t="n"/>
       <c r="U209" s="5" t="n"/>
       <c r="V209" s="5" t="n"/>
+      <c r="W209" s="5" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n"/>
@@ -6124,16 +6144,16 @@
       <c r="J210" s="5" t="n"/>
       <c r="K210" s="5" t="n"/>
       <c r="L210" s="5" t="n"/>
-      <c r="M210" s="5" t="n"/>
       <c r="N210" s="5" t="n"/>
-      <c r="O210" s="14" t="n"/>
-      <c r="P210" s="5" t="n"/>
+      <c r="O210" s="5" t="n"/>
+      <c r="P210" s="14" t="n"/>
       <c r="Q210" s="5" t="n"/>
       <c r="R210" s="5" t="n"/>
       <c r="S210" s="5" t="n"/>
       <c r="T210" s="5" t="n"/>
       <c r="U210" s="5" t="n"/>
       <c r="V210" s="5" t="n"/>
+      <c r="W210" s="5" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n"/>
@@ -6148,16 +6168,16 @@
       <c r="J211" s="5" t="n"/>
       <c r="K211" s="5" t="n"/>
       <c r="L211" s="5" t="n"/>
-      <c r="M211" s="5" t="n"/>
       <c r="N211" s="5" t="n"/>
-      <c r="O211" s="14" t="n"/>
-      <c r="P211" s="5" t="n"/>
+      <c r="O211" s="5" t="n"/>
+      <c r="P211" s="14" t="n"/>
       <c r="Q211" s="5" t="n"/>
       <c r="R211" s="5" t="n"/>
       <c r="S211" s="5" t="n"/>
       <c r="T211" s="5" t="n"/>
       <c r="U211" s="5" t="n"/>
       <c r="V211" s="5" t="n"/>
+      <c r="W211" s="5" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n"/>
@@ -6172,16 +6192,16 @@
       <c r="J212" s="5" t="n"/>
       <c r="K212" s="5" t="n"/>
       <c r="L212" s="5" t="n"/>
-      <c r="M212" s="5" t="n"/>
       <c r="N212" s="5" t="n"/>
-      <c r="O212" s="14" t="n"/>
-      <c r="P212" s="5" t="n"/>
+      <c r="O212" s="5" t="n"/>
+      <c r="P212" s="14" t="n"/>
       <c r="Q212" s="5" t="n"/>
       <c r="R212" s="5" t="n"/>
       <c r="S212" s="5" t="n"/>
       <c r="T212" s="5" t="n"/>
       <c r="U212" s="5" t="n"/>
       <c r="V212" s="5" t="n"/>
+      <c r="W212" s="5" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="n"/>
@@ -6196,16 +6216,16 @@
       <c r="J213" s="5" t="n"/>
       <c r="K213" s="5" t="n"/>
       <c r="L213" s="5" t="n"/>
-      <c r="M213" s="5" t="n"/>
       <c r="N213" s="5" t="n"/>
-      <c r="O213" s="14" t="n"/>
-      <c r="P213" s="5" t="n"/>
+      <c r="O213" s="5" t="n"/>
+      <c r="P213" s="14" t="n"/>
       <c r="Q213" s="5" t="n"/>
       <c r="R213" s="5" t="n"/>
       <c r="S213" s="5" t="n"/>
       <c r="T213" s="5" t="n"/>
       <c r="U213" s="5" t="n"/>
       <c r="V213" s="5" t="n"/>
+      <c r="W213" s="5" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="n"/>
@@ -6220,16 +6240,16 @@
       <c r="J214" s="5" t="n"/>
       <c r="K214" s="5" t="n"/>
       <c r="L214" s="5" t="n"/>
-      <c r="M214" s="5" t="n"/>
       <c r="N214" s="5" t="n"/>
-      <c r="O214" s="14" t="n"/>
-      <c r="P214" s="5" t="n"/>
+      <c r="O214" s="5" t="n"/>
+      <c r="P214" s="14" t="n"/>
       <c r="Q214" s="5" t="n"/>
       <c r="R214" s="5" t="n"/>
       <c r="S214" s="5" t="n"/>
       <c r="T214" s="5" t="n"/>
       <c r="U214" s="5" t="n"/>
       <c r="V214" s="5" t="n"/>
+      <c r="W214" s="5" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="n"/>
@@ -6244,16 +6264,16 @@
       <c r="J215" s="5" t="n"/>
       <c r="K215" s="5" t="n"/>
       <c r="L215" s="5" t="n"/>
-      <c r="M215" s="5" t="n"/>
       <c r="N215" s="5" t="n"/>
-      <c r="O215" s="14" t="n"/>
-      <c r="P215" s="5" t="n"/>
+      <c r="O215" s="5" t="n"/>
+      <c r="P215" s="14" t="n"/>
       <c r="Q215" s="5" t="n"/>
       <c r="R215" s="5" t="n"/>
       <c r="S215" s="5" t="n"/>
       <c r="T215" s="5" t="n"/>
       <c r="U215" s="5" t="n"/>
       <c r="V215" s="5" t="n"/>
+      <c r="W215" s="5" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n"/>
@@ -6268,16 +6288,16 @@
       <c r="J216" s="5" t="n"/>
       <c r="K216" s="5" t="n"/>
       <c r="L216" s="5" t="n"/>
-      <c r="M216" s="5" t="n"/>
       <c r="N216" s="5" t="n"/>
-      <c r="O216" s="14" t="n"/>
-      <c r="P216" s="5" t="n"/>
+      <c r="O216" s="5" t="n"/>
+      <c r="P216" s="14" t="n"/>
       <c r="Q216" s="5" t="n"/>
       <c r="R216" s="5" t="n"/>
       <c r="S216" s="5" t="n"/>
       <c r="T216" s="5" t="n"/>
       <c r="U216" s="5" t="n"/>
       <c r="V216" s="5" t="n"/>
+      <c r="W216" s="5" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n"/>
@@ -6292,16 +6312,16 @@
       <c r="J217" s="5" t="n"/>
       <c r="K217" s="5" t="n"/>
       <c r="L217" s="5" t="n"/>
-      <c r="M217" s="5" t="n"/>
       <c r="N217" s="5" t="n"/>
-      <c r="O217" s="14" t="n"/>
-      <c r="P217" s="5" t="n"/>
+      <c r="O217" s="5" t="n"/>
+      <c r="P217" s="14" t="n"/>
       <c r="Q217" s="5" t="n"/>
       <c r="R217" s="5" t="n"/>
       <c r="S217" s="5" t="n"/>
       <c r="T217" s="5" t="n"/>
       <c r="U217" s="5" t="n"/>
       <c r="V217" s="5" t="n"/>
+      <c r="W217" s="5" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="n"/>
@@ -6316,16 +6336,16 @@
       <c r="J218" s="5" t="n"/>
       <c r="K218" s="5" t="n"/>
       <c r="L218" s="5" t="n"/>
-      <c r="M218" s="5" t="n"/>
       <c r="N218" s="5" t="n"/>
-      <c r="O218" s="14" t="n"/>
-      <c r="P218" s="5" t="n"/>
+      <c r="O218" s="5" t="n"/>
+      <c r="P218" s="14" t="n"/>
       <c r="Q218" s="5" t="n"/>
       <c r="R218" s="5" t="n"/>
       <c r="S218" s="5" t="n"/>
       <c r="T218" s="5" t="n"/>
       <c r="U218" s="5" t="n"/>
       <c r="V218" s="5" t="n"/>
+      <c r="W218" s="5" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="n"/>
@@ -6340,16 +6360,16 @@
       <c r="J219" s="5" t="n"/>
       <c r="K219" s="5" t="n"/>
       <c r="L219" s="5" t="n"/>
-      <c r="M219" s="5" t="n"/>
       <c r="N219" s="5" t="n"/>
-      <c r="O219" s="14" t="n"/>
-      <c r="P219" s="5" t="n"/>
+      <c r="O219" s="5" t="n"/>
+      <c r="P219" s="14" t="n"/>
       <c r="Q219" s="5" t="n"/>
       <c r="R219" s="5" t="n"/>
       <c r="S219" s="5" t="n"/>
       <c r="T219" s="5" t="n"/>
       <c r="U219" s="5" t="n"/>
       <c r="V219" s="5" t="n"/>
+      <c r="W219" s="5" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="n"/>
@@ -6364,16 +6384,16 @@
       <c r="J220" s="5" t="n"/>
       <c r="K220" s="5" t="n"/>
       <c r="L220" s="5" t="n"/>
-      <c r="M220" s="5" t="n"/>
       <c r="N220" s="5" t="n"/>
-      <c r="O220" s="14" t="n"/>
-      <c r="P220" s="5" t="n"/>
+      <c r="O220" s="5" t="n"/>
+      <c r="P220" s="14" t="n"/>
       <c r="Q220" s="5" t="n"/>
       <c r="R220" s="5" t="n"/>
       <c r="S220" s="5" t="n"/>
       <c r="T220" s="5" t="n"/>
       <c r="U220" s="5" t="n"/>
       <c r="V220" s="5" t="n"/>
+      <c r="W220" s="5" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n"/>
@@ -6388,16 +6408,16 @@
       <c r="J221" s="5" t="n"/>
       <c r="K221" s="5" t="n"/>
       <c r="L221" s="5" t="n"/>
-      <c r="M221" s="5" t="n"/>
       <c r="N221" s="5" t="n"/>
-      <c r="O221" s="14" t="n"/>
-      <c r="P221" s="5" t="n"/>
+      <c r="O221" s="5" t="n"/>
+      <c r="P221" s="14" t="n"/>
       <c r="Q221" s="5" t="n"/>
       <c r="R221" s="5" t="n"/>
       <c r="S221" s="5" t="n"/>
       <c r="T221" s="5" t="n"/>
       <c r="U221" s="5" t="n"/>
       <c r="V221" s="5" t="n"/>
+      <c r="W221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n"/>
@@ -6412,16 +6432,16 @@
       <c r="J222" s="5" t="n"/>
       <c r="K222" s="5" t="n"/>
       <c r="L222" s="5" t="n"/>
-      <c r="M222" s="5" t="n"/>
       <c r="N222" s="5" t="n"/>
-      <c r="O222" s="14" t="n"/>
-      <c r="P222" s="5" t="n"/>
+      <c r="O222" s="5" t="n"/>
+      <c r="P222" s="14" t="n"/>
       <c r="Q222" s="5" t="n"/>
       <c r="R222" s="5" t="n"/>
       <c r="S222" s="5" t="n"/>
       <c r="T222" s="5" t="n"/>
       <c r="U222" s="5" t="n"/>
       <c r="V222" s="5" t="n"/>
+      <c r="W222" s="5" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="n"/>
@@ -6436,16 +6456,16 @@
       <c r="J223" s="5" t="n"/>
       <c r="K223" s="5" t="n"/>
       <c r="L223" s="5" t="n"/>
-      <c r="M223" s="5" t="n"/>
       <c r="N223" s="5" t="n"/>
-      <c r="O223" s="14" t="n"/>
-      <c r="P223" s="5" t="n"/>
+      <c r="O223" s="5" t="n"/>
+      <c r="P223" s="14" t="n"/>
       <c r="Q223" s="5" t="n"/>
       <c r="R223" s="5" t="n"/>
       <c r="S223" s="5" t="n"/>
       <c r="T223" s="5" t="n"/>
       <c r="U223" s="5" t="n"/>
       <c r="V223" s="5" t="n"/>
+      <c r="W223" s="5" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n"/>
@@ -6460,16 +6480,16 @@
       <c r="J224" s="5" t="n"/>
       <c r="K224" s="5" t="n"/>
       <c r="L224" s="5" t="n"/>
-      <c r="M224" s="5" t="n"/>
       <c r="N224" s="5" t="n"/>
-      <c r="O224" s="14" t="n"/>
-      <c r="P224" s="5" t="n"/>
+      <c r="O224" s="5" t="n"/>
+      <c r="P224" s="14" t="n"/>
       <c r="Q224" s="5" t="n"/>
       <c r="R224" s="5" t="n"/>
       <c r="S224" s="5" t="n"/>
       <c r="T224" s="5" t="n"/>
       <c r="U224" s="5" t="n"/>
       <c r="V224" s="5" t="n"/>
+      <c r="W224" s="5" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n"/>
@@ -6484,16 +6504,16 @@
       <c r="J225" s="5" t="n"/>
       <c r="K225" s="5" t="n"/>
       <c r="L225" s="5" t="n"/>
-      <c r="M225" s="5" t="n"/>
       <c r="N225" s="5" t="n"/>
-      <c r="O225" s="14" t="n"/>
-      <c r="P225" s="5" t="n"/>
+      <c r="O225" s="5" t="n"/>
+      <c r="P225" s="14" t="n"/>
       <c r="Q225" s="5" t="n"/>
       <c r="R225" s="5" t="n"/>
       <c r="S225" s="5" t="n"/>
       <c r="T225" s="5" t="n"/>
       <c r="U225" s="5" t="n"/>
       <c r="V225" s="5" t="n"/>
+      <c r="W225" s="5" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n"/>
@@ -6508,16 +6528,16 @@
       <c r="J226" s="5" t="n"/>
       <c r="K226" s="5" t="n"/>
       <c r="L226" s="5" t="n"/>
-      <c r="M226" s="5" t="n"/>
       <c r="N226" s="5" t="n"/>
-      <c r="O226" s="14" t="n"/>
-      <c r="P226" s="5" t="n"/>
+      <c r="O226" s="5" t="n"/>
+      <c r="P226" s="14" t="n"/>
       <c r="Q226" s="5" t="n"/>
       <c r="R226" s="5" t="n"/>
       <c r="S226" s="5" t="n"/>
       <c r="T226" s="5" t="n"/>
       <c r="U226" s="5" t="n"/>
       <c r="V226" s="5" t="n"/>
+      <c r="W226" s="5" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="n"/>
@@ -6532,16 +6552,16 @@
       <c r="J227" s="5" t="n"/>
       <c r="K227" s="5" t="n"/>
       <c r="L227" s="5" t="n"/>
-      <c r="M227" s="5" t="n"/>
       <c r="N227" s="5" t="n"/>
-      <c r="O227" s="14" t="n"/>
-      <c r="P227" s="5" t="n"/>
+      <c r="O227" s="5" t="n"/>
+      <c r="P227" s="14" t="n"/>
       <c r="Q227" s="5" t="n"/>
       <c r="R227" s="5" t="n"/>
       <c r="S227" s="5" t="n"/>
       <c r="T227" s="5" t="n"/>
       <c r="U227" s="5" t="n"/>
       <c r="V227" s="5" t="n"/>
+      <c r="W227" s="5" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="n"/>
@@ -6556,16 +6576,16 @@
       <c r="J228" s="5" t="n"/>
       <c r="K228" s="5" t="n"/>
       <c r="L228" s="5" t="n"/>
-      <c r="M228" s="5" t="n"/>
       <c r="N228" s="5" t="n"/>
-      <c r="O228" s="14" t="n"/>
-      <c r="P228" s="5" t="n"/>
+      <c r="O228" s="5" t="n"/>
+      <c r="P228" s="14" t="n"/>
       <c r="Q228" s="5" t="n"/>
       <c r="R228" s="5" t="n"/>
       <c r="S228" s="5" t="n"/>
       <c r="T228" s="5" t="n"/>
       <c r="U228" s="5" t="n"/>
       <c r="V228" s="5" t="n"/>
+      <c r="W228" s="5" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n"/>
@@ -6580,16 +6600,16 @@
       <c r="J229" s="5" t="n"/>
       <c r="K229" s="5" t="n"/>
       <c r="L229" s="5" t="n"/>
-      <c r="M229" s="5" t="n"/>
       <c r="N229" s="5" t="n"/>
-      <c r="O229" s="14" t="n"/>
-      <c r="P229" s="5" t="n"/>
+      <c r="O229" s="5" t="n"/>
+      <c r="P229" s="14" t="n"/>
       <c r="Q229" s="5" t="n"/>
       <c r="R229" s="5" t="n"/>
       <c r="S229" s="5" t="n"/>
       <c r="T229" s="5" t="n"/>
       <c r="U229" s="5" t="n"/>
       <c r="V229" s="5" t="n"/>
+      <c r="W229" s="5" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n"/>
@@ -6604,16 +6624,16 @@
       <c r="J230" s="5" t="n"/>
       <c r="K230" s="5" t="n"/>
       <c r="L230" s="5" t="n"/>
-      <c r="M230" s="5" t="n"/>
       <c r="N230" s="5" t="n"/>
-      <c r="O230" s="14" t="n"/>
-      <c r="P230" s="5" t="n"/>
+      <c r="O230" s="5" t="n"/>
+      <c r="P230" s="14" t="n"/>
       <c r="Q230" s="5" t="n"/>
       <c r="R230" s="5" t="n"/>
       <c r="S230" s="5" t="n"/>
       <c r="T230" s="5" t="n"/>
       <c r="U230" s="5" t="n"/>
       <c r="V230" s="5" t="n"/>
+      <c r="W230" s="5" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="n"/>
@@ -6628,16 +6648,16 @@
       <c r="J231" s="5" t="n"/>
       <c r="K231" s="5" t="n"/>
       <c r="L231" s="5" t="n"/>
-      <c r="M231" s="5" t="n"/>
       <c r="N231" s="5" t="n"/>
-      <c r="O231" s="14" t="n"/>
-      <c r="P231" s="5" t="n"/>
+      <c r="O231" s="5" t="n"/>
+      <c r="P231" s="14" t="n"/>
       <c r="Q231" s="5" t="n"/>
       <c r="R231" s="5" t="n"/>
       <c r="S231" s="5" t="n"/>
       <c r="T231" s="5" t="n"/>
       <c r="U231" s="5" t="n"/>
       <c r="V231" s="5" t="n"/>
+      <c r="W231" s="5" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n"/>
@@ -6652,16 +6672,16 @@
       <c r="J232" s="5" t="n"/>
       <c r="K232" s="5" t="n"/>
       <c r="L232" s="5" t="n"/>
-      <c r="M232" s="5" t="n"/>
       <c r="N232" s="5" t="n"/>
-      <c r="O232" s="14" t="n"/>
-      <c r="P232" s="5" t="n"/>
+      <c r="O232" s="5" t="n"/>
+      <c r="P232" s="14" t="n"/>
       <c r="Q232" s="5" t="n"/>
       <c r="R232" s="5" t="n"/>
       <c r="S232" s="5" t="n"/>
       <c r="T232" s="5" t="n"/>
       <c r="U232" s="5" t="n"/>
       <c r="V232" s="5" t="n"/>
+      <c r="W232" s="5" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n"/>
@@ -6676,16 +6696,16 @@
       <c r="J233" s="5" t="n"/>
       <c r="K233" s="5" t="n"/>
       <c r="L233" s="5" t="n"/>
-      <c r="M233" s="5" t="n"/>
       <c r="N233" s="5" t="n"/>
-      <c r="O233" s="14" t="n"/>
-      <c r="P233" s="5" t="n"/>
+      <c r="O233" s="5" t="n"/>
+      <c r="P233" s="14" t="n"/>
       <c r="Q233" s="5" t="n"/>
       <c r="R233" s="5" t="n"/>
       <c r="S233" s="5" t="n"/>
       <c r="T233" s="5" t="n"/>
       <c r="U233" s="5" t="n"/>
       <c r="V233" s="5" t="n"/>
+      <c r="W233" s="5" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n"/>
@@ -6700,16 +6720,16 @@
       <c r="J234" s="5" t="n"/>
       <c r="K234" s="5" t="n"/>
       <c r="L234" s="5" t="n"/>
-      <c r="M234" s="5" t="n"/>
       <c r="N234" s="5" t="n"/>
-      <c r="O234" s="14" t="n"/>
-      <c r="P234" s="5" t="n"/>
+      <c r="O234" s="5" t="n"/>
+      <c r="P234" s="14" t="n"/>
       <c r="Q234" s="5" t="n"/>
       <c r="R234" s="5" t="n"/>
       <c r="S234" s="5" t="n"/>
       <c r="T234" s="5" t="n"/>
       <c r="U234" s="5" t="n"/>
       <c r="V234" s="5" t="n"/>
+      <c r="W234" s="5" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="n"/>
@@ -6724,16 +6744,16 @@
       <c r="J235" s="5" t="n"/>
       <c r="K235" s="5" t="n"/>
       <c r="L235" s="5" t="n"/>
-      <c r="M235" s="5" t="n"/>
       <c r="N235" s="5" t="n"/>
-      <c r="O235" s="14" t="n"/>
-      <c r="P235" s="5" t="n"/>
+      <c r="O235" s="5" t="n"/>
+      <c r="P235" s="14" t="n"/>
       <c r="Q235" s="5" t="n"/>
       <c r="R235" s="5" t="n"/>
       <c r="S235" s="5" t="n"/>
       <c r="T235" s="5" t="n"/>
       <c r="U235" s="5" t="n"/>
       <c r="V235" s="5" t="n"/>
+      <c r="W235" s="5" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="n"/>
@@ -6748,16 +6768,16 @@
       <c r="J236" s="5" t="n"/>
       <c r="K236" s="5" t="n"/>
       <c r="L236" s="5" t="n"/>
-      <c r="M236" s="5" t="n"/>
       <c r="N236" s="5" t="n"/>
-      <c r="O236" s="14" t="n"/>
-      <c r="P236" s="5" t="n"/>
+      <c r="O236" s="5" t="n"/>
+      <c r="P236" s="14" t="n"/>
       <c r="Q236" s="5" t="n"/>
       <c r="R236" s="5" t="n"/>
       <c r="S236" s="5" t="n"/>
       <c r="T236" s="5" t="n"/>
       <c r="U236" s="5" t="n"/>
       <c r="V236" s="5" t="n"/>
+      <c r="W236" s="5" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="n"/>
@@ -6772,16 +6792,16 @@
       <c r="J237" s="5" t="n"/>
       <c r="K237" s="5" t="n"/>
       <c r="L237" s="5" t="n"/>
-      <c r="M237" s="5" t="n"/>
       <c r="N237" s="5" t="n"/>
-      <c r="O237" s="14" t="n"/>
-      <c r="P237" s="5" t="n"/>
+      <c r="O237" s="5" t="n"/>
+      <c r="P237" s="14" t="n"/>
       <c r="Q237" s="5" t="n"/>
       <c r="R237" s="5" t="n"/>
       <c r="S237" s="5" t="n"/>
       <c r="T237" s="5" t="n"/>
       <c r="U237" s="5" t="n"/>
       <c r="V237" s="5" t="n"/>
+      <c r="W237" s="5" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="n"/>
@@ -6796,16 +6816,16 @@
       <c r="J238" s="5" t="n"/>
       <c r="K238" s="5" t="n"/>
       <c r="L238" s="5" t="n"/>
-      <c r="M238" s="5" t="n"/>
       <c r="N238" s="5" t="n"/>
-      <c r="O238" s="14" t="n"/>
-      <c r="P238" s="5" t="n"/>
+      <c r="O238" s="5" t="n"/>
+      <c r="P238" s="14" t="n"/>
       <c r="Q238" s="5" t="n"/>
       <c r="R238" s="5" t="n"/>
       <c r="S238" s="5" t="n"/>
       <c r="T238" s="5" t="n"/>
       <c r="U238" s="5" t="n"/>
       <c r="V238" s="5" t="n"/>
+      <c r="W238" s="5" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n"/>
@@ -6820,16 +6840,16 @@
       <c r="J239" s="5" t="n"/>
       <c r="K239" s="5" t="n"/>
       <c r="L239" s="5" t="n"/>
-      <c r="M239" s="5" t="n"/>
       <c r="N239" s="5" t="n"/>
-      <c r="O239" s="14" t="n"/>
-      <c r="P239" s="5" t="n"/>
+      <c r="O239" s="5" t="n"/>
+      <c r="P239" s="14" t="n"/>
       <c r="Q239" s="5" t="n"/>
       <c r="R239" s="5" t="n"/>
       <c r="S239" s="5" t="n"/>
       <c r="T239" s="5" t="n"/>
       <c r="U239" s="5" t="n"/>
       <c r="V239" s="5" t="n"/>
+      <c r="W239" s="5" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="n"/>
@@ -6844,16 +6864,16 @@
       <c r="J240" s="5" t="n"/>
       <c r="K240" s="5" t="n"/>
       <c r="L240" s="5" t="n"/>
-      <c r="M240" s="5" t="n"/>
       <c r="N240" s="5" t="n"/>
-      <c r="O240" s="14" t="n"/>
-      <c r="P240" s="5" t="n"/>
+      <c r="O240" s="5" t="n"/>
+      <c r="P240" s="14" t="n"/>
       <c r="Q240" s="5" t="n"/>
       <c r="R240" s="5" t="n"/>
       <c r="S240" s="5" t="n"/>
       <c r="T240" s="5" t="n"/>
       <c r="U240" s="5" t="n"/>
       <c r="V240" s="5" t="n"/>
+      <c r="W240" s="5" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="5" t="n"/>
@@ -6868,16 +6888,16 @@
       <c r="J241" s="5" t="n"/>
       <c r="K241" s="5" t="n"/>
       <c r="L241" s="5" t="n"/>
-      <c r="M241" s="5" t="n"/>
       <c r="N241" s="5" t="n"/>
-      <c r="O241" s="14" t="n"/>
-      <c r="P241" s="5" t="n"/>
+      <c r="O241" s="5" t="n"/>
+      <c r="P241" s="14" t="n"/>
       <c r="Q241" s="5" t="n"/>
       <c r="R241" s="5" t="n"/>
       <c r="S241" s="5" t="n"/>
       <c r="T241" s="5" t="n"/>
       <c r="U241" s="5" t="n"/>
       <c r="V241" s="5" t="n"/>
+      <c r="W241" s="5" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="n"/>
@@ -6892,16 +6912,16 @@
       <c r="J242" s="5" t="n"/>
       <c r="K242" s="5" t="n"/>
       <c r="L242" s="5" t="n"/>
-      <c r="M242" s="5" t="n"/>
       <c r="N242" s="5" t="n"/>
-      <c r="O242" s="14" t="n"/>
-      <c r="P242" s="5" t="n"/>
+      <c r="O242" s="5" t="n"/>
+      <c r="P242" s="14" t="n"/>
       <c r="Q242" s="5" t="n"/>
       <c r="R242" s="5" t="n"/>
       <c r="S242" s="5" t="n"/>
       <c r="T242" s="5" t="n"/>
       <c r="U242" s="5" t="n"/>
       <c r="V242" s="5" t="n"/>
+      <c r="W242" s="5" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="5" t="n"/>
@@ -6916,16 +6936,16 @@
       <c r="J243" s="5" t="n"/>
       <c r="K243" s="5" t="n"/>
       <c r="L243" s="5" t="n"/>
-      <c r="M243" s="5" t="n"/>
       <c r="N243" s="5" t="n"/>
-      <c r="O243" s="14" t="n"/>
-      <c r="P243" s="5" t="n"/>
+      <c r="O243" s="5" t="n"/>
+      <c r="P243" s="14" t="n"/>
       <c r="Q243" s="5" t="n"/>
       <c r="R243" s="5" t="n"/>
       <c r="S243" s="5" t="n"/>
       <c r="T243" s="5" t="n"/>
       <c r="U243" s="5" t="n"/>
       <c r="V243" s="5" t="n"/>
+      <c r="W243" s="5" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="n"/>
@@ -6940,16 +6960,16 @@
       <c r="J244" s="5" t="n"/>
       <c r="K244" s="5" t="n"/>
       <c r="L244" s="5" t="n"/>
-      <c r="M244" s="5" t="n"/>
       <c r="N244" s="5" t="n"/>
-      <c r="O244" s="14" t="n"/>
-      <c r="P244" s="5" t="n"/>
+      <c r="O244" s="5" t="n"/>
+      <c r="P244" s="14" t="n"/>
       <c r="Q244" s="5" t="n"/>
       <c r="R244" s="5" t="n"/>
       <c r="S244" s="5" t="n"/>
       <c r="T244" s="5" t="n"/>
       <c r="U244" s="5" t="n"/>
       <c r="V244" s="5" t="n"/>
+      <c r="W244" s="5" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="n"/>
@@ -6964,16 +6984,16 @@
       <c r="J245" s="5" t="n"/>
       <c r="K245" s="5" t="n"/>
       <c r="L245" s="5" t="n"/>
-      <c r="M245" s="5" t="n"/>
       <c r="N245" s="5" t="n"/>
-      <c r="O245" s="14" t="n"/>
-      <c r="P245" s="5" t="n"/>
+      <c r="O245" s="5" t="n"/>
+      <c r="P245" s="14" t="n"/>
       <c r="Q245" s="5" t="n"/>
       <c r="R245" s="5" t="n"/>
       <c r="S245" s="5" t="n"/>
       <c r="T245" s="5" t="n"/>
       <c r="U245" s="5" t="n"/>
       <c r="V245" s="5" t="n"/>
+      <c r="W245" s="5" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="5" t="n"/>
@@ -6988,16 +7008,16 @@
       <c r="J246" s="5" t="n"/>
       <c r="K246" s="5" t="n"/>
       <c r="L246" s="5" t="n"/>
-      <c r="M246" s="5" t="n"/>
       <c r="N246" s="5" t="n"/>
-      <c r="O246" s="14" t="n"/>
-      <c r="P246" s="5" t="n"/>
+      <c r="O246" s="5" t="n"/>
+      <c r="P246" s="14" t="n"/>
       <c r="Q246" s="5" t="n"/>
       <c r="R246" s="5" t="n"/>
       <c r="S246" s="5" t="n"/>
       <c r="T246" s="5" t="n"/>
       <c r="U246" s="5" t="n"/>
       <c r="V246" s="5" t="n"/>
+      <c r="W246" s="5" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n"/>
@@ -7012,16 +7032,16 @@
       <c r="J247" s="5" t="n"/>
       <c r="K247" s="5" t="n"/>
       <c r="L247" s="5" t="n"/>
-      <c r="M247" s="5" t="n"/>
       <c r="N247" s="5" t="n"/>
-      <c r="O247" s="14" t="n"/>
-      <c r="P247" s="5" t="n"/>
+      <c r="O247" s="5" t="n"/>
+      <c r="P247" s="14" t="n"/>
       <c r="Q247" s="5" t="n"/>
       <c r="R247" s="5" t="n"/>
       <c r="S247" s="5" t="n"/>
       <c r="T247" s="5" t="n"/>
       <c r="U247" s="5" t="n"/>
       <c r="V247" s="5" t="n"/>
+      <c r="W247" s="5" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n"/>
@@ -7036,16 +7056,16 @@
       <c r="J248" s="5" t="n"/>
       <c r="K248" s="5" t="n"/>
       <c r="L248" s="5" t="n"/>
-      <c r="M248" s="5" t="n"/>
       <c r="N248" s="5" t="n"/>
-      <c r="O248" s="14" t="n"/>
-      <c r="P248" s="5" t="n"/>
+      <c r="O248" s="5" t="n"/>
+      <c r="P248" s="14" t="n"/>
       <c r="Q248" s="5" t="n"/>
       <c r="R248" s="5" t="n"/>
       <c r="S248" s="5" t="n"/>
       <c r="T248" s="5" t="n"/>
       <c r="U248" s="5" t="n"/>
       <c r="V248" s="5" t="n"/>
+      <c r="W248" s="5" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="5" t="n"/>
@@ -7060,16 +7080,16 @@
       <c r="J249" s="5" t="n"/>
       <c r="K249" s="5" t="n"/>
       <c r="L249" s="5" t="n"/>
-      <c r="M249" s="5" t="n"/>
       <c r="N249" s="5" t="n"/>
-      <c r="O249" s="14" t="n"/>
-      <c r="P249" s="5" t="n"/>
+      <c r="O249" s="5" t="n"/>
+      <c r="P249" s="14" t="n"/>
       <c r="Q249" s="5" t="n"/>
       <c r="R249" s="5" t="n"/>
       <c r="S249" s="5" t="n"/>
       <c r="T249" s="5" t="n"/>
       <c r="U249" s="5" t="n"/>
       <c r="V249" s="5" t="n"/>
+      <c r="W249" s="5" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="5" t="n"/>
@@ -7084,16 +7104,16 @@
       <c r="J250" s="5" t="n"/>
       <c r="K250" s="5" t="n"/>
       <c r="L250" s="5" t="n"/>
-      <c r="M250" s="5" t="n"/>
       <c r="N250" s="5" t="n"/>
-      <c r="O250" s="14" t="n"/>
-      <c r="P250" s="5" t="n"/>
+      <c r="O250" s="5" t="n"/>
+      <c r="P250" s="14" t="n"/>
       <c r="Q250" s="5" t="n"/>
       <c r="R250" s="5" t="n"/>
       <c r="S250" s="5" t="n"/>
       <c r="T250" s="5" t="n"/>
       <c r="U250" s="5" t="n"/>
       <c r="V250" s="5" t="n"/>
+      <c r="W250" s="5" t="n"/>
     </row>
     <row r="251">
       <c r="C251" s="2" t="n"/>
